--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FA5A79-7925-43F5-BDAB-2D232C56FC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="60" windowWidth="16550" windowHeight="7950" activeTab="1"/>
+    <workbookView xWindow="-21990" yWindow="2940" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="String_Hero" sheetId="3" r:id="rId2"/>
+    <sheet name="String" sheetId="4" r:id="rId2"/>
+    <sheet name="String_Hero" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,14 +251,94 @@
   </si>
   <si>
     <t>DESC_TALK_SHU_ZHUGELIANG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_SHU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고결한 이상 주의자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_SUB_SHU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인의와 명분으로 민심을 결속시키고 대업을 꿈꾸는 왕도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_SUB_WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_WU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_MASTER_DESC_SUB_WU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난세의 간웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실용적인 수호자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지형과 인재의 화합으로 세운 철벽의 수성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천하의 인재를 거느리며 판도를 흔드는 패도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_WEI_CAOCAO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CaoCao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_WU_SUNQUAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>손권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SunQuan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POPUP_REGION_SELECT_INFO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군주를 선택해 주세요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,13 +426,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -388,7 +478,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -422,6 +512,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -456,9 +547,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -631,9 +723,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -642,16 +734,62 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD3CC5B-3BAE-4EB8-AAC4-1E077903F39F}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="3" width="40.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="50.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="50.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -665,7 +803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -677,7 +815,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -688,7 +826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -699,7 +837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -710,7 +848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -721,7 +859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -732,154 +870,224 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="34">
-      <c r="A19" t="s">
+    <row r="21" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="34">
-      <c r="A20" t="s">
+    <row r="22" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="34">
-      <c r="A21" t="s">
+    <row r="23" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="34">
-      <c r="A23" t="s">
+    <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="3" t="s">
         <v>56</v>
       </c>
     </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A3:C41">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C43">
     <sortCondition ref="A3"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,23 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FA5A79-7925-43F5-BDAB-2D232C56FC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55912938-4858-4102-84AB-5001E37D72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21990" yWindow="2940" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2895" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="String" sheetId="4" r:id="rId2"/>
     <sheet name="String_Hero" sheetId="3" r:id="rId3"/>
+    <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="109">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -331,6 +348,132 @@
   </si>
   <si>
     <t>군주를 선택해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1.1_SHU_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#idx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면을 터치하면 내가 움직일 수도 있을거 같은데??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응? 적이 있으면 스스로 공격하는구나!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞에 황건적이네. 어쩌지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연회권? 동료를 얻을 수 있으려나? 주막에 가보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅇㅋ. 관우 형님도 같이 합시다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덩치야. 같이 의용병 콜??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋소. 태어난 날은 달라도 같은 날 죽읍시다. 내가 나이가 제일 많으니…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>술 값은 내가 내겠소. 무기도 필요하니 내가 준비해보겠소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돗자리나 파는 양반이 돈이 어딨오?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔 소리요? 이 지역 돗자리는 내가 다 납품하고 있구만.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형님, 잘 부탁하오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드 조작으로 내가 움직일 수 있을거 같은데? 방향키를 눌러보까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음?? 여긴..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOBILE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1.1_TUTORIAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼빠지게 생긴 넘이다!! 죽여라!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌진과 공격을 사용해보자.
+X가 공격이고, C는 돌진이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌진과 공격을 사용해보자.
+아래 버튼을 눌러봐.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 초상화를 누르면 스킬이 사용될거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 초상화를 누르거나 숫자 키를 누르면 스킬이 사용될거야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,6 +578,75 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="HeroData"/>
+      <sheetName val="EnemyData"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>_</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>BASE</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>유비</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>LiuBei</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>관우</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>GuanYu</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>장비</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>ZhangFei</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>조운</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>ZhaYun</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>제갈량</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>ZhugeLiang</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1094,4 +1306,520 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB81C2E-4BE2-4C93-83EC-C1AF98EC6DD2}">
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="50.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="str">
+        <f>_xlfn.CONCAT(A3, "_", B3, IF(D3&lt;&gt;"", "_"&amp;D3, ""))</f>
+        <v>1.1.1_TUTORIAL_0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f>A3</f>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B11" si="0">B3+1</f>
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" ref="C4" si="1">_xlfn.CONCAT(A4, "_", B4, IF(D4&lt;&gt;"", "_"&amp;D4, ""))</f>
+        <v>1.1.1_TUTORIAL_1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f>A4</f>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" ref="C5:C11" si="2">_xlfn.CONCAT(A5, "_", B5, IF(D5&lt;&gt;"", "_"&amp;D5, ""))</f>
+        <v>1.1.1_TUTORIAL_2</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" ref="A6:A12" si="3">A5</f>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_3</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_4_MOBILE</v>
+      </c>
+      <c r="D7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_5_PC</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_6_MOBILE</v>
+      </c>
+      <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_7_PC</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="2"/>
+        <v>1.1.1_TUTORIAL_8_MOBILE</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f t="shared" si="3"/>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12" si="4">B11+1</f>
+        <v>9</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" ref="C12" si="5">_xlfn.CONCAT(A12, "_", B12, IF(D12&lt;&gt;"", "_"&amp;D12, ""))</f>
+        <v>1.1.1_TUTORIAL_9_PC</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f>A11</f>
+        <v>1.1.1_TUTORIAL</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13" si="6">B11+1</f>
+        <v>9</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" ref="C13" si="7">_xlfn.CONCAT(A13, "_", B13, IF(D13&lt;&gt;"", "_"&amp;D13, ""))</f>
+        <v>1.1.1_TUTORIAL_9</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="str">
+        <f>_xlfn.CONCAT(A14, "_", B14, IF(D14&lt;&gt;"", "_"&amp;D14, ""))</f>
+        <v>1.1.1_SHU_START_0</v>
+      </c>
+      <c r="E14" t="str">
+        <f>VLOOKUP(F14,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f t="shared" ref="A15:A22" si="8">A14</f>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B15">
+        <f>B14+1</f>
+        <v>1</v>
+      </c>
+      <c r="C15" t="str">
+        <f>_xlfn.CONCAT(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
+        <v>1.1.1_SHU_START_1</v>
+      </c>
+      <c r="E15" t="str">
+        <f>VLOOKUP(F15,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B16">
+        <f>B15+1</f>
+        <v>2</v>
+      </c>
+      <c r="C16" t="str">
+        <f>_xlfn.CONCAT(A16, "_", B16, IF(D16&lt;&gt;"", "_"&amp;D16, ""))</f>
+        <v>1.1.1_SHU_START_2</v>
+      </c>
+      <c r="E16" t="str">
+        <f>VLOOKUP(F16,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B17">
+        <f>B16+1</f>
+        <v>3</v>
+      </c>
+      <c r="C17" t="str">
+        <f>_xlfn.CONCAT(A17, "_", B17, IF(D17&lt;&gt;"", "_"&amp;D17, ""))</f>
+        <v>1.1.1_SHU_START_3</v>
+      </c>
+      <c r="E17" t="str">
+        <f>VLOOKUP(F17,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B18">
+        <f>B17+1</f>
+        <v>4</v>
+      </c>
+      <c r="C18" t="str">
+        <f>_xlfn.CONCAT(A18, "_", B18, IF(D18&lt;&gt;"", "_"&amp;D18, ""))</f>
+        <v>1.1.1_SHU_START_4</v>
+      </c>
+      <c r="E18" t="str">
+        <f>VLOOKUP(F18,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B19">
+        <f>B18+1</f>
+        <v>5</v>
+      </c>
+      <c r="C19" t="str">
+        <f>_xlfn.CONCAT(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
+        <v>1.1.1_SHU_START_5</v>
+      </c>
+      <c r="E19" t="str">
+        <f>VLOOKUP(F19,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B20">
+        <f t="shared" ref="B20:B22" si="9">B19+1</f>
+        <v>6</v>
+      </c>
+      <c r="C20" t="str">
+        <f>_xlfn.CONCAT(A20, "_", B20, IF(D20&lt;&gt;"", "_"&amp;D20, ""))</f>
+        <v>1.1.1_SHU_START_6</v>
+      </c>
+      <c r="E20" t="str">
+        <f>VLOOKUP(F20,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="C21" t="str">
+        <f>_xlfn.CONCAT(A21, "_", B21, IF(D21&lt;&gt;"", "_"&amp;D21, ""))</f>
+        <v>1.1.1_SHU_START_7</v>
+      </c>
+      <c r="E21" t="str">
+        <f>VLOOKUP(F21,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="C22" t="str">
+        <f>_xlfn.CONCAT(A22, "_", B22, IF(D22&lt;&gt;"", "_"&amp;D22, ""))</f>
+        <v>1.1.1_SHU_START_8</v>
+      </c>
+      <c r="E22" t="str">
+        <f>VLOOKUP(F22,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F22" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G28"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G30"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G31"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55912938-4858-4102-84AB-5001E37D72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2895" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2210" yWindow="2900" windowWidth="21600" windowHeight="11300" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -16,7 +15,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="110">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -379,10 +378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>응? 적이 있으면 스스로 공격하는구나!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>앞에 황건적이네. 어쩌지?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -444,10 +439,6 @@
   </si>
   <si>
     <t>PC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.1.1_TUTORIAL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -474,14 +465,27 @@
   </si>
   <si>
     <t>영웅 초상화를 누르거나 숫자 키를 누르면 스킬이 사용될거야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황건적을 처치하자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응? 적이 있으면 스스로
+공격하는구나!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TUTORIAL_START</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,11 +585,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="HeroData"/>
@@ -650,9 +651,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -690,7 +691,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -724,7 +725,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -759,10 +759,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -935,9 +934,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -946,15 +945,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDD3CC5B-3BAE-4EB8-AAC4-1E077903F39F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="3" width="40.875" customWidth="1"/>
+    <col min="2" max="3" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -965,7 +964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -976,7 +975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -992,16 +991,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="50.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="50.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1015,7 +1014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1027,7 +1026,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1038,7 +1037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1060,7 +1059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1071,7 +1070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1082,7 +1081,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1093,7 +1092,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -1104,7 +1103,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1115,7 +1114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1126,7 +1125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1137,7 +1136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1148,7 +1147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1159,7 +1158,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1170,7 +1169,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1178,7 +1177,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1194,7 +1193,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1202,7 +1201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1210,7 +1209,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="34">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1218,7 +1217,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="34">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1226,7 +1225,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="34">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -1242,7 +1241,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="34">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1250,7 +1249,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1258,7 +1257,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1266,7 +1265,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -1282,7 +1281,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>64</v>
       </c>
@@ -1290,7 +1289,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>65</v>
       </c>
@@ -1299,7 +1298,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C43">
+  <sortState ref="A3:C43">
     <sortCondition ref="A3"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1309,21 +1308,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB81C2E-4BE2-4C93-83EC-C1AF98EC6DD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="5" max="5" width="9.58203125" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="50.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="50.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
@@ -1334,7 +1333,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>81</v>
@@ -1352,7 +1351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1379,442 +1378,459 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="str">
-        <f>_xlfn.CONCAT(A3, "_", B3, IF(D3&lt;&gt;"", "_"&amp;D3, ""))</f>
-        <v>1.1.1_TUTORIAL_0</v>
+        <f>CONCATENATE(A3, "_", B3, IF(D3&lt;&gt;"", "_"&amp;D3, ""))</f>
+        <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="str">
         <f>A3</f>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B11" si="0">B3+1</f>
+        <f t="shared" ref="B4:B14" si="0">B3+1</f>
         <v>1</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" ref="C4" si="1">_xlfn.CONCAT(A4, "_", B4, IF(D4&lt;&gt;"", "_"&amp;D4, ""))</f>
-        <v>1.1.1_TUTORIAL_1</v>
+        <f t="shared" ref="C4:C13" si="1">CONCATENATE(A4, "_", B4, IF(D4&lt;&gt;"", "_"&amp;D4, ""))</f>
+        <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="str">
         <f>A4</f>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" ref="C5:C11" si="2">_xlfn.CONCAT(A5, "_", B5, IF(D5&lt;&gt;"", "_"&amp;D5, ""))</f>
-        <v>1.1.1_TUTORIAL_2</v>
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="34">
       <c r="A6" t="str">
-        <f t="shared" ref="A6:A12" si="3">A5</f>
-        <v>1.1.1_TUTORIAL</v>
+        <f t="shared" ref="A6:A12" si="2">A5</f>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C6" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_3</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="str">
         <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_3</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_4_MOBILE</v>
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="34">
       <c r="A8" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
+        <f t="shared" si="2"/>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C8" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_5_PC</v>
+      </c>
+      <c r="D8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="34">
+      <c r="A9" t="str">
         <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_5_PC</v>
-      </c>
-      <c r="D8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C9" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_6_MOBILE</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34">
+      <c r="A10" t="str">
         <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_6_MOBILE</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C10" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_7_PC</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="str">
         <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_7_PC</v>
-      </c>
-      <c r="D10" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C11" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_8_MOBILE</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="34">
+      <c r="A12" t="str">
         <f t="shared" si="2"/>
-        <v>1.1.1_TUTORIAL_8_MOBILE</v>
-      </c>
-      <c r="D11" t="s">
+        <v>TUTORIAL_START</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_9_PC</v>
+      </c>
+      <c r="D12" t="s">
         <v>100</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="A12" t="str">
-        <f t="shared" si="3"/>
-        <v>1.1.1_TUTORIAL</v>
-      </c>
-      <c r="B12">
-        <f t="shared" ref="B12" si="4">B11+1</f>
-        <v>9</v>
-      </c>
-      <c r="C12" t="str">
-        <f t="shared" ref="C12" si="5">_xlfn.CONCAT(A12, "_", B12, IF(D12&lt;&gt;"", "_"&amp;D12, ""))</f>
-        <v>1.1.1_TUTORIAL_9_PC</v>
-      </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="str">
         <f>A11</f>
-        <v>1.1.1_TUTORIAL</v>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13" si="6">B11+1</f>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" ref="C13" si="7">_xlfn.CONCAT(A13, "_", B13, IF(D13&lt;&gt;"", "_"&amp;D13, ""))</f>
-        <v>1.1.1_TUTORIAL_9</v>
+        <f t="shared" si="1"/>
+        <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="str">
+        <f>A12</f>
+        <v>TUTORIAL_START</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" ref="C14" si="3">CONCATENATE(A14, "_", B14, IF(D14&lt;&gt;"", "_"&amp;D14, ""))</f>
+        <v>TUTORIAL_START_11</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
         <v>79</v>
       </c>
-      <c r="B14">
+      <c r="B15">
         <v>0</v>
       </c>
-      <c r="C14" t="str">
-        <f>_xlfn.CONCAT(A14, "_", B14, IF(D14&lt;&gt;"", "_"&amp;D14, ""))</f>
+      <c r="C15" t="str">
+        <f t="shared" ref="C15:C23" si="4">CONCATENATE(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
         <v>1.1.1_SHU_START_0</v>
-      </c>
-      <c r="E14" t="str">
-        <f>VLOOKUP(F14,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
-      </c>
-      <c r="F14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
-        <f t="shared" ref="A15:A22" si="8">A14</f>
-        <v>1.1.1_SHU_START</v>
-      </c>
-      <c r="B15">
-        <f>B14+1</f>
-        <v>1</v>
-      </c>
-      <c r="C15" t="str">
-        <f>_xlfn.CONCAT(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
-        <v>1.1.1_SHU_START_1</v>
       </c>
       <c r="E15" t="str">
         <f>VLOOKUP(F15,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>LiuBei</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="A16:A23" si="5">A15</f>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B16">
         <f>B15+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="str">
-        <f>_xlfn.CONCAT(A16, "_", B16, IF(D16&lt;&gt;"", "_"&amp;D16, ""))</f>
-        <v>1.1.1_SHU_START_2</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_1</v>
       </c>
       <c r="E16" t="str">
         <f>VLOOKUP(F16,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="34">
       <c r="A17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B17">
         <f>B16+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="str">
-        <f>_xlfn.CONCAT(A17, "_", B17, IF(D17&lt;&gt;"", "_"&amp;D17, ""))</f>
-        <v>1.1.1_SHU_START_3</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_2</v>
       </c>
       <c r="E17" t="str">
         <f>VLOOKUP(F17,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B18">
         <f>B17+1</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="str">
-        <f>_xlfn.CONCAT(A18, "_", B18, IF(D18&lt;&gt;"", "_"&amp;D18, ""))</f>
-        <v>1.1.1_SHU_START_4</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_3</v>
       </c>
       <c r="E18" t="str">
         <f>VLOOKUP(F18,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B19">
         <f>B18+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="str">
-        <f>_xlfn.CONCAT(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
-        <v>1.1.1_SHU_START_5</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_4</v>
       </c>
       <c r="E19" t="str">
         <f>VLOOKUP(F19,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B20">
-        <f t="shared" ref="B20:B22" si="9">B19+1</f>
-        <v>6</v>
+        <f>B19+1</f>
+        <v>5</v>
       </c>
       <c r="C20" t="str">
-        <f>_xlfn.CONCAT(A20, "_", B20, IF(D20&lt;&gt;"", "_"&amp;D20, ""))</f>
-        <v>1.1.1_SHU_START_6</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_5</v>
       </c>
       <c r="E20" t="str">
         <f>VLOOKUP(F20,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <f t="shared" ref="B21:B23" si="6">B20+1</f>
+        <v>6</v>
       </c>
       <c r="C21" t="str">
-        <f>_xlfn.CONCAT(A21, "_", B21, IF(D21&lt;&gt;"", "_"&amp;D21, ""))</f>
-        <v>1.1.1_SHU_START_7</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_6</v>
       </c>
       <c r="E21" t="str">
         <f>VLOOKUP(F21,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="str">
+        <f t="shared" si="5"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="str">
-        <f t="shared" si="8"/>
-        <v>1.1.1_SHU_START</v>
-      </c>
-      <c r="B22">
-        <f t="shared" si="9"/>
-        <v>8</v>
-      </c>
       <c r="C22" t="str">
-        <f>_xlfn.CONCAT(A22, "_", B22, IF(D22&lt;&gt;"", "_"&amp;D22, ""))</f>
-        <v>1.1.1_SHU_START_8</v>
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_7</v>
       </c>
       <c r="E22" t="str">
         <f>VLOOKUP(F22,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="str">
+        <f t="shared" si="5"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="4"/>
+        <v>1.1.1_SHU_START_8</v>
+      </c>
+      <c r="E23" t="str">
+        <f>VLOOKUP(F23,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>LiuBei</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="G28"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="G32"/>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9C8FDD-ADFD-4234-A520-0B798A346AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2210" yWindow="2900" windowWidth="21600" windowHeight="11300" activeTab="3"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,7 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="120">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,20 +248,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"죽음을 각오한 자 만이 내 창을 마주할 것이다"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DESC_TALK_SHU_ZHANGFEI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>DESC_TALK_SHU_ZHAYUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"하늘의 뜻은 이미 정해졌소.
-그대들이 어찌 내 계책을 벗어나겠소?"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -478,14 +468,64 @@
   </si>
   <si>
     <t>TUTORIAL_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_NORMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_ELITE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정예</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_GENERAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_HERO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_LEGEND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"하늘의 뜻은 이미 정해졌소.
+그대가 어찌 내 계책을 벗어나겠소?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"죽음을 각오한 자 만이
+나의 창을 마주할 것이다."</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,7 +625,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Overview"/>
@@ -643,6 +683,9 @@
             <v>ZhugeLiang</v>
           </cell>
         </row>
+        <row r="9">
+          <cell r="B9"/>
+        </row>
       </sheetData>
       <sheetData sheetId="2"/>
     </sheetDataSet>
@@ -693,7 +736,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -725,9 +768,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -759,6 +820,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -934,9 +1013,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -945,15 +1024,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="3" width="40.83203125" customWidth="1"/>
+    <col min="2" max="3" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -964,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -975,12 +1054,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -991,16 +1070,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="50.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="50.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1026,7 +1105,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1037,7 +1116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1048,7 +1127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1059,7 +1138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -1070,7 +1149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1081,29 +1160,29 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="C9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1114,7 +1193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1125,7 +1204,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1136,7 +1215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -1147,7 +1226,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1158,7 +1237,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1169,7 +1248,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1177,7 +1256,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1185,7 +1264,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1193,7 +1272,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1201,7 +1280,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1209,7 +1288,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="34">
+    <row r="21" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1217,7 +1296,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="34">
+    <row r="22" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1225,80 +1304,120 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="34">
+    <row r="23" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="34">
-      <c r="A25" t="s">
+      <c r="B25" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>58</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>60</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>62</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" t="s">
-        <v>68</v>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A3:C43">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C43">
     <sortCondition ref="A3"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1308,38 +1427,38 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.58203125" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="50.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="50.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
@@ -1351,12 +1470,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1378,9 +1497,9 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1390,10 +1509,10 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>A3</f>
         <v>TUTORIAL_START</v>
@@ -1407,13 +1526,13 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f>A4</f>
         <v>TUTORIAL_START</v>
@@ -1427,10 +1546,10 @@
         <v>TUTORIAL_START_2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" ref="A6:A12" si="2">A5</f>
         <v>TUTORIAL_START</v>
@@ -1444,10 +1563,10 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1461,13 +1580,13 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="34">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1481,13 +1600,13 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="34">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1501,13 +1620,13 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="34">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1521,13 +1640,13 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1541,13 +1660,13 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="34">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -1561,13 +1680,13 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f>A11</f>
         <v>TUTORIAL_START</v>
@@ -1581,10 +1700,10 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f>A12</f>
         <v>TUTORIAL_START</v>
@@ -1598,12 +1717,12 @@
         <v>TUTORIAL_START_11</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1620,10 +1739,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" ref="A16:A23" si="5">A15</f>
         <v>1.1.1_SHU_START</v>
@@ -1644,10 +1763,10 @@
         <v>9</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="34">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1668,10 +1787,10 @@
         <v>7</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1692,10 +1811,10 @@
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1716,10 +1835,10 @@
         <v>7</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1740,10 +1859,10 @@
         <v>9</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1764,10 +1883,10 @@
         <v>5</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1788,10 +1907,10 @@
         <v>7</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" si="5"/>
         <v>1.1.1_SHU_START</v>
@@ -1812,25 +1931,25 @@
         <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G28"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G32"/>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9C8FDD-ADFD-4234-A520-0B798A346AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FF16DB-31E7-4221-A235-14C70BB4993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="124">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -518,6 +518,22 @@
   <si>
     <t>"죽음을 각오한 자 만이
 나의 창을 마주할 것이다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자아! 이제 출발이다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아. 영웅을 출전시켜보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 얼굴을 눌러서 [+]를 누르자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 얼굴을 눌러서 [+]를 누르거나, 마우스 오른쪽 클릭을 해보자.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1428,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -1518,7 +1534,7 @@
         <v>TUTORIAL_START</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B14" si="0">B3+1</f>
+        <f t="shared" ref="B4:B18" si="0">B3+1</f>
         <v>1</v>
       </c>
       <c r="C4" t="str">
@@ -1721,135 +1737,113 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>77</v>
+      <c r="A15" t="str">
+        <f>A13</f>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" ref="C15:C23" si="4">CONCATENATE(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
-        <v>1.1.1_SHU_START_0</v>
-      </c>
-      <c r="E15" t="str">
-        <f>VLOOKUP(F15,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
-      </c>
-      <c r="F15" t="s">
-        <v>5</v>
+        <f t="shared" ref="C15" si="4">CONCATENATE(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
+        <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
-        <f t="shared" ref="A16:A23" si="5">A15</f>
-        <v>1.1.1_SHU_START</v>
+        <f>A14</f>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B16">
-        <f>B15+1</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_1</v>
-      </c>
-      <c r="E16" t="str">
-        <f>VLOOKUP(F16,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
+        <f t="shared" ref="C16" si="5">CONCATENATE(A16, "_", B16, IF(D16&lt;&gt;"", "_"&amp;D16, ""))</f>
+        <v>TUTORIAL_START_13_MOBILE</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
-        <f t="shared" si="5"/>
-        <v>1.1.1_SHU_START</v>
+        <f>A15</f>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B17">
-        <f>B16+1</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_2</v>
-      </c>
-      <c r="E17" t="str">
-        <f>VLOOKUP(F17,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F17" t="s">
-        <v>7</v>
+        <f t="shared" ref="C17" si="6">CONCATENATE(A17, "_", B17, IF(D17&lt;&gt;"", "_"&amp;D17, ""))</f>
+        <v>TUTORIAL_START_14_PC</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
-        <f t="shared" si="5"/>
-        <v>1.1.1_SHU_START</v>
+        <f>A16</f>
+        <v>TUTORIAL_START</v>
       </c>
       <c r="B18">
-        <f>B17+1</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_3</v>
-      </c>
-      <c r="E18" t="str">
-        <f>VLOOKUP(F18,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
-      </c>
-      <c r="F18" t="s">
-        <v>5</v>
+        <f t="shared" ref="C18" si="7">CONCATENATE(A18, "_", B18, IF(D18&lt;&gt;"", "_"&amp;D18, ""))</f>
+        <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="str">
-        <f t="shared" si="5"/>
-        <v>1.1.1_SHU_START</v>
+      <c r="A19" t="s">
+        <v>77</v>
       </c>
       <c r="B19">
-        <f>B18+1</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_4</v>
+        <f t="shared" ref="C19:C27" si="8">CONCATENATE(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
+        <v>1.1.1_SHU_START_0</v>
       </c>
       <c r="E19" t="str">
         <f>VLOOKUP(F19,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A20:A27" si="9">A19</f>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B20">
         <f>B19+1</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_5</v>
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_1</v>
       </c>
       <c r="E20" t="str">
         <f>VLOOKUP(F20,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1859,83 +1853,176 @@
         <v>9</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:B23" si="6">B20+1</f>
-        <v>6</v>
+        <f>B20+1</f>
+        <v>2</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_6</v>
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_2</v>
       </c>
       <c r="E21" t="str">
         <f>VLOOKUP(F21,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B22">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f>B21+1</f>
+        <v>3</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_7</v>
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_3</v>
       </c>
       <c r="E22" t="str">
         <f>VLOOKUP(F22,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B23">
-        <f t="shared" si="6"/>
-        <v>8</v>
+        <f>B22+1</f>
+        <v>4</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="4"/>
-        <v>1.1.1_SHU_START_8</v>
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_4</v>
       </c>
       <c r="E23" t="str">
         <f>VLOOKUP(F23,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F23" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B24">
+        <f>B23+1</f>
+        <v>5</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_5</v>
+      </c>
+      <c r="E24" t="str">
+        <f>VLOOKUP(F24,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ref="B25:B27" si="10">B24+1</f>
+        <v>6</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_6</v>
+      </c>
+      <c r="E25" t="str">
+        <f>VLOOKUP(F25,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>LiuBei</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F25" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_7</v>
+      </c>
+      <c r="E26" t="str">
+        <f>VLOOKUP(F26,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="str">
+        <f t="shared" si="9"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="10"/>
+        <v>8</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="8"/>
+        <v>1.1.1_SHU_START_8</v>
+      </c>
+      <c r="E27" t="str">
+        <f>VLOOKUP(F27,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G27"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G28"/>
@@ -1948,9 +2035,6 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G31"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FF16DB-31E7-4221-A235-14C70BB4993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740B8EB3-45C4-4221-B570-AFD13BB67914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -376,42 +376,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㅇㅋ. 관우 형님도 같이 합시다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>덩치야. 같이 의용병 콜??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>좋소. 태어난 날은 달라도 같은 날 죽읍시다. 내가 나이가 제일 많으니…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>술 값은 내가 내겠소. 무기도 필요하니 내가 준비해보겠소.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돗자리나 파는 양반이 돈이 어딨오?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뭔 소리요? 이 지역 돗자리는 내가 다 납품하고 있구만.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>형님, 잘 부탁하오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>응?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#PC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -534,6 +498,46 @@
   </si>
   <si>
     <t>영웅 얼굴을 눌러서 [+]를 누르거나, 마우스 오른쪽 클릭을 해보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러게 말입니다. 없는 살림에 너무 무리하시는건 아니신지..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔 소리야. 이 지역 돗자리는 내가 다 납품하고 있구만.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇다네요 형님ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런데 큰형님. 대체 돈은 어디서 난거요?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자아, 집중하자! 출진이다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오오!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관우 형님, 첫 출전인데 살살하쇼ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으휴.. 넌 힘 조절이나 잘 하거라.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1333,7 +1337,7 @@
         <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
@@ -1341,7 +1345,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1394,42 +1398,42 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1472,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>79</v>
@@ -1515,7 +1519,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1525,7 +1529,7 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1542,10 +1546,10 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1579,7 +1583,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1596,7 +1600,7 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>82</v>
@@ -1616,10 +1620,10 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1636,10 +1640,10 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1656,10 +1660,10 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1676,10 +1680,10 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1696,15 +1700,15 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
-        <f>A11</f>
+        <f t="shared" ref="A13:A18" si="3">A11</f>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B13">
@@ -1716,12 +1720,12 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
-        <f>A12</f>
+        <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B14">
@@ -1729,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" ref="C14" si="3">CONCATENATE(A14, "_", B14, IF(D14&lt;&gt;"", "_"&amp;D14, ""))</f>
+        <f t="shared" ref="C14" si="4">CONCATENATE(A14, "_", B14, IF(D14&lt;&gt;"", "_"&amp;D14, ""))</f>
         <v>TUTORIAL_START_11</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1738,7 +1742,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
-        <f>A13</f>
+        <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B15">
@@ -1746,16 +1750,16 @@
         <v>12</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" ref="C15" si="4">CONCATENATE(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
+        <f t="shared" ref="C15" si="5">CONCATENATE(A15, "_", B15, IF(D15&lt;&gt;"", "_"&amp;D15, ""))</f>
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
-        <f>A14</f>
+        <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B16">
@@ -1763,19 +1767,19 @@
         <v>13</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" ref="C16" si="5">CONCATENATE(A16, "_", B16, IF(D16&lt;&gt;"", "_"&amp;D16, ""))</f>
+        <f t="shared" ref="C16" si="6">CONCATENATE(A16, "_", B16, IF(D16&lt;&gt;"", "_"&amp;D16, ""))</f>
         <v>TUTORIAL_START_13_MOBILE</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
-        <f>A15</f>
+        <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B17">
@@ -1783,19 +1787,19 @@
         <v>14</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" ref="C17" si="6">CONCATENATE(A17, "_", B17, IF(D17&lt;&gt;"", "_"&amp;D17, ""))</f>
+        <f t="shared" ref="C17" si="7">CONCATENATE(A17, "_", B17, IF(D17&lt;&gt;"", "_"&amp;D17, ""))</f>
         <v>TUTORIAL_START_14_PC</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
-        <f>A16</f>
+        <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
       </c>
       <c r="B18">
@@ -1803,11 +1807,11 @@
         <v>15</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" ref="C18" si="7">CONCATENATE(A18, "_", B18, IF(D18&lt;&gt;"", "_"&amp;D18, ""))</f>
+        <f t="shared" ref="C18" si="8">CONCATENATE(A18, "_", B18, IF(D18&lt;&gt;"", "_"&amp;D18, ""))</f>
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1818,23 +1822,23 @@
         <v>0</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" ref="C19:C27" si="8">CONCATENATE(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
+        <f t="shared" ref="C19:C27" si="9">CONCATENATE(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
         <v>1.1.1_SHU_START_0</v>
       </c>
       <c r="E19" t="str">
         <f>VLOOKUP(F19,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" ref="A20:A27" si="9">A19</f>
+        <f t="shared" ref="A20:A29" si="10">A19</f>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B20">
@@ -1842,23 +1846,23 @@
         <v>1</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.1.1_SHU_START_1</v>
       </c>
       <c r="E20" t="str">
         <f>VLOOKUP(F20,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f t="shared" si="9"/>
+        <f>A20</f>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B21">
@@ -1866,23 +1870,23 @@
         <v>2</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C21:C26" si="11">CONCATENATE(A21, "_", B21, IF(D21&lt;&gt;"", "_"&amp;D21, ""))</f>
         <v>1.1.1_SHU_START_2</v>
       </c>
       <c r="E21" t="str">
         <f>VLOOKUP(F21,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B22">
@@ -1890,23 +1894,23 @@
         <v>3</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>1.1.1_SHU_START_3</v>
       </c>
       <c r="E22" t="str">
         <f>VLOOKUP(F22,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B23">
@@ -1914,7 +1918,7 @@
         <v>4</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C23:C28" si="12">CONCATENATE(A23, "_", B23, IF(D23&lt;&gt;"", "_"&amp;D23, ""))</f>
         <v>1.1.1_SHU_START_4</v>
       </c>
       <c r="E23" t="str">
@@ -1925,12 +1929,12 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B24">
@@ -1938,79 +1942,79 @@
         <v>5</v>
       </c>
       <c r="C24" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.1.1_SHU_START_5</v>
       </c>
       <c r="E24" t="str">
         <f>VLOOKUP(F24,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>LiuBei</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B25">
-        <f t="shared" ref="B25:B27" si="10">B24+1</f>
+        <f t="shared" ref="B24:B29" si="13">B24+1</f>
         <v>6</v>
       </c>
       <c r="C25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.1.1_SHU_START_6</v>
       </c>
       <c r="E25" t="str">
         <f>VLOOKUP(F25,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F25" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="C26" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.1.1_SHU_START_7</v>
       </c>
       <c r="E26" t="str">
         <f>VLOOKUP(F26,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1.1_SHU_START</v>
       </c>
       <c r="B27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="C27" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>1.1.1_SHU_START_8</v>
       </c>
       <c r="E27" t="str">
@@ -2021,14 +2025,56 @@
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G28"/>
+      <c r="A28" t="str">
+        <f t="shared" si="10"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="12"/>
+        <v>1.1.1_SHU_START_9</v>
+      </c>
+      <c r="E28" t="str">
+        <f>VLOOKUP(F28,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G29"/>
+      <c r="A29" t="str">
+        <f t="shared" si="10"/>
+        <v>1.1.1_SHU_START</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" ref="C29" si="14">CONCATENATE(A29, "_", B29, IF(D29&lt;&gt;"", "_"&amp;D29, ""))</f>
+        <v>1.1.1_SHU_START_10</v>
+      </c>
+      <c r="E29" t="str">
+        <f>VLOOKUP(F29,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G30"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740B8EB3-45C4-4221-B570-AFD13BB67914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7256D9B3-96A5-4BBB-92E4-65ACDAEF6FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -344,10 +344,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.1.1_SHU_START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>#name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -505,18 +501,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>뭔 소리야. 이 지역 돗자리는 내가 다 납품하고 있구만.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>..?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇다네요 형님ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그런데 큰형님. 대체 돈은 어디서 난거요?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -529,15 +513,49 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>관우 형님, 첫 출전인데 살살하쇼ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ㅋㅋㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>으휴.. 넌 힘 조절이나 잘 하거라.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_1_1_SHU_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 큰형님은 다르오ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너만 정신차리면 되겠구나.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한왕실의 재건을 위해 하는 일이니
+그런소리 마시게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔 소리야. 이 지역 돗자리는
+내가 다 납품하고 있구만.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관우 형님, 첫 출전인데 너무 무리하지 말고 살살하쇼ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니!! 부자였소?? 그런데 왜 그런 거지꼴로 다녔던거요??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐 딱히..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇다는구나 막내야ㅎ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1337,7 +1355,7 @@
         <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
@@ -1345,7 +1363,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1398,42 +1416,42 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1448,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -1466,19 +1484,19 @@
         <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
@@ -1495,7 +1513,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1519,7 +1537,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1529,7 +1547,7 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1546,10 +1564,10 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1566,7 +1584,7 @@
         <v>TUTORIAL_START_2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1583,7 +1601,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1600,10 +1618,10 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1620,10 +1638,10 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1640,10 +1658,10 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1660,10 +1678,10 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1680,10 +1698,10 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1700,10 +1718,10 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1720,7 +1738,7 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1737,7 +1755,7 @@
         <v>TUTORIAL_START_11</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1754,7 +1772,7 @@
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1771,10 +1789,10 @@
         <v>TUTORIAL_START_13_MOBILE</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1791,10 +1809,10 @@
         <v>TUTORIAL_START_14_PC</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1811,19 +1829,19 @@
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" ref="C19:C27" si="9">CONCATENATE(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
-        <v>1.1.1_SHU_START_0</v>
+        <f t="shared" ref="C19:C20" si="9">CONCATENATE(A19, "_", B19, IF(D19&lt;&gt;"", "_"&amp;D19, ""))</f>
+        <v>1_1_1_SHU_START_0</v>
       </c>
       <c r="E19" t="str">
         <f>VLOOKUP(F19,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1833,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" ref="A20:A29" si="10">A19</f>
-        <v>1.1.1_SHU_START</v>
+        <f t="shared" ref="A20:C33" si="10">A19</f>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B20">
         <f>B19+1</f>
@@ -1847,7 +1865,7 @@
       </c>
       <c r="C20" t="str">
         <f t="shared" si="9"/>
-        <v>1.1.1_SHU_START_1</v>
+        <v>1_1_1_SHU_START_1</v>
       </c>
       <c r="E20" t="str">
         <f>VLOOKUP(F20,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1857,21 +1875,21 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f>A20</f>
-        <v>1.1.1_SHU_START</v>
+        <f t="shared" si="10"/>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f>B20+1</f>
+        <f t="shared" ref="B21:D33" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" ref="C21:C26" si="11">CONCATENATE(A21, "_", B21, IF(D21&lt;&gt;"", "_"&amp;D21, ""))</f>
-        <v>1.1.1_SHU_START_2</v>
+        <f t="shared" ref="C21:C32" si="12">CONCATENATE(A21, "_", B21, IF(D21&lt;&gt;"", "_"&amp;D21, ""))</f>
+        <v>1_1_1_SHU_START_2</v>
       </c>
       <c r="E21" t="str">
         <f>VLOOKUP(F21,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1881,21 +1899,21 @@
         <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B22">
-        <f>B21+1</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="11"/>
-        <v>1.1.1_SHU_START_3</v>
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_3</v>
       </c>
       <c r="E22" t="str">
         <f>VLOOKUP(F22,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1905,21 +1923,21 @@
         <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B23">
-        <f>B22+1</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" ref="C23:C28" si="12">CONCATENATE(A23, "_", B23, IF(D23&lt;&gt;"", "_"&amp;D23, ""))</f>
-        <v>1.1.1_SHU_START_4</v>
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_4</v>
       </c>
       <c r="E23" t="str">
         <f>VLOOKUP(F23,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1929,21 +1947,21 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B24">
-        <f>B23+1</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="12"/>
-        <v>1.1.1_SHU_START_5</v>
+        <v>1_1_1_SHU_START_5</v>
       </c>
       <c r="E24" t="str">
         <f>VLOOKUP(F24,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -1953,45 +1971,48 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B25">
-        <f t="shared" ref="B24:B29" si="13">B24+1</f>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="12"/>
-        <v>1.1.1_SHU_START_6</v>
+        <v>1_1_1_SHU_START_6</v>
       </c>
       <c r="E25" t="str">
         <f>VLOOKUP(F25,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B26">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="12"/>
-        <v>1.1.1_SHU_START_7</v>
+        <v>1_1_1_SHU_START_7_1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
       </c>
       <c r="E26" t="str">
         <f>VLOOKUP(F26,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -2001,45 +2022,51 @@
         <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="12"/>
-        <v>1.1.1_SHU_START_8</v>
+        <v>1_1_1_SHU_START_8_1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
       </c>
       <c r="E27" t="str">
         <f>VLOOKUP(F27,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B28">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="12"/>
-        <v>1.1.1_SHU_START_9</v>
+        <v>1_1_1_SHU_START_9_2</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
       </c>
       <c r="E28" t="str">
         <f>VLOOKUP(F28,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -2049,38 +2076,134 @@
         <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" si="10"/>
-        <v>1.1.1_SHU_START</v>
+        <v>1_1_1_SHU_START</v>
       </c>
       <c r="B29">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="C29" t="str">
-        <f t="shared" ref="C29" si="14">CONCATENATE(A29, "_", B29, IF(D29&lt;&gt;"", "_"&amp;D29, ""))</f>
-        <v>1.1.1_SHU_START_10</v>
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_10_2</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
       </c>
       <c r="E29" t="str">
         <f>VLOOKUP(F29,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F29" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
+        <f t="shared" si="10"/>
+        <v>1_1_1_SHU_START</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_11_2</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="str">
+        <f>VLOOKUP(F30,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>GuanYu</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G30"/>
+      <c r="G30" s="3" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G31"/>
+      <c r="A31" t="str">
+        <f t="shared" si="10"/>
+        <v>1_1_1_SHU_START</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_12</v>
+      </c>
+      <c r="E31" t="str">
+        <f>VLOOKUP(F31,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F31" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="str">
+        <f t="shared" si="10"/>
+        <v>1_1_1_SHU_START</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="12"/>
+        <v>1_1_1_SHU_START_13</v>
+      </c>
+      <c r="E32" t="str">
+        <f>VLOOKUP(F32,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="str">
+        <f t="shared" si="10"/>
+        <v>1_1_1_SHU_START</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" ref="C33" si="13">CONCATENATE(A33, "_", B33, IF(D33&lt;&gt;"", "_"&amp;D33, ""))</f>
+        <v>1_1_1_SHU_START_14</v>
+      </c>
+      <c r="E33" t="str">
+        <f>VLOOKUP(F33,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7256D9B3-96A5-4BBB-92E4-65ACDAEF6FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274FD8A9-E5B8-4085-A248-55D81CC3ECC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5580" yWindow="2880" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -401,11 +401,6 @@
   </si>
   <si>
     <t>돌진과 공격을 사용해보자.
-X가 공격이고, C는 돌진이야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌진과 공격을 사용해보자.
 아래 버튼을 눌러봐.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -556,6 +551,47 @@
   </si>
   <si>
     <t>그렇다는구나 막내야ㅎ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME_GOLD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영혼석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연회권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME_SCROLL_PARTY</t>
+  </si>
+  <si>
+    <t>ITEM_NAME_RICE</t>
+  </si>
+  <si>
+    <t>ITEM_NAME_STONE_SOUL</t>
+  </si>
+  <si>
+    <t>ITEM_NAME_STONE_TIME</t>
+  </si>
+  <si>
+    <t>돌진과 공격을 사용해보자.
+Z가 공격이고, X는 돌진이야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1063,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1101,9 +1137,50 @@
       </c>
       <c r="C3" s="3"/>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1355,7 +1432,7 @@
         <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
@@ -1363,7 +1440,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1416,42 +1493,42 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1614,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1601,7 +1678,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1661,7 +1738,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1681,7 +1758,7 @@
         <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1701,7 +1778,7 @@
         <v>87</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1721,7 +1798,7 @@
         <v>88</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1738,7 +1815,7 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1772,7 +1849,7 @@
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1792,7 +1869,7 @@
         <v>87</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1812,7 +1889,7 @@
         <v>88</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1829,12 +1906,12 @@
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1851,12 +1928,12 @@
         <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" ref="A20:C33" si="10">A19</f>
+        <f t="shared" ref="A20:A33" si="10">A19</f>
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B20">
@@ -1875,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1884,7 +1961,7 @@
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:D33" si="11">B20+1</f>
+        <f t="shared" ref="B21:B33" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
@@ -1899,7 +1976,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1923,7 +2000,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1947,7 +2024,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1971,7 +2048,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1995,7 +2072,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2022,7 +2099,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2049,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2076,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2103,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2130,7 +2207,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2154,7 +2231,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2178,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2202,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274FD8A9-E5B8-4085-A248-55D81CC3ECC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26DA854-1D4E-4E15-A53D-D9AED5546355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2880" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,7 +591,7 @@
   </si>
   <si>
     <t>돌진과 공격을 사용해보자.
-Z가 공격이고, X는 돌진이야.</t>
+X가 공격이고, C는 돌진이야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26DA854-1D4E-4E15-A53D-D9AED5546355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869596A6-B62E-472E-9C9D-2058C75C3B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2880" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -590,8 +590,8 @@
     <t>ITEM_NAME_STONE_TIME</t>
   </si>
   <si>
-    <t>돌진과 공격을 사용해보자.
-X가 공격이고, C는 돌진이야.</t>
+    <t>공격과 돌진을 사용해보자.
+좌클릭이 공격이고, 스페이스가 돌진이야.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869596A6-B62E-472E-9C9D-2058C75C3B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB80989B-58B9-45FE-8F96-140C0B7F73D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,10 +376,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>키보드 조작으로 내가 움직일 수 있을거 같은데? 방향키를 눌러보까?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>음?? 여긴..?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -397,11 +393,6 @@
   </si>
   <si>
     <t>얼빠지게 생긴 넘이다!! 죽여라!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌진과 공격을 사용해보자.
-아래 버튼을 눌러봐.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -592,6 +583,16 @@
   <si>
     <t>공격과 돌진을 사용해보자.
 좌클릭이 공격이고, 스페이스가 돌진이야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드 조작으로 내가 움직일 수 있을거 같은데?
+[W,A,S,D]를 눌러보까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격과 돌진을 사용해보자.
+아래 버튼을 눌러봐.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1139,42 +1140,42 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1432,7 +1433,7 @@
         <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
@@ -1440,7 +1441,7 @@
         <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -1493,42 +1494,42 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1615,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1624,7 +1625,7 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1641,10 +1642,10 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1678,7 +1679,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1695,7 +1696,7 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>81</v>
@@ -1715,10 +1716,10 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1735,10 +1736,10 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1755,10 +1756,10 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1775,10 +1776,10 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1795,10 +1796,10 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1815,7 +1816,7 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1849,7 +1850,7 @@
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1866,10 +1867,10 @@
         <v>TUTORIAL_START_13_MOBILE</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1886,10 +1887,10 @@
         <v>TUTORIAL_START_14_PC</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1906,12 +1907,12 @@
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1928,7 +1929,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1952,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1976,7 +1977,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2000,7 +2001,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2024,7 +2025,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2048,7 +2049,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2072,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2099,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2126,7 +2127,7 @@
         <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2153,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2180,7 +2181,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2207,7 +2208,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2231,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2255,7 +2256,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2279,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB80989B-58B9-45FE-8F96-140C0B7F73D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0002B3-61B4-4411-9A45-953082DE0D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -106,10 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CLASSTYPE_CHAMPION</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>용장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,10 +146,6 @@
   </si>
   <si>
     <t>추격자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CLASSTYPE_SENTINEL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -593,6 +585,14 @@
   <si>
     <t>공격과 돌진을 사용해보자.
 아래 버튼을 눌러봐.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLASSTYPE_CHASER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CLASSTYPE_CHAMPION</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -705,7 +705,8 @@
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="HeroData"/>
-      <sheetName val="EnemyData"/>
+      <sheetName val="HeroStatData"/>
+      <sheetName val="EnemyStatData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -763,6 +764,7 @@
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1131,51 +1133,51 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1225,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -1234,7 +1236,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
@@ -1245,7 +1247,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
@@ -1256,7 +1258,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -1267,7 +1269,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -1278,24 +1280,24 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1311,225 +1313,225 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1559,22 +1561,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
@@ -1591,7 +1593,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1615,7 +1617,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1625,7 +1627,7 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1642,10 +1644,10 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1662,7 +1664,7 @@
         <v>TUTORIAL_START_2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1679,7 +1681,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1696,10 +1698,10 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1716,10 +1718,10 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1736,10 +1738,10 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1756,10 +1758,10 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1776,10 +1778,10 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -1796,10 +1798,10 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1816,7 +1818,7 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1833,7 +1835,7 @@
         <v>TUTORIAL_START_11</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1850,7 +1852,7 @@
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1867,10 +1869,10 @@
         <v>TUTORIAL_START_13_MOBILE</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -1887,10 +1889,10 @@
         <v>TUTORIAL_START_14_PC</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1907,12 +1909,12 @@
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1929,7 +1931,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1953,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1977,7 +1979,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2001,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2025,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2049,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -2073,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2100,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2127,7 +2129,7 @@
         <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2154,7 +2156,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2181,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2208,7 +2210,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2232,7 +2234,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2256,7 +2258,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2280,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0002B3-61B4-4411-9A45-953082DE0D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA62D1C1-33E6-4771-B64E-636D3C61B699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="159">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -593,6 +593,86 @@
   </si>
   <si>
     <t>CLASSTYPE_CHAMPION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_ATTACK_POWER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_DEFENCE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_ATTACK_SPEED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_HEALTH_MAX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_MOVE_SPEED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_LIFE_STEAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_CRITICAL_RATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_COOLDOWN_RATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_CRITICAL_DAMAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BATTLESTAT_BOSS_DAMAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력흡수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨타임감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명위력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스피해량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1102,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1180,6 +1260,126 @@
         <v>129</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1189,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -1492,46 +1692,6 @@
       </c>
       <c r="B31" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA62D1C1-33E6-4771-B64E-636D3C61B699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A50303-82DE-48D3-A314-500BD13D6EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1065" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="181">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -673,6 +673,94 @@
   </si>
   <si>
     <t>보스피해량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORESTAT_LEADERSHIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORESTAT_STRENGTH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORESTAT_POLITICS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORESTAT_CHARISMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통솔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CORESTAT_INTELLECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_PALACE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_FARM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_MARKET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_OFFICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_MERCHANT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CASTLE_OBJECT_GATE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1182,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1378,6 +1466,94 @@
       </c>
       <c r="B23" s="3" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A50303-82DE-48D3-A314-500BD13D6EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29C92EC-8262-44F6-9EEA-7ABA029CAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="1065" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27555" yWindow="2145" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,18 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29C92EC-8262-44F6-9EEA-7ABA029CAA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429726CF-9C51-41D7-B045-74F0D27D3908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27555" yWindow="2145" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2310" yWindow="3285" windowWidth="16200" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="String" sheetId="4" r:id="rId2"/>
-    <sheet name="String_Hero" sheetId="3" r:id="rId3"/>
-    <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId4"/>
+    <sheet name="String_Mission" sheetId="6" r:id="rId3"/>
+    <sheet name="String_Hero" sheetId="3" r:id="rId4"/>
+    <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="202">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -762,13 +763,77 @@
   <si>
     <t>궁성</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Mission Key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>military_training</t>
+  </si>
+  <si>
+    <t>rally_remnants</t>
+  </si>
+  <si>
+    <t>bandit_subjugation</t>
+  </si>
+  <si>
+    <t>border_defense</t>
+  </si>
+  <si>
+    <t>tax_reform</t>
+  </si>
+  <si>
+    <t>foreign_diplomacy</t>
+  </si>
+  <si>
+    <t>enemy_intelligence</t>
+  </si>
+  <si>
+    <t>tactics_research</t>
+  </si>
+  <si>
+    <t>refugee_persuasion</t>
+  </si>
+  <si>
+    <t>recruit_talent</t>
+  </si>
+  <si>
+    <t>군사 훈련 지휘</t>
+  </si>
+  <si>
+    <t>패잔병 수습</t>
+  </si>
+  <si>
+    <t>산적 토벌</t>
+  </si>
+  <si>
+    <t>변경 수비</t>
+  </si>
+  <si>
+    <t>조세 제도 정비</t>
+  </si>
+  <si>
+    <t>인근 제후국 외교</t>
+  </si>
+  <si>
+    <t>적진 첩보 수집</t>
+  </si>
+  <si>
+    <t>병법서 연구</t>
+  </si>
+  <si>
+    <t>유랑민 귀순 설득</t>
+  </si>
+  <si>
+    <t>재야 인재 영입</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,6 +857,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -837,7 +908,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,6 +920,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1564,6 +1653,180 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.25" style="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="8" t="str">
+        <f>UPPER(A3)&amp;"_TITLE"</f>
+        <v>MILITARY_TRAINING_TITLE</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="8" t="str">
+        <f t="shared" ref="B4:B12" si="0">UPPER(A4)&amp;"_TITLE"</f>
+        <v>RALLY_REMNANTS_TITLE</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>BANDIT_SUBJUGATION_TITLE</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>BORDER_DEFENSE_TITLE</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>TAX_REFORM_TITLE</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>FOREIGN_DIPLOMACY_TITLE</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>ENEMY_INTELLIGENCE_TITLE</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>TACTICS_RESEARCH_TITLE</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>REFUGEE_PERSUASION_TITLE</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>RECRUIT_TALENT_TITLE</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1880,7 +2143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{429726CF-9C51-41D7-B045-74F0D27D3908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E671DEEE-1E8E-422B-89B8-3464C52D12FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="3285" windowWidth="16200" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="211">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -827,6 +827,42 @@
   </si>
   <si>
     <t>재야 인재 영입</t>
+  </si>
+  <si>
+    <t>GRADETYPE_NORMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>극한</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>심연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADETYPE_ELITE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADETYPE_GENERAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADETYPE_HERO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADETYPE_LEGEND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -859,7 +895,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -908,7 +944,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -921,23 +957,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1654,22 +1696,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1677,13 +1719,13 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1701,7 +1743,7 @@
       <c r="C3" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
@@ -1714,7 +1756,7 @@
       <c r="C4" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1727,7 +1769,7 @@
       <c r="C5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
@@ -1740,7 +1782,7 @@
       <c r="C6" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
@@ -1753,7 +1795,7 @@
       <c r="C7" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -1766,7 +1808,7 @@
       <c r="C8" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1779,7 +1821,7 @@
       <c r="C9" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1792,7 +1834,7 @@
       <c r="C10" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
@@ -1805,7 +1847,7 @@
       <c r="C11" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1818,7 +1860,57 @@
       <c r="C12" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E671DEEE-1E8E-422B-89B8-3464C52D12FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EE2915-1B78-4FC8-B525-51A6D449A44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -562,16 +562,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ITEM_NAME_SCROLL_PARTY</t>
-  </si>
-  <si>
     <t>ITEM_NAME_RICE</t>
-  </si>
-  <si>
-    <t>ITEM_NAME_STONE_SOUL</t>
-  </si>
-  <si>
-    <t>ITEM_NAME_STONE_TIME</t>
   </si>
   <si>
     <t>공격과 돌진을 사용해보자.
@@ -862,6 +853,18 @@
   </si>
   <si>
     <t>GRADETYPE_LEGEND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME_NORMAL_GATCHA_TICKET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME_DEDICATED_SOUL_STONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITEM_NAME_TIME_STONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1449,7 +1452,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
         <v>126</v>
@@ -1457,7 +1460,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="B6" t="s">
         <v>127</v>
@@ -1465,7 +1468,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
         <v>128</v>
@@ -1473,7 +1476,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="B8" t="s">
         <v>129</v>
@@ -1521,170 +1524,170 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
         <v>173</v>
-      </c>
-      <c r="B33" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1706,7 +1709,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -1734,138 +1737,138 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>UPPER(A3)&amp;"_TITLE"</f>
         <v>MILITARY_TRAINING_TITLE</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B4" s="8" t="str">
         <f t="shared" ref="B4:B12" si="0">UPPER(A4)&amp;"_TITLE"</f>
         <v>RALLY_REMNANTS_TITLE</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>BANDIT_SUBJUGATION_TITLE</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>BORDER_DEFENSE_TITLE</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>TAX_REFORM_TITLE</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>FOREIGN_DIPLOMACY_TITLE</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B9" s="8" t="str">
         <f t="shared" si="0"/>
         <v>ENEMY_INTELLIGENCE_TITLE</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B10" s="8" t="str">
         <f t="shared" si="0"/>
         <v>TACTICS_RESEARCH_TITLE</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B11" s="8" t="str">
         <f t="shared" si="0"/>
         <v>REFUGEE_PERSUASION_TITLE</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B12" s="8" t="str">
         <f t="shared" si="0"/>
         <v>RECRUIT_TALENT_TITLE</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>94</v>
@@ -1875,40 +1878,40 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D17" s="11"/>
     </row>
@@ -2044,7 +2047,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
@@ -2066,7 +2069,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>28</v>
@@ -2412,7 +2415,7 @@
         <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -2432,7 +2435,7 @@
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -2452,7 +2455,7 @@
         <v>85</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,19 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EE2915-1B78-4FC8-B525-51A6D449A44F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D54BE11-ED68-4E3D-9DA9-E354767223D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="String" sheetId="4" r:id="rId2"/>
     <sheet name="String_Mission" sheetId="6" r:id="rId3"/>
     <sheet name="String_Hero" sheetId="3" r:id="rId4"/>
-    <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId5"/>
+    <sheet name="String_Treasure" sheetId="7" r:id="rId5"/>
+    <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="310">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -820,10 +821,6 @@
     <t>재야 인재 영입</t>
   </si>
   <si>
-    <t>GRADETYPE_NORMAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>난세</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -840,22 +837,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GRADETYPE_ELITE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRADETYPE_GENERAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRADETYPE_HERO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRADETYPE_LEGEND</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ITEM_NAME_NORMAL_GATCHA_TICKET</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -866,6 +847,332 @@
   <si>
     <t>ITEM_NAME_TIME_STONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_DIFFICULT_NORMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_DIFFICULT_ELITE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_DIFFICULT_GENERAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_DIFFICULT_HERO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRADE_DIFFICULT_LEGEND</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>촉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_WU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_SHU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_ETC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Treasure_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ganjiang_moye</t>
+  </si>
+  <si>
+    <t>liutao</t>
+  </si>
+  <si>
+    <t>sanlue</t>
+  </si>
+  <si>
+    <t>weiliaozi</t>
+  </si>
+  <si>
+    <t>commanders_banner</t>
+  </si>
+  <si>
+    <t>tiger_tally</t>
+  </si>
+  <si>
+    <t>war_drum_gong</t>
+  </si>
+  <si>
+    <t>sima_fa</t>
+  </si>
+  <si>
+    <t>wuzi</t>
+  </si>
+  <si>
+    <t>red_cliff_flame</t>
+  </si>
+  <si>
+    <t>bangcheonhwagug_shard</t>
+  </si>
+  <si>
+    <t>chungou</t>
+  </si>
+  <si>
+    <t>zhanlu</t>
+  </si>
+  <si>
+    <t>yuchang</t>
+  </si>
+  <si>
+    <t>taie</t>
+  </si>
+  <si>
+    <t>juque</t>
+  </si>
+  <si>
+    <t>shengxie</t>
+  </si>
+  <si>
+    <t>lords_war_bow</t>
+  </si>
+  <si>
+    <t>wujangwon_star</t>
+  </si>
+  <si>
+    <t>art_of_war</t>
+  </si>
+  <si>
+    <t>qimen_dunjia</t>
+  </si>
+  <si>
+    <t>i_ching</t>
+  </si>
+  <si>
+    <t>guiguzi</t>
+  </si>
+  <si>
+    <t>guanzi</t>
+  </si>
+  <si>
+    <t>han_feizi</t>
+  </si>
+  <si>
+    <t>su_shu_of_huangshi</t>
+  </si>
+  <si>
+    <t>mozi</t>
+  </si>
+  <si>
+    <t>emperors_seal</t>
+  </si>
+  <si>
+    <t>book_of_lord_shang</t>
+  </si>
+  <si>
+    <t>lushi_chunqiu</t>
+  </si>
+  <si>
+    <t>analects</t>
+  </si>
+  <si>
+    <t>wei_administrative_code</t>
+  </si>
+  <si>
+    <t>stratagems_of_warring_states</t>
+  </si>
+  <si>
+    <t>imperial_jade_seal</t>
+  </si>
+  <si>
+    <t>prefects_official_seal</t>
+  </si>
+  <si>
+    <t>huanglao_silk_manuscript</t>
+  </si>
+  <si>
+    <t>doewon_cup</t>
+  </si>
+  <si>
+    <t>hes_jade_disc</t>
+  </si>
+  <si>
+    <t>classic_of_mountains_and_seas</t>
+  </si>
+  <si>
+    <t>xuanhe_qin</t>
+  </si>
+  <si>
+    <t>phoenix_jade_pendant</t>
+  </si>
+  <si>
+    <t>book_of_rites</t>
+  </si>
+  <si>
+    <t>alliance_letter</t>
+  </si>
+  <si>
+    <t>hetu_luoshu</t>
+  </si>
+  <si>
+    <t>map_of_queen_mother_of_the_west</t>
+  </si>
+  <si>
+    <t>육도</t>
+  </si>
+  <si>
+    <t>삼략</t>
+  </si>
+  <si>
+    <t>위료자</t>
+  </si>
+  <si>
+    <t>장수기</t>
+  </si>
+  <si>
+    <t>호부</t>
+  </si>
+  <si>
+    <t>금고</t>
+  </si>
+  <si>
+    <t>사마법</t>
+  </si>
+  <si>
+    <t>오자</t>
+  </si>
+  <si>
+    <t>적벽의 화염</t>
+  </si>
+  <si>
+    <t>방천화극 파편</t>
+  </si>
+  <si>
+    <t>간장막야</t>
+  </si>
+  <si>
+    <t>순구</t>
+  </si>
+  <si>
+    <t>담로</t>
+  </si>
+  <si>
+    <t>어장</t>
+  </si>
+  <si>
+    <t>태아</t>
+  </si>
+  <si>
+    <t>거궐</t>
+  </si>
+  <si>
+    <t>승영</t>
+  </si>
+  <si>
+    <t>군왕궁</t>
+  </si>
+  <si>
+    <t>오장원의 별</t>
+  </si>
+  <si>
+    <t>손자병법</t>
+  </si>
+  <si>
+    <t>기문둔갑</t>
+  </si>
+  <si>
+    <t>주역</t>
+  </si>
+  <si>
+    <t>귀곡자</t>
+  </si>
+  <si>
+    <t>관자</t>
+  </si>
+  <si>
+    <t>한비자</t>
+  </si>
+  <si>
+    <t>황석공소서</t>
+  </si>
+  <si>
+    <t>묵자</t>
+  </si>
+  <si>
+    <t>황제의 인장</t>
+  </si>
+  <si>
+    <t>상군서</t>
+  </si>
+  <si>
+    <t>여씨춘추</t>
+  </si>
+  <si>
+    <t>논어</t>
+  </si>
+  <si>
+    <t>정전</t>
+  </si>
+  <si>
+    <t>전국책</t>
+  </si>
+  <si>
+    <t>옥새</t>
+  </si>
+  <si>
+    <t>군목 인장</t>
+  </si>
+  <si>
+    <t>황노백서</t>
+  </si>
+  <si>
+    <t>도원의 술잔</t>
+  </si>
+  <si>
+    <t>화씨벽</t>
+  </si>
+  <si>
+    <t>산해경</t>
+  </si>
+  <si>
+    <t>현학금</t>
+  </si>
+  <si>
+    <t>봉황패</t>
+  </si>
+  <si>
+    <t>예기</t>
+  </si>
+  <si>
+    <t>연환서</t>
+  </si>
+  <si>
+    <t>하도낙서</t>
+  </si>
+  <si>
+    <t>서왕모도</t>
   </si>
 </sst>
 </file>
@@ -918,7 +1225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -941,13 +1248,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -983,6 +1303,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1404,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1460,7 +1798,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
         <v>127</v>
@@ -1468,7 +1806,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
         <v>128</v>
@@ -1476,7 +1814,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
         <v>129</v>
@@ -1688,6 +2026,38 @@
       </c>
       <c r="B34" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1868,7 +2238,7 @@
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>94</v>
@@ -1878,46 +2248,47 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D15" s="11"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D17" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2239,6 +2610,688 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EE6A7D-8E38-47C7-B564-D54B5D506D09}">
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.25" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="6.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="16" t="str">
+        <f>"NAME_" &amp; UPPER(A3)</f>
+        <v>NAME_LIUTAO</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="16" t="str">
+        <f t="shared" ref="B4:B47" si="0">"NAME_" &amp; UPPER(A4)</f>
+        <v>NAME_SANLUE</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_WEILIAOZI</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_COMMANDERS_BANNER</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_TIGER_TALLY</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_WAR_DRUM_GONG</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_SIMA_FA</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_WUZI</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_RED_CLIFF_FLAME</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_BANGCHEONHWAGUG_SHARD</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_GANJIANG_MOYE</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_CHUNGOU</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_ZHANLU</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_YUCHANG</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B17" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_TAIE</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_JUQUE</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_SHENGXIE</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B20" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_LORDS_WAR_BOW</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B21" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_WUJANGWON_STAR</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_ART_OF_WAR</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_QIMEN_DUNJIA</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B24" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_I_CHING</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B25" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_GUIGUZI</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_GUANZI</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_HAN_FEIZI</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B28" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_SU_SHU_OF_HUANGSHI</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B29" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_MOZI</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="B30" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_EMPERORS_SEAL</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B31" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_BOOK_OF_LORD_SHANG</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B32" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_LUSHI_CHUNQIU</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="B33" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_ANALECTS</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_WEI_ADMINISTRATIVE_CODE</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_STRATAGEMS_OF_WARRING_STATES</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B36" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_IMPERIAL_JADE_SEAL</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B37" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_PREFECTS_OFFICIAL_SEAL</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B38" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_HUANGLAO_SILK_MANUSCRIPT</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B39" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_DOEWON_CUP</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_HES_JADE_DISC</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_CLASSIC_OF_MOUNTAINS_AND_SEAS</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B42" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_XUANHE_QIN</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_PHOENIX_JADE_PENDANT</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_BOOK_OF_RITES</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_ALLIANCE_LETTER</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_HETU_LUOSHU</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>NAME_MAP_OF_QUEEN_MOTHER_OF_THE_WEST</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D54BE11-ED68-4E3D-9DA9-E354767223D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3C7A29-7AEC-49B7-BDBB-164D4BFC62E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3C7A29-7AEC-49B7-BDBB-164D4BFC62E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F16CDEC-F9C9-46B3-A23A-1947E6AB2FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="325">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1173,6 +1173,67 @@
   </si>
   <si>
     <t>서왕모도</t>
+  </si>
+  <si>
+    <t>NAME_ETC_LUBU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여포</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LuBu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COURTESY_ETC_LUBU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESC_TALK_ETC_LUBU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>봉선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위나라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>촉나라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오나라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>군웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_SHU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_WU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_ETC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"누가 감히 나와 싸우겠느냐?
+귀큰 놈, 네 놈이냐?!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1267,7 +1328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1289,21 +1350,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1321,6 +1367,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1400,7 +1464,12 @@
           </cell>
         </row>
         <row r="9">
-          <cell r="B9"/>
+          <cell r="A9" t="str">
+            <v>여포</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>LuBu</v>
+          </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
@@ -1742,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2030,33 +2099,65 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>323</v>
+      </c>
+      <c r="B38" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B39" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>217</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B42" t="s">
         <v>218</v>
       </c>
     </row>
@@ -2092,198 +2193,198 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="8" t="str">
+      <c r="B3" s="17" t="str">
         <f>UPPER(A3)&amp;"_TITLE"</f>
         <v>MILITARY_TRAINING_TITLE</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="8" t="str">
+      <c r="B4" s="17" t="str">
         <f t="shared" ref="B4:B12" si="0">UPPER(A4)&amp;"_TITLE"</f>
         <v>RALLY_REMNANTS_TITLE</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="18"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B5" s="8" t="str">
+      <c r="B5" s="17" t="str">
         <f t="shared" si="0"/>
         <v>BANDIT_SUBJUGATION_TITLE</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="8" t="str">
+      <c r="B6" s="17" t="str">
         <f t="shared" si="0"/>
         <v>BORDER_DEFENSE_TITLE</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B7" s="8" t="str">
+      <c r="B7" s="17" t="str">
         <f t="shared" si="0"/>
         <v>TAX_REFORM_TITLE</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="18"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="8" t="str">
+      <c r="B8" s="17" t="str">
         <f t="shared" si="0"/>
         <v>FOREIGN_DIPLOMACY_TITLE</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="18"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="17" t="str">
         <f t="shared" si="0"/>
         <v>ENEMY_INTELLIGENCE_TITLE</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="8" t="str">
+      <c r="B10" s="17" t="str">
         <f t="shared" si="0"/>
         <v>TACTICS_RESEARCH_TITLE</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="18"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="17" t="str">
         <f t="shared" si="0"/>
         <v>REFUGEE_PERSUASION_TITLE</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="17" t="str">
         <f t="shared" si="0"/>
         <v>RECRUIT_TALENT_TITLE</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="18"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="18"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2294,7 +2395,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -2330,278 +2431,305 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>313</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>44</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>314</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B29" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B30" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B34" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C43">
-    <sortCondition ref="A3"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C34">
+    <sortCondition ref="A3:A34"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2614,675 +2742,675 @@
   <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.25" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.75" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="6.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="13"/>
+    <col min="1" max="1" width="29.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="6.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B3" s="16" t="str">
+      <c r="B3" s="11" t="str">
         <f>"NAME_" &amp; UPPER(A3)</f>
         <v>NAME_LIUTAO</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="16" t="str">
+      <c r="B4" s="11" t="str">
         <f t="shared" ref="B4:B47" si="0">"NAME_" &amp; UPPER(A4)</f>
         <v>NAME_SANLUE</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B5" s="16" t="str">
+      <c r="B5" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WEILIAOZI</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B6" s="16" t="str">
+      <c r="B6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_COMMANDERS_BANNER</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B7" s="16" t="str">
+      <c r="B7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_TIGER_TALLY</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="16" t="str">
+      <c r="B8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WAR_DRUM_GONG</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B9" s="16" t="str">
+      <c r="B9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SIMA_FA</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="12" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B10" s="16" t="str">
+      <c r="B10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WUZI</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B11" s="16" t="str">
+      <c r="B11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_RED_CLIFF_FLAME</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B12" s="16" t="str">
+      <c r="B12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BANGCHEONHWAGUG_SHARD</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="16" t="str">
+      <c r="B13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GANJIANG_MOYE</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="16" t="str">
+      <c r="B14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_CHUNGOU</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="16" t="str">
+      <c r="B15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ZHANLU</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B16" s="16" t="str">
+      <c r="B16" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_YUCHANG</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="16" t="str">
+      <c r="B17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_TAIE</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B18" s="16" t="str">
+      <c r="B18" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_JUQUE</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B19" s="16" t="str">
+      <c r="B19" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SHENGXIE</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B20" s="16" t="str">
+      <c r="B20" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_LORDS_WAR_BOW</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B21" s="16" t="str">
+      <c r="B21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WUJANGWON_STAR</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B22" s="16" t="str">
+      <c r="B22" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ART_OF_WAR</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B23" s="16" t="str">
+      <c r="B23" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_QIMEN_DUNJIA</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B24" s="16" t="str">
+      <c r="B24" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_I_CHING</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B25" s="16" t="str">
+      <c r="B25" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GUIGUZI</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="16" t="str">
+      <c r="B26" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GUANZI</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B27" s="16" t="str">
+      <c r="B27" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HAN_FEIZI</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B28" s="16" t="str">
+      <c r="B28" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SU_SHU_OF_HUANGSHI</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B29" s="16" t="str">
+      <c r="B29" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_MOZI</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B30" s="16" t="str">
+      <c r="B30" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_EMPERORS_SEAL</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B31" s="16" t="str">
+      <c r="B31" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BOOK_OF_LORD_SHANG</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B32" s="16" t="str">
+      <c r="B32" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_LUSHI_CHUNQIU</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="16" t="str">
+      <c r="B33" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ANALECTS</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B34" s="16" t="str">
+      <c r="B34" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WEI_ADMINISTRATIVE_CODE</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B35" s="16" t="str">
+      <c r="B35" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_STRATAGEMS_OF_WARRING_STATES</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B36" s="16" t="str">
+      <c r="B36" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_IMPERIAL_JADE_SEAL</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B37" s="16" t="str">
+      <c r="B37" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_PREFECTS_OFFICIAL_SEAL</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B38" s="16" t="str">
+      <c r="B38" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HUANGLAO_SILK_MANUSCRIPT</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B39" s="16" t="str">
+      <c r="B39" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_DOEWON_CUP</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B40" s="16" t="str">
+      <c r="B40" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HES_JADE_DISC</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B41" s="16" t="str">
+      <c r="B41" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_CLASSIC_OF_MOUNTAINS_AND_SEAS</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B42" s="16" t="str">
+      <c r="B42" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_XUANHE_QIN</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B43" s="16" t="str">
+      <c r="B43" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_PHOENIX_JADE_PENDANT</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B44" s="16" t="str">
+      <c r="B44" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BOOK_OF_RITES</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B45" s="16" t="str">
+      <c r="B45" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ALLIANCE_LETTER</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B46" s="16" t="str">
+      <c r="B46" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HETU_LUOSHU</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B47" s="16" t="str">
+      <c r="B47" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_MAP_OF_QUEEN_MOTHER_OF_THE_WEST</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F16CDEC-F9C9-46B3-A23A-1947E6AB2FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D675CCC6-4083-43EC-B01B-F4669319F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="370">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1233,6 +1233,186 @@
   <si>
     <t>"누가 감히 나와 싸우겠느냐?
 귀큰 놈, 네 놈이냐?!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_QINSHIHUANG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진시황</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_LIANPO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_XIANGYU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_YUEYI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_YANGYOUJI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양유기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>염파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_QINSHIHUANG_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_LIANPO_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_XIANGYU_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_YUEYI_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_YANGYOUJI_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최초의 황제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낚시꾼의 시조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백발백중의 신궁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연나라의 구국명장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최강의 역발산 패왕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백전백승의 노익장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_MONDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_TUESDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_WEDNESDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_THURSDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_FRIDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_SATURDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEEKDAY_SUNDAY_FULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일요일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thesday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wednesday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thursday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sunday</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_JIANGSHANG_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME_HISTORICAL_JIANGSHANG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1811,7 +1991,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2081,7 +2261,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>170</v>
       </c>
@@ -2089,7 +2269,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>171</v>
       </c>
@@ -2097,7 +2277,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>320</v>
       </c>
@@ -2105,7 +2285,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>321</v>
       </c>
@@ -2113,7 +2293,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>322</v>
       </c>
@@ -2121,7 +2301,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>323</v>
       </c>
@@ -2129,7 +2309,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>214</v>
       </c>
@@ -2137,7 +2317,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>216</v>
       </c>
@@ -2145,7 +2325,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>215</v>
       </c>
@@ -2153,12 +2333,89 @@
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>217</v>
       </c>
       <c r="B42" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>348</v>
+      </c>
+      <c r="B43" t="s">
+        <v>347</v>
+      </c>
+      <c r="C43" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>349</v>
+      </c>
+      <c r="B44" t="s">
+        <v>355</v>
+      </c>
+      <c r="C44" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>350</v>
+      </c>
+      <c r="B45" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>351</v>
+      </c>
+      <c r="B46" t="s">
+        <v>357</v>
+      </c>
+      <c r="C46" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>352</v>
+      </c>
+      <c r="B47" t="s">
+        <v>358</v>
+      </c>
+      <c r="C47" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>353</v>
+      </c>
+      <c r="B48" t="s">
+        <v>359</v>
+      </c>
+      <c r="C48" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>354</v>
+      </c>
+      <c r="B49" t="s">
+        <v>360</v>
+      </c>
+      <c r="C49" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -2395,7 +2652,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
@@ -2725,6 +2982,102 @@
       </c>
       <c r="B34" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>325</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>328</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>329</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>330</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>369</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>336</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>338</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>339</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>340</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>368</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D675CCC6-4083-43EC-B01B-F4669319F0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1E17BA-8A48-444A-9FE9-2981B4572C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18015" yWindow="4110" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -14,9 +14,10 @@
     <sheet name="String_Hero" sheetId="3" r:id="rId4"/>
     <sheet name="String_Treasure" sheetId="7" r:id="rId5"/>
     <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId6"/>
+    <sheet name="String_Story" sheetId="8" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="451">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1413,6 +1414,262 @@
   </si>
   <si>
     <t>NAME_HISTORICAL_JIANGSHANG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_1</t>
+  </si>
+  <si>
+    <t>node_2</t>
+  </si>
+  <si>
+    <t>node_3</t>
+  </si>
+  <si>
+    <t>node_4</t>
+  </si>
+  <si>
+    <t>node_5</t>
+  </si>
+  <si>
+    <t>node_6</t>
+  </si>
+  <si>
+    <t>node_7</t>
+  </si>
+  <si>
+    <t>node_8</t>
+  </si>
+  <si>
+    <t>node_9</t>
+  </si>
+  <si>
+    <t>node_10</t>
+  </si>
+  <si>
+    <t>node_11</t>
+  </si>
+  <si>
+    <t>node_12a</t>
+  </si>
+  <si>
+    <t>node_12b</t>
+  </si>
+  <si>
+    <t>node_13</t>
+  </si>
+  <si>
+    <t>node_14</t>
+  </si>
+  <si>
+    <t>node_15</t>
+  </si>
+  <si>
+    <t>node_16</t>
+  </si>
+  <si>
+    <t>node_17</t>
+  </si>
+  <si>
+    <t>node_18</t>
+  </si>
+  <si>
+    <t>node_19a</t>
+  </si>
+  <si>
+    <t>node_19b</t>
+  </si>
+  <si>
+    <t>node_20</t>
+  </si>
+  <si>
+    <t>node_21a</t>
+  </si>
+  <si>
+    <t>node_21b</t>
+  </si>
+  <si>
+    <t>node_22</t>
+  </si>
+  <si>
+    <t>node_23a</t>
+  </si>
+  <si>
+    <t>node_23b</t>
+  </si>
+  <si>
+    <t>node_24a</t>
+  </si>
+  <si>
+    <t>node_24b</t>
+  </si>
+  <si>
+    <t>node_25</t>
+  </si>
+  <si>
+    <t>node_26</t>
+  </si>
+  <si>
+    <t>node_27</t>
+  </si>
+  <si>
+    <t>node_28</t>
+  </si>
+  <si>
+    <t>node_29</t>
+  </si>
+  <si>
+    <t>황천당립</t>
+  </si>
+  <si>
+    <t>철벽</t>
+  </si>
+  <si>
+    <t>호로관 전투</t>
+  </si>
+  <si>
+    <t>호랑이의 몰락</t>
+  </si>
+  <si>
+    <t>한실의 기둥</t>
+  </si>
+  <si>
+    <t>서주학살</t>
+  </si>
+  <si>
+    <t>서주구원</t>
+  </si>
+  <si>
+    <t>담보가 된 옥</t>
+  </si>
+  <si>
+    <t>강동의 미주랑</t>
+  </si>
+  <si>
+    <t>칠척극</t>
+  </si>
+  <si>
+    <t>헌제 옹립</t>
+  </si>
+  <si>
+    <t>백호 사냥 A</t>
+  </si>
+  <si>
+    <t>백호 사냥 B</t>
+  </si>
+  <si>
+    <t>여포의 최후</t>
+  </si>
+  <si>
+    <t>청매자주논영웅</t>
+  </si>
+  <si>
+    <t>용의 산책</t>
+  </si>
+  <si>
+    <t>의의 갈림길</t>
+  </si>
+  <si>
+    <t>복수의 칼날</t>
+  </si>
+  <si>
+    <t>상산 조자룡</t>
+  </si>
+  <si>
+    <t>관도대전 A</t>
+  </si>
+  <si>
+    <t>관도대전 B</t>
+  </si>
+  <si>
+    <t>와룡</t>
+  </si>
+  <si>
+    <t>상산의 기개 A</t>
+  </si>
+  <si>
+    <t>상산의 기개 B</t>
+  </si>
+  <si>
+    <t>여인의 기개</t>
+  </si>
+  <si>
+    <t>손권의 결단 A</t>
+  </si>
+  <si>
+    <t>손권의 결단 B</t>
+  </si>
+  <si>
+    <t>강을 태운 불꽃 A</t>
+  </si>
+  <si>
+    <t>강을 태운 불꽃 B</t>
+  </si>
+  <si>
+    <t>화용도의 갈림길</t>
+  </si>
+  <si>
+    <t>백발의 명궁</t>
+  </si>
+  <si>
+    <t>의의 갈림길 2</t>
+  </si>
+  <si>
+    <t>의의 갈림길 3</t>
+  </si>
+  <si>
+    <t>의의 갈림길 4</t>
+  </si>
+  <si>
+    <t>#Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOICE_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복수의 칼날을 휘두른다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>학살을 막고 민심을 챙긴다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백성을 향한 마음만 받아간다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창천의 뜻을 잇는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥새를 맡기고 병력 지원을 받는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스스로의 힘으로 일어선다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_ALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1508,7 +1765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1565,6 +1822,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1991,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2022,403 +2303,454 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="B3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+        <v>139</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
+        <v>146</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" t="s">
-        <v>127</v>
+        <v>144</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" t="s">
-        <v>128</v>
+        <v>145</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
+        <v>143</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>148</v>
+        <v>170</v>
+      </c>
+      <c r="B16" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
+      </c>
+      <c r="B17" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>160</v>
+      <c r="A24" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>161</v>
+      <c r="A25" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>165</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>162</v>
+      <c r="A26" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>163</v>
+      <c r="A27" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>159</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>164</v>
+      <c r="A28" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>176</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>98</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" t="s">
-        <v>174</v>
+        <v>101</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>170</v>
-      </c>
-      <c r="B33" t="s">
-        <v>173</v>
+        <v>93</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>320</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
-        <v>316</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>321</v>
+        <v>203</v>
       </c>
       <c r="B36" t="s">
-        <v>317</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>318</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>323</v>
+        <v>205</v>
       </c>
       <c r="B38" t="s">
-        <v>319</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" t="s">
-        <v>211</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B40" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>449</v>
       </c>
       <c r="B41" t="s">
-        <v>213</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s">
-        <v>347</v>
-      </c>
-      <c r="C43" t="s">
-        <v>361</v>
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s">
-        <v>355</v>
-      </c>
-      <c r="C44" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s">
-        <v>356</v>
-      </c>
-      <c r="C45" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>357</v>
-      </c>
-      <c r="C46" t="s">
-        <v>364</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>352</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
-        <v>358</v>
-      </c>
-      <c r="C47" t="s">
-        <v>365</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>353</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s">
-        <v>359</v>
-      </c>
-      <c r="C48" t="s">
-        <v>366</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>352</v>
+      </c>
+      <c r="B49" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>348</v>
+      </c>
+      <c r="B50" t="s">
+        <v>347</v>
+      </c>
+      <c r="C50" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>353</v>
+      </c>
+      <c r="B51" t="s">
+        <v>359</v>
+      </c>
+      <c r="C51" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>354</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B52" t="s">
         <v>360</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C52" t="s">
         <v>367</v>
       </c>
     </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>351</v>
+      </c>
+      <c r="B53" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>349</v>
+      </c>
+      <c r="B54" t="s">
+        <v>355</v>
+      </c>
+      <c r="C54" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" t="s">
+        <v>356</v>
+      </c>
+      <c r="C55" t="s">
+        <v>363</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C54">
+    <sortCondition ref="A2:A54"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2595,52 +2927,22 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
-      <c r="B13" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="D13" s="18"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
-      <c r="B14" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>199</v>
-      </c>
       <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
-      <c r="B15" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>200</v>
-      </c>
       <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
-      <c r="B16" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>201</v>
-      </c>
       <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="17"/>
-      <c r="B17" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>202</v>
-      </c>
       <c r="D17" s="18"/>
     </row>
   </sheetData>
@@ -4518,4 +4820,1523 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC39210-5BFC-4779-981A-9157C4AD45DB}">
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.875" style="6" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="str">
+        <f t="shared" ref="D3:D35" si="0">UPPER(B3)&amp;"_TITLE"</f>
+        <v>NODE_1_TITLE</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_2_TITLE</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="F4" s="21"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_3_TITLE</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F5" s="21"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_4_TITLE</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_5_TITLE</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_6_TITLE</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_7_TITLE</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>439</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_8_TITLE</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="F10" s="21"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_9_TITLE</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_10_TITLE</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_11_TITLE</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_12A_TITLE</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>439</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_12B_TITLE</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>439</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_13_TITLE</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>439</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_14_TITLE</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>439</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_15_TITLE</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="F18" s="21"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>439</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_16_TITLE</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>439</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_17_TITLE</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_18_TITLE</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>439</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_19A_TITLE</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>439</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_19B_TITLE</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>439</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_20_TITLE</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>439</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_21A_TITLE</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>439</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_21B_TITLE</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="F26" s="21"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>439</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_22_TITLE</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="F27" s="21"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>439</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_23A_TITLE</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="F28" s="21"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>439</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_23B_TITLE</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="F29" s="21"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>439</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_24A_TITLE</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_24B_TITLE</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>439</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_25_TITLE</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="F32" s="21"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_26_TITLE</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="F33" s="21"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>439</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_27_TITLE</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" s="21"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>439</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>NODE_28_TITLE</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="F35" s="24"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="20" t="str">
+        <f t="shared" ref="D36" si="1">UPPER(B36)&amp;"_TITLE"</f>
+        <v>NODE_29_TITLE</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C37" s="26">
+        <v>1</v>
+      </c>
+      <c r="D37" s="20" t="str">
+        <f t="shared" ref="D37:D59" si="2">UPPER(B37)&amp;"_CHOICE_"&amp;C37</f>
+        <v>NODE_1_CHOICE_1</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C38" s="26">
+        <v>2</v>
+      </c>
+      <c r="D38" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_1_CHOICE_2</v>
+      </c>
+      <c r="E38" s="20"/>
+      <c r="F38" s="21"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C39" s="26">
+        <v>1</v>
+      </c>
+      <c r="D39" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_5_CHOICE_1</v>
+      </c>
+      <c r="E39" s="20"/>
+      <c r="F39" s="21"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C40" s="26">
+        <v>2</v>
+      </c>
+      <c r="D40" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_5_CHOICE_2</v>
+      </c>
+      <c r="E40" s="20"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C41" s="26">
+        <v>1</v>
+      </c>
+      <c r="D41" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_6_CHOICE_1</v>
+      </c>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42" s="26">
+        <v>2</v>
+      </c>
+      <c r="D42" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_6_CHOICE_2</v>
+      </c>
+      <c r="E42" s="20"/>
+      <c r="F42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C43" s="26">
+        <v>1</v>
+      </c>
+      <c r="D43" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_7_CHOICE_1</v>
+      </c>
+      <c r="E43" s="20"/>
+      <c r="F43" s="21"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C44" s="26">
+        <v>2</v>
+      </c>
+      <c r="D44" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_7_CHOICE_2</v>
+      </c>
+      <c r="E44" s="20"/>
+      <c r="F44" s="21"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C45" s="26">
+        <v>1</v>
+      </c>
+      <c r="D45" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_10_CHOICE_1</v>
+      </c>
+      <c r="E45" s="20"/>
+      <c r="F45" s="21"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C46" s="26">
+        <v>2</v>
+      </c>
+      <c r="D46" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_10_CHOICE_2</v>
+      </c>
+      <c r="E46" s="20"/>
+      <c r="F46" s="21"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C47" s="26">
+        <v>1</v>
+      </c>
+      <c r="D47" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_12B_CHOICE_1</v>
+      </c>
+      <c r="E47" s="20"/>
+      <c r="F47" s="21"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C48" s="26">
+        <v>2</v>
+      </c>
+      <c r="D48" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_12B_CHOICE_2</v>
+      </c>
+      <c r="E48" s="20"/>
+      <c r="F48" s="21"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C49" s="26">
+        <v>1</v>
+      </c>
+      <c r="D49" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_14_CHOICE_1</v>
+      </c>
+      <c r="E49" s="20"/>
+      <c r="F49" s="21"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C50" s="26">
+        <v>2</v>
+      </c>
+      <c r="D50" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_14_CHOICE_2</v>
+      </c>
+      <c r="E50" s="20"/>
+      <c r="F50" s="21"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C51" s="26">
+        <v>1</v>
+      </c>
+      <c r="D51" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_15_CHOICE_1</v>
+      </c>
+      <c r="E51" s="20"/>
+      <c r="F51" s="21"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C52" s="26">
+        <v>2</v>
+      </c>
+      <c r="D52" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_15_CHOICE_2</v>
+      </c>
+      <c r="E52" s="20"/>
+      <c r="F52" s="21"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C53" s="26">
+        <v>1</v>
+      </c>
+      <c r="D53" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_16_CHOICE_1</v>
+      </c>
+      <c r="E53" s="20"/>
+      <c r="F53" s="21"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C54" s="26">
+        <v>2</v>
+      </c>
+      <c r="D54" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_16_CHOICE_2</v>
+      </c>
+      <c r="E54" s="20"/>
+      <c r="F54" s="21"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C55" s="26">
+        <v>1</v>
+      </c>
+      <c r="D55" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_19B_CHOICE_1</v>
+      </c>
+      <c r="E55" s="20"/>
+      <c r="F55" s="21"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C56" s="26">
+        <v>2</v>
+      </c>
+      <c r="D56" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_19B_CHOICE_2</v>
+      </c>
+      <c r="E56" s="20"/>
+      <c r="F56" s="21"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C57" s="26">
+        <v>1</v>
+      </c>
+      <c r="D57" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_21B_CHOICE_1</v>
+      </c>
+      <c r="E57" s="20"/>
+      <c r="F57" s="21"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C58" s="26">
+        <v>2</v>
+      </c>
+      <c r="D58" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_21B_CHOICE_2</v>
+      </c>
+      <c r="E58" s="20"/>
+      <c r="F58" s="21"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C59" s="26">
+        <v>1</v>
+      </c>
+      <c r="D59" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_25_CHOICE_1</v>
+      </c>
+      <c r="E59" s="20"/>
+      <c r="F59" s="21"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C60" s="26">
+        <v>2</v>
+      </c>
+      <c r="D60" s="20" t="str">
+        <f>UPPER(B60)&amp;"_CHOICE_"&amp;C60</f>
+        <v>NODE_25_CHOICE_2</v>
+      </c>
+      <c r="E60" s="20"/>
+      <c r="F60" s="21"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C61" s="26">
+        <v>1</v>
+      </c>
+      <c r="D61" s="20" t="str">
+        <f>UPPER(B61)&amp;"_CHOICE_"&amp;C61&amp;"_DESC"</f>
+        <v>NODE_1_CHOICE_1_DESC</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="F61" s="21"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C62" s="26">
+        <v>2</v>
+      </c>
+      <c r="D62" s="20" t="str">
+        <f t="shared" ref="D62:D84" si="3">UPPER(B62)&amp;"_CHOICE_"&amp;C62&amp;"_DESC"</f>
+        <v>NODE_1_CHOICE_2_DESC</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F62" s="21"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="26">
+        <v>1</v>
+      </c>
+      <c r="D63" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_5_CHOICE_1_DESC</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="F63" s="21"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C64" s="26">
+        <v>2</v>
+      </c>
+      <c r="D64" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_5_CHOICE_2_DESC</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="F64" s="21"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C65" s="26">
+        <v>1</v>
+      </c>
+      <c r="D65" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_6_CHOICE_1_DESC</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="F65" s="21"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C66" s="26">
+        <v>2</v>
+      </c>
+      <c r="D66" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_6_CHOICE_2_DESC</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="F66" s="21"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C67" s="26">
+        <v>1</v>
+      </c>
+      <c r="D67" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_7_CHOICE_1_DESC</v>
+      </c>
+      <c r="E67" s="20" t="str">
+        <f t="shared" ref="E67:E83" si="4">"선택"&amp;C67</f>
+        <v>선택1</v>
+      </c>
+      <c r="F67" s="21"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C68" s="26">
+        <v>2</v>
+      </c>
+      <c r="D68" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_7_CHOICE_2_DESC</v>
+      </c>
+      <c r="E68" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F68" s="21"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C69" s="26">
+        <v>1</v>
+      </c>
+      <c r="D69" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_10_CHOICE_1_DESC</v>
+      </c>
+      <c r="E69" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F69" s="21"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C70" s="26">
+        <v>2</v>
+      </c>
+      <c r="D70" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_10_CHOICE_2_DESC</v>
+      </c>
+      <c r="E70" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F70" s="21"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C71" s="26">
+        <v>1</v>
+      </c>
+      <c r="D71" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_12B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E71" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F71" s="21"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C72" s="26">
+        <v>2</v>
+      </c>
+      <c r="D72" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_12B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E72" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F72" s="21"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="26">
+        <v>1</v>
+      </c>
+      <c r="D73" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_14_CHOICE_1_DESC</v>
+      </c>
+      <c r="E73" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F73" s="21"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C74" s="26">
+        <v>2</v>
+      </c>
+      <c r="D74" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_14_CHOICE_2_DESC</v>
+      </c>
+      <c r="E74" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F74" s="21"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C75" s="26">
+        <v>1</v>
+      </c>
+      <c r="D75" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_15_CHOICE_1_DESC</v>
+      </c>
+      <c r="E75" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F75" s="21"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C76" s="26">
+        <v>2</v>
+      </c>
+      <c r="D76" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_15_CHOICE_2_DESC</v>
+      </c>
+      <c r="E76" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F76" s="21"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C77" s="26">
+        <v>1</v>
+      </c>
+      <c r="D77" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_16_CHOICE_1_DESC</v>
+      </c>
+      <c r="E77" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F77" s="21"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C78" s="26">
+        <v>2</v>
+      </c>
+      <c r="D78" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_16_CHOICE_2_DESC</v>
+      </c>
+      <c r="E78" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F78" s="21"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C79" s="26">
+        <v>1</v>
+      </c>
+      <c r="D79" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_19B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E79" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F79" s="21"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C80" s="26">
+        <v>2</v>
+      </c>
+      <c r="D80" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_19B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E80" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F80" s="21"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B81" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C81" s="26">
+        <v>1</v>
+      </c>
+      <c r="D81" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_21B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E81" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F81" s="21"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C82" s="26">
+        <v>2</v>
+      </c>
+      <c r="D82" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_21B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E82" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F82" s="21"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C83" s="26">
+        <v>1</v>
+      </c>
+      <c r="D83" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_25_CHOICE_1_DESC</v>
+      </c>
+      <c r="E83" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F83" s="21"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C84" s="26">
+        <v>2</v>
+      </c>
+      <c r="D84" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_25_CHOICE_2_DESC</v>
+      </c>
+      <c r="E84" s="20" t="str">
+        <f>"선택"&amp;C84</f>
+        <v>선택2</v>
+      </c>
+      <c r="F84" s="21"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1E17BA-8A48-444A-9FE9-2981B4572C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D15EF8-6163-48B8-97EA-991492C846BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18015" yWindow="4110" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D15EF8-6163-48B8-97EA-991492C846BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA94AA72-50F6-41E1-A365-02B71E2D7008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="492">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1558,118 +1558,267 @@
     <t>백호 사냥 B</t>
   </si>
   <si>
+    <t>청매자주논영웅</t>
+  </si>
+  <si>
+    <t>용의 산책</t>
+  </si>
+  <si>
+    <t>의의 갈림길</t>
+  </si>
+  <si>
+    <t>복수의 칼날</t>
+  </si>
+  <si>
+    <t>상산 조자룡</t>
+  </si>
+  <si>
+    <t>관도대전 A</t>
+  </si>
+  <si>
+    <t>관도대전 B</t>
+  </si>
+  <si>
+    <t>와룡</t>
+  </si>
+  <si>
+    <t>상산의 기개 A</t>
+  </si>
+  <si>
+    <t>상산의 기개 B</t>
+  </si>
+  <si>
+    <t>여인의 기개</t>
+  </si>
+  <si>
+    <t>손권의 결단 A</t>
+  </si>
+  <si>
+    <t>손권의 결단 B</t>
+  </si>
+  <si>
+    <t>강을 태운 불꽃 A</t>
+  </si>
+  <si>
+    <t>강을 태운 불꽃 B</t>
+  </si>
+  <si>
+    <t>화용도의 갈림길</t>
+  </si>
+  <si>
+    <t>백발의 명궁</t>
+  </si>
+  <si>
+    <t>의의 갈림길 2</t>
+  </si>
+  <si>
+    <t>의의 갈림길 3</t>
+  </si>
+  <si>
+    <t>의의 갈림길 4</t>
+  </si>
+  <si>
+    <t>#Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOICE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#Value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHOICE_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION_NAME_FULL_ALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"강동의 소패왕 날개를 펴다"</t>
+  </si>
+  <si>
+    <t>"천하의 영웅은 그대와 나뿐이오"</t>
+  </si>
+  <si>
+    <t>"외사는 주유에게, 내사는 장소에게 물어라"</t>
+  </si>
+  <si>
+    <t>"나는 상산 진정 사람으로 성은 조요 이름은 운이며 자는 자룡이라"</t>
+  </si>
+  <si>
+    <t>"십승십패로 원본초를 무너뜨리리"</t>
+  </si>
+  <si>
+    <t>"오직 봉효만이 내 뜻을 아나니"</t>
+  </si>
+  <si>
+    <t>"와룡과 봉추, 둘 중 하나만 얻어도 천하를 안정시키리"</t>
+  </si>
+  <si>
+    <t>"나는 상산의 조자룡이다"</t>
+  </si>
+  <si>
+    <t>"필마단기로 주인을 구하다"</t>
+  </si>
+  <si>
+    <t>"기적적으로 사지를 벗어나 조운과 함께 돌아온 두 부인과 아두"</t>
+  </si>
+  <si>
+    <t>"공명과 주유의 날카로운 도발, 강동의 젊은 호랑이가 보검을 뽑아 들다"</t>
+  </si>
+  <si>
+    <t>"뜻밖의 동맹 엄백호의 외침, 동오 전체의 의기가 하나로 모이다"</t>
+  </si>
+  <si>
+    <t>"오판이 부른 지옥의 동풍, 장강을 덮은 백만 대군의 비명"</t>
+  </si>
+  <si>
+    <t>"화공의 덫을 꿰뚫은 혜안, 불타는 불길 속 사선을 뚫어내다"</t>
+  </si>
+  <si>
+    <t>"목숨을 빚진 자와 목숨을 구걸하는 자, 의리로 통곡하다"</t>
+  </si>
+  <si>
+    <t>"나이는 숫자에 불과하니, 시위를 당겨 천하를 꿰뚫다"</t>
+  </si>
+  <si>
+    <t>"뚫리지 않는 방패"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무너지는 강동의 호랑이"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"나의 장자방이로다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"천하보다 뜨거운 두 영웅의 의리"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"주군을 찾는 전사의 눈"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"붉은 피로 물들이다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"처절한 피난길의 끝은 난세의 영웅"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"소패왕의 자비 없는 진격"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무릎 꿇은 동오의 덕왕"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>여포의 최후</t>
-  </si>
-  <si>
-    <t>청매자주논영웅</t>
-  </si>
-  <si>
-    <t>용의 산책</t>
-  </si>
-  <si>
-    <t>의의 갈림길</t>
-  </si>
-  <si>
-    <t>복수의 칼날</t>
-  </si>
-  <si>
-    <t>상산 조자룡</t>
-  </si>
-  <si>
-    <t>관도대전 A</t>
-  </si>
-  <si>
-    <t>관도대전 B</t>
-  </si>
-  <si>
-    <t>와룡</t>
-  </si>
-  <si>
-    <t>상산의 기개 A</t>
-  </si>
-  <si>
-    <t>상산의 기개 B</t>
-  </si>
-  <si>
-    <t>여인의 기개</t>
-  </si>
-  <si>
-    <t>손권의 결단 A</t>
-  </si>
-  <si>
-    <t>손권의 결단 B</t>
-  </si>
-  <si>
-    <t>강을 태운 불꽃 A</t>
-  </si>
-  <si>
-    <t>강을 태운 불꽃 B</t>
-  </si>
-  <si>
-    <t>화용도의 갈림길</t>
-  </si>
-  <si>
-    <t>백발의 명궁</t>
-  </si>
-  <si>
-    <t>의의 갈림길 2</t>
-  </si>
-  <si>
-    <t>의의 갈림길 3</t>
-  </si>
-  <si>
-    <t>의의 갈림길 4</t>
-  </si>
-  <si>
-    <t>#Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TITLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHOICE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#Value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CHOICE_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>복수의 칼날을 휘두른다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>학살을 막고 민심을 챙긴다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백성을 향한 마음만 받아간다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>창천의 뜻을 잇는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>옥새를 맡기고 병력 지원을 받는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스스로의 힘으로 일어선다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REGION_NAME_FULL_ALL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"잠룡, 난세의 영웅을 만나다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"그에겐 그저 당연한 승리"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"천하를 뒤덮은 거대한 광기와 혼란"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"절대적 공포가 선사한 압도적인 무력감"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"무너진 무신의 그늘 아래 꺾이지 않는 기개"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"죽음의 문턱에서"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"길 잃은 명장, 인의의 깃발 아래로"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"수십만 대군에 맞선 결단"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"귀신 같은 지략, 빛을 잃다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"와룡 일어나다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"사선을 넘나드는 창"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"거대한 폭력에 맞선 신념"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"두 영웅이 열어젖힌 장판파의 혈로"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"사선에서 눈 뜬 여인"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"강동의 젊은 호랑이가 보검을 뽑아들다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"영웅들의 기개가 한 곳에 모이다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"천하통일의 꿈을 삼킨 적벽의 붉은 불길"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"귀재의 눈에는 그저 불장난일뿐"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1677,7 +1826,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1708,6 +1857,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1723,7 +1889,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1759,13 +1925,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1846,6 +2023,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2608,10 +2812,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B41" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -4824,37 +5028,40 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC39210-5BFC-4779-981A-9157C4AD45DB}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.75" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>178</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="31" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -4867,16 +5074,19 @@
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="32" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>439</v>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>370</v>
@@ -4886,14 +5096,14 @@
         <f t="shared" ref="D3:D35" si="0">UPPER(B3)&amp;"_TITLE"</f>
         <v>NODE_1_TITLE</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="33" t="s">
         <v>404</v>
       </c>
       <c r="F3" s="21"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>439</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>371</v>
@@ -4903,14 +5113,14 @@
         <f t="shared" si="0"/>
         <v>NODE_2_TITLE</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="33" t="s">
         <v>405</v>
       </c>
       <c r="F4" s="21"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>439</v>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>372</v>
@@ -4920,14 +5130,14 @@
         <f t="shared" si="0"/>
         <v>NODE_3_TITLE</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="33" t="s">
         <v>406</v>
       </c>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>439</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>373</v>
@@ -4937,14 +5147,14 @@
         <f t="shared" si="0"/>
         <v>NODE_4_TITLE</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="33" t="s">
         <v>407</v>
       </c>
       <c r="F6" s="21"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>439</v>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>374</v>
@@ -4954,14 +5164,14 @@
         <f t="shared" si="0"/>
         <v>NODE_5_TITLE</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="33" t="s">
         <v>408</v>
       </c>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>439</v>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>375</v>
@@ -4971,14 +5181,14 @@
         <f t="shared" si="0"/>
         <v>NODE_6_TITLE</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="33" t="s">
         <v>409</v>
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>439</v>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>376</v>
@@ -4988,14 +5198,14 @@
         <f t="shared" si="0"/>
         <v>NODE_7_TITLE</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="33" t="s">
         <v>410</v>
       </c>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>439</v>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>377</v>
@@ -5005,14 +5215,14 @@
         <f t="shared" si="0"/>
         <v>NODE_8_TITLE</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="33" t="s">
         <v>411</v>
       </c>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>439</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>378</v>
@@ -5022,14 +5232,14 @@
         <f t="shared" si="0"/>
         <v>NODE_9_TITLE</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="33" t="s">
         <v>412</v>
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>439</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>379</v>
@@ -5039,14 +5249,14 @@
         <f t="shared" si="0"/>
         <v>NODE_10_TITLE</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="33" t="s">
         <v>413</v>
       </c>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>439</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>380</v>
@@ -5056,14 +5266,14 @@
         <f t="shared" si="0"/>
         <v>NODE_11_TITLE</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="33" t="s">
         <v>414</v>
       </c>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>439</v>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>381</v>
@@ -5073,14 +5283,14 @@
         <f t="shared" si="0"/>
         <v>NODE_12A_TITLE</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="33" t="s">
         <v>415</v>
       </c>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>439</v>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>382</v>
@@ -5090,14 +5300,14 @@
         <f t="shared" si="0"/>
         <v>NODE_12B_TITLE</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="33" t="s">
         <v>416</v>
       </c>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>439</v>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>383</v>
@@ -5107,14 +5317,14 @@
         <f t="shared" si="0"/>
         <v>NODE_13_TITLE</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>417</v>
+      <c r="E16" s="33" t="s">
+        <v>470</v>
       </c>
       <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>439</v>
+      <c r="A17" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>384</v>
@@ -5124,14 +5334,14 @@
         <f t="shared" si="0"/>
         <v>NODE_14_TITLE</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>418</v>
+      <c r="E17" s="33" t="s">
+        <v>417</v>
       </c>
       <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>439</v>
+      <c r="A18" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>385</v>
@@ -5141,14 +5351,14 @@
         <f t="shared" si="0"/>
         <v>NODE_15_TITLE</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>419</v>
+      <c r="E18" s="33" t="s">
+        <v>418</v>
       </c>
       <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>439</v>
+      <c r="A19" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>386</v>
@@ -5158,14 +5368,14 @@
         <f t="shared" si="0"/>
         <v>NODE_16_TITLE</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>420</v>
+      <c r="E19" s="33" t="s">
+        <v>419</v>
       </c>
       <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>439</v>
+      <c r="A20" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>387</v>
@@ -5175,14 +5385,14 @@
         <f t="shared" si="0"/>
         <v>NODE_17_TITLE</v>
       </c>
-      <c r="E20" s="19" t="s">
-        <v>421</v>
+      <c r="E20" s="33" t="s">
+        <v>420</v>
       </c>
       <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>439</v>
+      <c r="A21" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>388</v>
@@ -5192,14 +5402,14 @@
         <f t="shared" si="0"/>
         <v>NODE_18_TITLE</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>422</v>
+      <c r="E21" s="33" t="s">
+        <v>421</v>
       </c>
       <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>439</v>
+      <c r="A22" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>389</v>
@@ -5209,14 +5419,14 @@
         <f t="shared" si="0"/>
         <v>NODE_19A_TITLE</v>
       </c>
-      <c r="E22" s="19" t="s">
-        <v>423</v>
+      <c r="E22" s="33" t="s">
+        <v>422</v>
       </c>
       <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>439</v>
+      <c r="A23" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>390</v>
@@ -5226,14 +5436,14 @@
         <f t="shared" si="0"/>
         <v>NODE_19B_TITLE</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>424</v>
+      <c r="E23" s="33" t="s">
+        <v>423</v>
       </c>
       <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>439</v>
+      <c r="A24" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>391</v>
@@ -5243,14 +5453,14 @@
         <f t="shared" si="0"/>
         <v>NODE_20_TITLE</v>
       </c>
-      <c r="E24" s="19" t="s">
-        <v>425</v>
+      <c r="E24" s="33" t="s">
+        <v>424</v>
       </c>
       <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>439</v>
+      <c r="A25" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>392</v>
@@ -5260,14 +5470,14 @@
         <f t="shared" si="0"/>
         <v>NODE_21A_TITLE</v>
       </c>
-      <c r="E25" s="19" t="s">
-        <v>426</v>
+      <c r="E25" s="33" t="s">
+        <v>425</v>
       </c>
       <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>439</v>
+      <c r="A26" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>393</v>
@@ -5277,14 +5487,14 @@
         <f t="shared" si="0"/>
         <v>NODE_21B_TITLE</v>
       </c>
-      <c r="E26" s="19" t="s">
-        <v>427</v>
+      <c r="E26" s="33" t="s">
+        <v>426</v>
       </c>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>439</v>
+      <c r="A27" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>394</v>
@@ -5294,14 +5504,14 @@
         <f t="shared" si="0"/>
         <v>NODE_22_TITLE</v>
       </c>
-      <c r="E27" s="19" t="s">
-        <v>428</v>
+      <c r="E27" s="33" t="s">
+        <v>427</v>
       </c>
       <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>439</v>
+      <c r="A28" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>395</v>
@@ -5311,14 +5521,14 @@
         <f t="shared" si="0"/>
         <v>NODE_23A_TITLE</v>
       </c>
-      <c r="E28" s="19" t="s">
-        <v>429</v>
+      <c r="E28" s="33" t="s">
+        <v>428</v>
       </c>
       <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>439</v>
+      <c r="A29" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>396</v>
@@ -5328,14 +5538,14 @@
         <f t="shared" si="0"/>
         <v>NODE_23B_TITLE</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>430</v>
+      <c r="E29" s="33" t="s">
+        <v>429</v>
       </c>
       <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>439</v>
+      <c r="A30" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>397</v>
@@ -5345,14 +5555,14 @@
         <f t="shared" si="0"/>
         <v>NODE_24A_TITLE</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>431</v>
+      <c r="E30" s="33" t="s">
+        <v>430</v>
       </c>
       <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>439</v>
+      <c r="A31" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>398</v>
@@ -5362,14 +5572,14 @@
         <f t="shared" si="0"/>
         <v>NODE_24B_TITLE</v>
       </c>
-      <c r="E31" s="19" t="s">
-        <v>432</v>
+      <c r="E31" s="33" t="s">
+        <v>431</v>
       </c>
       <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>439</v>
+      <c r="A32" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>399</v>
@@ -5379,14 +5589,14 @@
         <f t="shared" si="0"/>
         <v>NODE_25_TITLE</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>433</v>
+      <c r="E32" s="33" t="s">
+        <v>432</v>
       </c>
       <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>439</v>
+      <c r="A33" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>400</v>
@@ -5396,14 +5606,14 @@
         <f t="shared" si="0"/>
         <v>NODE_26_TITLE</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>434</v>
+      <c r="E33" s="33" t="s">
+        <v>433</v>
       </c>
       <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>439</v>
+      <c r="A34" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>401</v>
@@ -5413,14 +5623,14 @@
         <f t="shared" si="0"/>
         <v>NODE_27_TITLE</v>
       </c>
-      <c r="E34" s="19" t="s">
-        <v>435</v>
+      <c r="E34" s="33" t="s">
+        <v>434</v>
       </c>
       <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>439</v>
+      <c r="A35" s="27" t="s">
+        <v>438</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>402</v>
@@ -5430,14 +5640,14 @@
         <f t="shared" si="0"/>
         <v>NODE_28_TITLE</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>436</v>
+      <c r="E35" s="34" t="s">
+        <v>435</v>
       </c>
       <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>403</v>
@@ -5447,892 +5657,1527 @@
         <f t="shared" ref="D36" si="1">UPPER(B36)&amp;"_TITLE"</f>
         <v>NODE_29_TITLE</v>
       </c>
-      <c r="E36" s="19" t="s">
-        <v>437</v>
+      <c r="E36" s="33" t="s">
+        <v>436</v>
       </c>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B37" s="25" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B37" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="C37" s="26">
-        <v>1</v>
-      </c>
+      <c r="C37" s="19"/>
       <c r="D37" s="20" t="str">
-        <f t="shared" ref="D37:D59" si="2">UPPER(B37)&amp;"_CHOICE_"&amp;C37</f>
-        <v>NODE_1_CHOICE_1</v>
-      </c>
-      <c r="E37" s="20"/>
+        <f t="shared" ref="D37:D69" si="2">UPPER(B37)&amp;"_DESC"</f>
+        <v>NODE_1_DESC</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>475</v>
+      </c>
       <c r="F37" s="21"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>370</v>
-      </c>
-      <c r="C38" s="26">
-        <v>2</v>
-      </c>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C38" s="19"/>
       <c r="D38" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_1_CHOICE_2</v>
-      </c>
-      <c r="E38" s="20"/>
+        <v>NODE_2_DESC</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>461</v>
+      </c>
       <c r="F38" s="21"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C39" s="26">
-        <v>1</v>
-      </c>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C39" s="19"/>
       <c r="D39" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_5_CHOICE_1</v>
-      </c>
-      <c r="E39" s="20"/>
+        <v>NODE_3_DESC</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>476</v>
+      </c>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B40" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C40" s="26">
-        <v>2</v>
-      </c>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_5_CHOICE_2</v>
-      </c>
-      <c r="E40" s="20"/>
+        <v>NODE_4_DESC</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>462</v>
+      </c>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C41" s="26">
-        <v>1</v>
-      </c>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="C41" s="19"/>
       <c r="D41" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_6_CHOICE_1</v>
-      </c>
-      <c r="E41" s="20"/>
+        <v>NODE_5_DESC</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>463</v>
+      </c>
       <c r="F41" s="21"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B42" s="25" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="C42" s="26">
-        <v>2</v>
-      </c>
+      <c r="C42" s="19"/>
       <c r="D42" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_6_CHOICE_2</v>
-      </c>
-      <c r="E42" s="20"/>
+        <v>NODE_6_DESC</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>466</v>
+      </c>
       <c r="F42" s="21"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B43" s="25" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B43" s="19" t="s">
         <v>376</v>
       </c>
-      <c r="C43" s="26">
-        <v>1</v>
-      </c>
+      <c r="C43" s="19"/>
       <c r="D43" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_7_CHOICE_1</v>
-      </c>
-      <c r="E43" s="20"/>
+        <v>NODE_7_DESC</v>
+      </c>
+      <c r="E43" s="33" t="s">
+        <v>484</v>
+      </c>
       <c r="F43" s="21"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="C44" s="26">
-        <v>2</v>
-      </c>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="C44" s="19"/>
       <c r="D44" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_7_CHOICE_2</v>
-      </c>
-      <c r="E44" s="20"/>
+        <v>NODE_8_DESC</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>445</v>
+      </c>
       <c r="F44" s="21"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="C45" s="26">
-        <v>1</v>
-      </c>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C45" s="19"/>
       <c r="D45" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_10_CHOICE_1</v>
-      </c>
-      <c r="E45" s="20"/>
+        <v>NODE_9_DESC</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>464</v>
+      </c>
       <c r="F45" s="21"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B46" s="25" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B46" s="19" t="s">
         <v>379</v>
       </c>
-      <c r="C46" s="26">
-        <v>2</v>
-      </c>
+      <c r="C46" s="19"/>
       <c r="D46" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_10_CHOICE_2</v>
-      </c>
-      <c r="E46" s="20"/>
+        <v>NODE_10_DESC</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>465</v>
+      </c>
       <c r="F46" s="21"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="C47" s="26">
-        <v>1</v>
-      </c>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C47" s="19"/>
       <c r="D47" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_12B_CHOICE_1</v>
-      </c>
-      <c r="E47" s="20"/>
+        <v>NODE_11_DESC</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>467</v>
+      </c>
       <c r="F47" s="21"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="C48" s="26">
-        <v>2</v>
-      </c>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="C48" s="19"/>
       <c r="D48" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_12B_CHOICE_2</v>
-      </c>
-      <c r="E48" s="20"/>
+        <v>NODE_12A_DESC</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>468</v>
+      </c>
       <c r="F48" s="21"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="C49" s="26">
-        <v>1</v>
-      </c>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C49" s="19"/>
       <c r="D49" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_14_CHOICE_1</v>
-      </c>
-      <c r="E49" s="20"/>
+        <v>NODE_12B_DESC</v>
+      </c>
+      <c r="E49" s="33" t="s">
+        <v>469</v>
+      </c>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B50" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="C50" s="26">
-        <v>2</v>
-      </c>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C50" s="19"/>
       <c r="D50" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_14_CHOICE_2</v>
-      </c>
-      <c r="E50" s="20"/>
+        <v>NODE_13_DESC</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>477</v>
+      </c>
       <c r="F50" s="21"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B51" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="C51" s="26">
-        <v>1</v>
-      </c>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="C51" s="19"/>
       <c r="D51" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_15_CHOICE_1</v>
-      </c>
-      <c r="E51" s="20"/>
+        <v>NODE_14_DESC</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>446</v>
+      </c>
       <c r="F51" s="21"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B52" s="25" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B52" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="C52" s="26">
-        <v>2</v>
-      </c>
+      <c r="C52" s="19"/>
       <c r="D52" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_15_CHOICE_2</v>
-      </c>
-      <c r="E52" s="20"/>
+        <v>NODE_15_DESC</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>471</v>
+      </c>
       <c r="F52" s="21"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B53" s="25" t="s">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B53" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="C53" s="26">
-        <v>1</v>
-      </c>
+      <c r="C53" s="19"/>
       <c r="D53" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_16_CHOICE_1</v>
-      </c>
-      <c r="E53" s="20"/>
+        <v>NODE_16_DESC</v>
+      </c>
+      <c r="E53" s="33" t="s">
+        <v>472</v>
+      </c>
       <c r="F53" s="21"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="C54" s="26">
-        <v>2</v>
-      </c>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" s="19"/>
       <c r="D54" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_16_CHOICE_2</v>
-      </c>
-      <c r="E54" s="20"/>
+        <v>NODE_17_DESC</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>478</v>
+      </c>
       <c r="F54" s="21"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C55" s="26">
-        <v>1</v>
-      </c>
+      <c r="G54" s="35" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C55" s="19"/>
       <c r="D55" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_19B_CHOICE_1</v>
-      </c>
-      <c r="E55" s="20"/>
+        <v>NODE_18_DESC</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>479</v>
+      </c>
       <c r="F55" s="21"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C56" s="26">
-        <v>2</v>
-      </c>
+      <c r="G55" s="35" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="C56" s="19"/>
       <c r="D56" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_19B_CHOICE_2</v>
-      </c>
-      <c r="E56" s="20"/>
+        <v>NODE_19A_DESC</v>
+      </c>
+      <c r="E56" s="33" t="s">
+        <v>480</v>
+      </c>
       <c r="F56" s="21"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B57" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="C57" s="26">
-        <v>1</v>
-      </c>
+      <c r="G56" s="35" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>390</v>
+      </c>
+      <c r="C57" s="19"/>
       <c r="D57" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_21B_CHOICE_1</v>
-      </c>
-      <c r="E57" s="20"/>
+        <v>NODE_19B_DESC</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>481</v>
+      </c>
       <c r="F57" s="21"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="C58" s="26">
-        <v>2</v>
-      </c>
+      <c r="G57" s="35" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C58" s="19"/>
       <c r="D58" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_21B_CHOICE_2</v>
-      </c>
-      <c r="E58" s="20"/>
+        <v>NODE_20_DESC</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>482</v>
+      </c>
       <c r="F58" s="21"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>399</v>
-      </c>
-      <c r="C59" s="26">
-        <v>1</v>
-      </c>
+      <c r="G58" s="35" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="C59" s="19"/>
       <c r="D59" s="20" t="str">
         <f t="shared" si="2"/>
+        <v>NODE_21A_DESC</v>
+      </c>
+      <c r="E59" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="F59" s="21"/>
+      <c r="G59" s="35" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_21B_DESC</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>485</v>
+      </c>
+      <c r="F60" s="21"/>
+      <c r="G60" s="35" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_22_DESC</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="F61" s="21"/>
+      <c r="G61" s="35" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_23A_DESC</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="F62" s="21"/>
+      <c r="G62" s="35" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_23B_DESC</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="F63" s="21"/>
+      <c r="G63" s="35" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_24A_DESC</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="F64" s="21"/>
+      <c r="G64" s="35" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_24B_DESC</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="F65" s="21"/>
+      <c r="G65" s="35" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="C66" s="19"/>
+      <c r="D66" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_25_DESC</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F66" s="21"/>
+      <c r="G66" s="35" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_26_DESC</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="35" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="C68" s="19"/>
+      <c r="D68" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_27_DESC</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F68" s="21"/>
+      <c r="G68" s="35" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C69" s="22"/>
+      <c r="D69" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE_28_DESC</v>
+      </c>
+      <c r="E69" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F69" s="24"/>
+      <c r="G69" s="35" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>403</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="20" t="str">
+        <f>UPPER(B70)&amp;"_DESC"</f>
+        <v>NODE_29_DESC</v>
+      </c>
+      <c r="E70" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F70" s="21"/>
+      <c r="G70" s="35" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C71" s="26">
+        <v>1</v>
+      </c>
+      <c r="D71" s="20" t="str">
+        <f t="shared" ref="D71:D93" si="3">UPPER(B71)&amp;"_CHOICE_"&amp;C71</f>
+        <v>NODE_1_CHOICE_1</v>
+      </c>
+      <c r="E71" s="29"/>
+      <c r="F71" s="21"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C72" s="26">
+        <v>2</v>
+      </c>
+      <c r="D72" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_1_CHOICE_2</v>
+      </c>
+      <c r="E72" s="29"/>
+      <c r="F72" s="21"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C73" s="26">
+        <v>1</v>
+      </c>
+      <c r="D73" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_5_CHOICE_1</v>
+      </c>
+      <c r="E73" s="29"/>
+      <c r="F73" s="21"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C74" s="26">
+        <v>2</v>
+      </c>
+      <c r="D74" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_5_CHOICE_2</v>
+      </c>
+      <c r="E74" s="29"/>
+      <c r="F74" s="21"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="26">
+        <v>1</v>
+      </c>
+      <c r="D75" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_6_CHOICE_1</v>
+      </c>
+      <c r="E75" s="29"/>
+      <c r="F75" s="21"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C76" s="26">
+        <v>2</v>
+      </c>
+      <c r="D76" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_6_CHOICE_2</v>
+      </c>
+      <c r="E76" s="29"/>
+      <c r="F76" s="21"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C77" s="26">
+        <v>1</v>
+      </c>
+      <c r="D77" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_7_CHOICE_1</v>
+      </c>
+      <c r="E77" s="29"/>
+      <c r="F77" s="21"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" s="26">
+        <v>2</v>
+      </c>
+      <c r="D78" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_7_CHOICE_2</v>
+      </c>
+      <c r="E78" s="29"/>
+      <c r="F78" s="21"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C79" s="26">
+        <v>1</v>
+      </c>
+      <c r="D79" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_10_CHOICE_1</v>
+      </c>
+      <c r="E79" s="29"/>
+      <c r="F79" s="21"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C80" s="26">
+        <v>2</v>
+      </c>
+      <c r="D80" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_10_CHOICE_2</v>
+      </c>
+      <c r="E80" s="29"/>
+      <c r="F80" s="21"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B81" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C81" s="26">
+        <v>1</v>
+      </c>
+      <c r="D81" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_12B_CHOICE_1</v>
+      </c>
+      <c r="E81" s="29"/>
+      <c r="F81" s="21"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C82" s="26">
+        <v>2</v>
+      </c>
+      <c r="D82" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_12B_CHOICE_2</v>
+      </c>
+      <c r="E82" s="29"/>
+      <c r="F82" s="21"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="26">
+        <v>1</v>
+      </c>
+      <c r="D83" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_14_CHOICE_1</v>
+      </c>
+      <c r="E83" s="29"/>
+      <c r="F83" s="21"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C84" s="26">
+        <v>2</v>
+      </c>
+      <c r="D84" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_14_CHOICE_2</v>
+      </c>
+      <c r="E84" s="29"/>
+      <c r="F84" s="21"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C85" s="26">
+        <v>1</v>
+      </c>
+      <c r="D85" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_15_CHOICE_1</v>
+      </c>
+      <c r="E85" s="29"/>
+      <c r="F85" s="21"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C86" s="26">
+        <v>2</v>
+      </c>
+      <c r="D86" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_15_CHOICE_2</v>
+      </c>
+      <c r="E86" s="29"/>
+      <c r="F86" s="21"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C87" s="26">
+        <v>1</v>
+      </c>
+      <c r="D87" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_16_CHOICE_1</v>
+      </c>
+      <c r="E87" s="29"/>
+      <c r="F87" s="21"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C88" s="26">
+        <v>2</v>
+      </c>
+      <c r="D88" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_16_CHOICE_2</v>
+      </c>
+      <c r="E88" s="29"/>
+      <c r="F88" s="21"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C89" s="26">
+        <v>1</v>
+      </c>
+      <c r="D89" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_19B_CHOICE_1</v>
+      </c>
+      <c r="E89" s="29"/>
+      <c r="F89" s="21"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C90" s="26">
+        <v>2</v>
+      </c>
+      <c r="D90" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_19B_CHOICE_2</v>
+      </c>
+      <c r="E90" s="29"/>
+      <c r="F90" s="21"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C91" s="26">
+        <v>1</v>
+      </c>
+      <c r="D91" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_21B_CHOICE_1</v>
+      </c>
+      <c r="E91" s="29"/>
+      <c r="F91" s="21"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C92" s="26">
+        <v>2</v>
+      </c>
+      <c r="D92" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>NODE_21B_CHOICE_2</v>
+      </c>
+      <c r="E92" s="29"/>
+      <c r="F92" s="21"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C93" s="26">
+        <v>1</v>
+      </c>
+      <c r="D93" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>NODE_25_CHOICE_1</v>
       </c>
-      <c r="E59" s="20"/>
-      <c r="F59" s="21"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="B60" s="25" t="s">
+      <c r="E93" s="29"/>
+      <c r="F93" s="21"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="B94" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="C60" s="26">
+      <c r="C94" s="26">
         <v>2</v>
       </c>
-      <c r="D60" s="20" t="str">
-        <f>UPPER(B60)&amp;"_CHOICE_"&amp;C60</f>
+      <c r="D94" s="20" t="str">
+        <f>UPPER(B94)&amp;"_CHOICE_"&amp;C94</f>
         <v>NODE_25_CHOICE_2</v>
       </c>
-      <c r="E60" s="20"/>
-      <c r="F60" s="21"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B61" s="25" t="s">
+      <c r="E94" s="29"/>
+      <c r="F94" s="21"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B95" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="C61" s="26">
+      <c r="C95" s="26">
         <v>1</v>
       </c>
-      <c r="D61" s="20" t="str">
-        <f>UPPER(B61)&amp;"_CHOICE_"&amp;C61&amp;"_DESC"</f>
+      <c r="D95" s="20" t="str">
+        <f>UPPER(B95)&amp;"_CHOICE_"&amp;C95&amp;"_DESC"</f>
         <v>NODE_1_CHOICE_1_DESC</v>
       </c>
-      <c r="E61" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="F61" s="21"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B62" s="25" t="s">
+      <c r="E95" s="29" t="str">
+        <f t="shared" ref="E95:E118" si="4">"선택"&amp;C95</f>
+        <v>선택1</v>
+      </c>
+      <c r="F95" s="21"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B96" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="C62" s="26">
+      <c r="C96" s="26">
         <v>2</v>
       </c>
-      <c r="D62" s="20" t="str">
-        <f t="shared" ref="D62:D84" si="3">UPPER(B62)&amp;"_CHOICE_"&amp;C62&amp;"_DESC"</f>
+      <c r="D96" s="20" t="str">
+        <f t="shared" ref="D96:D118" si="5">UPPER(B96)&amp;"_CHOICE_"&amp;C96&amp;"_DESC"</f>
         <v>NODE_1_CHOICE_2_DESC</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="F62" s="21"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B63" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="26">
-        <v>1</v>
-      </c>
-      <c r="D63" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_5_CHOICE_1_DESC</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="F63" s="21"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B64" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C64" s="26">
-        <v>2</v>
-      </c>
-      <c r="D64" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_5_CHOICE_2_DESC</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="F64" s="21"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B65" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C65" s="26">
-        <v>1</v>
-      </c>
-      <c r="D65" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_6_CHOICE_1_DESC</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F65" s="21"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B66" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C66" s="26">
-        <v>2</v>
-      </c>
-      <c r="D66" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_6_CHOICE_2_DESC</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="F66" s="21"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B67" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="C67" s="26">
-        <v>1</v>
-      </c>
-      <c r="D67" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_7_CHOICE_1_DESC</v>
-      </c>
-      <c r="E67" s="20" t="str">
-        <f t="shared" ref="E67:E83" si="4">"선택"&amp;C67</f>
-        <v>선택1</v>
-      </c>
-      <c r="F67" s="21"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B68" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="C68" s="26">
-        <v>2</v>
-      </c>
-      <c r="D68" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_7_CHOICE_2_DESC</v>
-      </c>
-      <c r="E68" s="20" t="str">
+      <c r="E96" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F68" s="21"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B69" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="C69" s="26">
+      <c r="F96" s="21"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="C97" s="26">
         <v>1</v>
       </c>
-      <c r="D69" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_10_CHOICE_1_DESC</v>
-      </c>
-      <c r="E69" s="20" t="str">
+      <c r="D97" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_5_CHOICE_1_DESC</v>
+      </c>
+      <c r="E97" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F69" s="21"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B70" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="C70" s="26">
+      <c r="F97" s="21"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B98" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="C98" s="26">
         <v>2</v>
       </c>
-      <c r="D70" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_10_CHOICE_2_DESC</v>
-      </c>
-      <c r="E70" s="20" t="str">
+      <c r="D98" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_5_CHOICE_2_DESC</v>
+      </c>
+      <c r="E98" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F70" s="21"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B71" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="C71" s="26">
+      <c r="F98" s="21"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C99" s="26">
         <v>1</v>
       </c>
-      <c r="D71" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_12B_CHOICE_1_DESC</v>
-      </c>
-      <c r="E71" s="20" t="str">
+      <c r="D99" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_6_CHOICE_1_DESC</v>
+      </c>
+      <c r="E99" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F71" s="21"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="C72" s="26">
+      <c r="F99" s="21"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C100" s="26">
         <v>2</v>
       </c>
-      <c r="D72" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_12B_CHOICE_2_DESC</v>
-      </c>
-      <c r="E72" s="20" t="str">
+      <c r="D100" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_6_CHOICE_2_DESC</v>
+      </c>
+      <c r="E100" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F72" s="21"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="C73" s="26">
+      <c r="F100" s="21"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="26">
         <v>1</v>
       </c>
-      <c r="D73" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_14_CHOICE_1_DESC</v>
-      </c>
-      <c r="E73" s="20" t="str">
+      <c r="D101" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_7_CHOICE_1_DESC</v>
+      </c>
+      <c r="E101" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F73" s="21"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>384</v>
-      </c>
-      <c r="C74" s="26">
+      <c r="F101" s="21"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C102" s="26">
         <v>2</v>
       </c>
-      <c r="D74" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_14_CHOICE_2_DESC</v>
-      </c>
-      <c r="E74" s="20" t="str">
+      <c r="D102" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_7_CHOICE_2_DESC</v>
+      </c>
+      <c r="E102" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F74" s="21"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="C75" s="26">
+      <c r="F102" s="21"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C103" s="26">
         <v>1</v>
       </c>
-      <c r="D75" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_15_CHOICE_1_DESC</v>
-      </c>
-      <c r="E75" s="20" t="str">
+      <c r="D103" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_10_CHOICE_1_DESC</v>
+      </c>
+      <c r="E103" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F75" s="21"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="C76" s="26">
+      <c r="F103" s="21"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="C104" s="26">
         <v>2</v>
       </c>
-      <c r="D76" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_15_CHOICE_2_DESC</v>
-      </c>
-      <c r="E76" s="20" t="str">
+      <c r="D104" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_10_CHOICE_2_DESC</v>
+      </c>
+      <c r="E104" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F76" s="21"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B77" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="C77" s="26">
+      <c r="F104" s="21"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B105" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C105" s="26">
         <v>1</v>
       </c>
-      <c r="D77" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_16_CHOICE_1_DESC</v>
-      </c>
-      <c r="E77" s="20" t="str">
+      <c r="D105" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_12B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E105" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F77" s="21"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B78" s="25" t="s">
-        <v>386</v>
-      </c>
-      <c r="C78" s="26">
+      <c r="F105" s="21"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B106" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C106" s="26">
         <v>2</v>
       </c>
-      <c r="D78" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_16_CHOICE_2_DESC</v>
-      </c>
-      <c r="E78" s="20" t="str">
+      <c r="D106" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_12B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E106" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F78" s="21"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C79" s="26">
+      <c r="F106" s="21"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B107" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C107" s="26">
         <v>1</v>
       </c>
-      <c r="D79" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_19B_CHOICE_1_DESC</v>
-      </c>
-      <c r="E79" s="20" t="str">
+      <c r="D107" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_14_CHOICE_1_DESC</v>
+      </c>
+      <c r="E107" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F79" s="21"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B80" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C80" s="26">
+      <c r="F107" s="21"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B108" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="C108" s="26">
         <v>2</v>
       </c>
-      <c r="D80" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_19B_CHOICE_2_DESC</v>
-      </c>
-      <c r="E80" s="20" t="str">
+      <c r="D108" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_14_CHOICE_2_DESC</v>
+      </c>
+      <c r="E108" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F80" s="21"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B81" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="C81" s="26">
+      <c r="F108" s="21"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C109" s="26">
         <v>1</v>
       </c>
-      <c r="D81" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_21B_CHOICE_1_DESC</v>
-      </c>
-      <c r="E81" s="20" t="str">
+      <c r="D109" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_15_CHOICE_1_DESC</v>
+      </c>
+      <c r="E109" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F81" s="21"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>393</v>
-      </c>
-      <c r="C82" s="26">
+      <c r="F109" s="21"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C110" s="26">
         <v>2</v>
       </c>
-      <c r="D82" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_21B_CHOICE_2_DESC</v>
-      </c>
-      <c r="E82" s="20" t="str">
+      <c r="D110" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_15_CHOICE_2_DESC</v>
+      </c>
+      <c r="E110" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F82" s="21"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B83" s="25" t="s">
-        <v>399</v>
-      </c>
-      <c r="C83" s="26">
+      <c r="F110" s="21"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B111" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C111" s="26">
         <v>1</v>
       </c>
-      <c r="D83" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_25_CHOICE_1_DESC</v>
-      </c>
-      <c r="E83" s="20" t="str">
+      <c r="D111" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_16_CHOICE_1_DESC</v>
+      </c>
+      <c r="E111" s="29" t="str">
         <f t="shared" si="4"/>
         <v>선택1</v>
       </c>
-      <c r="F83" s="21"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="21" t="s">
-        <v>442</v>
-      </c>
-      <c r="B84" s="25" t="s">
+      <c r="F111" s="21"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B112" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="C112" s="26">
+        <v>2</v>
+      </c>
+      <c r="D112" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_16_CHOICE_2_DESC</v>
+      </c>
+      <c r="E112" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F112" s="21"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B113" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C113" s="26">
+        <v>1</v>
+      </c>
+      <c r="D113" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_19B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E113" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F113" s="21"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B114" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C114" s="26">
+        <v>2</v>
+      </c>
+      <c r="D114" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_19B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E114" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F114" s="21"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B115" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C115" s="26">
+        <v>1</v>
+      </c>
+      <c r="D115" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_21B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E115" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F115" s="21"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B116" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C116" s="26">
+        <v>2</v>
+      </c>
+      <c r="D116" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_21B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E116" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택2</v>
+      </c>
+      <c r="F116" s="21"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B117" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="C84" s="26">
+      <c r="C117" s="26">
+        <v>1</v>
+      </c>
+      <c r="D117" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>NODE_25_CHOICE_1_DESC</v>
+      </c>
+      <c r="E117" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>선택1</v>
+      </c>
+      <c r="F117" s="21"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="B118" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="C118" s="26">
         <v>2</v>
       </c>
-      <c r="D84" s="20" t="str">
-        <f t="shared" si="3"/>
+      <c r="D118" s="20" t="str">
+        <f t="shared" si="5"/>
         <v>NODE_25_CHOICE_2_DESC</v>
       </c>
-      <c r="E84" s="20" t="str">
-        <f>"선택"&amp;C84</f>
+      <c r="E118" s="29" t="str">
+        <f t="shared" si="4"/>
         <v>선택2</v>
       </c>
-      <c r="F84" s="21"/>
+      <c r="F118" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA94AA72-50F6-41E1-A365-02B71E2D7008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B145CA2-1309-4A5C-8CE4-EB2571D57924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="515">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1819,6 +1819,98 @@
   </si>
   <si>
     <t>node_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽여주마!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맹덕 형님이??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하후돈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>걱정마라 아만! 내가 있는데 뭐가 걱정인게야 캬캬캬!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하후연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형님 때문에 더 걱정입니다. 저번에도 혼자 돌격하시고.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 난세를 헤쳐 나가려면 힘을 키워야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 활이나 쏘는 주제에 말이 많구나ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야야 가만히 있지만 말고 니들도 나가서…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하!! 맹덕 형님! 나 자효가 왔습니다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형님, 사적인 정은 이제 접어두겠소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘부로 저와 제 군사는 오직 주공의 명만을 따를 것이니, 부디 천하를 바로잡아 주십시오!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일어나시게ㅋ 이제 곧 큰 싸움이 일어날텐데, 자효 그대의 활약을 기대하겠네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주공!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오오, 자효!! 이렇게 와주니 정말 고맙구만!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐야ㅋㅋ 자효잖아?ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NODE_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주공! 성 밖에 1000여명 되는 무리들이 이 쪽을 향해 오고 있습니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장!! 조조님이 드디어 거병하셨답니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋다!! 우리도 가서 힘을 보태자. 너희들도 나를 따라오너라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 아직도 도적 떼가 설치다니!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2078,7 +2170,7 @@
       <sheetName val="EnemyStatData"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="A3" t="str">
@@ -2122,23 +2214,79 @@
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>제갈량</v>
+            <v>황충</v>
           </cell>
           <cell r="B8" t="str">
-            <v>ZhugeLiang</v>
+            <v>HuangZhong</v>
           </cell>
         </row>
         <row r="9">
           <cell r="A9" t="str">
+            <v>제갈량</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>ZhugeLiang</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
             <v>여포</v>
           </cell>
-          <cell r="B9" t="str">
+          <cell r="B10" t="str">
             <v>LuBu</v>
           </cell>
         </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>조조</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>CaoCao</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>조인</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>CaoRen</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>하후돈</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>XiahouDun</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14" t="str">
+            <v>장료</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>ZhangLiao</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>하후연</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>XiahouYuan</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16" t="str">
+            <v>순욱</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>XunYu</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4280,7 +4428,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -4670,7 +4818,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" ref="A20:A33" si="10">A19</f>
+        <f t="shared" ref="A20:A54" si="10">A19</f>
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B20">
@@ -4698,7 +4846,7 @@
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:B33" si="11">B20+1</f>
+        <f t="shared" ref="B21:B54" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
@@ -5005,7 +5153,7 @@
         <v>14</v>
       </c>
       <c r="C33" t="str">
-        <f t="shared" ref="C33" si="13">CONCATENATE(A33, "_", B33, IF(D33&lt;&gt;"", "_"&amp;D33, ""))</f>
+        <f t="shared" ref="C33:C35" si="13">CONCATENATE(A33, "_", B33, IF(D33&lt;&gt;"", "_"&amp;D33, ""))</f>
         <v>1_1_1_SHU_START_14</v>
       </c>
       <c r="E33" t="str">
@@ -5017,6 +5165,470 @@
       </c>
       <c r="G33" s="3" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>510</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="13"/>
+        <v>NODE_2_0</v>
+      </c>
+      <c r="E34" t="str">
+        <f>VLOOKUP(F34,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F34" t="s">
+        <v>492</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="13"/>
+        <v>NODE_2_1</v>
+      </c>
+      <c r="E35" t="str">
+        <f>VLOOKUP(F35,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F35" t="s">
+        <v>492</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" ref="C36" si="14">CONCATENATE(A36, "_", B36, IF(D36&lt;&gt;"", "_"&amp;D36, ""))</f>
+        <v>NODE_2_2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" ref="C37:C50" si="15">CONCATENATE(A37, "_", B37, IF(D37&lt;&gt;"", "_"&amp;D37, ""))</f>
+        <v>NODE_2_3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>494</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_4</v>
+      </c>
+      <c r="E38" t="str">
+        <f>VLOOKUP(F38,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F38" t="s">
+        <v>492</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_5</v>
+      </c>
+      <c r="E39" t="str">
+        <f>VLOOKUP(F39,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F39" t="s">
+        <v>492</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_7</v>
+      </c>
+      <c r="E41" t="str">
+        <f>VLOOKUP(F41,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F41" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_8</v>
+      </c>
+      <c r="E42" t="str">
+        <f>VLOOKUP(F42,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F42" t="s">
+        <v>496</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_9</v>
+      </c>
+      <c r="E43" t="str">
+        <f>VLOOKUP(F43,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouYuan</v>
+      </c>
+      <c r="F43" t="s">
+        <v>498</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_10</v>
+      </c>
+      <c r="E44" t="str">
+        <f>VLOOKUP(F44,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F44" t="s">
+        <v>496</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_11</v>
+      </c>
+      <c r="E45" t="str">
+        <f>VLOOKUP(F45,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F45" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A46" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>494</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_14</v>
+      </c>
+      <c r="E48" t="str">
+        <f>VLOOKUP(F48,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F48" t="s">
+        <v>496</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_15</v>
+      </c>
+      <c r="E49" t="str">
+        <f>VLOOKUP(F49,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F49" t="s">
+        <v>492</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_2_16</v>
+      </c>
+      <c r="E50" t="str">
+        <f>VLOOKUP(F50,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" ref="C51:C54" si="16">CONCATENATE(A51, "_", B51, IF(D51&lt;&gt;"", "_"&amp;D51, ""))</f>
+        <v>NODE_2_17</v>
+      </c>
+      <c r="E51" t="str">
+        <f>VLOOKUP(F51,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F51" t="s">
+        <v>492</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A52" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="11"/>
+        <v>18</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="16"/>
+        <v>NODE_2_18</v>
+      </c>
+      <c r="E52" t="str">
+        <f>VLOOKUP(F52,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F52" t="s">
+        <v>492</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A53" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="16"/>
+        <v>NODE_2_19</v>
+      </c>
+      <c r="E53" t="str">
+        <f>VLOOKUP(F53,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="16"/>
+        <v>NODE_2_20</v>
+      </c>
+      <c r="E54" t="str">
+        <f>VLOOKUP(F54,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F54" t="s">
+        <v>492</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>507</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B145CA2-1309-4A5C-8CE4-EB2571D57924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619E4047-4440-425B-8060-E12B6404FF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="581">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,50 +177,6 @@
   </si>
   <si>
     <t>공명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_SHU_LIUBEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_SHU_GUANYU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_SHU_ZHANGFEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_SHU_ZHAYUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_SHU_ZHUGELIANG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_SHU_LIUBEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_SHU_GUANYU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_SHU_ZHANGFEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_SHU_ZHAYUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_SHU_ZHUGELIANG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESC_TALK_SHU_LIUBEI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -229,10 +185,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DESC_TALK_SHU_GUANYU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"연인 장익덕이 여기 있다!
 목숨이 아깝지 않은 놈부터 나와라!"</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -243,18 +195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DESC_TALK_SHU_ZHANGFEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESC_TALK_SHU_ZHAYUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESC_TALK_SHU_ZHUGELIANG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>REGION_MASTER_DESC_SHU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -303,27 +243,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME_WEI_CAOCAO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>조조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CaoCao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_WU_SUNQUAN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>손권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SunQuan</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1176,23 +1100,11 @@
     <t>서왕모도</t>
   </si>
   <si>
-    <t>NAME_ETC_LUBU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>여포</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>LuBu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COURTESY_ETC_LUBU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESC_TALK_ETC_LUBU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1237,30 +1149,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME_HISTORICAL_QINSHIHUANG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>진시황</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME_HISTORICAL_LIANPO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_XIANGYU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_YUEYI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_YANGYOUJI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>강상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1281,26 +1173,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME_HISTORICAL_QINSHIHUANG_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_LIANPO_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_XIANGYU_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_YUEYI_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_YANGYOUJI_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>최초의 황제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1409,14 +1281,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NAME_HISTORICAL_JIANGSHANG_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NAME_HISTORICAL_JIANGSHANG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>node_1</t>
   </si>
   <si>
@@ -1830,10 +1694,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Etc1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>맹덕 형님이??</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1862,10 +1722,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>야야 가만히 있지만 말고 니들도 나가서…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하하하!! 맹덕 형님! 나 자효가 왔습니다!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1906,12 +1762,376 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>좋다!! 우리도 가서 힘을 보태자. 너희들도 나를 따라오너라!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>흥! 아직도 도적 떼가 설치다니!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 별것도 아닌것들이..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋다!! 우리도 가서 힘을 보태자.\n너희들도 나를 따라오너라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호오..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야야 가만히 있지만 말고 니들도 나가서...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CaoCao</t>
+  </si>
+  <si>
+    <t>CaoRen</t>
+  </si>
+  <si>
+    <t>XiahouDun</t>
+  </si>
+  <si>
+    <t>ZhangLiao</t>
+  </si>
+  <si>
+    <t>XiahouYuan</t>
+  </si>
+  <si>
+    <t>XunYu</t>
+  </si>
+  <si>
+    <t>SunJian</t>
+  </si>
+  <si>
+    <t>SunQuan</t>
+  </si>
+  <si>
+    <t>HuangGai</t>
+  </si>
+  <si>
+    <t>SunCe</t>
+  </si>
+  <si>
+    <t>TaishiCi</t>
+  </si>
+  <si>
+    <t>HanDang</t>
+  </si>
+  <si>
+    <t>ZhouYu</t>
+  </si>
+  <si>
+    <t>HuangZhong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황충</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조조</t>
+  </si>
+  <si>
+    <t>조인</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>장료</t>
+  </si>
+  <si>
+    <t>하후연</t>
+  </si>
+  <si>
+    <t>순욱</t>
+  </si>
+  <si>
+    <t>손견</t>
+  </si>
+  <si>
+    <t>손권</t>
+  </si>
+  <si>
+    <t>황개</t>
+  </si>
+  <si>
+    <t>손책</t>
+  </si>
+  <si>
+    <t>태사자</t>
+  </si>
+  <si>
+    <t>한당</t>
+  </si>
+  <si>
+    <t>주유</t>
+  </si>
+  <si>
+    <t>#region</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAME</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_JIANGSHANG_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_LIANPO</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_LIANPO_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_QINSHIHUANG</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_QINSHIHUANG_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_XIANGYU</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_XIANGYU_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_YANGYOUJI</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_YANGYOUJI_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_YUEYI</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_YUEYI_DESC</t>
+  </si>
+  <si>
+    <t>HISTORICAL_NAME_JIANGSHANG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESC_TALK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"내 검과 방패가 살아있는 한,
+위나라의 깃발은 꺽이지 않는다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"내 눈이 뭐 어떻다고??
+찢어발겨주마!!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"천하를 도모할 판을 짜드리지요.
+가만, 누가 자꾸 내 도시락에 손을 대는 것이오!?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"손가 3대를 모셧다!
+내 이름은 대체 언제 외워줄텐가?!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"지체할 시간 없다.
+전군, 숨도 쉬지 말고 달려라."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"아직 젊은이들에게 뒤처질 순 없지.
+허허허"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"비켜라!
+강동을 평정하는 데는 한 달도 길다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"나의 검이 책상을 벤 뜻을 모르는가!
+이제 수성의 시간이다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"화웅을 벤 자가 누구라고?"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"백부가 가리키는 곳이 곧
+내가 화살을 날릴 과녁이다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"등짝은 조금 따끔했지만,
+적벽을 불태울 준비는 끝났다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"내가 천하를 등질지언정,
+천하가 나를 등지게 하지는 않겠소."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"불의 연주가 시작되었다.
+잔을 들어라."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"사나이란 죽을 때 깨끗이 죽는 법이다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COURTESY</t>
+  </si>
+  <si>
+    <t>항승</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맹덕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자효</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공근</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mengde</t>
+  </si>
+  <si>
+    <t>Zixiao</t>
+  </si>
+  <si>
+    <t>Yuanyang</t>
+  </si>
+  <si>
+    <t>Miaocai</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wenruo</t>
+  </si>
+  <si>
+    <t>Yigong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wenyuan</t>
+  </si>
+  <si>
+    <t>Gongfu</t>
+  </si>
+  <si>
+    <t>Baifu</t>
+  </si>
+  <si>
+    <t>Wentai</t>
+  </si>
+  <si>
+    <t>Zhongmou</t>
+  </si>
+  <si>
+    <t>Ziyi</t>
+  </si>
+  <si>
+    <t>Gongjin</t>
+  </si>
+  <si>
+    <t>Fengxian</t>
+  </si>
+  <si>
+    <t>Yunchang</t>
+  </si>
+  <si>
+    <t>Hansheng</t>
+  </si>
+  <si>
+    <t>Xiande</t>
+  </si>
+  <si>
+    <t>Yide</t>
+  </si>
+  <si>
+    <t>Zilong</t>
+  </si>
+  <si>
+    <t>Gongming</t>
   </si>
 </sst>
 </file>
@@ -2170,7 +2390,7 @@
       <sheetName val="EnemyStatData"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="A3" t="str">
@@ -2230,63 +2450,119 @@
         </row>
         <row r="10">
           <cell r="A10" t="str">
-            <v>여포</v>
+            <v>조조</v>
           </cell>
           <cell r="B10" t="str">
-            <v>LuBu</v>
+            <v>CaoCao</v>
           </cell>
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>조조</v>
+            <v>조인</v>
           </cell>
           <cell r="B11" t="str">
-            <v>CaoCao</v>
+            <v>CaoRen</v>
           </cell>
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>조인</v>
+            <v>하후돈</v>
           </cell>
           <cell r="B12" t="str">
-            <v>CaoRen</v>
+            <v>XiahouDun</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
-            <v>하후돈</v>
+            <v>장료</v>
           </cell>
           <cell r="B13" t="str">
-            <v>XiahouDun</v>
+            <v>ZhangLiao</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>장료</v>
+            <v>하후연</v>
           </cell>
           <cell r="B14" t="str">
-            <v>ZhangLiao</v>
+            <v>XiahouYuan</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>하후연</v>
+            <v>순욱</v>
           </cell>
           <cell r="B15" t="str">
-            <v>XiahouYuan</v>
+            <v>XunYu</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>순욱</v>
+            <v>손견</v>
           </cell>
           <cell r="B16" t="str">
-            <v>XunYu</v>
+            <v>SunJian</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17" t="str">
+            <v>손권</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>SunQuan</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18" t="str">
+            <v>황개</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>HuangGai</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19" t="str">
+            <v>손책</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>SunCe</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20" t="str">
+            <v>태사자</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>TaishiCi</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21" t="str">
+            <v>한당</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>HanDang</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22" t="str">
+            <v>주유</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>ZhouYu</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23" t="str">
+            <v>여포</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>LuBu</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2655,448 +2931,448 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>442</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s">
-        <v>443</v>
+        <v>409</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="B42" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="C49" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="C50" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="C52" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="C53" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="B54" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="C54" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="B55" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="C55" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +3397,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -3149,131 +3425,131 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="B3" s="17" t="str">
         <f>UPPER(A3)&amp;"_TITLE"</f>
         <v>MILITARY_TRAINING_TITLE</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D3" s="18"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B4" s="17" t="str">
         <f t="shared" ref="B4:B12" si="0">UPPER(A4)&amp;"_TITLE"</f>
         <v>RALLY_REMNANTS_TITLE</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D4" s="18"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="B5" s="17" t="str">
         <f t="shared" si="0"/>
         <v>BANDIT_SUBJUGATION_TITLE</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D5" s="18"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B6" s="17" t="str">
         <f t="shared" si="0"/>
         <v>BORDER_DEFENSE_TITLE</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B7" s="17" t="str">
         <f t="shared" si="0"/>
         <v>TAX_REFORM_TITLE</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="D7" s="18"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="B8" s="17" t="str">
         <f t="shared" si="0"/>
         <v>FOREIGN_DIPLOMACY_TITLE</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D8" s="18"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B9" s="17" t="str">
         <f t="shared" si="0"/>
         <v>ENEMY_INTELLIGENCE_TITLE</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B10" s="17" t="str">
         <f t="shared" si="0"/>
         <v>TACTICS_RESEARCH_TITLE</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D10" s="18"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B11" s="17" t="str">
         <f t="shared" si="0"/>
         <v>REFUGEE_PERSUASION_TITLE</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B12" s="17" t="str">
         <f t="shared" si="0"/>
         <v>RECRUIT_TALENT_TITLE</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D12" s="18"/>
     </row>
@@ -3306,437 +3582,1473 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="50.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="50.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>546</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D9" t="str">
+        <f>UPPER(A9)&amp;"_"&amp;UPPER(C9)&amp;"_"&amp;UPPER(B9)</f>
+        <v>COURTESY_ETC_LUBU</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>546</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D10" t="str">
+        <f>UPPER(A10)&amp;"_"&amp;UPPER(C10)&amp;"_"&amp;UPPER(B10)</f>
+        <v>COURTESY_SHU_GUANYU</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>546</v>
+      </c>
+      <c r="B11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D11" t="str">
+        <f>UPPER(A11)&amp;"_"&amp;UPPER(C11)&amp;"_"&amp;UPPER(B11)</f>
+        <v>COURTESY_SHU_HUANGZHONG</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>546</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D12" t="str">
+        <f>UPPER(A12)&amp;"_"&amp;UPPER(C12)&amp;"_"&amp;UPPER(B12)</f>
+        <v>COURTESY_SHU_LIUBEI</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>546</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D13" t="str">
+        <f>UPPER(A13)&amp;"_"&amp;UPPER(C13)&amp;"_"&amp;UPPER(B13)</f>
+        <v>COURTESY_SHU_ZHANGFEI</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>546</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D14" t="str">
+        <f>UPPER(A14)&amp;"_"&amp;UPPER(C14)&amp;"_"&amp;UPPER(B14)</f>
+        <v>COURTESY_SHU_ZHAYUN</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>546</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" t="str">
+        <f>UPPER(A15)&amp;"_"&amp;UPPER(C15)&amp;"_"&amp;UPPER(B15)</f>
+        <v>COURTESY_SHU_ZHUGELIANG</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>546</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D16" t="str">
+        <f>UPPER(A16)&amp;"_"&amp;UPPER(C16)&amp;"_"&amp;UPPER(B16)</f>
+        <v>COURTESY_WEI_CAOCAO</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="F16" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>546</v>
+      </c>
+      <c r="B17" t="s">
+        <v>485</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D17" t="str">
+        <f>UPPER(A17)&amp;"_"&amp;UPPER(C17)&amp;"_"&amp;UPPER(B17)</f>
+        <v>COURTESY_WEI_CAOREN</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="F17" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D18" t="str">
+        <f>UPPER(A18)&amp;"_"&amp;UPPER(C18)&amp;"_"&amp;UPPER(B18)</f>
+        <v>COURTESY_WEI_XIAHOUDUN</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>546</v>
+      </c>
+      <c r="B19" t="s">
+        <v>488</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D19" t="str">
+        <f>UPPER(A19)&amp;"_"&amp;UPPER(C19)&amp;"_"&amp;UPPER(B19)</f>
+        <v>COURTESY_WEI_XIAHOUYUAN</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>546</v>
+      </c>
+      <c r="B20" t="s">
+        <v>489</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D20" t="str">
+        <f>UPPER(A20)&amp;"_"&amp;UPPER(C20)&amp;"_"&amp;UPPER(B20)</f>
+        <v>COURTESY_WEI_XUNYU</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>546</v>
+      </c>
+      <c r="B21" t="s">
+        <v>487</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D21" t="str">
+        <f>UPPER(A21)&amp;"_"&amp;UPPER(C21)&amp;"_"&amp;UPPER(B21)</f>
+        <v>COURTESY_WEI_ZHANGLIAO</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>546</v>
+      </c>
+      <c r="B22" t="s">
+        <v>495</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D22" t="str">
+        <f>UPPER(A22)&amp;"_"&amp;UPPER(C22)&amp;"_"&amp;UPPER(B22)</f>
+        <v>COURTESY_WU_HANDANG</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F22" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>546</v>
+      </c>
+      <c r="B23" t="s">
+        <v>492</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D23" t="str">
+        <f>UPPER(A23)&amp;"_"&amp;UPPER(C23)&amp;"_"&amp;UPPER(B23)</f>
+        <v>COURTESY_WU_HUANGGAI</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F23" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>546</v>
+      </c>
+      <c r="B24" t="s">
+        <v>493</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D24" t="str">
+        <f>UPPER(A24)&amp;"_"&amp;UPPER(C24)&amp;"_"&amp;UPPER(B24)</f>
+        <v>COURTESY_WU_SUNCE</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F24" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>546</v>
+      </c>
+      <c r="B25" t="s">
+        <v>490</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D25" t="str">
+        <f>UPPER(A25)&amp;"_"&amp;UPPER(C25)&amp;"_"&amp;UPPER(B25)</f>
+        <v>COURTESY_WU_SUNJIAN</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="F25" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>546</v>
+      </c>
+      <c r="B26" t="s">
+        <v>491</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D26" t="str">
+        <f>UPPER(A26)&amp;"_"&amp;UPPER(C26)&amp;"_"&amp;UPPER(B26)</f>
+        <v>COURTESY_WU_SUNQUAN</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="F26" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>546</v>
+      </c>
+      <c r="B27" t="s">
+        <v>494</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D27" t="str">
+        <f>UPPER(A27)&amp;"_"&amp;UPPER(C27)&amp;"_"&amp;UPPER(B27)</f>
+        <v>COURTESY_WU_TAISHICI</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F27" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>546</v>
+      </c>
+      <c r="B28" t="s">
+        <v>496</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D28" t="str">
+        <f>UPPER(A28)&amp;"_"&amp;UPPER(C28)&amp;"_"&amp;UPPER(B28)</f>
+        <v>COURTESY_WU_ZHOUYU</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F28" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>531</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D29" t="str">
+        <f>UPPER(A29)&amp;"_"&amp;UPPER(C29)&amp;"_"&amp;UPPER(B29)</f>
+        <v>DESC_TALK_ETC_LUBU</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>531</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D30" t="str">
+        <f>UPPER(A30)&amp;"_"&amp;UPPER(C30)&amp;"_"&amp;UPPER(B30)</f>
+        <v>DESC_TALK_SHU_GUANYU</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>531</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D31" t="str">
+        <f>UPPER(A31)&amp;"_"&amp;UPPER(C31)&amp;"_"&amp;UPPER(B31)</f>
+        <v>DESC_TALK_SHU_LIUBEI</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>531</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D32" t="str">
+        <f>UPPER(A32)&amp;"_"&amp;UPPER(C32)&amp;"_"&amp;UPPER(B32)</f>
+        <v>DESC_TALK_SHU_ZHANGFEI</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>531</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D33" t="str">
+        <f>UPPER(A33)&amp;"_"&amp;UPPER(C33)&amp;"_"&amp;UPPER(B33)</f>
+        <v>DESC_TALK_SHU_ZHAYUN</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>531</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D34" t="str">
+        <f>UPPER(A34)&amp;"_"&amp;UPPER(C34)&amp;"_"&amp;UPPER(B34)</f>
+        <v>DESC_TALK_SHU_ZHUGELIANG</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>531</v>
+      </c>
+      <c r="B35" t="s">
+        <v>497</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D35" t="str">
+        <f>UPPER(A35)&amp;"_"&amp;UPPER(C35)&amp;"_"&amp;UPPER(B35)</f>
+        <v>DESC_TALK_SHU_HUANGZHONG</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>531</v>
+      </c>
+      <c r="B36" t="s">
+        <v>484</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D36" t="str">
+        <f>UPPER(A36)&amp;"_"&amp;UPPER(C36)&amp;"_"&amp;UPPER(B36)</f>
+        <v>DESC_TALK_WEI_CAOCAO</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>531</v>
+      </c>
+      <c r="B37" t="s">
+        <v>485</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D37" t="str">
+        <f>UPPER(A37)&amp;"_"&amp;UPPER(C37)&amp;"_"&amp;UPPER(B37)</f>
+        <v>DESC_TALK_WEI_CAOREN</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>531</v>
+      </c>
+      <c r="B38" t="s">
+        <v>486</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D38" t="str">
+        <f>UPPER(A38)&amp;"_"&amp;UPPER(C38)&amp;"_"&amp;UPPER(B38)</f>
+        <v>DESC_TALK_WEI_XIAHOUDUN</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>531</v>
+      </c>
+      <c r="B39" t="s">
+        <v>488</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D39" t="str">
+        <f>UPPER(A39)&amp;"_"&amp;UPPER(C39)&amp;"_"&amp;UPPER(B39)</f>
+        <v>DESC_TALK_WEI_XIAHOUYUAN</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>531</v>
+      </c>
+      <c r="B40" t="s">
+        <v>489</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D40" t="str">
+        <f>UPPER(A40)&amp;"_"&amp;UPPER(C40)&amp;"_"&amp;UPPER(B40)</f>
+        <v>DESC_TALK_WEI_XUNYU</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>531</v>
+      </c>
+      <c r="B41" t="s">
+        <v>487</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D41" t="str">
+        <f>UPPER(A41)&amp;"_"&amp;UPPER(C41)&amp;"_"&amp;UPPER(B41)</f>
+        <v>DESC_TALK_WEI_ZHANGLIAO</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>531</v>
+      </c>
+      <c r="B42" t="s">
+        <v>495</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D42" t="str">
+        <f>UPPER(A42)&amp;"_"&amp;UPPER(C42)&amp;"_"&amp;UPPER(B42)</f>
+        <v>DESC_TALK_WU_HANDANG</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>531</v>
+      </c>
+      <c r="B43" t="s">
+        <v>492</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D43" t="str">
+        <f>UPPER(A43)&amp;"_"&amp;UPPER(C43)&amp;"_"&amp;UPPER(B43)</f>
+        <v>DESC_TALK_WU_HUANGGAI</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F43" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>531</v>
+      </c>
+      <c r="B44" t="s">
+        <v>493</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D44" t="str">
+        <f>UPPER(A44)&amp;"_"&amp;UPPER(C44)&amp;"_"&amp;UPPER(B44)</f>
+        <v>DESC_TALK_WU_SUNCE</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>531</v>
+      </c>
+      <c r="B45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D45" t="str">
+        <f>UPPER(A45)&amp;"_"&amp;UPPER(C45)&amp;"_"&amp;UPPER(B45)</f>
+        <v>DESC_TALK_WU_SUNJIAN</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>531</v>
+      </c>
+      <c r="B46" t="s">
+        <v>491</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D46" t="str">
+        <f>UPPER(A46)&amp;"_"&amp;UPPER(C46)&amp;"_"&amp;UPPER(B46)</f>
+        <v>DESC_TALK_WU_SUNQUAN</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>531</v>
+      </c>
+      <c r="B47" t="s">
+        <v>494</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D47" t="str">
+        <f>UPPER(A47)&amp;"_"&amp;UPPER(C47)&amp;"_"&amp;UPPER(B47)</f>
+        <v>DESC_TALK_WU_TAISHICI</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>531</v>
+      </c>
+      <c r="B48" t="s">
+        <v>496</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D48" t="str">
+        <f>UPPER(A48)&amp;"_"&amp;UPPER(C48)&amp;"_"&amp;UPPER(B48)</f>
+        <v>DESC_TALK_WU_ZHOUYU</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F48" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>530</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F49" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>519</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F50" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>520</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F51" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>521</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>522</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F53" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>523</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F54" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>524</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F55" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>525</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="F56" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>526</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F57" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>527</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="F58" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>528</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F59" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>529</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F60" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>518</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D61" t="str">
+        <f>UPPER(A61)&amp;"_"&amp;UPPER(C61)&amp;"_"&amp;UPPER(B61)</f>
+        <v>NAME_ETC_LUBU</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>518</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D62" t="str">
+        <f>UPPER(A62)&amp;"_"&amp;UPPER(C62)&amp;"_"&amp;UPPER(B62)</f>
+        <v>NAME_SHU_GUANYU</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>518</v>
+      </c>
+      <c r="B63" t="s">
+        <v>497</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D63" t="str">
+        <f>UPPER(A63)&amp;"_"&amp;UPPER(C63)&amp;"_"&amp;UPPER(B63)</f>
+        <v>NAME_SHU_HUANGZHONG</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>518</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D64" t="str">
+        <f>UPPER(A64)&amp;"_"&amp;UPPER(C64)&amp;"_"&amp;UPPER(B64)</f>
+        <v>NAME_SHU_LIUBEI</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>518</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D65" t="str">
+        <f>UPPER(A65)&amp;"_"&amp;UPPER(C65)&amp;"_"&amp;UPPER(B65)</f>
+        <v>NAME_SHU_ZHANGFEI</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>518</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D66" t="str">
+        <f>UPPER(A66)&amp;"_"&amp;UPPER(C66)&amp;"_"&amp;UPPER(B66)</f>
+        <v>NAME_SHU_ZHAYUN</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>518</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D67" t="str">
+        <f>UPPER(A67)&amp;"_"&amp;UPPER(C67)&amp;"_"&amp;UPPER(B67)</f>
+        <v>NAME_SHU_ZHUGELIANG</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>518</v>
+      </c>
+      <c r="B68" t="s">
+        <v>484</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D68" t="str">
+        <f>UPPER(A68)&amp;"_"&amp;UPPER(C68)&amp;"_"&amp;UPPER(B68)</f>
+        <v>NAME_WEI_CAOCAO</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>518</v>
+      </c>
+      <c r="B69" t="s">
+        <v>485</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D69" t="str">
+        <f>UPPER(A69)&amp;"_"&amp;UPPER(C69)&amp;"_"&amp;UPPER(B69)</f>
+        <v>NAME_WEI_CAOREN</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>518</v>
+      </c>
+      <c r="B70" t="s">
+        <v>486</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D70" t="str">
+        <f>UPPER(A70)&amp;"_"&amp;UPPER(C70)&amp;"_"&amp;UPPER(B70)</f>
+        <v>NAME_WEI_XIAHOUDUN</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>518</v>
+      </c>
+      <c r="B71" t="s">
+        <v>488</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D71" t="str">
+        <f>UPPER(A71)&amp;"_"&amp;UPPER(C71)&amp;"_"&amp;UPPER(B71)</f>
+        <v>NAME_WEI_XIAHOUYUAN</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>518</v>
+      </c>
+      <c r="B72" t="s">
+        <v>489</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D72" t="str">
+        <f>UPPER(A72)&amp;"_"&amp;UPPER(C72)&amp;"_"&amp;UPPER(B72)</f>
+        <v>NAME_WEI_XUNYU</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>518</v>
+      </c>
+      <c r="B73" t="s">
+        <v>487</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D73" t="str">
+        <f>UPPER(A73)&amp;"_"&amp;UPPER(C73)&amp;"_"&amp;UPPER(B73)</f>
+        <v>NAME_WEI_ZHANGLIAO</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>518</v>
+      </c>
+      <c r="B74" t="s">
+        <v>495</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D74" t="str">
+        <f>UPPER(A74)&amp;"_"&amp;UPPER(C74)&amp;"_"&amp;UPPER(B74)</f>
+        <v>NAME_WU_HANDANG</v>
+      </c>
+      <c r="E74" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>518</v>
+      </c>
+      <c r="B75" t="s">
+        <v>492</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D75" t="str">
+        <f>UPPER(A75)&amp;"_"&amp;UPPER(C75)&amp;"_"&amp;UPPER(B75)</f>
+        <v>NAME_WU_HUANGGAI</v>
+      </c>
+      <c r="E75" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>518</v>
+      </c>
+      <c r="B76" t="s">
+        <v>493</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D76" t="str">
+        <f>UPPER(A76)&amp;"_"&amp;UPPER(C76)&amp;"_"&amp;UPPER(B76)</f>
+        <v>NAME_WU_SUNCE</v>
+      </c>
+      <c r="E76" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>518</v>
+      </c>
+      <c r="B77" t="s">
+        <v>490</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D77" t="str">
+        <f>UPPER(A77)&amp;"_"&amp;UPPER(C77)&amp;"_"&amp;UPPER(B77)</f>
+        <v>NAME_WU_SUNJIAN</v>
+      </c>
+      <c r="E77" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>518</v>
+      </c>
+      <c r="B78" t="s">
+        <v>491</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D78" t="str">
+        <f>UPPER(A78)&amp;"_"&amp;UPPER(C78)&amp;"_"&amp;UPPER(B78)</f>
+        <v>NAME_WU_SUNQUAN</v>
+      </c>
+      <c r="E78" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>518</v>
+      </c>
+      <c r="B79" t="s">
+        <v>494</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D79" t="str">
+        <f>UPPER(A79)&amp;"_"&amp;UPPER(C79)&amp;"_"&amp;UPPER(B79)</f>
+        <v>NAME_WU_TAISHICI</v>
+      </c>
+      <c r="E79" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>518</v>
+      </c>
+      <c r="B80" t="s">
+        <v>496</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D80" t="str">
+        <f>UPPER(A80)&amp;"_"&amp;UPPER(C80)&amp;"_"&amp;UPPER(B80)</f>
+        <v>NAME_WU_ZHOUYU</v>
+      </c>
+      <c r="E80" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="81" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    </row>
+    <row r="83" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D84" t="s">
+        <v>46</v>
+      </c>
+      <c r="E84" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D85" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="E85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D86" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>314</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="33" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="E86" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>325</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>327</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>328</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>329</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>330</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>369</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>336</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>337</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>338</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>339</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>340</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>368</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>342</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C34">
-    <sortCondition ref="A3:A34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G66">
+    <sortCondition ref="D3:D66"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3759,7 +5071,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>3</v>
@@ -3791,630 +5103,630 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B3" s="11" t="str">
         <f>"NAME_" &amp; UPPER(A3)</f>
         <v>NAME_LIUTAO</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="B4" s="11" t="str">
         <f t="shared" ref="B4:B47" si="0">"NAME_" &amp; UPPER(A4)</f>
         <v>NAME_SANLUE</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B5" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WEILIAOZI</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="B6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_COMMANDERS_BANNER</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="B7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_TIGER_TALLY</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WAR_DRUM_GONG</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="B9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SIMA_FA</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="B10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WUZI</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="B11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_RED_CLIFF_FLAME</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BANGCHEONHWAGUG_SHARD</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GANJIANG_MOYE</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="B14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_CHUNGOU</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="B15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ZHANLU</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B16" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_YUCHANG</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="B17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_TAIE</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="B18" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_JUQUE</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B19" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SHENGXIE</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="B20" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_LORDS_WAR_BOW</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="B21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WUJANGWON_STAR</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B22" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ART_OF_WAR</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="B23" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_QIMEN_DUNJIA</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="B24" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_I_CHING</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B25" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GUIGUZI</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B26" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_GUANZI</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="B27" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HAN_FEIZI</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B28" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_SU_SHU_OF_HUANGSHI</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="B29" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_MOZI</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B30" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_EMPERORS_SEAL</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="B31" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BOOK_OF_LORD_SHANG</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="B32" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_LUSHI_CHUNQIU</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="B33" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ANALECTS</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B34" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_WEI_ADMINISTRATIVE_CODE</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="B35" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_STRATAGEMS_OF_WARRING_STATES</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="B36" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_IMPERIAL_JADE_SEAL</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="B37" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_PREFECTS_OFFICIAL_SEAL</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B38" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HUANGLAO_SILK_MANUSCRIPT</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="B39" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_DOEWON_CUP</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="B40" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HES_JADE_DISC</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="B41" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_CLASSIC_OF_MOUNTAINS_AND_SEAS</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B42" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_XUANHE_QIN</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="B43" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_PHOENIX_JADE_PENDANT</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B44" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_BOOK_OF_RITES</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="B45" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_ALLIANCE_LETTER</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B46" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_HETU_LUOSHU</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="B47" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NAME_MAP_OF_QUEEN_MOTHER_OF_THE_WEST</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="D47" s="11"/>
       <c r="E47" s="11"/>
@@ -4428,7 +5740,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -4443,22 +5755,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>0</v>
@@ -4475,7 +5787,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -4499,7 +5811,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4509,7 +5821,7 @@
         <v>TUTORIAL_START_0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -4526,10 +5838,10 @@
         <v>TUTORIAL_START_1</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -4546,7 +5858,7 @@
         <v>TUTORIAL_START_2</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -4563,7 +5875,7 @@
         <v>TUTORIAL_START_3</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -4580,10 +5892,10 @@
         <v>TUTORIAL_START_4_MOBILE</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -4600,10 +5912,10 @@
         <v>TUTORIAL_START_5_PC</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -4620,10 +5932,10 @@
         <v>TUTORIAL_START_6_MOBILE</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -4640,10 +5952,10 @@
         <v>TUTORIAL_START_7_PC</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -4660,10 +5972,10 @@
         <v>TUTORIAL_START_8_MOBILE</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -4680,10 +5992,10 @@
         <v>TUTORIAL_START_9_PC</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -4700,7 +6012,7 @@
         <v>TUTORIAL_START_10</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -4717,7 +6029,7 @@
         <v>TUTORIAL_START_11</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -4734,7 +6046,7 @@
         <v>TUTORIAL_START_12</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -4751,10 +6063,10 @@
         <v>TUTORIAL_START_13_MOBILE</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -4771,10 +6083,10 @@
         <v>TUTORIAL_START_14_PC</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -4791,12 +6103,12 @@
         <v>TUTORIAL_START_15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -4813,12 +6125,12 @@
         <v>9</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f t="shared" ref="A20:A54" si="10">A19</f>
+        <f t="shared" ref="A20:A57" si="10">A19</f>
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B20">
@@ -4837,7 +6149,7 @@
         <v>7</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -4846,7 +6158,7 @@
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:B54" si="11">B20+1</f>
+        <f t="shared" ref="B21:B57" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
@@ -4861,7 +6173,7 @@
         <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -4885,7 +6197,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -4909,7 +6221,7 @@
         <v>7</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -4933,7 +6245,7 @@
         <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -4957,7 +6269,7 @@
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -4984,7 +6296,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -5011,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -5038,7 +6350,7 @@
         <v>9</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -5065,7 +6377,7 @@
         <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -5092,7 +6404,7 @@
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -5116,7 +6428,7 @@
         <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -5140,7 +6452,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -5164,12 +6476,12 @@
         <v>7</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>510</v>
+        <v>474</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -5183,10 +6495,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F34" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>514</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -5207,10 +6519,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F35" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>493</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -5240,11 +6552,15 @@
         <f t="shared" ref="C37:C50" si="15">CONCATENATE(A37, "_", B37, IF(D37&lt;&gt;"", "_"&amp;D37, ""))</f>
         <v>NODE_2_3</v>
       </c>
-      <c r="E37" t="s">
-        <v>494</v>
+      <c r="E37" t="str">
+        <f>VLOOKUP(F37,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F37" t="s">
+        <v>458</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>512</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -5260,15 +6576,11 @@
         <f t="shared" si="15"/>
         <v>NODE_2_4</v>
       </c>
-      <c r="E38" t="str">
-        <f>VLOOKUP(F38,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoRen</v>
-      </c>
-      <c r="F38" t="s">
-        <v>492</v>
+      <c r="E38" t="s">
+        <v>480</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -5289,13 +6601,13 @@
         <v>CaoRen</v>
       </c>
       <c r="F39" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -5307,6 +6619,16 @@
       <c r="C40" t="str">
         <f t="shared" si="15"/>
         <v>NODE_2_6</v>
+      </c>
+      <c r="E40" t="str">
+        <f>VLOOKUP(F40,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F40" t="s">
+        <v>458</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -5322,16 +6644,6 @@
         <f t="shared" si="15"/>
         <v>NODE_2_7</v>
       </c>
-      <c r="E41" t="str">
-        <f>VLOOKUP(F41,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
-      </c>
-      <c r="F41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>500</v>
-      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
@@ -5348,13 +6660,13 @@
       </c>
       <c r="E42" t="str">
         <f>VLOOKUP(F42,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>CaoCao</v>
       </c>
       <c r="F42" t="s">
-        <v>496</v>
+        <v>51</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -5372,13 +6684,13 @@
       </c>
       <c r="E43" t="str">
         <f>VLOOKUP(F43,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F43" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -5396,13 +6708,13 @@
       </c>
       <c r="E44" t="str">
         <f>VLOOKUP(F44,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F44" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>501</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -5420,16 +6732,16 @@
       </c>
       <c r="E45" t="str">
         <f>VLOOKUP(F45,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>461</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -5442,14 +6754,18 @@
         <f t="shared" si="15"/>
         <v>NODE_2_12</v>
       </c>
-      <c r="E46" t="s">
-        <v>494</v>
+      <c r="E46" t="str">
+        <f>VLOOKUP(F46,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F46" t="s">
+        <v>51</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -5461,6 +6777,12 @@
       <c r="C47" t="str">
         <f t="shared" si="15"/>
         <v>NODE_2_13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>480</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -5478,13 +6800,13 @@
       </c>
       <c r="E48" t="str">
         <f>VLOOKUP(F48,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F48" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -5502,13 +6824,13 @@
       </c>
       <c r="E49" t="str">
         <f>VLOOKUP(F49,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoRen</v>
+        <v>CaoCao</v>
       </c>
       <c r="F49" t="s">
-        <v>492</v>
+        <v>51</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -5524,16 +6846,6 @@
         <f t="shared" si="15"/>
         <v>NODE_2_16</v>
       </c>
-      <c r="E50" t="str">
-        <f>VLOOKUP(F50,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
-      </c>
-      <c r="F50" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>508</v>
-      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
@@ -5553,13 +6865,13 @@
         <v>CaoRen</v>
       </c>
       <c r="F51" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -5574,16 +6886,16 @@
       </c>
       <c r="E52" t="str">
         <f>VLOOKUP(F52,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoRen</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F52" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -5601,10 +6913,10 @@
         <v>CaoCao</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>506</v>
+        <v>472</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -5625,10 +6937,82 @@
         <v>CaoRen</v>
       </c>
       <c r="F54" t="s">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>507</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A55" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" ref="C55:C56" si="17">CONCATENATE(A55, "_", B55, IF(D55&lt;&gt;"", "_"&amp;D55, ""))</f>
+        <v>NODE_2_21</v>
+      </c>
+      <c r="E55" t="str">
+        <f>VLOOKUP(F55,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F55" t="s">
+        <v>458</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A56" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_2_22</v>
+      </c>
+      <c r="E56" t="str">
+        <f>VLOOKUP(F56,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoCao</v>
+      </c>
+      <c r="F56" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="str">
+        <f t="shared" si="10"/>
+        <v>NODE_2</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" ref="C57" si="18">CONCATENATE(A57, "_", B57, IF(D57&lt;&gt;"", "_"&amp;D57, ""))</f>
+        <v>NODE_2_23</v>
+      </c>
+      <c r="E57" t="str">
+        <f>VLOOKUP(F57,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>CaoRen</v>
+      </c>
+      <c r="F57" t="s">
+        <v>458</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -5652,13 +7036,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>440</v>
+        <v>406</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -5670,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>473</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5698,10 +7082,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C3" s="19"/>
       <c r="D3" s="20" t="str">
@@ -5709,16 +7093,16 @@
         <v>NODE_1_TITLE</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="str">
@@ -5726,16 +7110,16 @@
         <v>NODE_2_TITLE</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="20" t="str">
@@ -5743,16 +7127,16 @@
         <v>NODE_3_TITLE</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="20" t="str">
@@ -5760,16 +7144,16 @@
         <v>NODE_4_TITLE</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="20" t="str">
@@ -5777,16 +7161,16 @@
         <v>NODE_5_TITLE</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="20" t="str">
@@ -5794,16 +7178,16 @@
         <v>NODE_6_TITLE</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="20" t="str">
@@ -5811,16 +7195,16 @@
         <v>NODE_7_TITLE</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="20" t="str">
@@ -5828,16 +7212,16 @@
         <v>NODE_8_TITLE</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="20" t="str">
@@ -5845,16 +7229,16 @@
         <v>NODE_9_TITLE</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="20" t="str">
@@ -5862,16 +7246,16 @@
         <v>NODE_10_TITLE</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="20" t="str">
@@ -5879,16 +7263,16 @@
         <v>NODE_11_TITLE</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="20" t="str">
@@ -5896,16 +7280,16 @@
         <v>NODE_12A_TITLE</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="20" t="str">
@@ -5913,16 +7297,16 @@
         <v>NODE_12B_TITLE</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="20" t="str">
@@ -5930,16 +7314,16 @@
         <v>NODE_13_TITLE</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>470</v>
+        <v>436</v>
       </c>
       <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="20" t="str">
@@ -5947,16 +7331,16 @@
         <v>NODE_14_TITLE</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="20" t="str">
@@ -5964,16 +7348,16 @@
         <v>NODE_15_TITLE</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="20" t="str">
@@ -5981,16 +7365,16 @@
         <v>NODE_16_TITLE</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="20" t="str">
@@ -5998,16 +7382,16 @@
         <v>NODE_17_TITLE</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="20" t="str">
@@ -6015,16 +7399,16 @@
         <v>NODE_18_TITLE</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="20" t="str">
@@ -6032,16 +7416,16 @@
         <v>NODE_19A_TITLE</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="20" t="str">
@@ -6049,16 +7433,16 @@
         <v>NODE_19B_TITLE</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="20" t="str">
@@ -6066,16 +7450,16 @@
         <v>NODE_20_TITLE</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="20" t="str">
@@ -6083,16 +7467,16 @@
         <v>NODE_21A_TITLE</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="20" t="str">
@@ -6100,16 +7484,16 @@
         <v>NODE_21B_TITLE</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="20" t="str">
@@ -6117,16 +7501,16 @@
         <v>NODE_22_TITLE</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="20" t="str">
@@ -6134,16 +7518,16 @@
         <v>NODE_23A_TITLE</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="20" t="str">
@@ -6151,16 +7535,16 @@
         <v>NODE_23B_TITLE</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="20" t="str">
@@ -6168,16 +7552,16 @@
         <v>NODE_24A_TITLE</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="20" t="str">
@@ -6185,16 +7569,16 @@
         <v>NODE_24B_TITLE</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="20" t="str">
@@ -6202,16 +7586,16 @@
         <v>NODE_25_TITLE</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="C33" s="19"/>
       <c r="D33" s="20" t="str">
@@ -6219,16 +7603,16 @@
         <v>NODE_26_TITLE</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="20" t="str">
@@ -6236,16 +7620,16 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="C35" s="22"/>
       <c r="D35" s="23" t="str">
@@ -6253,16 +7637,16 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="20" t="str">
@@ -6270,16 +7654,16 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="F36" s="21"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="20" t="str">
@@ -6287,16 +7671,16 @@
         <v>NODE_1_DESC</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="F37" s="21"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="20" t="str">
@@ -6304,16 +7688,16 @@
         <v>NODE_2_DESC</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="F38" s="21"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="20" t="str">
@@ -6321,16 +7705,16 @@
         <v>NODE_3_DESC</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -6338,16 +7722,16 @@
         <v>NODE_4_DESC</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="F40" s="21"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="C41" s="19"/>
       <c r="D41" s="20" t="str">
@@ -6355,16 +7739,16 @@
         <v>NODE_5_DESC</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="F41" s="21"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="20" t="str">
@@ -6372,16 +7756,16 @@
         <v>NODE_6_DESC</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="F42" s="21"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="20" t="str">
@@ -6389,16 +7773,16 @@
         <v>NODE_7_DESC</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="F43" s="21"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="20" t="str">
@@ -6406,16 +7790,16 @@
         <v>NODE_8_DESC</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="20" t="str">
@@ -6423,16 +7807,16 @@
         <v>NODE_9_DESC</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="F45" s="21"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="20" t="str">
@@ -6440,16 +7824,16 @@
         <v>NODE_10_DESC</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>465</v>
+        <v>431</v>
       </c>
       <c r="F46" s="21"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="C47" s="19"/>
       <c r="D47" s="20" t="str">
@@ -6457,16 +7841,16 @@
         <v>NODE_11_DESC</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>467</v>
+        <v>433</v>
       </c>
       <c r="F47" s="21"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="C48" s="19"/>
       <c r="D48" s="20" t="str">
@@ -6474,16 +7858,16 @@
         <v>NODE_12A_DESC</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="F48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C49" s="19"/>
       <c r="D49" s="20" t="str">
@@ -6491,16 +7875,16 @@
         <v>NODE_12B_DESC</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20" t="str">
@@ -6508,16 +7892,16 @@
         <v>NODE_13_DESC</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>477</v>
+        <v>443</v>
       </c>
       <c r="F50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="20" t="str">
@@ -6525,16 +7909,16 @@
         <v>NODE_14_DESC</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="F51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="20" t="str">
@@ -6542,16 +7926,16 @@
         <v>NODE_15_DESC</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>471</v>
+        <v>437</v>
       </c>
       <c r="F52" s="21"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="20" t="str">
@@ -6559,16 +7943,16 @@
         <v>NODE_16_DESC</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>472</v>
+        <v>438</v>
       </c>
       <c r="F53" s="21"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20" t="str">
@@ -6576,19 +7960,19 @@
         <v>NODE_17_DESC</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="F54" s="21"/>
       <c r="G54" s="35" t="s">
-        <v>447</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="20" t="str">
@@ -6596,19 +7980,19 @@
         <v>NODE_18_DESC</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>479</v>
+        <v>445</v>
       </c>
       <c r="F55" s="21"/>
       <c r="G55" s="35" t="s">
-        <v>448</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="20" t="str">
@@ -6616,19 +8000,19 @@
         <v>NODE_19A_DESC</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="35" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C57" s="19"/>
       <c r="D57" s="20" t="str">
@@ -6636,19 +8020,19 @@
         <v>NODE_19B_DESC</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="35" t="s">
-        <v>450</v>
+        <v>416</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="20" t="str">
@@ -6656,19 +8040,19 @@
         <v>NODE_20_DESC</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="35" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="C59" s="19"/>
       <c r="D59" s="20" t="str">
@@ -6676,19 +8060,19 @@
         <v>NODE_21A_DESC</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>483</v>
+        <v>449</v>
       </c>
       <c r="F59" s="21"/>
       <c r="G59" s="35" t="s">
-        <v>452</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C60" s="19"/>
       <c r="D60" s="20" t="str">
@@ -6696,19 +8080,19 @@
         <v>NODE_21B_DESC</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="35" t="s">
-        <v>453</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="20" t="str">
@@ -6716,19 +8100,19 @@
         <v>NODE_22_DESC</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="F61" s="21"/>
       <c r="G61" s="35" t="s">
-        <v>454</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="20" t="str">
@@ -6736,19 +8120,19 @@
         <v>NODE_23A_DESC</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="F62" s="21"/>
       <c r="G62" s="35" t="s">
-        <v>455</v>
+        <v>421</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="C63" s="19"/>
       <c r="D63" s="20" t="str">
@@ -6756,19 +8140,19 @@
         <v>NODE_23B_DESC</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>488</v>
+        <v>454</v>
       </c>
       <c r="F63" s="21"/>
       <c r="G63" s="35" t="s">
-        <v>456</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C64" s="19"/>
       <c r="D64" s="20" t="str">
@@ -6776,19 +8160,19 @@
         <v>NODE_24A_DESC</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="F64" s="21"/>
       <c r="G64" s="35" t="s">
-        <v>457</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="20" t="str">
@@ -6796,19 +8180,19 @@
         <v>NODE_24B_DESC</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="F65" s="21"/>
       <c r="G65" s="35" t="s">
-        <v>458</v>
+        <v>424</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="20" t="str">
@@ -6816,19 +8200,19 @@
         <v>NODE_25_DESC</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="F66" s="21"/>
       <c r="G66" s="35" t="s">
-        <v>459</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="20" t="str">
@@ -6836,19 +8220,19 @@
         <v>NODE_26_DESC</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="F67" s="21"/>
       <c r="G67" s="35" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C68" s="19"/>
       <c r="D68" s="20" t="str">
@@ -6856,19 +8240,19 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="F68" s="21"/>
       <c r="G68" s="35" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="C69" s="22"/>
       <c r="D69" s="20" t="str">
@@ -6876,19 +8260,19 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="F69" s="24"/>
       <c r="G69" s="35" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="27" t="s">
-        <v>444</v>
+        <v>410</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="20" t="str">
@@ -6896,19 +8280,19 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>474</v>
+        <v>440</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="35" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C71" s="26">
         <v>1</v>
@@ -6922,10 +8306,10 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C72" s="26">
         <v>2</v>
@@ -6939,10 +8323,10 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="C73" s="26">
         <v>1</v>
@@ -6956,10 +8340,10 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="C74" s="26">
         <v>2</v>
@@ -6973,10 +8357,10 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C75" s="26">
         <v>1</v>
@@ -6990,10 +8374,10 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C76" s="26">
         <v>2</v>
@@ -7007,10 +8391,10 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C77" s="26">
         <v>1</v>
@@ -7024,10 +8408,10 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C78" s="26">
         <v>2</v>
@@ -7041,10 +8425,10 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C79" s="26">
         <v>1</v>
@@ -7058,10 +8442,10 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C80" s="26">
         <v>2</v>
@@ -7075,10 +8459,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C81" s="26">
         <v>1</v>
@@ -7092,10 +8476,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C82" s="26">
         <v>2</v>
@@ -7109,10 +8493,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C83" s="26">
         <v>1</v>
@@ -7126,10 +8510,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C84" s="26">
         <v>2</v>
@@ -7143,10 +8527,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C85" s="26">
         <v>1</v>
@@ -7160,10 +8544,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C86" s="26">
         <v>2</v>
@@ -7177,10 +8561,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C87" s="26">
         <v>1</v>
@@ -7194,10 +8578,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C88" s="26">
         <v>2</v>
@@ -7211,10 +8595,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C89" s="26">
         <v>1</v>
@@ -7228,10 +8612,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C90" s="26">
         <v>2</v>
@@ -7245,10 +8629,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C91" s="26">
         <v>1</v>
@@ -7262,10 +8646,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C92" s="26">
         <v>2</v>
@@ -7279,10 +8663,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C93" s="26">
         <v>1</v>
@@ -7296,10 +8680,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C94" s="26">
         <v>2</v>
@@ -7313,10 +8697,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C95" s="26">
         <v>1</v>
@@ -7333,10 +8717,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="C96" s="26">
         <v>2</v>
@@ -7353,10 +8737,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="C97" s="26">
         <v>1</v>
@@ -7373,10 +8757,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>491</v>
+        <v>457</v>
       </c>
       <c r="C98" s="26">
         <v>2</v>
@@ -7393,10 +8777,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C99" s="26">
         <v>1</v>
@@ -7413,10 +8797,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="C100" s="26">
         <v>2</v>
@@ -7433,10 +8817,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C101" s="26">
         <v>1</v>
@@ -7453,10 +8837,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="C102" s="26">
         <v>2</v>
@@ -7473,10 +8857,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C103" s="26">
         <v>1</v>
@@ -7493,10 +8877,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="C104" s="26">
         <v>2</v>
@@ -7513,10 +8897,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C105" s="26">
         <v>1</v>
@@ -7533,10 +8917,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
       <c r="C106" s="26">
         <v>2</v>
@@ -7553,10 +8937,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C107" s="26">
         <v>1</v>
@@ -7573,10 +8957,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
       <c r="C108" s="26">
         <v>2</v>
@@ -7593,10 +8977,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C109" s="26">
         <v>1</v>
@@ -7613,10 +8997,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="C110" s="26">
         <v>2</v>
@@ -7633,10 +9017,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C111" s="26">
         <v>1</v>
@@ -7653,10 +9037,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="C112" s="26">
         <v>2</v>
@@ -7673,10 +9057,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C113" s="26">
         <v>1</v>
@@ -7693,10 +9077,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C114" s="26">
         <v>2</v>
@@ -7713,10 +9097,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C115" s="26">
         <v>1</v>
@@ -7733,10 +9117,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="C116" s="26">
         <v>2</v>
@@ -7753,10 +9137,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C117" s="26">
         <v>1</v>
@@ -7773,10 +9157,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C118" s="26">
         <v>2</v>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619E4047-4440-425B-8060-E12B6404FF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C71317D-A012-4542-B68B-2298DF4591B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20745" yWindow="3765" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="598">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2132,6 +2132,74 @@
   </si>
   <si>
     <t>Gongming</t>
+  </si>
+  <si>
+    <t>ZhaoYun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_SCREEN_HERO_TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_CASTLE_TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_GACHA_TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_TIMELOOP_TITLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_SCREEN_HERO_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_CASTLE_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_GACHA_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPGRADE_GUIDE_TIMELOOP_DESC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영지 방문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연회 열기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간 되돌리기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장수 강화 하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>승급 / 강화 / 유물강화 / 보물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 초기화 / 시간석 획득</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영혼석 획득 / 장수모집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재화 획득 / 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2390,7 +2458,7 @@
       <sheetName val="EnemyStatData"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="A3" t="str">
@@ -2429,7 +2497,7 @@
             <v>조운</v>
           </cell>
           <cell r="B7" t="str">
-            <v>ZhaYun</v>
+            <v>ZhaoYun</v>
           </cell>
         </row>
         <row r="8">
@@ -2561,8 +2629,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2900,10 +2968,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="38.125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3373,6 +3441,70 @@
       </c>
       <c r="C55" t="s">
         <v>331</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>582</v>
+      </c>
+      <c r="B56" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>583</v>
+      </c>
+      <c r="B57" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>584</v>
+      </c>
+      <c r="B58" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>585</v>
+      </c>
+      <c r="B59" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>586</v>
+      </c>
+      <c r="B60" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>587</v>
+      </c>
+      <c r="B61" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>588</v>
+      </c>
+      <c r="B62" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>589</v>
+      </c>
+      <c r="B63" t="s">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -3713,7 +3845,7 @@
         <v>516</v>
       </c>
       <c r="D9" t="str">
-        <f>UPPER(A9)&amp;"_"&amp;UPPER(C9)&amp;"_"&amp;UPPER(B9)</f>
+        <f t="shared" ref="D9:D48" si="0">UPPER(A9)&amp;"_"&amp;UPPER(C9)&amp;"_"&amp;UPPER(B9)</f>
         <v>COURTESY_ETC_LUBU</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -3734,7 +3866,7 @@
         <v>513</v>
       </c>
       <c r="D10" t="str">
-        <f>UPPER(A10)&amp;"_"&amp;UPPER(C10)&amp;"_"&amp;UPPER(B10)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_SHU_GUANYU</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -3755,7 +3887,7 @@
         <v>513</v>
       </c>
       <c r="D11" t="str">
-        <f>UPPER(A11)&amp;"_"&amp;UPPER(C11)&amp;"_"&amp;UPPER(B11)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_SHU_HUANGZHONG</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -3776,7 +3908,7 @@
         <v>513</v>
       </c>
       <c r="D12" t="str">
-        <f>UPPER(A12)&amp;"_"&amp;UPPER(C12)&amp;"_"&amp;UPPER(B12)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_SHU_LIUBEI</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -3797,7 +3929,7 @@
         <v>513</v>
       </c>
       <c r="D13" t="str">
-        <f>UPPER(A13)&amp;"_"&amp;UPPER(C13)&amp;"_"&amp;UPPER(B13)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_SHU_ZHANGFEI</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -3812,14 +3944,14 @@
         <v>546</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>581</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>513</v>
       </c>
       <c r="D14" t="str">
-        <f>UPPER(A14)&amp;"_"&amp;UPPER(C14)&amp;"_"&amp;UPPER(B14)</f>
-        <v>COURTESY_SHU_ZHAYUN</v>
+        <f t="shared" si="0"/>
+        <v>COURTESY_SHU_ZHAOYUN</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>34</v>
@@ -3839,7 +3971,7 @@
         <v>513</v>
       </c>
       <c r="D15" t="str">
-        <f>UPPER(A15)&amp;"_"&amp;UPPER(C15)&amp;"_"&amp;UPPER(B15)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_SHU_ZHUGELIANG</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -3860,7 +3992,7 @@
         <v>514</v>
       </c>
       <c r="D16" t="str">
-        <f>UPPER(A16)&amp;"_"&amp;UPPER(C16)&amp;"_"&amp;UPPER(B16)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_CAOCAO</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -3881,7 +4013,7 @@
         <v>514</v>
       </c>
       <c r="D17" t="str">
-        <f>UPPER(A17)&amp;"_"&amp;UPPER(C17)&amp;"_"&amp;UPPER(B17)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_CAOREN</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -3902,7 +4034,7 @@
         <v>514</v>
       </c>
       <c r="D18" t="str">
-        <f>UPPER(A18)&amp;"_"&amp;UPPER(C18)&amp;"_"&amp;UPPER(B18)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUDUN</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -3923,7 +4055,7 @@
         <v>514</v>
       </c>
       <c r="D19" t="str">
-        <f>UPPER(A19)&amp;"_"&amp;UPPER(C19)&amp;"_"&amp;UPPER(B19)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -3944,7 +4076,7 @@
         <v>514</v>
       </c>
       <c r="D20" t="str">
-        <f>UPPER(A20)&amp;"_"&amp;UPPER(C20)&amp;"_"&amp;UPPER(B20)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_XUNYU</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -3965,7 +4097,7 @@
         <v>514</v>
       </c>
       <c r="D21" t="str">
-        <f>UPPER(A21)&amp;"_"&amp;UPPER(C21)&amp;"_"&amp;UPPER(B21)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WEI_ZHANGLIAO</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -3986,7 +4118,7 @@
         <v>515</v>
       </c>
       <c r="D22" t="str">
-        <f>UPPER(A22)&amp;"_"&amp;UPPER(C22)&amp;"_"&amp;UPPER(B22)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_HANDANG</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -4007,7 +4139,7 @@
         <v>515</v>
       </c>
       <c r="D23" t="str">
-        <f>UPPER(A23)&amp;"_"&amp;UPPER(C23)&amp;"_"&amp;UPPER(B23)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_HUANGGAI</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4028,7 +4160,7 @@
         <v>515</v>
       </c>
       <c r="D24" t="str">
-        <f>UPPER(A24)&amp;"_"&amp;UPPER(C24)&amp;"_"&amp;UPPER(B24)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNCE</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -4049,7 +4181,7 @@
         <v>515</v>
       </c>
       <c r="D25" t="str">
-        <f>UPPER(A25)&amp;"_"&amp;UPPER(C25)&amp;"_"&amp;UPPER(B25)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNJIAN</v>
       </c>
       <c r="E25" s="3" t="s">
@@ -4070,7 +4202,7 @@
         <v>515</v>
       </c>
       <c r="D26" t="str">
-        <f>UPPER(A26)&amp;"_"&amp;UPPER(C26)&amp;"_"&amp;UPPER(B26)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNQUAN</v>
       </c>
       <c r="E26" s="3" t="s">
@@ -4091,7 +4223,7 @@
         <v>515</v>
       </c>
       <c r="D27" t="str">
-        <f>UPPER(A27)&amp;"_"&amp;UPPER(C27)&amp;"_"&amp;UPPER(B27)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_TAISHICI</v>
       </c>
       <c r="E27" s="3" t="s">
@@ -4112,7 +4244,7 @@
         <v>515</v>
       </c>
       <c r="D28" t="str">
-        <f>UPPER(A28)&amp;"_"&amp;UPPER(C28)&amp;"_"&amp;UPPER(B28)</f>
+        <f t="shared" si="0"/>
         <v>COURTESY_WU_ZHOUYU</v>
       </c>
       <c r="E28" s="3" t="s">
@@ -4133,7 +4265,7 @@
         <v>516</v>
       </c>
       <c r="D29" t="str">
-        <f>UPPER(A29)&amp;"_"&amp;UPPER(C29)&amp;"_"&amp;UPPER(B29)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_ETC_LUBU</v>
       </c>
       <c r="E29" s="3" t="s">
@@ -4151,7 +4283,7 @@
         <v>513</v>
       </c>
       <c r="D30" t="str">
-        <f>UPPER(A30)&amp;"_"&amp;UPPER(C30)&amp;"_"&amp;UPPER(B30)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_GUANYU</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -4169,7 +4301,7 @@
         <v>513</v>
       </c>
       <c r="D31" t="str">
-        <f>UPPER(A31)&amp;"_"&amp;UPPER(C31)&amp;"_"&amp;UPPER(B31)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_LIUBEI</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -4187,7 +4319,7 @@
         <v>513</v>
       </c>
       <c r="D32" t="str">
-        <f>UPPER(A32)&amp;"_"&amp;UPPER(C32)&amp;"_"&amp;UPPER(B32)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_ZHANGFEI</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -4199,14 +4331,14 @@
         <v>531</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>13</v>
+        <v>581</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>513</v>
       </c>
       <c r="D33" t="str">
-        <f>UPPER(A33)&amp;"_"&amp;UPPER(C33)&amp;"_"&amp;UPPER(B33)</f>
-        <v>DESC_TALK_SHU_ZHAYUN</v>
+        <f t="shared" si="0"/>
+        <v>DESC_TALK_SHU_ZHAOYUN</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>85</v>
@@ -4223,7 +4355,7 @@
         <v>513</v>
       </c>
       <c r="D34" t="str">
-        <f>UPPER(A34)&amp;"_"&amp;UPPER(C34)&amp;"_"&amp;UPPER(B34)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_ZHUGELIANG</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -4241,7 +4373,7 @@
         <v>513</v>
       </c>
       <c r="D35" t="str">
-        <f>UPPER(A35)&amp;"_"&amp;UPPER(C35)&amp;"_"&amp;UPPER(B35)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_HUANGZHONG</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -4259,7 +4391,7 @@
         <v>514</v>
       </c>
       <c r="D36" t="str">
-        <f>UPPER(A36)&amp;"_"&amp;UPPER(C36)&amp;"_"&amp;UPPER(B36)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOCAO</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -4277,7 +4409,7 @@
         <v>514</v>
       </c>
       <c r="D37" t="str">
-        <f>UPPER(A37)&amp;"_"&amp;UPPER(C37)&amp;"_"&amp;UPPER(B37)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOREN</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -4295,7 +4427,7 @@
         <v>514</v>
       </c>
       <c r="D38" t="str">
-        <f>UPPER(A38)&amp;"_"&amp;UPPER(C38)&amp;"_"&amp;UPPER(B38)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUDUN</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -4313,7 +4445,7 @@
         <v>514</v>
       </c>
       <c r="D39" t="str">
-        <f>UPPER(A39)&amp;"_"&amp;UPPER(C39)&amp;"_"&amp;UPPER(B39)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -4331,7 +4463,7 @@
         <v>514</v>
       </c>
       <c r="D40" t="str">
-        <f>UPPER(A40)&amp;"_"&amp;UPPER(C40)&amp;"_"&amp;UPPER(B40)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XUNYU</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -4349,7 +4481,7 @@
         <v>514</v>
       </c>
       <c r="D41" t="str">
-        <f>UPPER(A41)&amp;"_"&amp;UPPER(C41)&amp;"_"&amp;UPPER(B41)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_ZHANGLIAO</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -4370,7 +4502,7 @@
         <v>515</v>
       </c>
       <c r="D42" t="str">
-        <f>UPPER(A42)&amp;"_"&amp;UPPER(C42)&amp;"_"&amp;UPPER(B42)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HANDANG</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -4391,7 +4523,7 @@
         <v>515</v>
       </c>
       <c r="D43" t="str">
-        <f>UPPER(A43)&amp;"_"&amp;UPPER(C43)&amp;"_"&amp;UPPER(B43)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HUANGGAI</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -4412,7 +4544,7 @@
         <v>515</v>
       </c>
       <c r="D44" t="str">
-        <f>UPPER(A44)&amp;"_"&amp;UPPER(C44)&amp;"_"&amp;UPPER(B44)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNCE</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -4433,7 +4565,7 @@
         <v>515</v>
       </c>
       <c r="D45" t="str">
-        <f>UPPER(A45)&amp;"_"&amp;UPPER(C45)&amp;"_"&amp;UPPER(B45)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNJIAN</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -4454,7 +4586,7 @@
         <v>515</v>
       </c>
       <c r="D46" t="str">
-        <f>UPPER(A46)&amp;"_"&amp;UPPER(C46)&amp;"_"&amp;UPPER(B46)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNQUAN</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -4475,7 +4607,7 @@
         <v>515</v>
       </c>
       <c r="D47" t="str">
-        <f>UPPER(A47)&amp;"_"&amp;UPPER(C47)&amp;"_"&amp;UPPER(B47)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_TAISHICI</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -4496,7 +4628,7 @@
         <v>515</v>
       </c>
       <c r="D48" t="str">
-        <f>UPPER(A48)&amp;"_"&amp;UPPER(C48)&amp;"_"&amp;UPPER(B48)</f>
+        <f t="shared" si="0"/>
         <v>DESC_TALK_WU_ZHOUYU</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -4649,7 +4781,7 @@
         <v>516</v>
       </c>
       <c r="D61" t="str">
-        <f>UPPER(A61)&amp;"_"&amp;UPPER(C61)&amp;"_"&amp;UPPER(B61)</f>
+        <f t="shared" ref="D61:D80" si="1">UPPER(A61)&amp;"_"&amp;UPPER(C61)&amp;"_"&amp;UPPER(B61)</f>
         <v>NAME_ETC_LUBU</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -4667,7 +4799,7 @@
         <v>513</v>
       </c>
       <c r="D62" t="str">
-        <f>UPPER(A62)&amp;"_"&amp;UPPER(C62)&amp;"_"&amp;UPPER(B62)</f>
+        <f t="shared" si="1"/>
         <v>NAME_SHU_GUANYU</v>
       </c>
       <c r="E62" s="3" t="s">
@@ -4685,7 +4817,7 @@
         <v>513</v>
       </c>
       <c r="D63" t="str">
-        <f>UPPER(A63)&amp;"_"&amp;UPPER(C63)&amp;"_"&amp;UPPER(B63)</f>
+        <f t="shared" si="1"/>
         <v>NAME_SHU_HUANGZHONG</v>
       </c>
       <c r="E63" s="3" t="s">
@@ -4703,7 +4835,7 @@
         <v>513</v>
       </c>
       <c r="D64" t="str">
-        <f>UPPER(A64)&amp;"_"&amp;UPPER(C64)&amp;"_"&amp;UPPER(B64)</f>
+        <f t="shared" si="1"/>
         <v>NAME_SHU_LIUBEI</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -4721,7 +4853,7 @@
         <v>513</v>
       </c>
       <c r="D65" t="str">
-        <f>UPPER(A65)&amp;"_"&amp;UPPER(C65)&amp;"_"&amp;UPPER(B65)</f>
+        <f t="shared" si="1"/>
         <v>NAME_SHU_ZHANGFEI</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -4733,14 +4865,14 @@
         <v>518</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>581</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>513</v>
       </c>
       <c r="D66" t="str">
-        <f>UPPER(A66)&amp;"_"&amp;UPPER(C66)&amp;"_"&amp;UPPER(B66)</f>
-        <v>NAME_SHU_ZHAYUN</v>
+        <f t="shared" si="1"/>
+        <v>NAME_SHU_ZHAOYUN</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>11</v>
@@ -4757,7 +4889,7 @@
         <v>513</v>
       </c>
       <c r="D67" t="str">
-        <f>UPPER(A67)&amp;"_"&amp;UPPER(C67)&amp;"_"&amp;UPPER(B67)</f>
+        <f t="shared" si="1"/>
         <v>NAME_SHU_ZHUGELIANG</v>
       </c>
       <c r="E67" s="3" t="s">
@@ -4775,7 +4907,7 @@
         <v>514</v>
       </c>
       <c r="D68" t="str">
-        <f>UPPER(A68)&amp;"_"&amp;UPPER(C68)&amp;"_"&amp;UPPER(B68)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_CAOCAO</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -4793,7 +4925,7 @@
         <v>514</v>
       </c>
       <c r="D69" t="str">
-        <f>UPPER(A69)&amp;"_"&amp;UPPER(C69)&amp;"_"&amp;UPPER(B69)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_CAOREN</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -4811,7 +4943,7 @@
         <v>514</v>
       </c>
       <c r="D70" t="str">
-        <f>UPPER(A70)&amp;"_"&amp;UPPER(C70)&amp;"_"&amp;UPPER(B70)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUDUN</v>
       </c>
       <c r="E70" s="3" t="s">
@@ -4829,7 +4961,7 @@
         <v>514</v>
       </c>
       <c r="D71" t="str">
-        <f>UPPER(A71)&amp;"_"&amp;UPPER(C71)&amp;"_"&amp;UPPER(B71)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E71" s="3" t="s">
@@ -4847,7 +4979,7 @@
         <v>514</v>
       </c>
       <c r="D72" t="str">
-        <f>UPPER(A72)&amp;"_"&amp;UPPER(C72)&amp;"_"&amp;UPPER(B72)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_XUNYU</v>
       </c>
       <c r="E72" s="3" t="s">
@@ -4865,7 +4997,7 @@
         <v>514</v>
       </c>
       <c r="D73" t="str">
-        <f>UPPER(A73)&amp;"_"&amp;UPPER(C73)&amp;"_"&amp;UPPER(B73)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WEI_ZHANGLIAO</v>
       </c>
       <c r="E73" s="3" t="s">
@@ -4883,7 +5015,7 @@
         <v>515</v>
       </c>
       <c r="D74" t="str">
-        <f>UPPER(A74)&amp;"_"&amp;UPPER(C74)&amp;"_"&amp;UPPER(B74)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_HANDANG</v>
       </c>
       <c r="E74" t="s">
@@ -4901,7 +5033,7 @@
         <v>515</v>
       </c>
       <c r="D75" t="str">
-        <f>UPPER(A75)&amp;"_"&amp;UPPER(C75)&amp;"_"&amp;UPPER(B75)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_HUANGGAI</v>
       </c>
       <c r="E75" t="s">
@@ -4919,7 +5051,7 @@
         <v>515</v>
       </c>
       <c r="D76" t="str">
-        <f>UPPER(A76)&amp;"_"&amp;UPPER(C76)&amp;"_"&amp;UPPER(B76)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_SUNCE</v>
       </c>
       <c r="E76" t="s">
@@ -4937,7 +5069,7 @@
         <v>515</v>
       </c>
       <c r="D77" t="str">
-        <f>UPPER(A77)&amp;"_"&amp;UPPER(C77)&amp;"_"&amp;UPPER(B77)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_SUNJIAN</v>
       </c>
       <c r="E77" t="s">
@@ -4955,7 +5087,7 @@
         <v>515</v>
       </c>
       <c r="D78" t="str">
-        <f>UPPER(A78)&amp;"_"&amp;UPPER(C78)&amp;"_"&amp;UPPER(B78)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_SUNQUAN</v>
       </c>
       <c r="E78" t="s">
@@ -4973,7 +5105,7 @@
         <v>515</v>
       </c>
       <c r="D79" t="str">
-        <f>UPPER(A79)&amp;"_"&amp;UPPER(C79)&amp;"_"&amp;UPPER(B79)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_TAISHICI</v>
       </c>
       <c r="E79" t="s">
@@ -4991,7 +5123,7 @@
         <v>515</v>
       </c>
       <c r="D80" t="str">
-        <f>UPPER(A80)&amp;"_"&amp;UPPER(C80)&amp;"_"&amp;UPPER(B80)</f>
+        <f t="shared" si="1"/>
         <v>NAME_WU_ZHOUYU</v>
       </c>
       <c r="E80" t="s">

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C71317D-A012-4542-B68B-2298DF4591B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF4295C-D5DB-4D51-855E-7C7DE5B65A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20745" yWindow="3765" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="619">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1407,9 +1407,6 @@
     <t>담보가 된 옥</t>
   </si>
   <si>
-    <t>강동의 미주랑</t>
-  </si>
-  <si>
     <t>칠척극</t>
   </si>
   <si>
@@ -1470,9 +1467,6 @@
     <t>화용도의 갈림길</t>
   </si>
   <si>
-    <t>백발의 명궁</t>
-  </si>
-  <si>
     <t>의의 갈림길 2</t>
   </si>
   <si>
@@ -1499,10 +1493,6 @@
   </si>
   <si>
     <t>CHOICE_DESC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REGION_NAME_FULL_ALL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2199,6 +2189,97 @@
   </si>
   <si>
     <t>재화 획득 / 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도원결의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>간웅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"오랜 친우들과 첫 발을 내딛다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"술잔 아래 의리를 다지다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강동의 호랑이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"맹장을 이끌고 천하로 포효하다"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"의와 의의 충돌"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노익장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"세월을 거스른 백발의 활시위"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미주랑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_30a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_30b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>node_30c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>CLASS</t>
+  </si>
+  <si>
+    <t>GRADE</t>
+  </si>
+  <si>
+    <t>LEVEL</t>
+  </si>
+  <si>
+    <t>POWER</t>
+  </si>
+  <si>
+    <t>국가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역할</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAB_ALL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2968,548 +3049,614 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="40.875" customWidth="1"/>
+    <col min="2" max="2" width="38.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>117</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>148</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>152</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>149</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>151</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>150</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>146</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
         <v>138</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="17" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="C25" s="17" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="17" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="C27" s="17" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>79</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>185</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>105</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
         <v>184</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>111</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
         <v>186</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
         <v>198</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>408</v>
-      </c>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
         <v>301</v>
       </c>
+      <c r="C41" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
         <v>299</v>
       </c>
+      <c r="C42" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
         <v>298</v>
       </c>
+      <c r="C43" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
         <v>300</v>
       </c>
+      <c r="C44" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
         <v>197</v>
       </c>
+      <c r="C45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
         <v>195</v>
       </c>
+      <c r="C46" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+      <c r="C47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>196</v>
-      </c>
-      <c r="B48" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+      <c r="B48" t="str">
+        <f>"SORTTYPE_"&amp;A48</f>
+        <v>SORTTYPE_CLASS</v>
+      </c>
+      <c r="C48" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>610</v>
+      </c>
+      <c r="B49" t="str">
+        <f>"SORTTYPE_"&amp;A49</f>
+        <v>SORTTYPE_GRADE</v>
+      </c>
+      <c r="C49" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>611</v>
+      </c>
+      <c r="B50" t="str">
+        <f>"SORTTYPE_"&amp;A50</f>
+        <v>SORTTYPE_LEVEL</v>
+      </c>
+      <c r="C50" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>612</v>
+      </c>
+      <c r="B51" t="str">
+        <f>"SORTTYPE_"&amp;A51</f>
+        <v>SORTTYPE_POWER</v>
+      </c>
+      <c r="C51" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>608</v>
+      </c>
+      <c r="B52" t="str">
+        <f>"SORTTYPE_"&amp;A52</f>
+        <v>SORTTYPE_REGION</v>
+      </c>
+      <c r="C52" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>618</v>
+      </c>
+      <c r="C53" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>584</v>
+      </c>
+      <c r="C54" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>580</v>
+      </c>
+      <c r="C55" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>585</v>
+      </c>
+      <c r="C56" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>581</v>
+      </c>
+      <c r="C57" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>583</v>
+      </c>
+      <c r="C58" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>579</v>
+      </c>
+      <c r="C59" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>586</v>
+      </c>
+      <c r="C60" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>582</v>
+      </c>
+      <c r="C61" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
         <v>320</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C62" t="s">
         <v>326</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D62" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
         <v>316</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C63" t="s">
         <v>315</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D63" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
         <v>321</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C64" t="s">
         <v>327</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D64" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
         <v>322</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C65" t="s">
         <v>328</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D65" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
         <v>319</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C66" t="s">
         <v>325</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D66" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
         <v>317</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C67" t="s">
         <v>323</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D67" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
         <v>318</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C68" t="s">
         <v>324</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D68" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>582</v>
-      </c>
-      <c r="B56" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>583</v>
-      </c>
-      <c r="B57" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>584</v>
-      </c>
-      <c r="B58" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>585</v>
-      </c>
-      <c r="B59" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>586</v>
-      </c>
-      <c r="B60" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>587</v>
-      </c>
-      <c r="B61" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>588</v>
-      </c>
-      <c r="B62" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>589</v>
-      </c>
-      <c r="B63" t="s">
-        <v>595</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C54">
-    <sortCondition ref="A2:A54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
+    <sortCondition ref="B3:B68"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3726,13 +3873,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -3836,13 +3983,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" ref="D9:D48" si="0">UPPER(A9)&amp;"_"&amp;UPPER(C9)&amp;"_"&amp;UPPER(B9)</f>
@@ -3852,18 +3999,18 @@
         <v>293</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
@@ -3873,39 +4020,39 @@
         <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_SHU_HUANGZHONG</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
@@ -3915,18 +4062,18 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -3936,18 +4083,18 @@
         <v>33</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -3957,18 +4104,18 @@
         <v>34</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -3978,291 +4125,291 @@
         <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_CAOCAO</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F16" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B17" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>COURTESY_WEI_CAOREN</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="B17" t="s">
-        <v>485</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D17" t="str">
-        <f t="shared" si="0"/>
-        <v>COURTESY_WEI_CAOREN</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>549</v>
-      </c>
       <c r="F17" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUDUN</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B19" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XUNYU</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B21" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_ZHANGLIAO</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B22" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_HANDANG</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F22" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_HUANGGAI</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F23" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B24" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D24" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNCE</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F24" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B25" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNJIAN</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F25" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B26" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNQUAN</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F26" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_TAISHICI</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F27" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B28" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_ZHOUYU</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F28" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
@@ -4274,13 +4421,13 @@
     </row>
     <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
@@ -4292,13 +4439,13 @@
     </row>
     <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="0"/>
@@ -4310,13 +4457,13 @@
     </row>
     <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="0"/>
@@ -4328,13 +4475,13 @@
     </row>
     <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D33" t="str">
         <f t="shared" si="0"/>
@@ -4346,13 +4493,13 @@
     </row>
     <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D34" t="str">
         <f t="shared" si="0"/>
@@ -4364,128 +4511,128 @@
     </row>
     <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B35" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D35" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_HUANGZHONG</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B36" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D36" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOCAO</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B37" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D37" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOREN</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B38" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUDUN</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B39" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D39" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>528</v>
+      </c>
+      <c r="B40" t="s">
+        <v>486</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>DESC_TALK_WEI_XUNYU</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="B40" t="s">
-        <v>489</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D40" t="str">
-        <f t="shared" si="0"/>
-        <v>DESC_TALK_WEI_XUNYU</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B41" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_ZHANGLIAO</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>292</v>
@@ -4493,20 +4640,20 @@
     </row>
     <row r="42" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B42" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HANDANG</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>8</v>
@@ -4514,41 +4661,41 @@
     </row>
     <row r="43" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B43" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HUANGGAI</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F43" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B44" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNCE</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>6</v>
@@ -4556,20 +4703,20 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B45" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNJIAN</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>10</v>
@@ -4577,20 +4724,20 @@
     </row>
     <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B46" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNQUAN</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>13</v>
@@ -4598,20 +4745,20 @@
     </row>
     <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B47" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D47" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_TAISHICI</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>14</v>
@@ -4619,166 +4766,166 @@
     </row>
     <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B48" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_ZHOUYU</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F48" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>304</v>
       </c>
       <c r="F49" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>310</v>
       </c>
       <c r="F50" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F51" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>314</v>
       </c>
       <c r="F52" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>303</v>
       </c>
       <c r="F53" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>309</v>
       </c>
       <c r="F54" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>308</v>
       </c>
       <c r="F55" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>313</v>
       </c>
       <c r="F56" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>305</v>
       </c>
       <c r="F57" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>311</v>
       </c>
       <c r="F58" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F59" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>312</v>
       </c>
       <c r="F60" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" ref="D61:D80" si="1">UPPER(A61)&amp;"_"&amp;UPPER(C61)&amp;"_"&amp;UPPER(B61)</f>
@@ -4790,13 +4937,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="1"/>
@@ -4808,31 +4955,31 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="1"/>
         <v>NAME_SHU_HUANGZHONG</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="1"/>
@@ -4844,13 +4991,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" si="1"/>
@@ -4862,13 +5009,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="1"/>
@@ -4880,13 +5027,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D67" t="str">
         <f t="shared" si="1"/>
@@ -4898,236 +5045,236 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B68" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D68" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_CAOCAO</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B69" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D69" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_CAOREN</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D70" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUDUN</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D71" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D72" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XUNYU</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D73" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_ZHANGLIAO</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B74" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D74" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_HANDANG</v>
       </c>
       <c r="E74" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D75" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_HUANGGAI</v>
       </c>
       <c r="E75" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B76" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D76" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNCE</v>
       </c>
       <c r="E76" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D77" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNJIAN</v>
       </c>
       <c r="E77" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B78" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D78" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNQUAN</v>
       </c>
       <c r="E78" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D79" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_TAISHICI</v>
       </c>
       <c r="E79" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D80" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_ZHOUYU</v>
       </c>
       <c r="E80" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="81" spans="4:5" x14ac:dyDescent="0.3">
@@ -6613,7 +6760,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6627,10 +6774,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F34" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -6651,10 +6798,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F35" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -6689,10 +6836,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F37" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -6709,10 +6856,10 @@
         <v>NODE_2_4</v>
       </c>
       <c r="E38" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -6733,10 +6880,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -6757,10 +6904,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F40" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -6798,7 +6945,7 @@
         <v>51</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6819,10 +6966,10 @@
         <v>XiahouDun</v>
       </c>
       <c r="F43" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6843,10 +6990,10 @@
         <v>XiahouYuan</v>
       </c>
       <c r="F44" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -6867,10 +7014,10 @@
         <v>XiahouDun</v>
       </c>
       <c r="F45" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -6894,7 +7041,7 @@
         <v>51</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -6911,10 +7058,10 @@
         <v>NODE_2_13</v>
       </c>
       <c r="E47" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -6935,10 +7082,10 @@
         <v>XiahouYuan</v>
       </c>
       <c r="F48" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -6962,7 +7109,7 @@
         <v>51</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -6997,10 +7144,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F51" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -7021,10 +7168,10 @@
         <v>XiahouDun</v>
       </c>
       <c r="F52" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -7048,7 +7195,7 @@
         <v>51</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -7069,10 +7216,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F54" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -7093,10 +7240,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F55" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -7120,7 +7267,7 @@
         <v>51</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -7141,10 +7288,10 @@
         <v>CaoRen</v>
       </c>
       <c r="F57" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -7156,7 +7303,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC39210-5BFC-4779-981A-9157C4AD45DB}">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -7168,13 +7315,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -7186,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7214,7 +7361,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>336</v>
@@ -7231,7 +7378,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>337</v>
@@ -7248,7 +7395,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>338</v>
@@ -7265,7 +7412,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>339</v>
@@ -7282,7 +7429,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>340</v>
@@ -7299,7 +7446,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>341</v>
@@ -7316,7 +7463,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>342</v>
@@ -7333,7 +7480,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>343</v>
@@ -7350,7 +7497,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>344</v>
@@ -7361,13 +7508,13 @@
         <v>NODE_9_TITLE</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>378</v>
+        <v>604</v>
       </c>
       <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>345</v>
@@ -7378,13 +7525,13 @@
         <v>NODE_10_TITLE</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>346</v>
@@ -7395,13 +7542,13 @@
         <v>NODE_11_TITLE</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>347</v>
@@ -7412,13 +7559,13 @@
         <v>NODE_12A_TITLE</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>348</v>
@@ -7429,13 +7576,13 @@
         <v>NODE_12B_TITLE</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>349</v>
@@ -7446,13 +7593,13 @@
         <v>NODE_13_TITLE</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>350</v>
@@ -7463,13 +7610,13 @@
         <v>NODE_14_TITLE</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>351</v>
@@ -7480,13 +7627,13 @@
         <v>NODE_15_TITLE</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>352</v>
@@ -7497,13 +7644,13 @@
         <v>NODE_16_TITLE</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>353</v>
@@ -7514,13 +7661,13 @@
         <v>NODE_17_TITLE</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>354</v>
@@ -7531,13 +7678,13 @@
         <v>NODE_18_TITLE</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>355</v>
@@ -7548,13 +7695,13 @@
         <v>NODE_19A_TITLE</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>356</v>
@@ -7565,13 +7712,13 @@
         <v>NODE_19B_TITLE</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>357</v>
@@ -7582,13 +7729,13 @@
         <v>NODE_20_TITLE</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>358</v>
@@ -7599,13 +7746,13 @@
         <v>NODE_21A_TITLE</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>359</v>
@@ -7616,13 +7763,13 @@
         <v>NODE_21B_TITLE</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>360</v>
@@ -7633,13 +7780,13 @@
         <v>NODE_22_TITLE</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>361</v>
@@ -7650,13 +7797,13 @@
         <v>NODE_23A_TITLE</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>362</v>
@@ -7667,13 +7814,13 @@
         <v>NODE_23B_TITLE</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>363</v>
@@ -7684,13 +7831,13 @@
         <v>NODE_24A_TITLE</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>364</v>
@@ -7701,13 +7848,13 @@
         <v>NODE_24B_TITLE</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>365</v>
@@ -7718,13 +7865,13 @@
         <v>NODE_25_TITLE</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>366</v>
@@ -7735,13 +7882,13 @@
         <v>NODE_26_TITLE</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>399</v>
+        <v>602</v>
       </c>
       <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>367</v>
@@ -7752,13 +7899,13 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>368</v>
@@ -7769,13 +7916,13 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F35" s="24"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>369</v>
@@ -7786,1526 +7933,1628 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="F36" s="21"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="27" t="s">
-        <v>410</v>
-      </c>
       <c r="B37" s="19" t="s">
-        <v>336</v>
+        <v>605</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="20" t="str">
-        <f t="shared" ref="D37:D69" si="2">UPPER(B37)&amp;"_DESC"</f>
-        <v>NODE_1_DESC</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>441</v>
-      </c>
-      <c r="F37" s="21"/>
+        <f t="shared" ref="D37:D39" si="2">UPPER(B37)&amp;"_TITLE"</f>
+        <v>NODE_30A_TITLE</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="F37" s="33"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="27" t="s">
-        <v>410</v>
+      <c r="A38" s="21" t="s">
+        <v>402</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>337</v>
+        <v>606</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_2_DESC</v>
+        <v>NODE_30B_TITLE</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>427</v>
+        <v>595</v>
       </c>
       <c r="F38" s="21"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="27" t="s">
-        <v>410</v>
+      <c r="A39" s="21" t="s">
+        <v>402</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>338</v>
+        <v>607</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>NODE_3_DESC</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>442</v>
+        <v>NODE_30C_TITLE</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>599</v>
       </c>
       <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_4_DESC</v>
-      </c>
-      <c r="E40" s="33" t="s">
-        <v>428</v>
+        <f t="shared" ref="D40:D72" si="3">UPPER(B40)&amp;"_DESC"</f>
+        <v>NODE_1_DESC</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>438</v>
       </c>
       <c r="F40" s="21"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C41" s="19"/>
       <c r="D41" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_5_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_2_DESC</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F41" s="21"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_6_DESC</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>432</v>
+        <f t="shared" si="3"/>
+        <v>NODE_3_DESC</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>439</v>
       </c>
       <c r="F42" s="21"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_7_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_4_DESC</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="F43" s="21"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_8_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_5_DESC</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_9_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_6_DESC</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F45" s="21"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_10_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_7_DESC</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="F46" s="21"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C47" s="19"/>
       <c r="D47" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_11_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_8_DESC</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="F47" s="21"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C48" s="19"/>
       <c r="D48" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_12A_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_9_DESC</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="F48" s="21"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C49" s="19"/>
       <c r="D49" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_12B_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_10_DESC</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C50" s="19"/>
       <c r="D50" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_13_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_11_DESC</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="F50" s="21"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C51" s="19"/>
       <c r="D51" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_14_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_12A_DESC</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="F51" s="21"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_15_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_12B_DESC</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F52" s="21"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C53" s="19"/>
       <c r="D53" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_16_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_13_DESC</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F53" s="21"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C54" s="19"/>
       <c r="D54" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_17_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_14_DESC</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="F54" s="21"/>
       <c r="G54" s="35" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_18_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_15_DESC</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F55" s="21"/>
       <c r="G55" s="35" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_19A_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_16_DESC</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="F56" s="21"/>
       <c r="G56" s="35" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C57" s="19"/>
       <c r="D57" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_19B_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_17_DESC</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F57" s="21"/>
       <c r="G57" s="35" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_20_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_18_DESC</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F58" s="21"/>
       <c r="G58" s="35" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C59" s="19"/>
       <c r="D59" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_21A_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_19A_DESC</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="F59" s="21"/>
       <c r="G59" s="35" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C60" s="19"/>
       <c r="D60" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_21B_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_19B_DESC</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="35" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_22_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_20_DESC</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="F61" s="21"/>
       <c r="G61" s="35" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C62" s="19"/>
       <c r="D62" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_23A_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_21A_DESC</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="F62" s="21"/>
       <c r="G62" s="35" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C63" s="19"/>
       <c r="D63" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_23B_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_21B_DESC</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="F63" s="21"/>
       <c r="G63" s="35" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C64" s="19"/>
       <c r="D64" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_24A_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_22_DESC</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F64" s="21"/>
       <c r="G64" s="35" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C65" s="19"/>
       <c r="D65" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_24B_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_23A_DESC</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F65" s="21"/>
       <c r="G65" s="35" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C66" s="19"/>
       <c r="D66" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_25_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_23B_DESC</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="F66" s="21"/>
       <c r="G66" s="35" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_26_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_24A_DESC</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="F67" s="21"/>
       <c r="G67" s="35" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C68" s="19"/>
       <c r="D68" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_27_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_24B_DESC</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F68" s="21"/>
       <c r="G68" s="35" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="27" t="s">
-        <v>410</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="C69" s="22"/>
+        <v>407</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C69" s="19"/>
       <c r="D69" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE_28_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_25_DESC</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>440</v>
-      </c>
-      <c r="F69" s="24"/>
+        <v>601</v>
+      </c>
+      <c r="F69" s="21"/>
       <c r="G69" s="35" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C70" s="19"/>
       <c r="D70" s="20" t="str">
-        <f>UPPER(B70)&amp;"_DESC"</f>
-        <v>NODE_29_DESC</v>
+        <f t="shared" si="3"/>
+        <v>NODE_26_DESC</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>440</v>
+        <v>603</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="35" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B71" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="C71" s="26">
-        <v>1</v>
-      </c>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C71" s="19"/>
       <c r="D71" s="20" t="str">
-        <f t="shared" ref="D71:D93" si="3">UPPER(B71)&amp;"_CHOICE_"&amp;C71</f>
-        <v>NODE_1_CHOICE_1</v>
-      </c>
-      <c r="E71" s="29"/>
+        <f t="shared" si="3"/>
+        <v>NODE_27_DESC</v>
+      </c>
+      <c r="E71" s="33" t="s">
+        <v>437</v>
+      </c>
       <c r="F71" s="21"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B72" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="C72" s="26">
-        <v>2</v>
-      </c>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="C72" s="22"/>
       <c r="D72" s="20" t="str">
         <f t="shared" si="3"/>
-        <v>NODE_1_CHOICE_2</v>
-      </c>
-      <c r="E72" s="29"/>
-      <c r="F72" s="21"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B73" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="C73" s="26">
-        <v>1</v>
-      </c>
+        <v>NODE_28_DESC</v>
+      </c>
+      <c r="E72" s="33" t="s">
+        <v>437</v>
+      </c>
+      <c r="F72" s="24"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="C73" s="19"/>
       <c r="D73" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_5_CHOICE_1</v>
-      </c>
-      <c r="E73" s="29"/>
+        <f>UPPER(B73)&amp;"_DESC"</f>
+        <v>NODE_29_DESC</v>
+      </c>
+      <c r="E73" s="33" t="s">
+        <v>437</v>
+      </c>
       <c r="F73" s="21"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="C74" s="26">
-        <v>2</v>
-      </c>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>605</v>
+      </c>
+      <c r="C74" s="19"/>
       <c r="D74" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_5_CHOICE_2</v>
-      </c>
-      <c r="E74" s="29"/>
-      <c r="F74" s="21"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>341</v>
-      </c>
-      <c r="C75" s="26">
-        <v>1</v>
-      </c>
+        <f t="shared" ref="D74:D75" si="4">UPPER(B74)&amp;"_DESC"</f>
+        <v>NODE_30A_DESC</v>
+      </c>
+      <c r="E74" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="F74" s="33"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="C75" s="22"/>
       <c r="D75" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_6_CHOICE_1</v>
-      </c>
-      <c r="E75" s="29"/>
-      <c r="F75" s="21"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>341</v>
-      </c>
-      <c r="C76" s="26">
-        <v>2</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>NODE_30B_DESC</v>
+      </c>
+      <c r="E75" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="C76" s="19"/>
       <c r="D76" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_6_CHOICE_2</v>
-      </c>
-      <c r="E76" s="29"/>
+        <f>UPPER(B76)&amp;"_DESC"</f>
+        <v>NODE_30C_DESC</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>600</v>
+      </c>
       <c r="F76" s="21"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C77" s="26">
         <v>1</v>
       </c>
       <c r="D77" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_7_CHOICE_1</v>
+        <f t="shared" ref="D77:D99" si="5">UPPER(B77)&amp;"_CHOICE_"&amp;C77</f>
+        <v>NODE_1_CHOICE_1</v>
       </c>
       <c r="E77" s="29"/>
       <c r="F77" s="21"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C78" s="26">
         <v>2</v>
       </c>
       <c r="D78" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_7_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_1_CHOICE_2</v>
       </c>
       <c r="E78" s="29"/>
       <c r="F78" s="21"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C79" s="26">
         <v>1</v>
       </c>
       <c r="D79" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_10_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_5_CHOICE_1</v>
       </c>
       <c r="E79" s="29"/>
       <c r="F79" s="21"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C80" s="26">
         <v>2</v>
       </c>
       <c r="D80" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_10_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_5_CHOICE_2</v>
       </c>
       <c r="E80" s="29"/>
       <c r="F80" s="21"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C81" s="26">
         <v>1</v>
       </c>
       <c r="D81" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_12B_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_6_CHOICE_1</v>
       </c>
       <c r="E81" s="29"/>
       <c r="F81" s="21"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C82" s="26">
         <v>2</v>
       </c>
       <c r="D82" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_12B_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_6_CHOICE_2</v>
       </c>
       <c r="E82" s="29"/>
       <c r="F82" s="21"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C83" s="26">
         <v>1</v>
       </c>
       <c r="D83" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_14_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_7_CHOICE_1</v>
       </c>
       <c r="E83" s="29"/>
       <c r="F83" s="21"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C84" s="26">
         <v>2</v>
       </c>
       <c r="D84" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_14_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_7_CHOICE_2</v>
       </c>
       <c r="E84" s="29"/>
       <c r="F84" s="21"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C85" s="26">
         <v>1</v>
       </c>
       <c r="D85" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_15_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_10_CHOICE_1</v>
       </c>
       <c r="E85" s="29"/>
       <c r="F85" s="21"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C86" s="26">
         <v>2</v>
       </c>
       <c r="D86" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_15_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_10_CHOICE_2</v>
       </c>
       <c r="E86" s="29"/>
       <c r="F86" s="21"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C87" s="26">
         <v>1</v>
       </c>
       <c r="D87" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_16_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_12B_CHOICE_1</v>
       </c>
       <c r="E87" s="29"/>
       <c r="F87" s="21"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C88" s="26">
         <v>2</v>
       </c>
       <c r="D88" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_16_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_12B_CHOICE_2</v>
       </c>
       <c r="E88" s="29"/>
       <c r="F88" s="21"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C89" s="26">
         <v>1</v>
       </c>
       <c r="D89" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_19B_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_14_CHOICE_1</v>
       </c>
       <c r="E89" s="29"/>
       <c r="F89" s="21"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C90" s="26">
         <v>2</v>
       </c>
       <c r="D90" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_19B_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_14_CHOICE_2</v>
       </c>
       <c r="E90" s="29"/>
       <c r="F90" s="21"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C91" s="26">
         <v>1</v>
       </c>
       <c r="D91" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_21B_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_15_CHOICE_1</v>
       </c>
       <c r="E91" s="29"/>
       <c r="F91" s="21"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C92" s="26">
         <v>2</v>
       </c>
       <c r="D92" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_21B_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_15_CHOICE_2</v>
       </c>
       <c r="E92" s="29"/>
       <c r="F92" s="21"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C93" s="26">
         <v>1</v>
       </c>
       <c r="D93" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>NODE_25_CHOICE_1</v>
+        <f t="shared" si="5"/>
+        <v>NODE_16_CHOICE_1</v>
       </c>
       <c r="E93" s="29"/>
       <c r="F93" s="21"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C94" s="26">
         <v>2</v>
       </c>
       <c r="D94" s="20" t="str">
-        <f>UPPER(B94)&amp;"_CHOICE_"&amp;C94</f>
-        <v>NODE_25_CHOICE_2</v>
+        <f t="shared" si="5"/>
+        <v>NODE_16_CHOICE_2</v>
       </c>
       <c r="E94" s="29"/>
       <c r="F94" s="21"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C95" s="26">
         <v>1</v>
       </c>
       <c r="D95" s="20" t="str">
-        <f>UPPER(B95)&amp;"_CHOICE_"&amp;C95&amp;"_DESC"</f>
-        <v>NODE_1_CHOICE_1_DESC</v>
-      </c>
-      <c r="E95" s="29" t="str">
-        <f t="shared" ref="E95:E118" si="4">"선택"&amp;C95</f>
-        <v>선택1</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>NODE_19B_CHOICE_1</v>
+      </c>
+      <c r="E95" s="29"/>
       <c r="F95" s="21"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="C96" s="26">
         <v>2</v>
       </c>
       <c r="D96" s="20" t="str">
-        <f t="shared" ref="D96:D118" si="5">UPPER(B96)&amp;"_CHOICE_"&amp;C96&amp;"_DESC"</f>
-        <v>NODE_1_CHOICE_2_DESC</v>
-      </c>
-      <c r="E96" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>선택2</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v>NODE_19B_CHOICE_2</v>
+      </c>
+      <c r="E96" s="29"/>
       <c r="F96" s="21"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>457</v>
+        <v>359</v>
       </c>
       <c r="C97" s="26">
         <v>1</v>
       </c>
       <c r="D97" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>NODE_5_CHOICE_1_DESC</v>
-      </c>
-      <c r="E97" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>선택1</v>
-      </c>
+        <v>NODE_21B_CHOICE_1</v>
+      </c>
+      <c r="E97" s="29"/>
       <c r="F97" s="21"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>457</v>
+        <v>359</v>
       </c>
       <c r="C98" s="26">
         <v>2</v>
       </c>
       <c r="D98" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>NODE_5_CHOICE_2_DESC</v>
-      </c>
-      <c r="E98" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>선택2</v>
-      </c>
+        <v>NODE_21B_CHOICE_2</v>
+      </c>
+      <c r="E98" s="29"/>
       <c r="F98" s="21"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C99" s="26">
         <v>1</v>
       </c>
       <c r="D99" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>NODE_6_CHOICE_1_DESC</v>
-      </c>
-      <c r="E99" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>선택1</v>
-      </c>
+        <v>NODE_25_CHOICE_1</v>
+      </c>
+      <c r="E99" s="29"/>
       <c r="F99" s="21"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B100" s="25" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C100" s="26">
         <v>2</v>
       </c>
       <c r="D100" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_6_CHOICE_2_DESC</v>
-      </c>
-      <c r="E100" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>선택2</v>
-      </c>
+        <f>UPPER(B100)&amp;"_CHOICE_"&amp;C100</f>
+        <v>NODE_25_CHOICE_2</v>
+      </c>
+      <c r="E100" s="29"/>
       <c r="F100" s="21"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B101" s="25" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C101" s="26">
         <v>1</v>
       </c>
       <c r="D101" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_7_CHOICE_1_DESC</v>
+        <f>UPPER(B101)&amp;"_CHOICE_"&amp;C101&amp;"_DESC"</f>
+        <v>NODE_1_CHOICE_1_DESC</v>
       </c>
       <c r="E101" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E101:E124" si="6">"선택"&amp;C101</f>
         <v>선택1</v>
       </c>
       <c r="F101" s="21"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C102" s="26">
         <v>2</v>
       </c>
       <c r="D102" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_7_CHOICE_2_DESC</v>
+        <f t="shared" ref="D102:D124" si="7">UPPER(B102)&amp;"_CHOICE_"&amp;C102&amp;"_DESC"</f>
+        <v>NODE_1_CHOICE_2_DESC</v>
       </c>
       <c r="E102" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F102" s="21"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>345</v>
+        <v>454</v>
       </c>
       <c r="C103" s="26">
         <v>1</v>
       </c>
       <c r="D103" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_10_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_5_CHOICE_1_DESC</v>
       </c>
       <c r="E103" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F103" s="21"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>345</v>
+        <v>454</v>
       </c>
       <c r="C104" s="26">
         <v>2</v>
       </c>
       <c r="D104" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_10_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_5_CHOICE_2_DESC</v>
       </c>
       <c r="E104" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F104" s="21"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C105" s="26">
         <v>1</v>
       </c>
       <c r="D105" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_12B_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_6_CHOICE_1_DESC</v>
       </c>
       <c r="E105" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F105" s="21"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C106" s="26">
         <v>2</v>
       </c>
       <c r="D106" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_12B_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_6_CHOICE_2_DESC</v>
       </c>
       <c r="E106" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F106" s="21"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C107" s="26">
         <v>1</v>
       </c>
       <c r="D107" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_14_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_7_CHOICE_1_DESC</v>
       </c>
       <c r="E107" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F107" s="21"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C108" s="26">
         <v>2</v>
       </c>
       <c r="D108" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_14_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_7_CHOICE_2_DESC</v>
       </c>
       <c r="E108" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F108" s="21"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C109" s="26">
         <v>1</v>
       </c>
       <c r="D109" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_15_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_10_CHOICE_1_DESC</v>
       </c>
       <c r="E109" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F109" s="21"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C110" s="26">
         <v>2</v>
       </c>
       <c r="D110" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_15_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_10_CHOICE_2_DESC</v>
       </c>
       <c r="E110" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F110" s="21"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C111" s="26">
         <v>1</v>
       </c>
       <c r="D111" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_16_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_12B_CHOICE_1_DESC</v>
       </c>
       <c r="E111" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F111" s="21"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C112" s="26">
         <v>2</v>
       </c>
       <c r="D112" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_16_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_12B_CHOICE_2_DESC</v>
       </c>
       <c r="E112" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C113" s="26">
         <v>1</v>
       </c>
       <c r="D113" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_19B_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_14_CHOICE_1_DESC</v>
       </c>
       <c r="E113" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F113" s="21"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C114" s="26">
         <v>2</v>
       </c>
       <c r="D114" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_19B_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_14_CHOICE_2_DESC</v>
       </c>
       <c r="E114" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F114" s="21"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C115" s="26">
         <v>1</v>
       </c>
       <c r="D115" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_21B_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_15_CHOICE_1_DESC</v>
       </c>
       <c r="E115" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F115" s="21"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C116" s="26">
         <v>2</v>
       </c>
       <c r="D116" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_21B_CHOICE_2_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_15_CHOICE_2_DESC</v>
       </c>
       <c r="E116" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
       <c r="F116" s="21"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C117" s="26">
         <v>1</v>
       </c>
       <c r="D117" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>NODE_25_CHOICE_1_DESC</v>
+        <f t="shared" si="7"/>
+        <v>NODE_16_CHOICE_1_DESC</v>
       </c>
       <c r="E117" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>선택1</v>
       </c>
       <c r="F117" s="21"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C118" s="26">
         <v>2</v>
       </c>
       <c r="D118" s="20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>NODE_16_CHOICE_2_DESC</v>
+      </c>
+      <c r="E118" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택2</v>
+      </c>
+      <c r="F118" s="21"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B119" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C119" s="26">
+        <v>1</v>
+      </c>
+      <c r="D119" s="20" t="str">
+        <f t="shared" si="7"/>
+        <v>NODE_19B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E119" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택1</v>
+      </c>
+      <c r="F119" s="21"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B120" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C120" s="26">
+        <v>2</v>
+      </c>
+      <c r="D120" s="20" t="str">
+        <f t="shared" si="7"/>
+        <v>NODE_19B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E120" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택2</v>
+      </c>
+      <c r="F120" s="21"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B121" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C121" s="26">
+        <v>1</v>
+      </c>
+      <c r="D121" s="20" t="str">
+        <f t="shared" si="7"/>
+        <v>NODE_21B_CHOICE_1_DESC</v>
+      </c>
+      <c r="E121" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택1</v>
+      </c>
+      <c r="F121" s="21"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B122" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C122" s="26">
+        <v>2</v>
+      </c>
+      <c r="D122" s="20" t="str">
+        <f t="shared" si="7"/>
+        <v>NODE_21B_CHOICE_2_DESC</v>
+      </c>
+      <c r="E122" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택2</v>
+      </c>
+      <c r="F122" s="21"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B123" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="C123" s="26">
+        <v>1</v>
+      </c>
+      <c r="D123" s="20" t="str">
+        <f t="shared" si="7"/>
+        <v>NODE_25_CHOICE_1_DESC</v>
+      </c>
+      <c r="E123" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>선택1</v>
+      </c>
+      <c r="F123" s="21"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="B124" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="C124" s="26">
+        <v>2</v>
+      </c>
+      <c r="D124" s="20" t="str">
+        <f t="shared" si="7"/>
         <v>NODE_25_CHOICE_2_DESC</v>
       </c>
-      <c r="E118" s="29" t="str">
-        <f t="shared" si="4"/>
+      <c r="E124" s="29" t="str">
+        <f t="shared" si="6"/>
         <v>선택2</v>
       </c>
-      <c r="F118" s="21"/>
+      <c r="F124" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF4295C-D5DB-4D51-855E-7C7DE5B65A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C74CA8F-BA3D-49E7-BF90-A182C0F2FFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="638">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2172,10 +2172,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장수 강화 하기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>승급 / 강화 / 유물강화 / 보물</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2280,6 +2276,90 @@
   </si>
   <si>
     <t>TAB_ALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장수 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NODE_30A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의용군이라.. 에휴..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사내가 먼 한숨이오?? 한심하기는!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음.. 의용군에게는 뛰어난 지도자가 필요하오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇다면 그대가 지도자가 되면 될 거 아니오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 우리가 도와주겠소이다! 어디 가서 술이나 한잔 합시다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나에게는 그럴 힘이 없소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오오! 복숭아 밭 파티장이라니ㅋ 근사하구만ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>없는 살림에 너무 무리하시는거 아니오?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무슨 소리신지, 이 근방 돗자리는
+모두 내가 납품하고 있소만.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 큰 뜻을 품고 있었구려ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고맙소. 태어난 날은 다르나 
+한날 한시에 죽을 것을 맹세합시다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응?? 그건 좀….</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨거운 맹세! 영원히 변치 않을 것입니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>않을 것입니다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 뜻에 동참하겠소.
+형님으로 모시겠습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한왕실의 재건을 위해 그대들을 
+맞이하는 것이니 그런소리 마시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도자 없는 의용군은 오합지졸일 뿐..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하! 좋소이다! 큰 형님으로 모실테니 큰 뜻을 품어주십시오ㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2539,7 +2619,7 @@
       <sheetName val="EnemyStatData"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="A3" t="str">
@@ -2710,8 +2790,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3447,67 +3527,67 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B48" t="str">
         <f>"SORTTYPE_"&amp;A48</f>
         <v>SORTTYPE_CLASS</v>
       </c>
       <c r="C48" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B49" t="str">
         <f>"SORTTYPE_"&amp;A49</f>
         <v>SORTTYPE_GRADE</v>
       </c>
       <c r="C49" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B50" t="str">
         <f>"SORTTYPE_"&amp;A50</f>
         <v>SORTTYPE_LEVEL</v>
       </c>
       <c r="C50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B51" t="str">
         <f>"SORTTYPE_"&amp;A51</f>
         <v>SORTTYPE_POWER</v>
       </c>
       <c r="C51" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B52" t="str">
         <f>"SORTTYPE_"&amp;A52</f>
         <v>SORTTYPE_REGION</v>
       </c>
       <c r="C52" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C53" t="s">
         <v>406</v>
@@ -3518,7 +3598,7 @@
         <v>584</v>
       </c>
       <c r="C54" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -3534,7 +3614,7 @@
         <v>585</v>
       </c>
       <c r="C56" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -3550,7 +3630,7 @@
         <v>583</v>
       </c>
       <c r="C58" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -3558,7 +3638,7 @@
         <v>579</v>
       </c>
       <c r="C59" t="s">
-        <v>590</v>
+        <v>618</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -3566,7 +3646,7 @@
         <v>586</v>
       </c>
       <c r="C60" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -6019,7 +6099,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -6028,7 +6108,8 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.625" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="50.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="39.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="50.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6385,7 +6466,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -6437,7 +6518,7 @@
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:B57" si="11">B20+1</f>
+        <f t="shared" ref="B21:B78" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
@@ -6605,7 +6686,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" si="10"/>
         <v>1_1_1_SHU_START</v>
@@ -6948,7 +7029,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -6972,7 +7053,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7292,6 +7373,493 @@
       </c>
       <c r="G57" s="3" t="s">
         <v>468</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>619</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" ref="C58" si="19">CONCATENATE(A58, "_", B58, IF(D58&lt;&gt;"", "_"&amp;D58, ""))</f>
+        <v>NODE_30A_0</v>
+      </c>
+      <c r="E58" t="str">
+        <f>VLOOKUP(F58,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F58" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>619</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" ref="C59" si="20">CONCATENATE(A59, "_", B59, IF(D59&lt;&gt;"", "_"&amp;D59, ""))</f>
+        <v>NODE_30A_1</v>
+      </c>
+      <c r="E59" t="str">
+        <f>VLOOKUP(F59,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F59" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>619</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" ref="C60:C78" si="21">CONCATENATE(A60, "_", B60, IF(D60&lt;&gt;"", "_"&amp;D60, ""))</f>
+        <v>NODE_30A_2</v>
+      </c>
+      <c r="E60" t="str">
+        <f>VLOOKUP(F60,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F60" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>619</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_3</v>
+      </c>
+      <c r="E61" t="str">
+        <f>VLOOKUP(F61,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F61" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>619</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_4</v>
+      </c>
+      <c r="E62" t="str">
+        <f>VLOOKUP(F62,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F62" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>619</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_5</v>
+      </c>
+      <c r="E63" t="str">
+        <f>VLOOKUP(F63,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F63" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>619</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_6</v>
+      </c>
+      <c r="E64" t="str">
+        <f>VLOOKUP(F64,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>619</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>619</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_8</v>
+      </c>
+      <c r="E66" t="str">
+        <f>VLOOKUP(F66,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F66" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>619</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_9</v>
+      </c>
+      <c r="E67" t="str">
+        <f>VLOOKUP(F67,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>619</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_10</v>
+      </c>
+      <c r="E68" t="str">
+        <f>VLOOKUP(F68,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F68" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>619</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_11</v>
+      </c>
+      <c r="E69" t="str">
+        <f>VLOOKUP(F69,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F69" t="s">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>619</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_12_1</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70" t="str">
+        <f>VLOOKUP(F70,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F70" t="s">
+        <v>9</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>619</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_13_1</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="str">
+        <f>VLOOKUP(F71,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F71" t="s">
+        <v>7</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>619</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="11"/>
+        <v>14</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_14_2</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72" t="str">
+        <f>VLOOKUP(F72,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F72" t="s">
+        <v>9</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>619</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_15_2</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+      <c r="E73" t="str">
+        <f>VLOOKUP(F73,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F73" t="s">
+        <v>5</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>619</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="11"/>
+        <v>16</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_16_2</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74" t="str">
+        <f>VLOOKUP(F74,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>619</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="11"/>
+        <v>17</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_17</v>
+      </c>
+      <c r="E75" t="str">
+        <f>VLOOKUP(F75,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F75" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>619</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="11"/>
+        <v>18</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_18</v>
+      </c>
+      <c r="E76" t="str">
+        <f>VLOOKUP(F76,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F76" t="s">
+        <v>9</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>619</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="11"/>
+        <v>19</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_19</v>
+      </c>
+      <c r="E77" t="str">
+        <f>VLOOKUP(F77,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F77" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>619</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30A_20</v>
+      </c>
+      <c r="E78" t="str">
+        <f>VLOOKUP(F78,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -7508,7 +8076,7 @@
         <v>NODE_9_TITLE</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -7882,7 +8450,7 @@
         <v>NODE_26_TITLE</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F33" s="21"/>
     </row>
@@ -7942,7 +8510,7 @@
         <v>402</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="20" t="str">
@@ -7950,7 +8518,7 @@
         <v>NODE_30A_TITLE</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F37" s="33"/>
     </row>
@@ -7959,7 +8527,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="20" t="str">
@@ -7967,7 +8535,7 @@
         <v>NODE_30B_TITLE</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F38" s="21"/>
     </row>
@@ -7976,7 +8544,7 @@
         <v>402</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="20" t="str">
@@ -7984,7 +8552,7 @@
         <v>NODE_30C_TITLE</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F39" s="21"/>
     </row>
@@ -8539,7 +9107,7 @@
         <v>NODE_25_DESC</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="35" t="s">
@@ -8559,7 +9127,7 @@
         <v>NODE_26_DESC</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="35" t="s">
@@ -8622,7 +9190,7 @@
         <v>407</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="20" t="str">
@@ -8630,7 +9198,7 @@
         <v>NODE_30A_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F74" s="33"/>
     </row>
@@ -8639,7 +9207,7 @@
         <v>407</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C75" s="22"/>
       <c r="D75" s="20" t="str">
@@ -8647,7 +9215,7 @@
         <v>NODE_30B_DESC</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F75" s="24"/>
     </row>
@@ -8656,7 +9224,7 @@
         <v>407</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="20" t="str">
@@ -8664,7 +9232,7 @@
         <v>NODE_30C_DESC</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F76" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C74CA8F-BA3D-49E7-BF90-A182C0F2FFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F946C760-2A88-4758-B736-4BBD5FFA65F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="642">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1692,26 +1692,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>걱정마라 아만! 내가 있는데 뭐가 걱정인게야 캬캬캬!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하후연</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>형님 때문에 더 걱정입니다. 저번에도 혼자 돌격하시고.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 난세를 헤쳐 나가려면 힘을 키워야 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뒤에서 활이나 쏘는 주제에 말이 많구나ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하하하!! 맹덕 형님! 나 자효가 왔습니다!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1720,14 +1704,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘부로 저와 제 군사는 오직 주공의 명만을 따를 것이니, 부디 천하를 바로잡아 주십시오!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일어나시게ㅋ 이제 곧 큰 싸움이 일어날텐데, 자효 그대의 활약을 기대하겠네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>주공!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1744,14 +1720,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주공! 성 밖에 1000여명 되는 무리들이 이 쪽을 향해 오고 있습니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대장!! 조조님이 드디어 거병하셨답니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>흥! 아직도 도적 떼가 설치다니!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1768,15 +1736,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>좋다!! 우리도 가서 힘을 보태자.\n너희들도 나를 따라오너라!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>호오..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야야 가만히 있지만 말고 니들도 나가서...</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2283,39 +2243,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NODE_30A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>의용군이라.. 에휴..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사내가 먼 한숨이오?? 한심하기는!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>음.. 의용군에게는 뛰어난 지도자가 필요하오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇다면 그대가 지도자가 되면 될 거 아니오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흥! 우리가 도와주겠소이다! 어디 가서 술이나 한잔 합시다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>나에게는 그럴 힘이 없소.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오오! 복숭아 밭 파티장이라니ㅋ 근사하구만ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>없는 살림에 너무 무리하시는거 아니오?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2333,18 +2261,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>응?? 그건 좀….</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>뜨거운 맹세! 영원히 변치 않을 것입니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>않을 것입니다!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그 뜻에 동참하겠소.
 형님으로 모시겠습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2355,11 +2271,133 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지도자 없는 의용군은 오합지졸일 뿐..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하하하! 좋소이다! 큰 형님으로 모실테니 큰 뜻을 품어주십시오ㅋ</t>
+    <t>않을 것이오!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.. 의용군이라.. 에휴..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흠흠.. 나도 함께 가지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NODE_30B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇다면 그대가 지도자가
+되면 될 거 아니오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 내가 도와주겠소이다!
+어디 가서 술이나 한잔 합시다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘부로 저와 제 군사는 오직 주공의 명만을 따를 것이니, 천하를 바로잡아 주십시오!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>형님 때문에 더 걱정입니다.
+저번에도 혼자 돌격하시고.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>걱정마라 아만!
+내가 있는데 뭐가 걱정인게야 캬캬캬!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋다!! 우리도 가서 힘을 보태자.
+너희들도 나를 따라오너라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오오! 복숭아 밭 파티장이라니ㅋ
+근사하구만ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨거운 맹세!
+영원히 변치 않을 것입니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도자 없는 의용군은
+오합지졸일 뿐..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일어나시게ㅋ
+이제 곧 큰 싸움이 일어날텐데,
+자효 그대의 활약을 기대하겠네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주공!
+성 밖에 1000여명 되는 무리들이
+이 쪽을 향해 오고 있습니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤에서 활이나 쏘는 주제에
+말이 많구나ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야야 가만히 있지만 말고,
+니들도 나가서...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 난세를 헤쳐 나가려면
+힘을 키워야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장!!
+조조님이 드디어 거병하셨답니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하아.. 지금 의용군에게는
+뛰어난 지도자가 필요하단 말이오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하! 좋소이다! 형님으로
+모실테니 큰 뜻을 품어주십시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니!! 부자였소?? 그런데 
+왜 그런 거지꼴로 다녔던거요??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>없는 살림에 너무
+무리하시는게 아닐런지..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 내가 좋은 곳을 알고
+있으니, 따라 오시겠오?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사내가 뭔 한숨이오??
+한심하기는!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>응?? 그건 좀..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3527,67 +3565,67 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B48" t="str">
         <f>"SORTTYPE_"&amp;A48</f>
         <v>SORTTYPE_CLASS</v>
       </c>
       <c r="C48" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="B49" t="str">
         <f>"SORTTYPE_"&amp;A49</f>
         <v>SORTTYPE_GRADE</v>
       </c>
       <c r="C49" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B50" t="str">
         <f>"SORTTYPE_"&amp;A50</f>
         <v>SORTTYPE_LEVEL</v>
       </c>
       <c r="C50" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="B51" t="str">
         <f>"SORTTYPE_"&amp;A51</f>
         <v>SORTTYPE_POWER</v>
       </c>
       <c r="C51" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="B52" t="str">
         <f>"SORTTYPE_"&amp;A52</f>
         <v>SORTTYPE_REGION</v>
       </c>
       <c r="C52" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C53" t="s">
         <v>406</v>
@@ -3595,66 +3633,66 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="C54" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="C55" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="C56" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C57" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="C58" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C59" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C60" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C61" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -3953,13 +3991,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -4063,13 +4101,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" ref="D9:D48" si="0">UPPER(A9)&amp;"_"&amp;UPPER(C9)&amp;"_"&amp;UPPER(B9)</f>
@@ -4079,18 +4117,18 @@
         <v>293</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
@@ -4100,39 +4138,39 @@
         <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B11" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_SHU_HUANGZHONG</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
@@ -4142,18 +4180,18 @@
         <v>31</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D13" t="str">
         <f t="shared" si="0"/>
@@ -4163,18 +4201,18 @@
         <v>33</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D14" t="str">
         <f t="shared" si="0"/>
@@ -4184,18 +4222,18 @@
         <v>34</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D15" t="str">
         <f t="shared" si="0"/>
@@ -4205,291 +4243,291 @@
         <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D16" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_CAOCAO</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="F16" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B17" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D17" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_CAOREN</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F17" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B18" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D18" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUDUN</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B19" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D19" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B20" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D20" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_XUNYU</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B21" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D21" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WEI_ZHANGLIAO</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B22" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D22" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_HANDANG</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="F22" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B23" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D23" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_HUANGGAI</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="F23" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>533</v>
+      </c>
+      <c r="B24" t="s">
+        <v>480</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>COURTESY_WU_SUNCE</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B24" t="s">
-        <v>490</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="D24" t="str">
-        <f t="shared" si="0"/>
-        <v>COURTESY_WU_SUNCE</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>553</v>
-      </c>
       <c r="F24" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B25" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D25" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNJIAN</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="F25" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B26" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D26" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_SUNQUAN</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="F26" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B27" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D27" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_TAISHICI</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="F27" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="B28" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D28" t="str">
         <f t="shared" si="0"/>
         <v>COURTESY_WU_ZHOUYU</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="F28" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D29" t="str">
         <f t="shared" si="0"/>
@@ -4501,13 +4539,13 @@
     </row>
     <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D30" t="str">
         <f t="shared" si="0"/>
@@ -4519,13 +4557,13 @@
     </row>
     <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D31" t="str">
         <f t="shared" si="0"/>
@@ -4537,13 +4575,13 @@
     </row>
     <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D32" t="str">
         <f t="shared" si="0"/>
@@ -4555,13 +4593,13 @@
     </row>
     <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D33" t="str">
         <f t="shared" si="0"/>
@@ -4573,13 +4611,13 @@
     </row>
     <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D34" t="str">
         <f t="shared" si="0"/>
@@ -4591,128 +4629,128 @@
     </row>
     <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B35" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D35" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_SHU_HUANGZHONG</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B36" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D36" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOCAO</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B37" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D37" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_CAOREN</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B38" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D38" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUDUN</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B39" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D39" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B40" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D40" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_XUNYU</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B41" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D41" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WEI_ZHANGLIAO</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>292</v>
@@ -4720,20 +4758,20 @@
     </row>
     <row r="42" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B42" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D42" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HANDANG</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>8</v>
@@ -4741,41 +4779,41 @@
     </row>
     <row r="43" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B43" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D43" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_HUANGGAI</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="F43" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B44" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D44" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNCE</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>6</v>
@@ -4783,20 +4821,20 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B45" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D45" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNJIAN</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>10</v>
@@ -4804,20 +4842,20 @@
     </row>
     <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B46" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D46" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_SUNQUAN</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>13</v>
@@ -4825,20 +4863,20 @@
     </row>
     <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>518</v>
+      </c>
+      <c r="B47" t="s">
+        <v>481</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v>DESC_TALK_WU_TAISHICI</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="B47" t="s">
-        <v>491</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="D47" t="str">
-        <f t="shared" si="0"/>
-        <v>DESC_TALK_WU_TAISHICI</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>14</v>
@@ -4846,166 +4884,166 @@
     </row>
     <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="B48" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D48" t="str">
         <f t="shared" si="0"/>
         <v>DESC_TALK_WU_ZHOUYU</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="F48" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>304</v>
       </c>
       <c r="F49" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>310</v>
       </c>
       <c r="F50" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>307</v>
       </c>
       <c r="F51" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>314</v>
       </c>
       <c r="F52" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>303</v>
       </c>
       <c r="F53" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>309</v>
       </c>
       <c r="F54" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>308</v>
       </c>
       <c r="F55" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>313</v>
       </c>
       <c r="F56" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>305</v>
       </c>
       <c r="F57" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>311</v>
       </c>
       <c r="F58" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>306</v>
       </c>
       <c r="F59" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>312</v>
       </c>
       <c r="F60" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D61" t="str">
         <f t="shared" ref="D61:D80" si="1">UPPER(A61)&amp;"_"&amp;UPPER(C61)&amp;"_"&amp;UPPER(B61)</f>
@@ -5017,13 +5055,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D62" t="str">
         <f t="shared" si="1"/>
@@ -5035,31 +5073,31 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B63" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D63" t="str">
         <f t="shared" si="1"/>
         <v>NAME_SHU_HUANGZHONG</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D64" t="str">
         <f t="shared" si="1"/>
@@ -5071,13 +5109,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D65" t="str">
         <f t="shared" si="1"/>
@@ -5089,13 +5127,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D66" t="str">
         <f t="shared" si="1"/>
@@ -5107,13 +5145,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="D67" t="str">
         <f t="shared" si="1"/>
@@ -5125,236 +5163,236 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B68" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D68" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_CAOCAO</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D69" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_CAOREN</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D70" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUDUN</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B71" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D71" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XIAHOUYUAN</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B72" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D72" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_XUNYU</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D73" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WEI_ZHANGLIAO</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B74" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D74" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_HANDANG</v>
       </c>
       <c r="E74" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D75" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_HUANGGAI</v>
       </c>
       <c r="E75" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D76" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNCE</v>
       </c>
       <c r="E76" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D77" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNJIAN</v>
       </c>
       <c r="E77" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B78" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D78" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_SUNQUAN</v>
       </c>
       <c r="E78" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D79" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_TAISHICI</v>
       </c>
       <c r="E79" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="B80" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D80" t="str">
         <f t="shared" si="1"/>
         <v>NAME_WU_ZHOUYU</v>
       </c>
       <c r="E80" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="81" spans="4:5" x14ac:dyDescent="0.3">
@@ -6099,7 +6137,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -6108,7 +6146,7 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.625" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="37.875" style="3" customWidth="1"/>
     <col min="8" max="8" width="50.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
@@ -6238,7 +6276,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -6258,7 +6296,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" si="2"/>
         <v>TUTORIAL_START</v>
@@ -6375,7 +6413,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" si="3"/>
         <v>TUTORIAL_START</v>
@@ -6518,7 +6556,7 @@
         <v>1_1_1_SHU_START</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:B78" si="11">B20+1</f>
+        <f t="shared" ref="B21:B81" si="11">B20+1</f>
         <v>2</v>
       </c>
       <c r="C21" t="str">
@@ -6841,7 +6879,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -6858,7 +6896,7 @@
         <v>455</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -6920,10 +6958,10 @@
         <v>455</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -6937,10 +6975,10 @@
         <v>NODE_2_4</v>
       </c>
       <c r="E38" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>473</v>
+        <v>633</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -6988,7 +7026,7 @@
         <v>455</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>478</v>
+        <v>624</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -7005,7 +7043,7 @@
         <v>NODE_2_7</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7026,7 +7064,7 @@
         <v>51</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>462</v>
+        <v>632</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -7050,7 +7088,7 @@
         <v>458</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>459</v>
+        <v>623</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -7071,13 +7109,13 @@
         <v>XiahouYuan</v>
       </c>
       <c r="F44" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7098,10 +7136,10 @@
         <v>458</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7122,10 +7160,10 @@
         <v>51</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7139,10 +7177,10 @@
         <v>NODE_2_13</v>
       </c>
       <c r="E47" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>472</v>
+        <v>629</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -7163,10 +7201,10 @@
         <v>XiahouYuan</v>
       </c>
       <c r="F48" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -7190,7 +7228,7 @@
         <v>51</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -7228,7 +7266,7 @@
         <v>455</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -7252,7 +7290,7 @@
         <v>458</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -7276,7 +7314,7 @@
         <v>51</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -7300,7 +7338,7 @@
         <v>455</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -7324,10 +7362,10 @@
         <v>455</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" si="10"/>
         <v>NODE_2</v>
@@ -7348,7 +7386,7 @@
         <v>51</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>467</v>
+        <v>628</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -7372,19 +7410,19 @@
         <v>455</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" ref="C58" si="19">CONCATENATE(A58, "_", B58, IF(D58&lt;&gt;"", "_"&amp;D58, ""))</f>
-        <v>NODE_30A_0</v>
+        <v>NODE_30B_0</v>
       </c>
       <c r="E58" t="str">
         <f>VLOOKUP(F58,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7394,12 +7432,13 @@
         <v>5</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>619</v>
+        <v>616</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A59" t="str">
+        <f>A58</f>
+        <v>NODE_30B</v>
       </c>
       <c r="B59">
         <f t="shared" si="11"/>
@@ -7407,7 +7446,7 @@
       </c>
       <c r="C59" t="str">
         <f t="shared" ref="C59" si="20">CONCATENATE(A59, "_", B59, IF(D59&lt;&gt;"", "_"&amp;D59, ""))</f>
-        <v>NODE_30A_1</v>
+        <v>NODE_30B_1</v>
       </c>
       <c r="E59" t="str">
         <f>VLOOKUP(F59,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7417,20 +7456,21 @@
         <v>9</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>619</v>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A60" t="str">
+        <f t="shared" ref="A60:A81" si="21">A59</f>
+        <v>NODE_30B</v>
       </c>
       <c r="B60">
         <f t="shared" si="11"/>
         <v>2</v>
       </c>
       <c r="C60" t="str">
-        <f t="shared" ref="C60:C78" si="21">CONCATENATE(A60, "_", B60, IF(D60&lt;&gt;"", "_"&amp;D60, ""))</f>
-        <v>NODE_30A_2</v>
+        <f t="shared" ref="C60:C65" si="22">CONCATENATE(A60, "_", B60, IF(D60&lt;&gt;"", "_"&amp;D60, ""))</f>
+        <v>NODE_30B_2</v>
       </c>
       <c r="E60" t="str">
         <f>VLOOKUP(F60,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7440,20 +7480,21 @@
         <v>5</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>619</v>
+        <v>635</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A61" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B61">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="C61" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_3</v>
+        <f t="shared" si="22"/>
+        <v>NODE_30B_3</v>
       </c>
       <c r="E61" t="str">
         <f>VLOOKUP(F61,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7463,20 +7504,21 @@
         <v>5</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>619</v>
+        <v>627</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A62" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B62">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="C62" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_4</v>
+        <f t="shared" si="22"/>
+        <v>NODE_30B_4</v>
       </c>
       <c r="E62" t="str">
         <f>VLOOKUP(F62,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7486,20 +7528,21 @@
         <v>7</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>619</v>
+      <c r="A63" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B63">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="C63" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_5</v>
+        <f t="shared" si="22"/>
+        <v>NODE_30B_5</v>
       </c>
       <c r="E63" t="str">
         <f>VLOOKUP(F63,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7509,20 +7552,21 @@
         <v>5</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>619</v>
+      <c r="A64" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B64">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="C64" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_6</v>
+        <f t="shared" si="22"/>
+        <v>NODE_30B_6</v>
       </c>
       <c r="E64" t="str">
         <f>VLOOKUP(F64,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7532,232 +7576,233 @@
         <v>9</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>619</v>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A65" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B65">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="C65" t="str">
+        <f t="shared" si="22"/>
+        <v>NODE_30B_7</v>
+      </c>
+      <c r="E65" t="str">
+        <f>VLOOKUP(F65,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F65" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="str">
         <f t="shared" si="21"/>
-        <v>NODE_30A_7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>619</v>
+        <v>NODE_30B</v>
       </c>
       <c r="B66">
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="C66" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_8</v>
+        <f>CONCATENATE(A66, "_", B66, IF(D66&lt;&gt;"", "_"&amp;D66, ""))</f>
+        <v>NODE_30B_8</v>
       </c>
       <c r="E66" t="str">
         <f>VLOOKUP(F66,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>619</v>
+      <c r="A67" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B67">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="C67" t="str">
+        <f t="shared" ref="C67:C81" si="23">CONCATENATE(A67, "_", B67, IF(D67&lt;&gt;"", "_"&amp;D67, ""))</f>
+        <v>NODE_30B_9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A68" t="str">
         <f t="shared" si="21"/>
-        <v>NODE_30A_9</v>
-      </c>
-      <c r="E67" t="str">
-        <f>VLOOKUP(F67,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>619</v>
+        <v>NODE_30B</v>
       </c>
       <c r="B68">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_10</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_10</v>
       </c>
       <c r="E68" t="str">
         <f>VLOOKUP(F68,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F68" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>619</v>
+      <c r="A69" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B69">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
       <c r="C69" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_11</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_11</v>
       </c>
       <c r="E69" t="str">
         <f>VLOOKUP(F69,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F69" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>619</v>
+      <c r="A70" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B70">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="C70" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_12_1</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_12</v>
       </c>
       <c r="E70" t="str">
         <f>VLOOKUP(F70,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>LiuBei</v>
       </c>
       <c r="F70" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>619</v>
+      <c r="A71" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B71">
         <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="C71" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_13_1</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_13</v>
       </c>
       <c r="E71" t="str">
         <f>VLOOKUP(F71,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>LiuBei</v>
       </c>
       <c r="F71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>619</v>
+      <c r="A72" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B72">
         <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="C72" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_14_2</v>
-      </c>
-      <c r="D72">
-        <v>2</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_14</v>
       </c>
       <c r="E72" t="str">
         <f>VLOOKUP(F72,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>LiuBei</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>102</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>619</v>
+      <c r="A73" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B73">
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="C73" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_15_2</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_15_1</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="str">
         <f>VLOOKUP(F73,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F73" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>103</v>
+        <v>611</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>619</v>
+      <c r="A74" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B74">
         <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="C74" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_16_2</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_16_1</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="str">
         <f>VLOOKUP(F74,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7767,66 +7812,78 @@
         <v>7</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>637</v>
+        <v>613</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>619</v>
+      <c r="A75" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B75">
         <f t="shared" si="11"/>
         <v>17</v>
       </c>
       <c r="C75" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_17</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_17_2</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
       </c>
       <c r="E75" t="str">
         <f>VLOOKUP(F75,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F75" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>619</v>
+      <c r="A76" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B76">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="C76" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_18</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_18_2</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
       </c>
       <c r="E76" t="str">
         <f>VLOOKUP(F76,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>LiuBei</v>
       </c>
       <c r="F76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>619</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A77" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B77">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="C77" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_19</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_19_2</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
       </c>
       <c r="E77" t="str">
         <f>VLOOKUP(F77,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -7836,30 +7893,103 @@
         <v>7</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>619</v>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A78" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
       </c>
       <c r="B78">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="C78" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_30A_20</v>
+        <f t="shared" si="23"/>
+        <v>NODE_30B_20</v>
       </c>
       <c r="E78" t="str">
         <f>VLOOKUP(F78,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F78" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_30B_21</v>
+      </c>
+      <c r="E79" t="str">
+        <f>VLOOKUP(F79,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>ZhangFei</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F79" t="s">
         <v>9</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>633</v>
+      <c r="G79" s="3" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A80" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_30B_22</v>
+      </c>
+      <c r="E80" t="str">
+        <f>VLOOKUP(F80,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_30B</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_30B_23</v>
+      </c>
+      <c r="E81" t="str">
+        <f>VLOOKUP(F81,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F81" t="s">
+        <v>9</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -8076,7 +8206,7 @@
         <v>NODE_9_TITLE</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="F11" s="21"/>
     </row>
@@ -8450,7 +8580,7 @@
         <v>NODE_26_TITLE</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F33" s="21"/>
     </row>
@@ -8510,7 +8640,7 @@
         <v>402</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="20" t="str">
@@ -8518,7 +8648,7 @@
         <v>NODE_30A_TITLE</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="F37" s="33"/>
     </row>
@@ -8527,7 +8657,7 @@
         <v>402</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="20" t="str">
@@ -8535,7 +8665,7 @@
         <v>NODE_30B_TITLE</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="F38" s="21"/>
     </row>
@@ -8544,7 +8674,7 @@
         <v>402</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="20" t="str">
@@ -8552,7 +8682,7 @@
         <v>NODE_30C_TITLE</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="F39" s="21"/>
     </row>
@@ -9107,7 +9237,7 @@
         <v>NODE_25_DESC</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="35" t="s">
@@ -9127,7 +9257,7 @@
         <v>NODE_26_DESC</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="35" t="s">
@@ -9190,7 +9320,7 @@
         <v>407</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="20" t="str">
@@ -9198,7 +9328,7 @@
         <v>NODE_30A_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="F74" s="33"/>
     </row>
@@ -9207,7 +9337,7 @@
         <v>407</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C75" s="22"/>
       <c r="D75" s="20" t="str">
@@ -9215,7 +9345,7 @@
         <v>NODE_30B_DESC</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="F75" s="24"/>
     </row>
@@ -9224,7 +9354,7 @@
         <v>407</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="20" t="str">
@@ -9232,7 +9362,7 @@
         <v>NODE_30C_DESC</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="F76" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586F95D3-ABEC-4705-8665-F5C0FA953406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F23B46F-1705-41CD-9B1F-99D3942C8B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="814">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2208,10 +2208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>곤란하신 일이 있으신가봅니다, 조공.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2440,11 +2436,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>응? 수염? 현덕공이
-말한 자가 저자인가?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그저 '나 죽여주시오'
 하는 것 같습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2511,11 +2502,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이이!! 저 자는 분명 관우지 않소!
-어떻게 된것이오 현덕공!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>조심하십시오. 원소진영내
 최고의 무장입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2542,21 +2528,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>원소군에 의탁해 있던 현덕공이
-원소의 의해 처형당했다 합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관공!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>어찌 이리 어리석은!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조공. 그대에겐 이미 공을 세워
-빚을 다 갚았다 생각하오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2614,16 +2590,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>관공과 하늘 앞에
-맹세하겠소.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조공, 마지막으로 부탁이 있소.
-내게 병력을 내어주시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">병력을..? </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2746,10 +2712,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자룡?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기척도 없이? 누구지?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2793,10 +2755,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그냥 지나가 주시게. 자룡.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>안됩니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3061,27 +3019,6 @@
     <t>가서 안량과 문추에게
 안부나 전해주시게. 에잇!</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나를 도와 한왕실을 부흥을 시키고,
-천하를 안정토록 하면 될 것 아니오?</t>
-  </si>
-  <si>
-    <t>조공, 그대에게 한왕실은
-그저 도구일 뿐이지 않소.</t>
-  </si>
-  <si>
-    <t>만약 한왕실의 녹을 받으면서
-한치라도 그런 마음을 먹는다면
-천벌을 받아 마땅할 것이오!!</t>
-  </si>
-  <si>
-    <t>조공.. 그대는 진심으로 한왕실을 위하고,
-백성을 먼저 생각하는 길을 갈 수 있겠소?</t>
-  </si>
-  <si>
-    <t>한왕실의 재건을 위해 그대들을 
-맞이하는 것이니 그런 소리 마시오.</t>
   </si>
   <si>
     <t>악귀가 되려는겐가?
@@ -3148,16 +3085,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>유비 형님이 안계신 이상
-한왕실의 운명도 여기까지요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>.. 저기..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - -+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3180,6 +3108,88 @@
   <si>
     <t>한날 한시에 죽겠다는 맹세,
 결코 헛되지 않을 것이오!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다..당연히..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원소군에 의탁해 있던 유비님이
+원소에 의해 처형당했다 합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조조님, 마지막으로 부탁이 있소.
+내게 병력을 내어주시오.</t>
+  </si>
+  <si>
+    <t>곤란하신 일이 있으신가봅니다, 조조님.</t>
+  </si>
+  <si>
+    <t>조조님. 그대에겐 이미 공을 세워
+빚을 다 갚았다 생각하오.</t>
+  </si>
+  <si>
+    <t>응? 수염? 유비가
+말한 자가 저자인가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이이!! 저 자는 분명 관우지 않소!
+어떻게 된것이오 유비!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조운?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그냥 지나가 주시게. 조운.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 왕실의 재건을 위해 그대들을 
+맞이하는 것이니 그런 소리 마시오.</t>
+  </si>
+  <si>
+    <t>유비 형님이 안계신 이상
+한 왕실의 운명도 여기까지요.</t>
+  </si>
+  <si>
+    <t>조조님, 그대에게 한 왕실은
+그저 도구일 뿐이지 않소.</t>
+  </si>
+  <si>
+    <t>만약 한 왕실의 녹을 받으면서
+한치라도 그런 마음을 먹는다면
+천벌을 받아 마땅할 것이오!!</t>
+  </si>
+  <si>
+    <t>조조님.. 그대는 진심으로 한 왕실을 위하고,
+백성을 먼저 생각하는 길을 갈 수 있겠소?</t>
+  </si>
+  <si>
+    <t>음?? 갑자기 번개가..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나를 도와 한 왕실을 부흥 시키고,
+천하를 안정토록 하면 될 것 아니오?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앗! 관장군!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋소! 나 조맹덕,
+관공과 하늘 앞에 맹세하겠소!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도탄에 빠진 백성을 구하고, 한 왕실의
+부흥을 위해 목숨을 바치겠소이다!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6426,7 +6436,7 @@
         <v>451</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>449</v>
@@ -6436,7 +6446,7 @@
         <v>NAME_ETC_YUANSHAO</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F87" s="38"/>
     </row>
@@ -6445,7 +6455,7 @@
         <v>451</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C88" s="27" t="s">
         <v>449</v>
@@ -6464,7 +6474,7 @@
         <v>451</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C89" s="27" t="s">
         <v>449</v>
@@ -6474,7 +6484,7 @@
         <v>NAME_ETC_WENCHOU</v>
       </c>
       <c r="E89" s="27" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F89" s="38"/>
     </row>
@@ -6483,7 +6493,7 @@
         <v>451</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C90" s="27" t="s">
         <v>449</v>
@@ -6493,7 +6503,7 @@
         <v>NAME_ETC_SONGXIAN</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F90" s="38"/>
     </row>
@@ -6502,7 +6512,7 @@
         <v>451</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C91" s="27" t="s">
         <v>449</v>
@@ -6512,7 +6522,7 @@
         <v>NAME_ETC_WEIXU</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="F91" s="38"/>
     </row>
@@ -6521,7 +6531,7 @@
         <v>451</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C92" s="27" t="s">
         <v>447</v>
@@ -6531,7 +6541,7 @@
         <v>NAME_WEI_XUHUANG</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F92" s="38"/>
     </row>
@@ -6540,7 +6550,7 @@
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C93" s="27" t="s">
         <v>449</v>
@@ -6550,7 +6560,7 @@
         <v>NAME_ETC_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="F93" s="38"/>
     </row>
@@ -6559,7 +6569,7 @@
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="C94" s="27" t="s">
         <v>449</v>
@@ -6569,7 +6579,7 @@
         <v>NAME_ETC_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="F94" s="38"/>
     </row>
@@ -6578,7 +6588,7 @@
         <v>479</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C95" s="27" t="s">
         <v>449</v>
@@ -6588,7 +6598,7 @@
         <v>COURTESY_ETC_YUANSHAO</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F95" s="38"/>
     </row>
@@ -6597,7 +6607,7 @@
         <v>479</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C96" s="27" t="s">
         <v>449</v>
@@ -6616,7 +6626,7 @@
         <v>479</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C97" s="27" t="s">
         <v>449</v>
@@ -6635,7 +6645,7 @@
         <v>479</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C98" s="27" t="s">
         <v>447</v>
@@ -6654,7 +6664,7 @@
         <v>464</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C99" s="27" t="s">
         <v>449</v>
@@ -6664,7 +6674,7 @@
         <v>DESC_TALK_ETC_YUANSHAO</v>
       </c>
       <c r="E99" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F99" s="38"/>
     </row>
@@ -6673,7 +6683,7 @@
         <v>464</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C100" s="27" t="s">
         <v>449</v>
@@ -6683,7 +6693,7 @@
         <v>DESC_TALK_ETC_YANLIANG</v>
       </c>
       <c r="E100" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F100" s="38"/>
     </row>
@@ -6692,7 +6702,7 @@
         <v>464</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C101" s="27" t="s">
         <v>449</v>
@@ -6702,7 +6712,7 @@
         <v>DESC_TALK_ETC_WENCHOU</v>
       </c>
       <c r="E101" s="38" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F101" s="38"/>
     </row>
@@ -6711,7 +6721,7 @@
         <v>464</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C102" s="27" t="s">
         <v>447</v>
@@ -6721,7 +6731,7 @@
         <v>DESC_TALK_WEI_XUHUANG</v>
       </c>
       <c r="E102" s="38" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F102" s="38"/>
     </row>
@@ -7419,7 +7429,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I258"/>
+  <dimension ref="A1:J262"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -7878,7 +7888,7 @@
         <v>403</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -7926,7 +7936,7 @@
         <v>51</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -8260,7 +8270,7 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -8394,7 +8404,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8625,7 +8635,7 @@
         <v>7</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -8671,7 +8681,7 @@
         <v>51</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8695,7 +8705,7 @@
         <v>51</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8743,7 +8753,7 @@
         <v>406</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8767,7 +8777,7 @@
         <v>406</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8791,7 +8801,7 @@
         <v>407</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8815,7 +8825,7 @@
         <v>406</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -8839,7 +8849,7 @@
         <v>406</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -8887,7 +8897,7 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>591</v>
+        <v>798</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -8908,10 +8918,10 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F64" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -8932,10 +8942,10 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F65" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -8959,7 +8969,7 @@
         <v>51</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -8983,7 +8993,7 @@
         <v>51</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
@@ -9007,7 +9017,7 @@
         <v>51</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9031,7 +9041,7 @@
         <v>7</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9055,7 +9065,7 @@
         <v>51</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9079,7 +9089,7 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9103,7 +9113,7 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>644</v>
+        <v>800</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
@@ -9126,10 +9136,10 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F73" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9153,7 +9163,7 @@
         <v>589</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -9177,7 +9187,7 @@
         <v>589</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
@@ -9198,10 +9208,10 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F76" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9225,7 +9235,7 @@
         <v>51</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -9249,7 +9259,7 @@
         <v>7</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
@@ -9273,7 +9283,7 @@
         <v>406</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
@@ -9297,7 +9307,7 @@
         <v>407</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -9321,7 +9331,7 @@
         <v>7</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9342,10 +9352,10 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F82" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9366,10 +9376,10 @@
         <v>WenChou</v>
       </c>
       <c r="F83" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -9393,7 +9403,7 @@
         <v>5</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -9417,7 +9427,7 @@
         <v>5</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -9438,10 +9448,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F86" t="s">
+        <v>600</v>
+      </c>
+      <c r="G86" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -9462,10 +9472,10 @@
         <v>WenChou</v>
       </c>
       <c r="F87" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -9486,10 +9496,10 @@
         <v>WenChou</v>
       </c>
       <c r="F88" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -9510,10 +9520,10 @@
         <v>WenChou</v>
       </c>
       <c r="F89" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -9537,7 +9547,7 @@
         <v>7</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9558,10 +9568,10 @@
         <v>WenChou</v>
       </c>
       <c r="F91" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -9582,10 +9592,10 @@
         <v>WenChou</v>
       </c>
       <c r="F92" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -9609,7 +9619,7 @@
         <v>7</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -9630,10 +9640,10 @@
         <v>WenChou</v>
       </c>
       <c r="F94" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9654,10 +9664,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F95" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>659</v>
+        <v>801</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9681,7 +9691,7 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -9702,10 +9712,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F97" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -9729,7 +9739,7 @@
         <v>7</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9753,7 +9763,7 @@
         <v>7</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9777,7 +9787,7 @@
         <v>7</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9804,7 +9814,7 @@
         <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9831,7 +9841,7 @@
         <v>5</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -9855,10 +9865,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F103" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9885,7 +9895,7 @@
         <v>5</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9912,7 +9922,7 @@
         <v>5</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9936,10 +9946,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F106" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9963,10 +9973,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F107" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -9993,7 +10003,7 @@
         <v>5</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -10017,10 +10027,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F109" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -10047,7 +10057,7 @@
         <v>5</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10071,10 +10081,10 @@
         <v>YuanShao</v>
       </c>
       <c r="F111" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10101,10 +10111,10 @@
         <v>5</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10125,13 +10135,13 @@
         <v>YuanShao</v>
       </c>
       <c r="F113" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10155,10 +10165,10 @@
         <v>5</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10179,13 +10189,13 @@
         <v>YuanShao</v>
       </c>
       <c r="F115" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f t="shared" ref="A116:A119" si="10">A115</f>
         <v>NODE_16</v>
@@ -10209,10 +10219,10 @@
         <v>5</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10233,13 +10243,13 @@
         <v>YuanShao</v>
       </c>
       <c r="F117" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10263,10 +10273,10 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10290,18 +10300,18 @@
         <v>7</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121" t="str">
-        <f t="shared" ref="C121:C129" si="12">CONCATENATE(A121, "_", B121, IF(D121&lt;&gt;"", "_"&amp;D121, ""))</f>
+        <f t="shared" ref="C121:C123" si="12">CONCATENATE(A121, "_", B121, IF(D121&lt;&gt;"", "_"&amp;D121, ""))</f>
         <v>NODE_27_0</v>
       </c>
       <c r="E121" t="str">
@@ -10312,15 +10322,15 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B122">
-        <f t="shared" ref="B122:B155" si="13">B121+1</f>
+        <f t="shared" ref="B122:B159" si="13">B121+1</f>
         <v>1</v>
       </c>
       <c r="C122" t="str">
@@ -10332,15 +10342,15 @@
         <v>ZhangLiao</v>
       </c>
       <c r="F122" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B123">
         <f t="shared" si="13"/>
@@ -10358,19 +10368,19 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B124">
         <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="C124" t="str">
-        <f t="shared" ref="C124:C155" si="14">CONCATENATE(A124, "_", B124, IF(D124&lt;&gt;"", "_"&amp;D124, ""))</f>
+        <f t="shared" ref="C124:C125" si="14">CONCATENATE(A124, "_", B124, IF(D124&lt;&gt;"", "_"&amp;D124, ""))</f>
         <v>NODE_27_3</v>
       </c>
       <c r="E124" t="str">
@@ -10381,12 +10391,12 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B125">
         <f t="shared" si="13"/>
@@ -10404,42 +10414,43 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+      <c r="J125" s="3"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B126">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="C126" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="C126:C159" si="15">CONCATENATE(A126, "_", B126, IF(D126&lt;&gt;"", "_"&amp;D126, ""))</f>
         <v>NODE_27_5</v>
       </c>
       <c r="E126" t="str">
         <f>VLOOKUP(F126,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F126" t="s">
-        <v>51</v>
+        <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B127">
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="C127" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_6</v>
       </c>
       <c r="E127" t="str">
@@ -10450,42 +10461,42 @@
         <v>51</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B128">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="C128" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_7</v>
       </c>
       <c r="E128" t="str">
         <f>VLOOKUP(F128,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F128" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B129">
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="C129" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_8</v>
       </c>
       <c r="E129" t="str">
@@ -10496,157 +10507,157 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B130">
         <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_9</v>
       </c>
       <c r="E130" t="str">
         <f>VLOOKUP(F130,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F130" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B131">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
       <c r="C131" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_10</v>
       </c>
       <c r="E131" t="str">
         <f>VLOOKUP(F131,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F131" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>803</v>
+        <v>665</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B132">
         <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="C132" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_11</v>
       </c>
       <c r="E132" t="str">
         <f>VLOOKUP(F132,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F132" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B133">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="C133" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_12</v>
       </c>
       <c r="E133" t="str">
         <f>VLOOKUP(F133,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F133" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B134">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="C134" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_13</v>
       </c>
       <c r="E134" t="str">
         <f>VLOOKUP(F134,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F134" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>673</v>
+        <v>806</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B135">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
       <c r="C135" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_14</v>
       </c>
       <c r="E135" t="str">
         <f>VLOOKUP(F135,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XunYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F135" t="s">
-        <v>672</v>
+        <v>51</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B136">
         <f t="shared" si="13"/>
         <v>15</v>
       </c>
       <c r="C136" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_15</v>
       </c>
       <c r="E136" t="str">
@@ -10654,68 +10665,68 @@
         <v>XunYu</v>
       </c>
       <c r="F136" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B137">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
       <c r="C137" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_16</v>
       </c>
       <c r="E137" t="str">
         <f>VLOOKUP(F137,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XunYu</v>
       </c>
       <c r="F137" t="s">
-        <v>51</v>
+        <v>667</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B138">
         <f t="shared" si="13"/>
         <v>17</v>
       </c>
       <c r="C138" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_17</v>
       </c>
       <c r="E138" t="str">
         <f>VLOOKUP(F138,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XunYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F138" t="s">
-        <v>672</v>
+        <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B139">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="C139" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_18</v>
       </c>
       <c r="E139" t="str">
@@ -10723,206 +10734,206 @@
         <v>XunYu</v>
       </c>
       <c r="F139" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>674</v>
+        <v>807</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B140">
         <f t="shared" si="13"/>
         <v>19</v>
       </c>
       <c r="C140" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_19</v>
       </c>
       <c r="E140" t="str">
         <f>VLOOKUP(F140,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XunYu</v>
       </c>
       <c r="F140" t="s">
-        <v>51</v>
+        <v>667</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>805</v>
+        <v>669</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B141">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
       <c r="C141" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_20</v>
       </c>
       <c r="E141" t="str">
         <f>VLOOKUP(F141,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XunYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F141" t="s">
-        <v>672</v>
+        <v>51</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B142">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="C142" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_21</v>
       </c>
       <c r="E142" t="str">
         <f>VLOOKUP(F142,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XunYu</v>
       </c>
       <c r="F142" t="s">
-        <v>51</v>
+        <v>667</v>
       </c>
       <c r="G142" s="3" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>676</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>681</v>
       </c>
       <c r="B143">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
       <c r="C143" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_22</v>
       </c>
       <c r="E143" t="str">
         <f>VLOOKUP(F143,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F143" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B144">
         <f t="shared" si="13"/>
         <v>23</v>
       </c>
       <c r="C144" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_23</v>
       </c>
       <c r="E144" t="str">
         <f>VLOOKUP(F144,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F144" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>675</v>
+        <v>597</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B145">
         <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="C145" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_24</v>
       </c>
       <c r="E145" t="str">
         <f>VLOOKUP(F145,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F145" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B146">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
       <c r="C146" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_25</v>
       </c>
       <c r="E146" t="str">
         <f>VLOOKUP(F146,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F146" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B147">
         <f t="shared" si="13"/>
         <v>26</v>
       </c>
       <c r="C147" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_26</v>
       </c>
       <c r="E147" t="str">
         <f>VLOOKUP(F147,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F147" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>679</v>
+        <v>795</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B148">
         <f t="shared" si="13"/>
         <v>27</v>
       </c>
       <c r="C148" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_27</v>
       </c>
       <c r="E148" t="str">
@@ -10933,502 +10944,502 @@
         <v>7</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B149">
         <f t="shared" si="13"/>
         <v>28</v>
       </c>
       <c r="C149" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_28</v>
       </c>
       <c r="E149" t="str">
         <f>VLOOKUP(F149,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F149" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B150">
         <f t="shared" si="13"/>
         <v>29</v>
       </c>
       <c r="C150" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_29</v>
       </c>
       <c r="E150" t="str">
         <f>VLOOKUP(F150,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XunYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F150" t="s">
-        <v>672</v>
+        <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B151">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
       <c r="C151" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_30</v>
       </c>
       <c r="E151" t="str">
         <f>VLOOKUP(F151,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F151" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>683</v>
+        <v>813</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B152">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="C152" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_31</v>
       </c>
       <c r="E152" t="str">
         <f>VLOOKUP(F152,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XunYu</v>
       </c>
       <c r="F152" t="s">
-        <v>51</v>
+        <v>667</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B153">
         <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="C153" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_32</v>
       </c>
       <c r="E153" t="str">
         <f>VLOOKUP(F153,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F153" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B154">
         <f t="shared" si="13"/>
         <v>33</v>
       </c>
       <c r="C154" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_33</v>
       </c>
       <c r="E154" t="str">
         <f>VLOOKUP(F154,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F154" t="s">
-        <v>592</v>
+        <v>7</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B155">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
       <c r="C155" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>NODE_27_34</v>
       </c>
       <c r="E155" t="str">
         <f>VLOOKUP(F155,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F155" t="s">
+        <v>7</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>676</v>
+      </c>
+      <c r="B156">
+        <f t="shared" si="13"/>
+        <v>35</v>
+      </c>
+      <c r="C156" t="str">
+        <f t="shared" si="15"/>
+        <v>NODE_27_35</v>
+      </c>
+      <c r="E156" t="str">
+        <f>VLOOKUP(F156,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>CaoCao</v>
       </c>
-      <c r="F155" t="s">
+      <c r="F156" t="s">
         <v>51</v>
       </c>
-      <c r="G155" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G156" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <f t="shared" si="13"/>
+        <v>36</v>
       </c>
       <c r="C157" t="str">
-        <f>CONCATENATE(A157, "_", B157, IF(D157&lt;&gt;"", "_"&amp;D157, ""))</f>
-        <v>NODE_28_0</v>
+        <f t="shared" si="15"/>
+        <v>NODE_27_36</v>
       </c>
       <c r="E157" t="str">
         <f>VLOOKUP(F157,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F157" t="s">
-        <v>592</v>
+        <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="B158">
-        <f t="shared" ref="B158:B177" si="15">B157+1</f>
-        <v>1</v>
+        <f t="shared" si="13"/>
+        <v>37</v>
       </c>
       <c r="C158" t="str">
-        <f>CONCATENATE(A158, "_", B158, IF(D158&lt;&gt;"", "_"&amp;D158, ""))</f>
-        <v>NODE_28_1</v>
+        <f t="shared" si="15"/>
+        <v>NODE_27_37</v>
       </c>
       <c r="E158" t="str">
         <f>VLOOKUP(F158,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>ZhangLiao</v>
       </c>
       <c r="F158" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="B159">
+        <f t="shared" si="13"/>
+        <v>38</v>
+      </c>
+      <c r="C159" t="str">
         <f t="shared" si="15"/>
-        <v>2</v>
-      </c>
-      <c r="C159" t="str">
-        <f t="shared" ref="C159:C173" si="16">CONCATENATE(A159, "_", B159, IF(D159&lt;&gt;"", "_"&amp;D159, ""))</f>
-        <v>NODE_28_2</v>
+        <v>NODE_27_38</v>
       </c>
       <c r="E159" t="str">
         <f>VLOOKUP(F159,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F159" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>701</v>
-      </c>
-      <c r="B160">
-        <f t="shared" si="15"/>
-        <v>3</v>
-      </c>
-      <c r="C160" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_3</v>
-      </c>
-      <c r="E160" t="str">
-        <f>VLOOKUP(F160,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
-      </c>
-      <c r="F160" t="s">
-        <v>406</v>
-      </c>
-      <c r="G160" s="3" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B161">
-        <f t="shared" si="15"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C161" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_4</v>
+        <f>CONCATENATE(A161, "_", B161, IF(D161&lt;&gt;"", "_"&amp;D161, ""))</f>
+        <v>NODE_28_0</v>
       </c>
       <c r="E161" t="str">
         <f>VLOOKUP(F161,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F161" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B162">
-        <f t="shared" si="15"/>
-        <v>5</v>
+        <f t="shared" ref="B162:B181" si="16">B161+1</f>
+        <v>1</v>
       </c>
       <c r="C162" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_5</v>
+        <f>CONCATENATE(A162, "_", B162, IF(D162&lt;&gt;"", "_"&amp;D162, ""))</f>
+        <v>NODE_28_1</v>
       </c>
       <c r="E162" t="str">
         <f>VLOOKUP(F162,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F162" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B163">
-        <f t="shared" si="15"/>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>2</v>
       </c>
       <c r="C163" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_6</v>
+        <f t="shared" ref="C163:C177" si="17">CONCATENATE(A163, "_", B163, IF(D163&lt;&gt;"", "_"&amp;D163, ""))</f>
+        <v>NODE_28_2</v>
       </c>
       <c r="E163" t="str">
         <f>VLOOKUP(F163,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>GuanYu</v>
       </c>
       <c r="F163" t="s">
-        <v>407</v>
+        <v>7</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B164">
-        <f t="shared" si="15"/>
-        <v>7</v>
+        <f t="shared" si="16"/>
+        <v>3</v>
       </c>
       <c r="C164" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_7</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_3</v>
       </c>
       <c r="E164" t="str">
         <f>VLOOKUP(F164,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F164" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B165">
-        <f t="shared" si="15"/>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="C165" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_8</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_4</v>
       </c>
       <c r="E165" t="str">
         <f>VLOOKUP(F165,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F165" t="s">
-        <v>592</v>
+        <v>7</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>692</v>
+        <v>597</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B166">
-        <f t="shared" si="15"/>
-        <v>9</v>
+        <f t="shared" si="16"/>
+        <v>5</v>
       </c>
       <c r="C166" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_9</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_5</v>
       </c>
       <c r="E166" t="str">
         <f>VLOOKUP(F166,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F166" t="s">
-        <v>592</v>
+        <v>406</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B167">
-        <f t="shared" si="15"/>
-        <v>10</v>
+        <f t="shared" si="16"/>
+        <v>6</v>
       </c>
       <c r="C167" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_10</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_6</v>
       </c>
       <c r="E167" t="str">
         <f>VLOOKUP(F167,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F167" t="s">
+        <v>407</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>694</v>
+      </c>
+      <c r="B168">
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
-      <c r="G167" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>701</v>
-      </c>
-      <c r="B168">
-        <f t="shared" si="15"/>
-        <v>11</v>
-      </c>
       <c r="C168" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_11</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_7</v>
       </c>
       <c r="E168" t="str">
         <f>VLOOKUP(F168,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F168" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B169">
-        <f t="shared" si="15"/>
-        <v>12</v>
+        <f t="shared" si="16"/>
+        <v>8</v>
       </c>
       <c r="C169" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_12</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_8</v>
       </c>
       <c r="E169" t="str">
         <f>VLOOKUP(F169,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F169" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B170">
-        <f t="shared" si="15"/>
-        <v>13</v>
+        <f t="shared" si="16"/>
+        <v>9</v>
       </c>
       <c r="C170" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_13</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_9</v>
       </c>
       <c r="E170" t="str">
         <f>VLOOKUP(F170,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>ZhangLiao</v>
       </c>
       <c r="F170" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B171">
-        <f t="shared" si="15"/>
-        <v>14</v>
+        <f t="shared" si="16"/>
+        <v>10</v>
       </c>
       <c r="C171" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_14</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_10</v>
       </c>
       <c r="E171" t="str">
         <f>VLOOKUP(F171,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11438,42 +11449,43 @@
         <v>7</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>414</v>
+        <v>687</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B172">
-        <f t="shared" si="15"/>
-        <v>15</v>
+        <f t="shared" si="16"/>
+        <v>11</v>
       </c>
       <c r="C172" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28_11</v>
+      </c>
+      <c r="E172" t="str">
+        <f>VLOOKUP(F172,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F172" t="s">
+        <v>406</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>694</v>
+      </c>
+      <c r="B173">
         <f t="shared" si="16"/>
-        <v>NODE_28_15</v>
-      </c>
-      <c r="E172" t="s">
-        <v>697</v>
-      </c>
-      <c r="F172" t="s">
-        <v>697</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>701</v>
-      </c>
-      <c r="B173">
-        <f t="shared" si="15"/>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C173" t="str">
-        <f t="shared" si="16"/>
-        <v>NODE_28_16</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_12</v>
       </c>
       <c r="E173" t="str">
         <f>VLOOKUP(F173,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11483,87 +11495,88 @@
         <v>7</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B174">
-        <f t="shared" si="15"/>
-        <v>17</v>
+        <f t="shared" si="16"/>
+        <v>13</v>
       </c>
       <c r="C174" t="str">
-        <f t="shared" ref="C174:C177" si="17">CONCATENATE(A174, "_", B174, IF(D174&lt;&gt;"", "_"&amp;D174, ""))</f>
-        <v>NODE_28_17</v>
-      </c>
-      <c r="E174" t="s">
-        <v>697</v>
+        <f t="shared" si="17"/>
+        <v>NODE_28_13</v>
+      </c>
+      <c r="E174" t="str">
+        <f>VLOOKUP(F174,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangLiao</v>
       </c>
       <c r="F174" t="s">
-        <v>697</v>
+        <v>591</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B175">
-        <f t="shared" si="15"/>
-        <v>18</v>
+        <f t="shared" si="16"/>
+        <v>14</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="17"/>
-        <v>NODE_28_18</v>
+        <v>NODE_28_14</v>
       </c>
       <c r="E175" t="str">
         <f>VLOOKUP(F175,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F175" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B176">
-        <f t="shared" si="15"/>
-        <v>19</v>
+        <f t="shared" si="16"/>
+        <v>15</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="17"/>
-        <v>NODE_28_19</v>
+        <v>NODE_28_15</v>
       </c>
       <c r="E176" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="F176" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>790</v>
+        <v>691</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B177">
-        <f t="shared" si="15"/>
-        <v>20</v>
+        <f t="shared" si="16"/>
+        <v>16</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="17"/>
-        <v>NODE_28_20</v>
+        <v>NODE_28_16</v>
       </c>
       <c r="E177" t="str">
         <f>VLOOKUP(F177,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11573,341 +11586,339 @@
         <v>7</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>598</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>694</v>
+      </c>
+      <c r="B178">
+        <f t="shared" si="16"/>
+        <v>17</v>
+      </c>
+      <c r="C178" t="str">
+        <f t="shared" ref="C178:C181" si="18">CONCATENATE(A178, "_", B178, IF(D178&lt;&gt;"", "_"&amp;D178, ""))</f>
+        <v>NODE_28_17</v>
+      </c>
+      <c r="E178" t="s">
+        <v>690</v>
+      </c>
+      <c r="F178" t="s">
+        <v>690</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>18</v>
       </c>
       <c r="C179" t="str">
-        <f t="shared" ref="C179:C180" si="18">CONCATENATE(A179, "_", B179, IF(D179&lt;&gt;"", "_"&amp;D179, ""))</f>
-        <v>NODE_29_0</v>
+        <f t="shared" si="18"/>
+        <v>NODE_28_18</v>
       </c>
       <c r="E179" t="str">
         <f>VLOOKUP(F179,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F179" t="s">
-        <v>592</v>
+        <v>406</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B180">
-        <f>B179+1</f>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>19</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="18"/>
-        <v>NODE_29_1</v>
-      </c>
-      <c r="E180" t="str">
-        <f>VLOOKUP(F180,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>NODE_28_19</v>
+      </c>
+      <c r="E180" t="s">
+        <v>690</v>
       </c>
       <c r="F180" t="s">
-        <v>406</v>
+        <v>690</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B181">
-        <f t="shared" ref="B181:B219" si="19">B180+1</f>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>20</v>
       </c>
       <c r="C181" t="str">
-        <f t="shared" ref="C181:C219" si="20">CONCATENATE(A181, "_", B181, IF(D181&lt;&gt;"", "_"&amp;D181, ""))</f>
-        <v>NODE_29_2</v>
+        <f t="shared" si="18"/>
+        <v>NODE_28_20</v>
       </c>
       <c r="E181" t="str">
         <f>VLOOKUP(F181,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F181" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>704</v>
-      </c>
-      <c r="B182">
-        <f t="shared" si="19"/>
-        <v>3</v>
-      </c>
-      <c r="C182" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_3</v>
-      </c>
-      <c r="E182" t="str">
-        <f>VLOOKUP(F182,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F182" t="s">
-        <v>7</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B183">
-        <f t="shared" si="19"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C183" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_4</v>
+        <f t="shared" ref="C183:C184" si="19">CONCATENATE(A183, "_", B183, IF(D183&lt;&gt;"", "_"&amp;D183, ""))</f>
+        <v>NODE_29_0</v>
       </c>
       <c r="E183" t="str">
         <f>VLOOKUP(F183,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F183" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B184">
+        <f>B183+1</f>
+        <v>1</v>
+      </c>
+      <c r="C184" t="str">
         <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
-      <c r="C184" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_5</v>
+        <v>NODE_29_1</v>
       </c>
       <c r="E184" t="str">
         <f>VLOOKUP(F184,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F184" t="s">
-        <v>592</v>
+        <v>406</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B185">
-        <f t="shared" si="19"/>
-        <v>6</v>
+        <f t="shared" ref="B185:B223" si="20">B184+1</f>
+        <v>2</v>
       </c>
       <c r="C185" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_6</v>
+        <f t="shared" ref="C185:C223" si="21">CONCATENATE(A185, "_", B185, IF(D185&lt;&gt;"", "_"&amp;D185, ""))</f>
+        <v>NODE_29_2</v>
       </c>
       <c r="E185" t="str">
         <f>VLOOKUP(F185,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F185" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B186">
-        <f t="shared" si="19"/>
-        <v>7</v>
+        <f t="shared" si="20"/>
+        <v>3</v>
       </c>
       <c r="C186" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_7</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_3</v>
       </c>
       <c r="E186" t="str">
         <f>VLOOKUP(F186,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>GuanYu</v>
       </c>
       <c r="F186" t="s">
-        <v>407</v>
+        <v>7</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B187">
-        <f t="shared" si="19"/>
-        <v>8</v>
+        <f t="shared" si="20"/>
+        <v>4</v>
       </c>
       <c r="C187" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_8</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_4</v>
       </c>
       <c r="E187" t="str">
         <f>VLOOKUP(F187,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F187" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B188">
-        <f t="shared" si="19"/>
-        <v>9</v>
+        <f t="shared" si="20"/>
+        <v>5</v>
       </c>
       <c r="C188" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_9</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_5</v>
       </c>
       <c r="E188" t="str">
         <f>VLOOKUP(F188,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F188" t="s">
-        <v>11</v>
+        <v>591</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B189">
-        <f t="shared" si="19"/>
-        <v>10</v>
+        <f t="shared" si="20"/>
+        <v>6</v>
       </c>
       <c r="C189" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_10</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_6</v>
       </c>
       <c r="E189" t="str">
         <f>VLOOKUP(F189,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F189" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>697</v>
+      </c>
+      <c r="B190">
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
-      <c r="G189" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>704</v>
-      </c>
-      <c r="B190">
-        <f t="shared" si="19"/>
-        <v>11</v>
-      </c>
       <c r="C190" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_11</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_7</v>
       </c>
       <c r="E190" t="str">
         <f>VLOOKUP(F190,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F190" t="s">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B191">
-        <f t="shared" si="19"/>
-        <v>12</v>
+        <f t="shared" si="20"/>
+        <v>8</v>
       </c>
       <c r="C191" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_12</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_8</v>
       </c>
       <c r="E191" t="str">
         <f>VLOOKUP(F191,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F191" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>715</v>
+        <v>802</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B192">
-        <f t="shared" si="19"/>
-        <v>13</v>
+        <f t="shared" si="20"/>
+        <v>9</v>
       </c>
       <c r="C192" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_13</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_9</v>
       </c>
       <c r="E192" t="str">
         <f>VLOOKUP(F192,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F192" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>782</v>
+        <v>704</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B193">
-        <f t="shared" si="19"/>
-        <v>14</v>
+        <f t="shared" si="20"/>
+        <v>10</v>
       </c>
       <c r="C193" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_14</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_10</v>
       </c>
       <c r="E193" t="str">
         <f>VLOOKUP(F193,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11917,66 +11928,66 @@
         <v>7</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B194">
-        <f t="shared" si="19"/>
-        <v>15</v>
+        <f t="shared" si="20"/>
+        <v>11</v>
       </c>
       <c r="C194" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_15</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_11</v>
       </c>
       <c r="E194" t="str">
         <f>VLOOKUP(F194,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F194" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B195">
-        <f t="shared" si="19"/>
-        <v>16</v>
+        <f t="shared" si="20"/>
+        <v>12</v>
       </c>
       <c r="C195" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_16</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_12</v>
       </c>
       <c r="E195" t="str">
         <f>VLOOKUP(F195,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F195" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B196">
-        <f t="shared" si="19"/>
-        <v>17</v>
+        <f t="shared" si="20"/>
+        <v>13</v>
       </c>
       <c r="C196" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_17</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_13</v>
       </c>
       <c r="E196" t="str">
         <f>VLOOKUP(F196,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11986,20 +11997,20 @@
         <v>406</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>598</v>
+        <v>773</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B197">
-        <f t="shared" si="19"/>
-        <v>18</v>
+        <f t="shared" si="20"/>
+        <v>14</v>
       </c>
       <c r="C197" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_18</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_14</v>
       </c>
       <c r="E197" t="str">
         <f>VLOOKUP(F197,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12009,181 +12020,181 @@
         <v>7</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B198">
-        <f t="shared" si="19"/>
-        <v>19</v>
+        <f t="shared" si="20"/>
+        <v>15</v>
       </c>
       <c r="C198" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_19</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_15</v>
       </c>
       <c r="E198" t="str">
         <f>VLOOKUP(F198,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F198" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B199">
-        <f t="shared" si="19"/>
-        <v>20</v>
+        <f t="shared" si="20"/>
+        <v>16</v>
       </c>
       <c r="C199" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_20</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_16</v>
       </c>
       <c r="E199" t="str">
         <f>VLOOKUP(F199,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F199" t="s">
-        <v>7</v>
+        <v>407</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B200">
-        <f t="shared" si="19"/>
-        <v>21</v>
+        <f t="shared" si="20"/>
+        <v>17</v>
       </c>
       <c r="C200" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_21</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_17</v>
       </c>
       <c r="E200" t="str">
         <f>VLOOKUP(F200,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F200" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>791</v>
+        <v>597</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B201">
-        <f t="shared" si="19"/>
-        <v>22</v>
+        <f t="shared" si="20"/>
+        <v>18</v>
       </c>
       <c r="C201" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_22</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_18</v>
       </c>
       <c r="E201" t="str">
         <f>VLOOKUP(F201,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F201" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B202">
-        <f t="shared" si="19"/>
-        <v>23</v>
+        <f t="shared" si="20"/>
+        <v>19</v>
       </c>
       <c r="C202" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_23</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_19</v>
       </c>
       <c r="E202" t="str">
         <f>VLOOKUP(F202,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F202" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B203">
-        <f t="shared" si="19"/>
-        <v>24</v>
+        <f t="shared" si="20"/>
+        <v>20</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_24</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_20</v>
       </c>
       <c r="E203" t="str">
         <f>VLOOKUP(F203,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F203" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>724</v>
+        <v>597</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B204">
-        <f t="shared" si="19"/>
-        <v>25</v>
+        <f t="shared" si="20"/>
+        <v>21</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_25</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_21</v>
       </c>
       <c r="E204" t="str">
         <f>VLOOKUP(F204,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F204" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>735</v>
+        <v>777</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B205">
-        <f t="shared" si="19"/>
-        <v>26</v>
+        <f t="shared" si="20"/>
+        <v>22</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_26</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_22</v>
       </c>
       <c r="E205" t="str">
         <f>VLOOKUP(F205,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12193,20 +12204,20 @@
         <v>11</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>598</v>
+        <v>714</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B206">
-        <f t="shared" si="19"/>
-        <v>27</v>
+        <f t="shared" si="20"/>
+        <v>23</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_27</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_23</v>
       </c>
       <c r="E206" t="str">
         <f>VLOOKUP(F206,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12216,20 +12227,20 @@
         <v>7</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>736</v>
+        <v>803</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B207">
-        <f t="shared" si="19"/>
-        <v>28</v>
+        <f t="shared" si="20"/>
+        <v>24</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_28</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_24</v>
       </c>
       <c r="E207" t="str">
         <f>VLOOKUP(F207,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12239,89 +12250,89 @@
         <v>11</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>598</v>
+        <v>715</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B208">
-        <f t="shared" si="19"/>
-        <v>29</v>
+        <f t="shared" si="20"/>
+        <v>25</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_29</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_25</v>
       </c>
       <c r="E208" t="str">
         <f>VLOOKUP(F208,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F208" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B209">
-        <f t="shared" si="19"/>
-        <v>30</v>
+        <f t="shared" si="20"/>
+        <v>26</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_30</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_26</v>
       </c>
       <c r="E209" t="str">
         <f>VLOOKUP(F209,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F209" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>726</v>
+        <v>597</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B210">
-        <f t="shared" si="19"/>
-        <v>31</v>
+        <f t="shared" si="20"/>
+        <v>27</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_31</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_27</v>
       </c>
       <c r="E210" t="str">
         <f>VLOOKUP(F210,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F210" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>696</v>
+        <v>727</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B211">
-        <f t="shared" si="19"/>
-        <v>32</v>
+        <f t="shared" si="20"/>
+        <v>28</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_32</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_28</v>
       </c>
       <c r="E211" t="str">
         <f>VLOOKUP(F211,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12331,43 +12342,43 @@
         <v>11</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>727</v>
+        <v>597</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B212">
-        <f t="shared" si="19"/>
-        <v>33</v>
+        <f t="shared" si="20"/>
+        <v>29</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_33</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_29</v>
       </c>
       <c r="E212" t="str">
         <f>VLOOKUP(F212,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F212" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B213">
-        <f t="shared" si="19"/>
-        <v>34</v>
+        <f t="shared" si="20"/>
+        <v>30</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_34</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_30</v>
       </c>
       <c r="E213" t="str">
         <f>VLOOKUP(F213,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12377,20 +12388,20 @@
         <v>7</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B214">
-        <f t="shared" si="19"/>
-        <v>35</v>
+        <f t="shared" si="20"/>
+        <v>31</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_35</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_31</v>
       </c>
       <c r="E214" t="str">
         <f>VLOOKUP(F214,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12400,43 +12411,43 @@
         <v>406</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>730</v>
+        <v>689</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B215">
-        <f t="shared" si="19"/>
-        <v>36</v>
+        <f t="shared" si="20"/>
+        <v>32</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_36</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_32</v>
       </c>
       <c r="E215" t="str">
         <f>VLOOKUP(F215,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F215" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B216">
-        <f t="shared" si="19"/>
-        <v>37</v>
+        <f t="shared" si="20"/>
+        <v>33</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_37</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_33</v>
       </c>
       <c r="E216" t="str">
         <f>VLOOKUP(F216,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12446,20 +12457,20 @@
         <v>406</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B217">
-        <f t="shared" si="19"/>
-        <v>38</v>
+        <f t="shared" si="20"/>
+        <v>34</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_38</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_34</v>
       </c>
       <c r="E217" t="str">
         <f>VLOOKUP(F217,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12469,43 +12480,43 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B218">
-        <f t="shared" si="19"/>
-        <v>39</v>
+        <f t="shared" si="20"/>
+        <v>35</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_39</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_35</v>
       </c>
       <c r="E218" t="str">
         <f>VLOOKUP(F218,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F218" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="B219">
-        <f t="shared" si="19"/>
-        <v>40</v>
+        <f t="shared" si="20"/>
+        <v>36</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_40</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_36</v>
       </c>
       <c r="E219" t="str">
         <f>VLOOKUP(F219,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12515,65 +12526,89 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>734</v>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>697</v>
+      </c>
+      <c r="B220">
+        <f t="shared" si="20"/>
+        <v>37</v>
+      </c>
+      <c r="C220" t="str">
+        <f t="shared" si="21"/>
+        <v>NODE_29_37</v>
+      </c>
+      <c r="E220" t="str">
+        <f>VLOOKUP(F220,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F220" t="s">
+        <v>406</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>765</v>
+        <v>697</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>38</v>
       </c>
       <c r="C221" t="str">
-        <f>CONCATENATE(A221, "_", B221, IF(D221&lt;&gt;"", "_"&amp;D221, ""))</f>
-        <v>NODE_31_0</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_38</v>
       </c>
       <c r="E221" t="str">
         <f>VLOOKUP(F221,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F221" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>739</v>
+        <v>724</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>765</v>
+        <v>697</v>
       </c>
       <c r="B222">
-        <f t="shared" ref="B222:B258" si="21">B221+1</f>
-        <v>1</v>
+        <f t="shared" si="20"/>
+        <v>39</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" ref="C222:C258" si="22">CONCATENATE(A222, "_", B222, IF(D222&lt;&gt;"", "_"&amp;D222, ""))</f>
-        <v>NODE_31_1</v>
+        <f t="shared" si="21"/>
+        <v>NODE_29_39</v>
       </c>
       <c r="E222" t="str">
         <f>VLOOKUP(F222,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F222" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>792</v>
+        <v>728</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>765</v>
+        <v>697</v>
       </c>
       <c r="B223">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="C223" t="str">
         <f t="shared" si="21"/>
-        <v>2</v>
-      </c>
-      <c r="C223" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_2</v>
+        <v>NODE_29_40</v>
       </c>
       <c r="E223" t="str">
         <f>VLOOKUP(F223,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12583,43 +12618,19 @@
         <v>7</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>765</v>
-      </c>
-      <c r="B224">
-        <f t="shared" si="21"/>
-        <v>3</v>
-      </c>
-      <c r="C224" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_3</v>
-      </c>
-      <c r="E224" t="str">
-        <f>VLOOKUP(F224,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
-      </c>
-      <c r="F224" t="s">
-        <v>9</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>793</v>
+        <v>725</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B225">
-        <f t="shared" si="21"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C225" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_4</v>
+        <f>CONCATENATE(A225, "_", B225, IF(D225&lt;&gt;"", "_"&amp;D225, ""))</f>
+        <v>NODE_31_0</v>
       </c>
       <c r="E225" t="str">
         <f>VLOOKUP(F225,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12629,66 +12640,66 @@
         <v>9</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B226">
-        <f t="shared" si="21"/>
-        <v>5</v>
+        <f t="shared" ref="B226:B262" si="22">B225+1</f>
+        <v>1</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_5</v>
+        <f t="shared" ref="C226:C262" si="23">CONCATENATE(A226, "_", B226, IF(D226&lt;&gt;"", "_"&amp;D226, ""))</f>
+        <v>NODE_31_1</v>
       </c>
       <c r="E226" t="str">
         <f>VLOOKUP(F226,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B227">
-        <f t="shared" si="21"/>
-        <v>6</v>
+        <f t="shared" si="22"/>
+        <v>2</v>
       </c>
       <c r="C227" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_6</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_2</v>
       </c>
       <c r="E227" t="str">
         <f>VLOOKUP(F227,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F227" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B228">
-        <f t="shared" si="21"/>
-        <v>7</v>
+        <f t="shared" si="22"/>
+        <v>3</v>
       </c>
       <c r="C228" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_7</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_3</v>
       </c>
       <c r="E228" t="str">
         <f>VLOOKUP(F228,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12698,89 +12709,89 @@
         <v>9</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B229">
-        <f t="shared" si="21"/>
-        <v>8</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="C229" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_8</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_4</v>
       </c>
       <c r="E229" t="str">
         <f>VLOOKUP(F229,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F229" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B230">
-        <f t="shared" si="21"/>
-        <v>9</v>
+        <f t="shared" si="22"/>
+        <v>5</v>
       </c>
       <c r="C230" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_9</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_5</v>
       </c>
       <c r="E230" t="str">
         <f>VLOOKUP(F230,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F230" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B231">
-        <f t="shared" si="21"/>
-        <v>10</v>
+        <f t="shared" si="22"/>
+        <v>6</v>
       </c>
       <c r="C231" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_10</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_6</v>
       </c>
       <c r="E231" t="str">
         <f>VLOOKUP(F231,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F231" t="s">
+        <v>9</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>756</v>
+      </c>
+      <c r="B232">
+        <f t="shared" si="22"/>
         <v>7</v>
       </c>
-      <c r="G231" s="3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>765</v>
-      </c>
-      <c r="B232">
-        <f t="shared" si="21"/>
-        <v>11</v>
-      </c>
       <c r="C232" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_11</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_7</v>
       </c>
       <c r="E232" t="str">
         <f>VLOOKUP(F232,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12790,20 +12801,20 @@
         <v>9</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
     </row>
     <row r="233" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B233">
-        <f t="shared" si="21"/>
-        <v>12</v>
+        <f t="shared" si="22"/>
+        <v>8</v>
       </c>
       <c r="C233" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_12</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_8</v>
       </c>
       <c r="E233" t="str">
         <f>VLOOKUP(F233,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12813,43 +12824,43 @@
         <v>7</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B234">
-        <f t="shared" si="21"/>
-        <v>13</v>
+        <f t="shared" si="22"/>
+        <v>9</v>
       </c>
       <c r="C234" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_13</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_9</v>
       </c>
       <c r="E234" t="str">
         <f>VLOOKUP(F234,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F234" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B235">
-        <f t="shared" si="21"/>
-        <v>14</v>
+        <f t="shared" si="22"/>
+        <v>10</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_14</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_10</v>
       </c>
       <c r="E235" t="str">
         <f>VLOOKUP(F235,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12859,20 +12870,20 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>662</v>
+        <v>733</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B236">
-        <f t="shared" si="21"/>
-        <v>15</v>
+        <f t="shared" si="22"/>
+        <v>11</v>
       </c>
       <c r="C236" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_15</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_11</v>
       </c>
       <c r="E236" t="str">
         <f>VLOOKUP(F236,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12882,20 +12893,20 @@
         <v>9</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B237">
-        <f t="shared" si="21"/>
-        <v>16</v>
+        <f t="shared" si="22"/>
+        <v>12</v>
       </c>
       <c r="C237" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_16</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_12</v>
       </c>
       <c r="E237" t="str">
         <f>VLOOKUP(F237,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12905,43 +12916,43 @@
         <v>7</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B238">
-        <f t="shared" si="21"/>
-        <v>17</v>
+        <f t="shared" si="22"/>
+        <v>13</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_17</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_13</v>
       </c>
       <c r="E238" t="str">
         <f>VLOOKUP(F238,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F238" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B239">
-        <f t="shared" si="21"/>
-        <v>18</v>
+        <f t="shared" si="22"/>
+        <v>14</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_18</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_14</v>
       </c>
       <c r="E239" t="str">
         <f>VLOOKUP(F239,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12951,112 +12962,112 @@
         <v>7</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>796</v>
+        <v>659</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B240">
-        <f t="shared" si="21"/>
-        <v>19</v>
+        <f t="shared" si="22"/>
+        <v>15</v>
       </c>
       <c r="C240" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_19</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_15</v>
       </c>
       <c r="E240" t="str">
         <f>VLOOKUP(F240,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F240" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>797</v>
+        <v>737</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B241">
-        <f t="shared" si="21"/>
-        <v>20</v>
+        <f t="shared" si="22"/>
+        <v>16</v>
       </c>
       <c r="C241" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_20</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_16</v>
       </c>
       <c r="E241" t="str">
         <f>VLOOKUP(F241,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F241" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B242">
-        <f t="shared" si="21"/>
-        <v>21</v>
+        <f t="shared" si="22"/>
+        <v>17</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_21</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_17</v>
       </c>
       <c r="E242" t="str">
         <f>VLOOKUP(F242,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B243">
-        <f t="shared" si="21"/>
-        <v>22</v>
+        <f t="shared" si="22"/>
+        <v>18</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_22</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_18</v>
       </c>
       <c r="E243" t="str">
         <f>VLOOKUP(F243,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F243" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>749</v>
+        <v>782</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B244">
-        <f t="shared" si="21"/>
-        <v>23</v>
+        <f t="shared" si="22"/>
+        <v>19</v>
       </c>
       <c r="C244" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_23</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_19</v>
       </c>
       <c r="E244" t="str">
         <f>VLOOKUP(F244,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13066,20 +13077,20 @@
         <v>7</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B245">
-        <f t="shared" si="21"/>
-        <v>24</v>
+        <f t="shared" si="22"/>
+        <v>20</v>
       </c>
       <c r="C245" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_24</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_20</v>
       </c>
       <c r="E245" t="str">
         <f>VLOOKUP(F245,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13089,273 +13100,273 @@
         <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B246">
-        <f t="shared" si="21"/>
-        <v>25</v>
+        <f t="shared" si="22"/>
+        <v>21</v>
       </c>
       <c r="C246" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_25</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_21</v>
       </c>
       <c r="E246" t="str">
         <f>VLOOKUP(F246,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>GuanYu</v>
       </c>
       <c r="F246" t="s">
-        <v>761</v>
+        <v>7</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>751</v>
+        <v>784</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B247">
-        <f t="shared" si="21"/>
-        <v>26</v>
+        <f t="shared" si="22"/>
+        <v>22</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_26</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_22</v>
       </c>
       <c r="E247" t="str">
         <f>VLOOKUP(F247,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F247" t="s">
-        <v>762</v>
+        <v>9</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B248">
-        <f t="shared" si="21"/>
-        <v>27</v>
+        <f t="shared" si="22"/>
+        <v>23</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_27</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_23</v>
       </c>
       <c r="E248" t="str">
         <f>VLOOKUP(F248,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F248" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B249">
-        <f t="shared" si="21"/>
-        <v>28</v>
+        <f t="shared" si="22"/>
+        <v>24</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_28</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_24</v>
       </c>
       <c r="E249" t="str">
         <f>VLOOKUP(F249,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>754</v>
+        <v>594</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B250">
-        <f t="shared" si="21"/>
-        <v>29</v>
+        <f t="shared" si="22"/>
+        <v>25</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_29</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_25</v>
       </c>
       <c r="E250" t="str">
         <f>VLOOKUP(F250,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>FanJiang</v>
       </c>
       <c r="F250" t="s">
-        <v>11</v>
+        <v>752</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B251">
-        <f t="shared" si="21"/>
-        <v>30</v>
+        <f t="shared" si="22"/>
+        <v>26</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_30</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_26</v>
       </c>
       <c r="E251" t="str">
         <f>VLOOKUP(F251,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F251" t="s">
-        <v>11</v>
+        <v>753</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>799</v>
+        <v>743</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B252">
-        <f t="shared" si="21"/>
-        <v>31</v>
+        <f t="shared" si="22"/>
+        <v>27</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_31</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_27</v>
       </c>
       <c r="E252" t="str">
         <f>VLOOKUP(F252,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F252" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B253">
-        <f t="shared" si="21"/>
-        <v>32</v>
+        <f t="shared" si="22"/>
+        <v>28</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_32</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_28</v>
       </c>
       <c r="E253" t="str">
         <f>VLOOKUP(F253,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F253" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B254">
-        <f t="shared" si="21"/>
-        <v>33</v>
+        <f t="shared" si="22"/>
+        <v>29</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_33</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_29</v>
       </c>
       <c r="E254" t="str">
         <f>VLOOKUP(F254,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F254" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B255">
-        <f t="shared" si="21"/>
-        <v>34</v>
+        <f t="shared" si="22"/>
+        <v>30</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_34</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_30</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F255" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B256">
-        <f t="shared" si="21"/>
-        <v>35</v>
+        <f t="shared" si="22"/>
+        <v>31</v>
       </c>
       <c r="C256" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_35</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_31</v>
       </c>
       <c r="E256" t="str">
         <f>VLOOKUP(F256,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F256" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B257">
-        <f t="shared" si="21"/>
-        <v>36</v>
+        <f t="shared" si="22"/>
+        <v>32</v>
       </c>
       <c r="C257" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_36</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_32</v>
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13365,20 +13376,20 @@
         <v>5</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="B258">
-        <f t="shared" si="21"/>
-        <v>37</v>
+        <f t="shared" si="22"/>
+        <v>33</v>
       </c>
       <c r="C258" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_31_37</v>
+        <f t="shared" si="23"/>
+        <v>NODE_31_33</v>
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13388,7 +13399,99 @@
         <v>5</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>800</v>
+        <v>749</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>756</v>
+      </c>
+      <c r="B259">
+        <f t="shared" si="22"/>
+        <v>34</v>
+      </c>
+      <c r="C259" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_31_34</v>
+      </c>
+      <c r="E259" t="str">
+        <f>VLOOKUP(F259,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F259" t="s">
+        <v>5</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>756</v>
+      </c>
+      <c r="B260">
+        <f t="shared" si="22"/>
+        <v>35</v>
+      </c>
+      <c r="C260" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_31_35</v>
+      </c>
+      <c r="E260" t="str">
+        <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F260" t="s">
+        <v>5</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>756</v>
+      </c>
+      <c r="B261">
+        <f t="shared" si="22"/>
+        <v>36</v>
+      </c>
+      <c r="C261" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_31_36</v>
+      </c>
+      <c r="E261" t="str">
+        <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F261" t="s">
+        <v>5</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>756</v>
+      </c>
+      <c r="B262">
+        <f t="shared" si="22"/>
+        <v>37</v>
+      </c>
+      <c r="C262" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_31_37</v>
+      </c>
+      <c r="E262" t="str">
+        <f>VLOOKUP(F262,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F262" t="s">
+        <v>5</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -13996,7 +14099,7 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="F34" s="21"/>
     </row>
@@ -14013,7 +14116,7 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="F35" s="24"/>
     </row>
@@ -14030,7 +14133,7 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="F36" s="21"/>
     </row>
@@ -14090,7 +14193,7 @@
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -14098,7 +14201,7 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="F40" s="21"/>
     </row>
@@ -14659,7 +14762,7 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="F72" s="21"/>
     </row>
@@ -14676,7 +14779,7 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="F73" s="24"/>
     </row>
@@ -14693,7 +14796,7 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="F74" s="21"/>
     </row>
@@ -14753,7 +14856,7 @@
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -14761,7 +14864,7 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="F78" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F23B46F-1705-41CD-9B1F-99D3942C8B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AF9244-CA99-4008-9FD6-3F18BEA480B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="823">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2468,11 +2468,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>캬캬캬 애꾸놈 우라통 터지는게
-여기까지 느껴지는구나ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하하하! 역시 그대는
 하늘이 내린 신장이오!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2625,37 +2620,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>장군! 그 자는 군인이 아니오!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자..장군.. 어찌하여..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>어차피 나중에 적이 되어 돌아올테지..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>왜 그러시오. 서주가 떠올라 흥분되오?
-나 역시 그렇군ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장군!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>못봐주겠군ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금도 상당히 볼만한데,
-어디까지 망가지려는게요?ㅋㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2672,11 +2641,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>아무래도 미움을
-단단히 산 모양이군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NODE_29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2968,10 +2932,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"진정 무신은 아수라가 되려하는가"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"무신은 무신을 위하여"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3018,11 +2978,6 @@
   <si>
     <t>가서 안량과 문추에게
 안부나 전해주시게. 에잇!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>악귀가 되려는겐가?
-흥! 아직은 때가 아님을 감사히 여기쇼.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3190,6 +3145,89 @@
   <si>
     <t>도탄에 빠진 백성을 구하고, 한 왕실의
 부흥을 위해 목숨을 바치겠소이다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네놈, 악귀가 되려는겐가..?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무래도 미움을
+단단히 산 모양이군요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캬캬캬 애꾸놈 울화통 터지는게
+여기까지 느껴지는구나ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쳇.. 무안하게시리.. - _-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 아직 내가 나설 수
+없음을 감사히 여기쇼!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후훗.. 서주가 떠올라 흥분되오?
+나 역시 그렇군ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>못봐주겠구만ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금도 상당히 볼만한데,
+어디까지 망가지려 하는가ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝이군요. 이로써
+형주까지 우리 수중에..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장군?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그만두라고 이 자식아!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐하는거요, 장군.
+그는 일반 백성일 뿐이오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사..살려주세요ㅜㅜ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진정 무신은 전장의 귀신이 되려하는가"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으윽.. 이 악귀놈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으아악!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악귀..라..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6550,7 +6588,7 @@
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="C93" s="27" t="s">
         <v>449</v>
@@ -6560,7 +6598,7 @@
         <v>NAME_ETC_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="F93" s="38"/>
     </row>
@@ -6569,7 +6607,7 @@
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="C94" s="27" t="s">
         <v>449</v>
@@ -6579,7 +6617,7 @@
         <v>NAME_ETC_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="F94" s="38"/>
     </row>
@@ -7429,7 +7467,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J262"/>
+  <dimension ref="A1:J271"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -8270,7 +8308,7 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -8404,7 +8442,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8635,7 +8673,7 @@
         <v>7</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -8753,7 +8791,7 @@
         <v>406</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8777,7 +8815,7 @@
         <v>406</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8897,7 +8935,7 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -9089,7 +9127,7 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>650</v>
+        <v>806</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9113,7 +9151,7 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
@@ -9139,7 +9177,7 @@
         <v>591</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9211,7 +9249,7 @@
         <v>591</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9235,7 +9273,7 @@
         <v>51</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -9379,7 +9417,7 @@
         <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -9427,7 +9465,7 @@
         <v>5</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -9571,7 +9609,7 @@
         <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -9667,7 +9705,7 @@
         <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9814,7 +9852,7 @@
         <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9841,7 +9879,7 @@
         <v>5</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -9895,7 +9933,7 @@
         <v>5</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10192,7 +10230,7 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10246,7 +10284,7 @@
         <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -10273,7 +10311,7 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -10300,12 +10338,12 @@
         <v>7</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -10322,12 +10360,12 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B122">
         <f t="shared" ref="B122:B159" si="13">B121+1</f>
@@ -10345,12 +10383,12 @@
         <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B123">
         <f t="shared" si="13"/>
@@ -10368,12 +10406,12 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B124">
         <f t="shared" si="13"/>
@@ -10391,12 +10429,12 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B125">
         <f t="shared" si="13"/>
@@ -10414,13 +10452,13 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="J125" s="3"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B126">
         <f t="shared" si="13"/>
@@ -10438,12 +10476,12 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B127">
         <f t="shared" si="13"/>
@@ -10461,12 +10499,12 @@
         <v>51</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B128">
         <f t="shared" si="13"/>
@@ -10484,12 +10522,12 @@
         <v>51</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B129">
         <f t="shared" si="13"/>
@@ -10507,12 +10545,12 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B130">
         <f t="shared" si="13"/>
@@ -10530,12 +10568,12 @@
         <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B131">
         <f t="shared" si="13"/>
@@ -10553,12 +10591,12 @@
         <v>51</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B132">
         <f t="shared" si="13"/>
@@ -10576,12 +10614,12 @@
         <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B133">
         <f t="shared" si="13"/>
@@ -10599,12 +10637,12 @@
         <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B134">
         <f t="shared" si="13"/>
@@ -10622,12 +10660,12 @@
         <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B135">
         <f t="shared" si="13"/>
@@ -10645,12 +10683,12 @@
         <v>51</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B136">
         <f t="shared" si="13"/>
@@ -10665,15 +10703,15 @@
         <v>XunYu</v>
       </c>
       <c r="F136" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B137">
         <f t="shared" si="13"/>
@@ -10688,15 +10726,15 @@
         <v>XunYu</v>
       </c>
       <c r="F137" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B138">
         <f t="shared" si="13"/>
@@ -10714,12 +10752,12 @@
         <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B139">
         <f t="shared" si="13"/>
@@ -10734,15 +10772,15 @@
         <v>XunYu</v>
       </c>
       <c r="F139" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B140">
         <f t="shared" si="13"/>
@@ -10757,15 +10795,15 @@
         <v>XunYu</v>
       </c>
       <c r="F140" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B141">
         <f t="shared" si="13"/>
@@ -10783,12 +10821,12 @@
         <v>51</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B142">
         <f t="shared" si="13"/>
@@ -10803,15 +10841,15 @@
         <v>XunYu</v>
       </c>
       <c r="F142" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B143">
         <f t="shared" si="13"/>
@@ -10829,12 +10867,12 @@
         <v>51</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B144">
         <f t="shared" si="13"/>
@@ -10857,7 +10895,7 @@
     </row>
     <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B145">
         <f t="shared" si="13"/>
@@ -10875,12 +10913,12 @@
         <v>51</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B146">
         <f t="shared" si="13"/>
@@ -10898,12 +10936,12 @@
         <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B147">
         <f t="shared" si="13"/>
@@ -10921,12 +10959,12 @@
         <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B148">
         <f t="shared" si="13"/>
@@ -10944,12 +10982,12 @@
         <v>7</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B149">
         <f t="shared" si="13"/>
@@ -10967,12 +11005,12 @@
         <v>7</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B150">
         <f t="shared" si="13"/>
@@ -10990,12 +11028,12 @@
         <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B151">
         <f t="shared" si="13"/>
@@ -11013,12 +11051,12 @@
         <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B152">
         <f t="shared" si="13"/>
@@ -11033,15 +11071,15 @@
         <v>XunYu</v>
       </c>
       <c r="F152" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B153">
         <f t="shared" si="13"/>
@@ -11059,12 +11097,12 @@
         <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B154">
         <f t="shared" si="13"/>
@@ -11087,7 +11125,7 @@
     </row>
     <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B155">
         <f t="shared" si="13"/>
@@ -11105,12 +11143,12 @@
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B156">
         <f t="shared" si="13"/>
@@ -11128,12 +11166,12 @@
         <v>51</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B157">
         <f t="shared" si="13"/>
@@ -11151,12 +11189,12 @@
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B158">
         <f t="shared" si="13"/>
@@ -11174,12 +11212,12 @@
         <v>591</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B159">
         <f t="shared" si="13"/>
@@ -11197,12 +11235,12 @@
         <v>51</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -11219,15 +11257,15 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B162">
-        <f t="shared" ref="B162:B181" si="16">B161+1</f>
+        <f t="shared" ref="B162:B191" si="16">B161+1</f>
         <v>1</v>
       </c>
       <c r="C162" t="str">
@@ -11242,19 +11280,19 @@
         <v>591</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B163">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="C163" t="str">
-        <f t="shared" ref="C163:C177" si="17">CONCATENATE(A163, "_", B163, IF(D163&lt;&gt;"", "_"&amp;D163, ""))</f>
+        <f t="shared" ref="C163:C169" si="17">CONCATENATE(A163, "_", B163, IF(D163&lt;&gt;"", "_"&amp;D163, ""))</f>
         <v>NODE_28_2</v>
       </c>
       <c r="E163" t="str">
@@ -11265,12 +11303,12 @@
         <v>7</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B164">
         <f t="shared" si="16"/>
@@ -11288,12 +11326,12 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B165">
         <f t="shared" si="16"/>
@@ -11316,7 +11354,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B166">
         <f t="shared" si="16"/>
@@ -11334,12 +11372,12 @@
         <v>406</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B167">
         <f t="shared" si="16"/>
@@ -11351,18 +11389,18 @@
       </c>
       <c r="E167" t="str">
         <f>VLOOKUP(F167,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F167" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>696</v>
+        <v>807</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B168">
         <f t="shared" si="16"/>
@@ -11374,18 +11412,18 @@
       </c>
       <c r="E168" t="str">
         <f>VLOOKUP(F168,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F168" t="s">
-        <v>7</v>
+        <v>407</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B169">
         <f t="shared" si="16"/>
@@ -11397,230 +11435,219 @@
       </c>
       <c r="E169" t="str">
         <f>VLOOKUP(F169,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F169" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B170">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="C170" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="C170:C177" si="18">CONCATENATE(A170, "_", B170, IF(D170&lt;&gt;"", "_"&amp;D170, ""))</f>
         <v>NODE_28_9</v>
       </c>
       <c r="E170" t="str">
         <f>VLOOKUP(F170,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F170" t="s">
-        <v>591</v>
+        <v>406</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>686</v>
+        <v>597</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B171">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="C171" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_10</v>
-      </c>
-      <c r="E171" t="str">
-        <f>VLOOKUP(F171,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F171" t="s">
-        <v>7</v>
-      </c>
-      <c r="G171" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B172">
         <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="C172" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_11</v>
       </c>
-      <c r="E172" t="str">
-        <f>VLOOKUP(F172,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+      <c r="E172" t="s">
+        <v>809</v>
       </c>
       <c r="F172" t="s">
-        <v>406</v>
+        <v>809</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B173">
         <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="C173" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="C173:C191" si="19">CONCATENATE(A173, "_", B173, IF(D173&lt;&gt;"", "_"&amp;D173, ""))</f>
         <v>NODE_28_12</v>
       </c>
-      <c r="E173" t="str">
-        <f>VLOOKUP(F173,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+      <c r="E173" t="s">
+        <v>809</v>
       </c>
       <c r="F173" t="s">
-        <v>7</v>
+        <v>809</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>688</v>
+        <v>821</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B174">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="C174" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_13</v>
       </c>
       <c r="E174" t="str">
         <f>VLOOKUP(F174,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F174" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B175">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="C175" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_14</v>
       </c>
       <c r="E175" t="str">
         <f>VLOOKUP(F175,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F175" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>414</v>
+        <v>814</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B176">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="C176" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_15</v>
       </c>
-      <c r="E176" t="s">
-        <v>690</v>
+      <c r="E176" t="str">
+        <f>VLOOKUP(F176,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
       </c>
       <c r="F176" t="s">
-        <v>690</v>
+        <v>7</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>691</v>
+        <v>594</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B177">
         <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="C177" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_16</v>
       </c>
       <c r="E177" t="str">
         <f>VLOOKUP(F177,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F177" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B178">
         <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="C178" t="str">
-        <f t="shared" ref="C178:C181" si="18">CONCATENATE(A178, "_", B178, IF(D178&lt;&gt;"", "_"&amp;D178, ""))</f>
+        <f t="shared" si="19"/>
         <v>NODE_28_17</v>
       </c>
       <c r="E178" t="s">
-        <v>690</v>
+        <v>415</v>
       </c>
       <c r="F178" t="s">
-        <v>690</v>
+        <v>415</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B179">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="C179" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_18</v>
       </c>
       <c r="E179" t="str">
@@ -11631,87 +11658,112 @@
         <v>406</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>693</v>
+        <v>817</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B180">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
       <c r="C180" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_19</v>
       </c>
-      <c r="E180" t="s">
-        <v>690</v>
+      <c r="E180" t="str">
+        <f>VLOOKUP(F180,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
       </c>
       <c r="F180" t="s">
-        <v>690</v>
+        <v>7</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>776</v>
+        <v>810</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="B181">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="C181" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_20</v>
       </c>
       <c r="E181" t="str">
         <f>VLOOKUP(F181,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F181" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>597</v>
+        <v>816</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>687</v>
+      </c>
+      <c r="B182">
+        <f t="shared" si="16"/>
+        <v>21</v>
+      </c>
+      <c r="C182" t="str">
+        <f t="shared" si="19"/>
+        <v>NODE_28_21</v>
+      </c>
+      <c r="E182" t="str">
+        <f>VLOOKUP(F182,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangLiao</v>
+      </c>
+      <c r="F182" t="s">
+        <v>591</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>22</v>
       </c>
       <c r="C183" t="str">
-        <f t="shared" ref="C183:C184" si="19">CONCATENATE(A183, "_", B183, IF(D183&lt;&gt;"", "_"&amp;D183, ""))</f>
-        <v>NODE_29_0</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_22</v>
       </c>
       <c r="E183" t="str">
         <f>VLOOKUP(F183,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F183" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B184">
-        <f>B183+1</f>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>23</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="19"/>
-        <v>NODE_29_1</v>
+        <v>NODE_28_23</v>
       </c>
       <c r="E184" t="str">
         <f>VLOOKUP(F184,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11721,89 +11773,87 @@
         <v>406</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B185">
-        <f t="shared" ref="B185:B223" si="20">B184+1</f>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>24</v>
       </c>
       <c r="C185" t="str">
-        <f t="shared" ref="C185:C223" si="21">CONCATENATE(A185, "_", B185, IF(D185&lt;&gt;"", "_"&amp;D185, ""))</f>
-        <v>NODE_29_2</v>
-      </c>
-      <c r="E185" t="str">
-        <f>VLOOKUP(F185,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_24</v>
+      </c>
+      <c r="E185" t="s">
+        <v>685</v>
       </c>
       <c r="F185" t="s">
-        <v>406</v>
+        <v>685</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B186">
-        <f t="shared" si="20"/>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>25</v>
       </c>
       <c r="C186" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_3</v>
-      </c>
-      <c r="E186" t="str">
-        <f>VLOOKUP(F186,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_25</v>
+      </c>
+      <c r="E186" t="s">
+        <v>685</v>
       </c>
       <c r="F186" t="s">
-        <v>7</v>
+        <v>685</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B187">
-        <f t="shared" si="20"/>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>26</v>
       </c>
       <c r="C187" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_4</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_26</v>
       </c>
       <c r="E187" t="str">
         <f>VLOOKUP(F187,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F187" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>700</v>
+        <v>594</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B188">
-        <f t="shared" si="20"/>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>27</v>
       </c>
       <c r="C188" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_5</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_27</v>
       </c>
       <c r="E188" t="str">
         <f>VLOOKUP(F188,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11813,66 +11863,64 @@
         <v>591</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B189">
-        <f t="shared" si="20"/>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>28</v>
       </c>
       <c r="C189" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_6</v>
-      </c>
-      <c r="E189" t="str">
-        <f>VLOOKUP(F189,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_28</v>
+      </c>
+      <c r="E189" t="s">
+        <v>685</v>
       </c>
       <c r="F189" t="s">
-        <v>11</v>
+        <v>685</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B190">
-        <f t="shared" si="20"/>
-        <v>7</v>
+        <f t="shared" si="16"/>
+        <v>29</v>
       </c>
       <c r="C190" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_7</v>
-      </c>
-      <c r="E190" t="str">
-        <f>VLOOKUP(F190,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_29</v>
+      </c>
+      <c r="E190" t="s">
+        <v>685</v>
       </c>
       <c r="F190" t="s">
-        <v>407</v>
+        <v>685</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>705</v>
+        <v>808</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B191">
-        <f t="shared" si="20"/>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>30</v>
       </c>
       <c r="C191" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_8</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_30</v>
       </c>
       <c r="E191" t="str">
         <f>VLOOKUP(F191,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11882,112 +11930,88 @@
         <v>7</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>697</v>
-      </c>
-      <c r="B192">
-        <f t="shared" si="20"/>
-        <v>9</v>
-      </c>
-      <c r="C192" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_9</v>
-      </c>
-      <c r="E192" t="str">
-        <f>VLOOKUP(F192,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
-      </c>
-      <c r="F192" t="s">
-        <v>11</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B193">
-        <f t="shared" si="20"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C193" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_10</v>
+        <f t="shared" ref="C193:C194" si="20">CONCATENATE(A193, "_", B193, IF(D193&lt;&gt;"", "_"&amp;D193, ""))</f>
+        <v>NODE_29_0</v>
       </c>
       <c r="E193" t="str">
         <f>VLOOKUP(F193,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F193" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>712</v>
+        <v>690</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B194">
+        <f>B193+1</f>
+        <v>1</v>
+      </c>
+      <c r="C194" t="str">
         <f t="shared" si="20"/>
-        <v>11</v>
-      </c>
-      <c r="C194" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_11</v>
+        <v>NODE_29_1</v>
       </c>
       <c r="E194" t="str">
         <f>VLOOKUP(F194,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F194" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B195">
-        <f t="shared" si="20"/>
-        <v>12</v>
+        <f t="shared" ref="B195:B232" si="21">B194+1</f>
+        <v>2</v>
       </c>
       <c r="C195" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_12</v>
+        <f t="shared" ref="C195:C232" si="22">CONCATENATE(A195, "_", B195, IF(D195&lt;&gt;"", "_"&amp;D195, ""))</f>
+        <v>NODE_29_2</v>
       </c>
       <c r="E195" t="str">
         <f>VLOOKUP(F195,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F195" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B196">
-        <f t="shared" si="20"/>
-        <v>13</v>
+        <f t="shared" si="21"/>
+        <v>3</v>
       </c>
       <c r="C196" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_13</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_3</v>
       </c>
       <c r="E196" t="str">
         <f>VLOOKUP(F196,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -11997,66 +12021,66 @@
         <v>406</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>773</v>
+        <v>692</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B197">
-        <f t="shared" si="20"/>
-        <v>14</v>
+        <f t="shared" si="21"/>
+        <v>4</v>
       </c>
       <c r="C197" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_14</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_4</v>
       </c>
       <c r="E197" t="str">
         <f>VLOOKUP(F197,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F197" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B198">
-        <f t="shared" si="20"/>
-        <v>15</v>
+        <f t="shared" si="21"/>
+        <v>5</v>
       </c>
       <c r="C198" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_15</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_5</v>
       </c>
       <c r="E198" t="str">
         <f>VLOOKUP(F198,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F198" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B199">
-        <f t="shared" si="20"/>
-        <v>16</v>
+        <f t="shared" si="21"/>
+        <v>6</v>
       </c>
       <c r="C199" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_16</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_6</v>
       </c>
       <c r="E199" t="str">
         <f>VLOOKUP(F199,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12066,158 +12090,158 @@
         <v>407</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B200">
-        <f t="shared" si="20"/>
-        <v>17</v>
+        <f t="shared" si="21"/>
+        <v>7</v>
       </c>
       <c r="C200" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_17</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_7</v>
       </c>
       <c r="E200" t="str">
         <f>VLOOKUP(F200,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F200" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>597</v>
+        <v>792</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B201">
-        <f t="shared" si="20"/>
-        <v>18</v>
+        <f t="shared" si="21"/>
+        <v>8</v>
       </c>
       <c r="C201" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_18</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_8</v>
       </c>
       <c r="E201" t="str">
         <f>VLOOKUP(F201,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F201" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B202">
-        <f t="shared" si="20"/>
-        <v>19</v>
+        <f t="shared" si="21"/>
+        <v>9</v>
       </c>
       <c r="C202" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_19</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_9</v>
       </c>
       <c r="E202" t="str">
         <f>VLOOKUP(F202,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F202" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B203">
-        <f t="shared" si="20"/>
-        <v>20</v>
+        <f t="shared" si="21"/>
+        <v>10</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_20</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_10</v>
       </c>
       <c r="E203" t="str">
         <f>VLOOKUP(F203,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F203" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>597</v>
+        <v>698</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B204">
-        <f t="shared" si="20"/>
-        <v>21</v>
+        <f t="shared" si="21"/>
+        <v>11</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_21</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_11</v>
       </c>
       <c r="E204" t="str">
         <f>VLOOKUP(F204,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F204" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>777</v>
+        <v>699</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B205">
-        <f t="shared" si="20"/>
-        <v>22</v>
+        <f t="shared" si="21"/>
+        <v>12</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_22</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_12</v>
       </c>
       <c r="E205" t="str">
         <f>VLOOKUP(F205,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F205" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>714</v>
+        <v>764</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B206">
-        <f t="shared" si="20"/>
-        <v>23</v>
+        <f t="shared" si="21"/>
+        <v>13</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_23</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_13</v>
       </c>
       <c r="E206" t="str">
         <f>VLOOKUP(F206,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12227,73 +12251,73 @@
         <v>7</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>803</v>
+        <v>700</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B207">
-        <f t="shared" si="20"/>
-        <v>24</v>
+        <f t="shared" si="21"/>
+        <v>14</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_24</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_14</v>
       </c>
       <c r="E207" t="str">
         <f>VLOOKUP(F207,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F207" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B208">
-        <f t="shared" si="20"/>
-        <v>25</v>
+        <f t="shared" si="21"/>
+        <v>15</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_25</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_15</v>
       </c>
       <c r="E208" t="str">
         <f>VLOOKUP(F208,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F208" t="s">
-        <v>7</v>
+        <v>407</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>726</v>
+        <v>702</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B209">
-        <f t="shared" si="20"/>
-        <v>26</v>
+        <f t="shared" si="21"/>
+        <v>16</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_26</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_16</v>
       </c>
       <c r="E209" t="str">
         <f>VLOOKUP(F209,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F209" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>597</v>
@@ -12301,15 +12325,15 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B210">
-        <f t="shared" si="20"/>
-        <v>27</v>
+        <f t="shared" si="21"/>
+        <v>17</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_27</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_17</v>
       </c>
       <c r="E210" t="str">
         <f>VLOOKUP(F210,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12319,20 +12343,20 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B211">
-        <f t="shared" si="20"/>
-        <v>28</v>
+        <f t="shared" si="21"/>
+        <v>18</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_28</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_18</v>
       </c>
       <c r="E211" t="str">
         <f>VLOOKUP(F211,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12342,135 +12366,135 @@
         <v>11</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B212">
-        <f t="shared" si="20"/>
-        <v>29</v>
+        <f t="shared" si="21"/>
+        <v>19</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_29</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_19</v>
       </c>
       <c r="E212" t="str">
         <f>VLOOKUP(F212,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F212" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B213">
-        <f t="shared" si="20"/>
-        <v>30</v>
+        <f t="shared" si="21"/>
+        <v>20</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_30</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_20</v>
       </c>
       <c r="E213" t="str">
         <f>VLOOKUP(F213,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F213" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>717</v>
+        <v>767</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B214">
-        <f t="shared" si="20"/>
-        <v>31</v>
+        <f t="shared" si="21"/>
+        <v>21</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_31</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_21</v>
       </c>
       <c r="E214" t="str">
         <f>VLOOKUP(F214,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F214" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B215">
-        <f t="shared" si="20"/>
-        <v>32</v>
+        <f t="shared" si="21"/>
+        <v>22</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_32</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_22</v>
       </c>
       <c r="E215" t="str">
         <f>VLOOKUP(F215,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F215" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B216">
-        <f t="shared" si="20"/>
-        <v>33</v>
+        <f t="shared" si="21"/>
+        <v>23</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_33</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_23</v>
       </c>
       <c r="E216" t="str">
         <f>VLOOKUP(F216,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F216" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B217">
-        <f t="shared" si="20"/>
-        <v>34</v>
+        <f t="shared" si="21"/>
+        <v>24</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_34</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_24</v>
       </c>
       <c r="E217" t="str">
         <f>VLOOKUP(F217,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12480,43 +12504,43 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B218">
-        <f t="shared" si="20"/>
-        <v>35</v>
+        <f t="shared" si="21"/>
+        <v>25</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_35</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_25</v>
       </c>
       <c r="E218" t="str">
         <f>VLOOKUP(F218,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F218" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>721</v>
+        <v>597</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B219">
-        <f t="shared" si="20"/>
-        <v>36</v>
+        <f t="shared" si="21"/>
+        <v>26</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_36</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_26</v>
       </c>
       <c r="E219" t="str">
         <f>VLOOKUP(F219,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12526,66 +12550,66 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B220">
-        <f t="shared" si="20"/>
-        <v>37</v>
+        <f t="shared" si="21"/>
+        <v>27</v>
       </c>
       <c r="C220" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_37</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_27</v>
       </c>
       <c r="E220" t="str">
         <f>VLOOKUP(F220,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F220" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B221">
-        <f t="shared" si="20"/>
-        <v>38</v>
+        <f t="shared" si="21"/>
+        <v>28</v>
       </c>
       <c r="C221" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_38</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_28</v>
       </c>
       <c r="E221" t="str">
         <f>VLOOKUP(F221,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F221" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B222">
-        <f t="shared" si="20"/>
-        <v>39</v>
+        <f t="shared" si="21"/>
+        <v>29</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_39</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_29</v>
       </c>
       <c r="E222" t="str">
         <f>VLOOKUP(F222,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12595,157 +12619,181 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B223">
-        <f t="shared" si="20"/>
-        <v>40</v>
+        <f t="shared" si="21"/>
+        <v>30</v>
       </c>
       <c r="C223" t="str">
-        <f t="shared" si="21"/>
-        <v>NODE_29_40</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_30</v>
       </c>
       <c r="E223" t="str">
         <f>VLOOKUP(F223,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F223" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>689</v>
+      </c>
+      <c r="B224">
+        <f t="shared" si="21"/>
+        <v>31</v>
+      </c>
+      <c r="C224" t="str">
+        <f t="shared" si="22"/>
+        <v>NODE_29_31</v>
+      </c>
+      <c r="E224" t="str">
+        <f>VLOOKUP(F224,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F224" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>32</v>
       </c>
       <c r="C225" t="str">
-        <f>CONCATENATE(A225, "_", B225, IF(D225&lt;&gt;"", "_"&amp;D225, ""))</f>
-        <v>NODE_31_0</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_32</v>
       </c>
       <c r="E225" t="str">
         <f>VLOOKUP(F225,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F225" t="s">
-        <v>9</v>
+        <v>406</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B226">
-        <f t="shared" ref="B226:B262" si="22">B225+1</f>
-        <v>1</v>
+        <f t="shared" si="21"/>
+        <v>33</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" ref="C226:C262" si="23">CONCATENATE(A226, "_", B226, IF(D226&lt;&gt;"", "_"&amp;D226, ""))</f>
-        <v>NODE_31_1</v>
+        <f t="shared" si="22"/>
+        <v>NODE_29_33</v>
       </c>
       <c r="E226" t="str">
         <f>VLOOKUP(F226,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F226" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B227">
+        <f t="shared" si="21"/>
+        <v>34</v>
+      </c>
+      <c r="C227" t="str">
         <f t="shared" si="22"/>
-        <v>2</v>
-      </c>
-      <c r="C227" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_2</v>
+        <v>NODE_29_34</v>
       </c>
       <c r="E227" t="str">
         <f>VLOOKUP(F227,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F227" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B228">
+        <f t="shared" si="21"/>
+        <v>35</v>
+      </c>
+      <c r="C228" t="str">
         <f t="shared" si="22"/>
-        <v>3</v>
-      </c>
-      <c r="C228" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_3</v>
+        <v>NODE_29_35</v>
       </c>
       <c r="E228" t="str">
         <f>VLOOKUP(F228,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F228" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B229">
+        <f t="shared" si="21"/>
+        <v>36</v>
+      </c>
+      <c r="C229" t="str">
         <f t="shared" si="22"/>
-        <v>4</v>
-      </c>
-      <c r="C229" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_4</v>
+        <v>NODE_29_36</v>
       </c>
       <c r="E229" t="str">
         <f>VLOOKUP(F229,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F229" t="s">
-        <v>9</v>
+        <v>406</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>755</v>
+        <v>715</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B230">
+        <f t="shared" si="21"/>
+        <v>37</v>
+      </c>
+      <c r="C230" t="str">
         <f t="shared" si="22"/>
-        <v>5</v>
-      </c>
-      <c r="C230" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_5</v>
+        <v>NODE_29_37</v>
       </c>
       <c r="E230" t="str">
         <f>VLOOKUP(F230,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12755,89 +12803,65 @@
         <v>7</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B231">
+        <f t="shared" si="21"/>
+        <v>38</v>
+      </c>
+      <c r="C231" t="str">
         <f t="shared" si="22"/>
-        <v>6</v>
-      </c>
-      <c r="C231" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_6</v>
+        <v>NODE_29_38</v>
       </c>
       <c r="E231" t="str">
         <f>VLOOKUP(F231,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F231" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>756</v>
+        <v>689</v>
       </c>
       <c r="B232">
+        <f t="shared" si="21"/>
+        <v>39</v>
+      </c>
+      <c r="C232" t="str">
         <f t="shared" si="22"/>
-        <v>7</v>
-      </c>
-      <c r="C232" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_7</v>
+        <v>NODE_29_39</v>
       </c>
       <c r="E232" t="str">
         <f>VLOOKUP(F232,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F232" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>756</v>
-      </c>
-      <c r="B233">
-        <f t="shared" si="22"/>
-        <v>8</v>
-      </c>
-      <c r="C233" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_8</v>
-      </c>
-      <c r="E233" t="str">
-        <f>VLOOKUP(F233,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F233" t="s">
-        <v>7</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B234">
-        <f t="shared" si="22"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C234" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_9</v>
+        <f>CONCATENATE(A234, "_", B234, IF(D234&lt;&gt;"", "_"&amp;D234, ""))</f>
+        <v>NODE_31_0</v>
       </c>
       <c r="E234" t="str">
         <f>VLOOKUP(F234,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12847,112 +12871,112 @@
         <v>9</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B235">
-        <f t="shared" si="22"/>
-        <v>10</v>
+        <f t="shared" ref="B235:B271" si="23">B234+1</f>
+        <v>1</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_10</v>
+        <f t="shared" ref="C235" si="24">CONCATENATE(A235, "_", B235, IF(D235&lt;&gt;"", "_"&amp;D235, ""))</f>
+        <v>NODE_31_1</v>
       </c>
       <c r="E235" t="str">
         <f>VLOOKUP(F235,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F235" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B236">
-        <f t="shared" si="22"/>
-        <v>11</v>
+        <f t="shared" si="23"/>
+        <v>2</v>
       </c>
       <c r="C236" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_11</v>
+        <f t="shared" ref="C236:C271" si="25">CONCATENATE(A236, "_", B236, IF(D236&lt;&gt;"", "_"&amp;D236, ""))</f>
+        <v>NODE_31_2</v>
       </c>
       <c r="E236" t="str">
         <f>VLOOKUP(F236,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F236" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>734</v>
+        <v>597</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B237">
-        <f t="shared" si="22"/>
-        <v>12</v>
+        <f t="shared" si="23"/>
+        <v>3</v>
       </c>
       <c r="C237" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_12</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_3</v>
       </c>
       <c r="E237" t="str">
         <f>VLOOKUP(F237,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F237" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B238">
-        <f t="shared" si="22"/>
-        <v>13</v>
+        <f t="shared" si="23"/>
+        <v>4</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_13</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_4</v>
       </c>
       <c r="E238" t="str">
         <f>VLOOKUP(F238,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F238" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B239">
-        <f t="shared" si="22"/>
-        <v>14</v>
+        <f t="shared" si="23"/>
+        <v>5</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_14</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_5</v>
       </c>
       <c r="E239" t="str">
         <f>VLOOKUP(F239,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12962,20 +12986,20 @@
         <v>7</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>659</v>
+        <v>721</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B240">
-        <f t="shared" si="22"/>
-        <v>15</v>
+        <f t="shared" si="23"/>
+        <v>6</v>
       </c>
       <c r="C240" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_15</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_6</v>
       </c>
       <c r="E240" t="str">
         <f>VLOOKUP(F240,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12985,89 +13009,89 @@
         <v>9</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B241">
-        <f t="shared" si="22"/>
-        <v>16</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="C241" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_16</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_7</v>
       </c>
       <c r="E241" t="str">
         <f>VLOOKUP(F241,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F241" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B242">
-        <f t="shared" si="22"/>
-        <v>17</v>
+        <f t="shared" si="23"/>
+        <v>8</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_17</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_8</v>
       </c>
       <c r="E242" t="str">
         <f>VLOOKUP(F242,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F242" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>738</v>
+        <v>723</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B243">
-        <f t="shared" si="22"/>
-        <v>18</v>
+        <f t="shared" si="23"/>
+        <v>9</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_18</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_9</v>
       </c>
       <c r="E243" t="str">
         <f>VLOOKUP(F243,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F243" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B244">
-        <f t="shared" si="22"/>
-        <v>19</v>
+        <f t="shared" si="23"/>
+        <v>10</v>
       </c>
       <c r="C244" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_19</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_10</v>
       </c>
       <c r="E244" t="str">
         <f>VLOOKUP(F244,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13077,20 +13101,20 @@
         <v>7</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>783</v>
+        <v>725</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B245">
-        <f t="shared" si="22"/>
-        <v>20</v>
+        <f t="shared" si="23"/>
+        <v>11</v>
       </c>
       <c r="C245" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_20</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_11</v>
       </c>
       <c r="E245" t="str">
         <f>VLOOKUP(F245,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13100,20 +13124,20 @@
         <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B246">
-        <f t="shared" si="22"/>
-        <v>21</v>
+        <f t="shared" si="23"/>
+        <v>12</v>
       </c>
       <c r="C246" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_21</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_12</v>
       </c>
       <c r="E246" t="str">
         <f>VLOOKUP(F246,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13123,43 +13147,43 @@
         <v>7</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B247">
-        <f t="shared" si="22"/>
-        <v>22</v>
+        <f t="shared" si="23"/>
+        <v>13</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_22</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_13</v>
       </c>
       <c r="E247" t="str">
         <f>VLOOKUP(F247,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F247" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B248">
-        <f t="shared" si="22"/>
-        <v>23</v>
+        <f t="shared" si="23"/>
+        <v>14</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_23</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_14</v>
       </c>
       <c r="E248" t="str">
         <f>VLOOKUP(F248,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13169,20 +13193,20 @@
         <v>7</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B249">
-        <f t="shared" si="22"/>
-        <v>24</v>
+        <f t="shared" si="23"/>
+        <v>15</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_24</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_15</v>
       </c>
       <c r="E249" t="str">
         <f>VLOOKUP(F249,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13192,89 +13216,89 @@
         <v>9</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B250">
-        <f t="shared" si="22"/>
-        <v>25</v>
+        <f t="shared" si="23"/>
+        <v>16</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_25</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_16</v>
       </c>
       <c r="E250" t="str">
         <f>VLOOKUP(F250,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>GuanYu</v>
       </c>
       <c r="F250" t="s">
-        <v>752</v>
+        <v>7</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>742</v>
+        <v>771</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B251">
-        <f t="shared" si="22"/>
-        <v>26</v>
+        <f t="shared" si="23"/>
+        <v>17</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_26</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_17</v>
       </c>
       <c r="E251" t="str">
         <f>VLOOKUP(F251,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F251" t="s">
-        <v>753</v>
+        <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B252">
-        <f t="shared" si="22"/>
-        <v>27</v>
+        <f t="shared" si="23"/>
+        <v>18</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_27</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_18</v>
       </c>
       <c r="E252" t="str">
         <f>VLOOKUP(F252,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F252" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B253">
-        <f t="shared" si="22"/>
-        <v>28</v>
+        <f t="shared" si="23"/>
+        <v>19</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_28</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_19</v>
       </c>
       <c r="E253" t="str">
         <f>VLOOKUP(F253,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13284,214 +13308,421 @@
         <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B254">
-        <f t="shared" si="22"/>
-        <v>29</v>
+        <f t="shared" si="23"/>
+        <v>20</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_29</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_20</v>
       </c>
       <c r="E254" t="str">
         <f>VLOOKUP(F254,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F254" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B255">
-        <f t="shared" si="22"/>
-        <v>30</v>
+        <f t="shared" si="23"/>
+        <v>21</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_30</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_21</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F255" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B256">
-        <f t="shared" si="22"/>
-        <v>31</v>
+        <f t="shared" si="23"/>
+        <v>22</v>
       </c>
       <c r="C256" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_31</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_22</v>
       </c>
       <c r="E256" t="str">
         <f>VLOOKUP(F256,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F256" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B257">
-        <f t="shared" si="22"/>
-        <v>32</v>
+        <f t="shared" si="23"/>
+        <v>23</v>
       </c>
       <c r="C257" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_32</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_23</v>
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F257" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G257" s="3" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>756</v>
-      </c>
       <c r="B258">
-        <f t="shared" si="22"/>
-        <v>33</v>
+        <f t="shared" si="23"/>
+        <v>24</v>
       </c>
       <c r="C258" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_33</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_24</v>
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F258" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B259">
-        <f t="shared" si="22"/>
-        <v>34</v>
+        <f t="shared" si="23"/>
+        <v>25</v>
       </c>
       <c r="C259" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_34</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_25</v>
       </c>
       <c r="E259" t="str">
         <f>VLOOKUP(F259,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>FanJiang</v>
       </c>
       <c r="F259" t="s">
-        <v>5</v>
+        <v>744</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B260">
-        <f t="shared" si="22"/>
-        <v>35</v>
+        <f t="shared" si="23"/>
+        <v>26</v>
       </c>
       <c r="C260" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_35</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_26</v>
       </c>
       <c r="E260" t="str">
         <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F260" t="s">
-        <v>5</v>
+        <v>745</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B261">
-        <f t="shared" si="22"/>
-        <v>36</v>
+        <f t="shared" si="23"/>
+        <v>27</v>
       </c>
       <c r="C261" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_36</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_27</v>
       </c>
       <c r="E261" t="str">
         <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F261" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>751</v>
+        <v>736</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="B262">
-        <f t="shared" si="22"/>
-        <v>37</v>
+        <f t="shared" si="23"/>
+        <v>28</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" si="23"/>
-        <v>NODE_31_37</v>
+        <f t="shared" si="25"/>
+        <v>NODE_31_28</v>
       </c>
       <c r="E262" t="str">
         <f>VLOOKUP(F262,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F262" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>748</v>
+      </c>
+      <c r="B263">
+        <f t="shared" si="23"/>
+        <v>29</v>
+      </c>
+      <c r="C263" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_29</v>
+      </c>
+      <c r="E263" t="str">
+        <f>VLOOKUP(F263,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F263" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>748</v>
+      </c>
+      <c r="B264">
+        <f t="shared" si="23"/>
+        <v>30</v>
+      </c>
+      <c r="C264" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_30</v>
+      </c>
+      <c r="E264" t="str">
+        <f>VLOOKUP(F264,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F264" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>748</v>
+      </c>
+      <c r="B265">
+        <f t="shared" si="23"/>
+        <v>31</v>
+      </c>
+      <c r="C265" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_31</v>
+      </c>
+      <c r="E265" t="str">
+        <f>VLOOKUP(F265,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F265" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>748</v>
+      </c>
+      <c r="B266">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="C266" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_32</v>
+      </c>
+      <c r="E266" t="str">
+        <f>VLOOKUP(F266,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>LiuBei</v>
       </c>
-      <c r="F262" t="s">
+      <c r="F266" t="s">
         <v>5</v>
       </c>
-      <c r="G262" s="3" t="s">
-        <v>786</v>
+      <c r="G266" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>748</v>
+      </c>
+      <c r="B267">
+        <f t="shared" si="23"/>
+        <v>33</v>
+      </c>
+      <c r="C267" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_33</v>
+      </c>
+      <c r="E267" t="str">
+        <f>VLOOKUP(F267,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F267" t="s">
+        <v>5</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>748</v>
+      </c>
+      <c r="B268">
+        <f t="shared" si="23"/>
+        <v>34</v>
+      </c>
+      <c r="C268" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_34</v>
+      </c>
+      <c r="E268" t="str">
+        <f>VLOOKUP(F268,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F268" t="s">
+        <v>5</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>748</v>
+      </c>
+      <c r="B269">
+        <f t="shared" si="23"/>
+        <v>35</v>
+      </c>
+      <c r="C269" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_35</v>
+      </c>
+      <c r="E269" t="str">
+        <f>VLOOKUP(F269,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F269" t="s">
+        <v>5</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>748</v>
+      </c>
+      <c r="B270">
+        <f t="shared" si="23"/>
+        <v>36</v>
+      </c>
+      <c r="C270" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_36</v>
+      </c>
+      <c r="E270" t="str">
+        <f>VLOOKUP(F270,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F270" t="s">
+        <v>5</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>748</v>
+      </c>
+      <c r="B271">
+        <f t="shared" si="23"/>
+        <v>37</v>
+      </c>
+      <c r="C271" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_31_37</v>
+      </c>
+      <c r="E271" t="str">
+        <f>VLOOKUP(F271,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F271" t="s">
+        <v>5</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>776</v>
       </c>
     </row>
   </sheetData>
@@ -14099,7 +14330,7 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="F34" s="21"/>
     </row>
@@ -14116,7 +14347,7 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="F35" s="24"/>
     </row>
@@ -14133,7 +14364,7 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="F36" s="21"/>
     </row>
@@ -14193,7 +14424,7 @@
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -14201,7 +14432,7 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F40" s="21"/>
     </row>
@@ -14762,7 +14993,7 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="F72" s="21"/>
     </row>
@@ -14779,7 +15010,7 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="F73" s="24"/>
     </row>
@@ -14796,7 +15027,7 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>764</v>
+        <v>819</v>
       </c>
       <c r="F74" s="21"/>
     </row>
@@ -14856,7 +15087,7 @@
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -14864,7 +15095,7 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="F78" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AF9244-CA99-4008-9FD6-3F18BEA480B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8418DF0-241E-4B9E-AF1A-3D7F70F64723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="831">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2449,20 +2449,11 @@
 장수가 안량이오.</t>
   </si>
   <si>
-    <t>주군, 제가 관장군과 함께
-급습해 보겠습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이보시오, 당신이 관운장이오?
 우리 진영에 지금..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>와주셨군요, 관장군!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>역시 그대답소ㅋ 좋다!
 관공과 장료는 바로 출진하시오!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2506,10 +2497,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>으윽..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>흐음.. 갑자기 형님이 그립군..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2535,10 +2522,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>관장군! 말씀이 너무 지나치시오!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>순욱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2597,10 +2580,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>과연 대단하십니다, 관장군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하북 지역을 1년만에 평정하시고,
 쉬지도 않은 채 곧바로 형주 정벌이라니..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2611,11 +2590,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>하하하. 역시 관장군이오.
-대단하십니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>하하;;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2645,68 +2619,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>하하하! 수성의 달인이라더니
-1년을 못버티는군ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>.. - -+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅋㅋ 언제까지 내탓을 할꺼요?ㅋ
-유비가 그렇게 된건 사실은..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>음? 누구냐!?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>역시 관장군이오!! 허도로 귀환해서
-얼른 술에 취해 버립시다ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕하십니까, 관우님.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기억해주시는군요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기척도 없이? 누구지?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴히 드릴 말씀이 있습니다.
-시간을 좀 내주시지요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흥! 그대가 그 유명한 창술의 달인,
-상산 조자룡이로군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다들 먼저 귀환들 하시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.. 이보시오, 관장군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>형님, 저희 먼저 가십시다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이게 뭐하는 짓인가?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.. 어쩐 일인가?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2715,80 +2628,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이대로 가다가는..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안됩니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇군요. 알겠습니다.
-그 때 동안 화기를 잘 다루십시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나도 알고 있네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그럼 전 이만..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장군, 큰일났습니다.
-조승상께서 위험하십니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>음? 무슨 일인겐가?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금 허도에 악귀가 나타나
-도륙을 내고 있습니다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>악귀라고?? 어찌..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>모두가 공포에 질려 꿈적도 못합니다.
-승상을 구할 사람은 장군 밖에 없습니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.. 앞장 서시게..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>후훗, 기대가 되는군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아무래도 신선술을 익힌 모양이네만
-나의 상대가 될 순 없네.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>곧 마무리가 될테니..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도륙치고는.. 급소는 모두 피해
-생명에는 지장이 없지 않은가..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘 지냈느냐, 막내야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅎㅎㅎ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>.. 배불뚝이.. 짐승같은 눈매..
 아름답지 못한 턱수염.. 그리고..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2808,16 +2647,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>크읔..ㅋㅋ 무엇을 
-망설이는 것이냐?ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3년동안 제삿밥만 먹더니
-애꾸놈만도 못해진것이냐?ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>뭐냐!! 네 녀석이라면 충분히
 막을 수 있었을텐데.. 이놈!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2845,23 +2674,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내가 이 악귀의 심장을 뚫었다!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>크윽.. 형님..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>.. 막내야??</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>이..이런!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 이 세계는 끝이야.. 으으..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2892,14 +2709,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>뭐야!! 어떻게 알아챈 거냐!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>역시 난 똑똑해 캬캬캬..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NODE_31</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2967,10 +2776,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>나와 한 번 자웅을..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>네 놈의 목을 쳐그들의
 원한을 풀어주겠다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2978,41 +2783,6 @@
   <si>
     <t>가서 안량과 문추에게
 안부나 전해주시게. 에잇!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관우님도 느끼시고 있으실 겁니다.
-악귀의 기운을..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>어서 오거라, 안귀놈.
-피 냄새가 진동을 하는군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조조를 죽인다고 하니 달려오는군.
-내가 네놈을 찾으러 다닐 필요가 없지ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘 지내긴!! 3년상을 치르느라
-내가 얼마나.. 응?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>큭.. 이제 마지막인데,
-끝까지 반말이냐, 막내야?ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>난 형님을 죽이고 천하를
-공포로 떨어트린 악귀..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>너는.. 그 악귀를 물리친
-영웅이 되거라ㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3022,11 +2792,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>크..큰일났다!!
-악귀가 현생으로 소환된다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>자 그럼, 다음에 또 보자고~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3093,14 +2858,6 @@
   <si>
     <t>이이!! 저 자는 분명 관우지 않소!
 어떻게 된것이오 유비!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조운?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그냥 지나가 주시게. 조운.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3134,10 +2891,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>앗! 관장군!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>좋소! 나 조맹덕,
 관공과 하늘 앞에 맹세하겠소!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3148,10 +2901,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>네놈, 악귀가 되려는겐가..?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아무래도 미움을
 단단히 산 모양이군요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3166,11 +2915,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>흥! 아직 내가 나설 수
-없음을 감사히 여기쇼!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Enemy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3188,11 +2932,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지금도 상당히 볼만한데,
-어디까지 망가지려 하는가ㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>끝이군요. 이로써
 형주까지 우리 수중에..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3202,32 +2941,326 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그만두라고 이 자식아!!</t>
+    <t>사..살려주세요ㅜㅜ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"진정 무신은 전장의 귀신이 되려하는가"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으윽.. 이 악귀놈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으아악!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악귀..라..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으으..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어차피 살려줘봤자 나중에는
+복수한답시고 달려들테지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 아직 내가 나설 수
+없음을 감사히 여기거라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미리 싹을 없애버리는 것 또한
+전술 중 일부일 뿐ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멧돼지 같은게,
+엄청 빠르군.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>뭐하는거요, 장군.
-그는 일반 백성일 뿐이오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사..살려주세요ㅜㅜ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"진정 무신은 전장의 귀신이 되려하는가"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>으윽.. 이 악귀놈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>으아악!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>악귀..라..</t>
+그자는 그저 농사꾼이지 않소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐!? 그만두라고 이 자식아!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 전장을 피로 물들이더니,
+이제 백성까지 공격하는 것이냐!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어이가 없군ㅋㅋ
+악귀가 따로 없지 않은가ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 견고하던 강동을 평정하는데
+1년이 채 안걸리다니!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체통좀 지키시오, 형님.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무래도 신선술을
+익힌 모양이군..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>허나, 자네에게 내 목을
+내어줄 순 없네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>..? 무슨 말씀이신지..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇군요. 알겠습니다.
+그 때까지 화기를 잘 다루십시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(누구였지? 아무런 기척도
+못 느꼈었는데..)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아!! 큰일났습니다. 지금 허도에 괴물같은
+자가 나타나 궁으로 돌격하고 있습니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모두가 공포에 질려 꿈쩍도
+못하고 잇습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무래도 승상을 노리는 것 같은데,
+그 괴물을 상대할 자는 장군 밖에 없습니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.. 앞장 서시게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후훗..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와주셨군요, 관 장군!</t>
+  </si>
+  <si>
+    <t>주군, 제가 관 장군과 함께
+급습해 보겠습니다.</t>
+  </si>
+  <si>
+    <t>앗! 관 장군!</t>
+  </si>
+  <si>
+    <t>관 장군! 말씀이 너무 지나치시오!</t>
+  </si>
+  <si>
+    <t>과연 대단하십니다, 관 장군.</t>
+  </si>
+  <si>
+    <t>하하하. 역시 관 장군이오.
+대단하십니다!</t>
+  </si>
+  <si>
+    <t>ㅋㅋ 늦으시면 승상께서 내리신 술은
+내가 다 마셔버릴 거요! 캬캬캬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안됩니다. 더 늦었다간..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무슨일인가, 문원.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멈추어라! 폐하가 머무는
+곳에서 살육이라니!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 역적 놈이 어디서
+폐하 운운하느냐!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역적이라고??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동소라고 했던가? 네놈을 위왕에
+봉하라는 상소를 올렸다지?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥, 난 한 나라의 신하일 뿐,
+천하를 편안하게 하는 것 외엔 관심없다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으읔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>..? 관 장군?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 번개가 안치는군요, 승상.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3년동안 제삿밥만 먹더니
+살이 많이 빠졌구나, 막내야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!? 어..어떻게 안 것이냐!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이놈이!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3년상만 아니었어도.. 에잇!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>난 형님을 죽이고 천하를
+공포에 떨어트린 악귀..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(3년간 술과 고기를 멀리 하더니,
+무의의 경지에 올랐구나.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>겨우 이정도가 장익덕의 힘이더냐?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크윽..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제야 안심이구나ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는.. 그 악귀를 물리친
+영웅이 되는 것이다.. 크읔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내가 이 괴물같은 녀석의
+심장을 뚫었다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크읔.. 혀..형님..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 이 세계는 끝이야..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관우님도 느끼고 있으실 것입니다.
+아수라의 기운을..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크..큰일났다!!
+아수라가.. 소환된다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곧 죽을 놈이 말이 많구나!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 전장의 귀신! 관 장군이오!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캬캬! 또 말이 없으시군ㅋㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 귀환들 하시오.
+난 따로 볼일 좀 보고 가겠소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>!?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창끝이 더 날카로워졌군, 자룡.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그냥 지나가 주시게, 자룡.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곧 끝이 날 걸세.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럴 수만은 없다네..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알고 있네. 혹시..
+만약에 말일세..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>괴물치고는..
+급소는 모두 피했군.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으으.. 관 장군..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>.. 전 이만 가보겠습니다.
+늦기 전에 찾아뵙지요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음.. 알겠네.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6588,7 +6621,7 @@
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>757</v>
+        <v>713</v>
       </c>
       <c r="C93" s="27" t="s">
         <v>449</v>
@@ -6598,7 +6631,7 @@
         <v>NAME_ETC_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>744</v>
+        <v>702</v>
       </c>
       <c r="F93" s="38"/>
     </row>
@@ -6607,7 +6640,7 @@
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>758</v>
+        <v>714</v>
       </c>
       <c r="C94" s="27" t="s">
         <v>449</v>
@@ -6617,7 +6650,7 @@
         <v>NAME_ETC_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>745</v>
+        <v>703</v>
       </c>
       <c r="F94" s="38"/>
     </row>
@@ -7467,7 +7500,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J271"/>
+  <dimension ref="A1:J281"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -8308,7 +8341,7 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -8442,7 +8475,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>794</v>
+        <v>739</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8673,7 +8706,7 @@
         <v>7</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -8791,7 +8824,7 @@
         <v>406</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8815,7 +8848,7 @@
         <v>406</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8935,7 +8968,7 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>788</v>
+        <v>735</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -8959,7 +8992,7 @@
         <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>648</v>
+        <v>785</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -8983,7 +9016,7 @@
         <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>646</v>
+        <v>786</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -9103,7 +9136,7 @@
         <v>51</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9127,7 +9160,7 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>806</v>
+        <v>749</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9151,7 +9184,7 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>790</v>
+        <v>737</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
@@ -9177,7 +9210,7 @@
         <v>591</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9201,7 +9234,7 @@
         <v>589</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
@@ -9249,7 +9282,7 @@
         <v>591</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9273,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -9417,7 +9450,7 @@
         <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -9465,7 +9498,7 @@
         <v>5</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -9609,7 +9642,7 @@
         <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>760</v>
+        <v>716</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -9705,7 +9738,7 @@
         <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>791</v>
+        <v>738</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9852,7 +9885,7 @@
         <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -9879,7 +9912,7 @@
         <v>5</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -9933,7 +9966,7 @@
         <v>5</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10230,7 +10263,7 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>765</v>
+        <v>720</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10284,7 +10317,7 @@
         <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>766</v>
+        <v>721</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -10311,7 +10344,7 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -10338,12 +10371,12 @@
         <v>7</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -10360,12 +10393,12 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>762</v>
+        <v>718</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B122">
         <f t="shared" ref="B122:B159" si="13">B121+1</f>
@@ -10383,12 +10416,12 @@
         <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>786</v>
+        <v>733</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B123">
         <f t="shared" si="13"/>
@@ -10406,12 +10439,12 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>759</v>
+        <v>715</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B124">
         <f t="shared" si="13"/>
@@ -10429,12 +10462,12 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>783</v>
+        <v>730</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B125">
         <f t="shared" si="13"/>
@@ -10452,13 +10485,13 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>784</v>
+        <v>731</v>
       </c>
       <c r="J125" s="3"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B126">
         <f t="shared" si="13"/>
@@ -10476,12 +10509,12 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B127">
         <f t="shared" si="13"/>
@@ -10499,12 +10532,12 @@
         <v>51</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B128">
         <f t="shared" si="13"/>
@@ -10522,12 +10555,12 @@
         <v>51</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B129">
         <f t="shared" si="13"/>
@@ -10545,12 +10578,12 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>789</v>
+        <v>736</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B130">
         <f t="shared" si="13"/>
@@ -10568,12 +10601,12 @@
         <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>778</v>
+        <v>725</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B131">
         <f t="shared" si="13"/>
@@ -10591,12 +10624,12 @@
         <v>51</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B132">
         <f t="shared" si="13"/>
@@ -10614,12 +10647,12 @@
         <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>795</v>
+        <v>740</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B133">
         <f t="shared" si="13"/>
@@ -10637,12 +10670,12 @@
         <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>800</v>
+        <v>745</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B134">
         <f t="shared" si="13"/>
@@ -10660,12 +10693,12 @@
         <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>796</v>
+        <v>741</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B135">
         <f t="shared" si="13"/>
@@ -10683,12 +10716,12 @@
         <v>51</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B136">
         <f t="shared" si="13"/>
@@ -10703,15 +10736,15 @@
         <v>XunYu</v>
       </c>
       <c r="F136" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>665</v>
+        <v>788</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B137">
         <f t="shared" si="13"/>
@@ -10726,15 +10759,15 @@
         <v>XunYu</v>
       </c>
       <c r="F137" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>763</v>
+        <v>719</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B138">
         <f t="shared" si="13"/>
@@ -10752,12 +10785,12 @@
         <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>779</v>
+        <v>726</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B139">
         <f t="shared" si="13"/>
@@ -10772,15 +10805,15 @@
         <v>XunYu</v>
       </c>
       <c r="F139" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>797</v>
+        <v>742</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B140">
         <f t="shared" si="13"/>
@@ -10795,15 +10828,15 @@
         <v>XunYu</v>
       </c>
       <c r="F140" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B141">
         <f t="shared" si="13"/>
@@ -10821,12 +10854,12 @@
         <v>51</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B142">
         <f t="shared" si="13"/>
@@ -10841,15 +10874,15 @@
         <v>XunYu</v>
       </c>
       <c r="F142" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>780</v>
+        <v>727</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B143">
         <f t="shared" si="13"/>
@@ -10867,12 +10900,12 @@
         <v>51</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B144">
         <f t="shared" si="13"/>
@@ -10895,7 +10928,7 @@
     </row>
     <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B145">
         <f t="shared" si="13"/>
@@ -10913,12 +10946,12 @@
         <v>51</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B146">
         <f t="shared" si="13"/>
@@ -10936,12 +10969,12 @@
         <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>798</v>
+        <v>743</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B147">
         <f t="shared" si="13"/>
@@ -10959,12 +10992,12 @@
         <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>785</v>
+        <v>732</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B148">
         <f t="shared" si="13"/>
@@ -10982,12 +11015,12 @@
         <v>7</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B149">
         <f t="shared" si="13"/>
@@ -11005,12 +11038,12 @@
         <v>7</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B150">
         <f t="shared" si="13"/>
@@ -11028,12 +11061,12 @@
         <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>802</v>
+        <v>746</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B151">
         <f t="shared" si="13"/>
@@ -11051,12 +11084,12 @@
         <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>803</v>
+        <v>747</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B152">
         <f t="shared" si="13"/>
@@ -11071,15 +11104,15 @@
         <v>XunYu</v>
       </c>
       <c r="F152" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>781</v>
+        <v>728</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B153">
         <f t="shared" si="13"/>
@@ -11097,12 +11130,12 @@
         <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>799</v>
+        <v>744</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B154">
         <f t="shared" si="13"/>
@@ -11125,7 +11158,7 @@
     </row>
     <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B155">
         <f t="shared" si="13"/>
@@ -11143,12 +11176,12 @@
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>787</v>
+        <v>734</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B156">
         <f t="shared" si="13"/>
@@ -11166,12 +11199,12 @@
         <v>51</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B157">
         <f t="shared" si="13"/>
@@ -11189,12 +11222,12 @@
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>782</v>
+        <v>729</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B158">
         <f t="shared" si="13"/>
@@ -11212,12 +11245,12 @@
         <v>591</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B159">
         <f t="shared" si="13"/>
@@ -11235,12 +11268,12 @@
         <v>51</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -11257,15 +11290,15 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>679</v>
+        <v>789</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B162">
-        <f t="shared" ref="B162:B191" si="16">B161+1</f>
+        <f t="shared" ref="B162:B199" si="16">B161+1</f>
         <v>1</v>
       </c>
       <c r="C162" t="str">
@@ -11280,12 +11313,12 @@
         <v>591</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B163">
         <f t="shared" si="16"/>
@@ -11303,12 +11336,12 @@
         <v>7</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B164">
         <f t="shared" si="16"/>
@@ -11326,12 +11359,12 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>682</v>
+        <v>790</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B165">
         <f t="shared" si="16"/>
@@ -11354,7 +11387,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B166">
         <f t="shared" si="16"/>
@@ -11372,12 +11405,12 @@
         <v>406</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B167">
         <f t="shared" si="16"/>
@@ -11395,12 +11428,12 @@
         <v>406</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>807</v>
+        <v>750</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B168">
         <f t="shared" si="16"/>
@@ -11418,12 +11451,12 @@
         <v>407</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>805</v>
+        <v>748</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B169">
         <f t="shared" si="16"/>
@@ -11441,35 +11474,35 @@
         <v>7</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B170">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="C170" t="str">
-        <f t="shared" ref="C170:C177" si="18">CONCATENATE(A170, "_", B170, IF(D170&lt;&gt;"", "_"&amp;D170, ""))</f>
+        <f t="shared" ref="C170:C193" si="18">CONCATENATE(A170, "_", B170, IF(D170&lt;&gt;"", "_"&amp;D170, ""))</f>
         <v>NODE_28_9</v>
       </c>
       <c r="E170" t="str">
         <f>VLOOKUP(F170,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F170" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>597</v>
+        <v>728</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B171">
         <f t="shared" si="16"/>
@@ -11479,10 +11512,20 @@
         <f t="shared" si="18"/>
         <v>NODE_28_10</v>
       </c>
+      <c r="E171" t="str">
+        <f>VLOOKUP(F171,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F171" t="s">
+        <v>406</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B172">
         <f t="shared" si="16"/>
@@ -11492,94 +11535,83 @@
         <f t="shared" si="18"/>
         <v>NODE_28_11</v>
       </c>
-      <c r="E172" t="s">
-        <v>809</v>
-      </c>
-      <c r="F172" t="s">
-        <v>809</v>
-      </c>
-      <c r="G172" s="3" t="s">
-        <v>820</v>
-      </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B173">
         <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="C173" t="str">
-        <f t="shared" ref="C173:C191" si="19">CONCATENATE(A173, "_", B173, IF(D173&lt;&gt;"", "_"&amp;D173, ""))</f>
+        <f t="shared" si="18"/>
         <v>NODE_28_12</v>
       </c>
       <c r="E173" t="s">
-        <v>809</v>
+        <v>751</v>
       </c>
       <c r="F173" t="s">
-        <v>809</v>
+        <v>751</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>821</v>
+        <v>759</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B174">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="C174" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_13</v>
       </c>
-      <c r="E174" t="str">
-        <f>VLOOKUP(F174,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+      <c r="E174" t="s">
+        <v>751</v>
       </c>
       <c r="F174" t="s">
-        <v>7</v>
+        <v>751</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B175">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="C175" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_14</v>
       </c>
-      <c r="E175" t="str">
-        <f>VLOOKUP(F175,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+      <c r="E175" t="s">
+        <v>751</v>
       </c>
       <c r="F175" t="s">
-        <v>591</v>
+        <v>751</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>814</v>
+        <v>762</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B176">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="C176" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_15</v>
       </c>
       <c r="E176" t="str">
@@ -11590,19 +11622,19 @@
         <v>7</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B177">
         <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="C177" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_16</v>
       </c>
       <c r="E177" t="str">
@@ -11613,87 +11645,87 @@
         <v>591</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>815</v>
+        <v>755</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B178">
         <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="C178" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_17</v>
       </c>
-      <c r="E178" t="s">
-        <v>415</v>
+      <c r="E178" t="str">
+        <f>VLOOKUP(F178,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
       </c>
       <c r="F178" t="s">
-        <v>415</v>
+        <v>7</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B179">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="C179" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_18</v>
       </c>
       <c r="E179" t="str">
         <f>VLOOKUP(F179,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F179" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B180">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
       <c r="C180" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_19</v>
       </c>
-      <c r="E180" t="str">
-        <f>VLOOKUP(F180,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+      <c r="E180" t="s">
+        <v>415</v>
       </c>
       <c r="F180" t="s">
-        <v>7</v>
+        <v>415</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B181">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="C181" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_20</v>
       </c>
       <c r="E181" t="str">
@@ -11704,498 +11736,495 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B182">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
       <c r="C182" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_21</v>
       </c>
       <c r="E182" t="str">
         <f>VLOOKUP(F182,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F182" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>811</v>
+        <v>752</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B183">
         <f t="shared" si="16"/>
         <v>22</v>
       </c>
       <c r="C183" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_22</v>
       </c>
       <c r="E183" t="str">
         <f>VLOOKUP(F183,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F183" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>414</v>
+        <v>769</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B184">
         <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="C184" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_23</v>
       </c>
       <c r="E184" t="str">
         <f>VLOOKUP(F184,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F184" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>597</v>
+        <v>753</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B185">
         <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="C185" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_24</v>
       </c>
-      <c r="E185" t="s">
-        <v>685</v>
+      <c r="E185" t="str">
+        <f>VLOOKUP(F185,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
       </c>
       <c r="F185" t="s">
-        <v>685</v>
+        <v>7</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B186">
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="C186" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_25</v>
       </c>
       <c r="E186" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F186" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>813</v>
+        <v>765</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B187">
         <f t="shared" si="16"/>
         <v>26</v>
       </c>
       <c r="C187" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_26</v>
       </c>
-      <c r="E187" t="str">
-        <f>VLOOKUP(F187,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+      <c r="E187" t="s">
+        <v>679</v>
       </c>
       <c r="F187" t="s">
-        <v>7</v>
+        <v>679</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>594</v>
+        <v>754</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B188">
         <f t="shared" si="16"/>
         <v>27</v>
       </c>
       <c r="C188" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_27</v>
       </c>
       <c r="E188" t="str">
         <f>VLOOKUP(F188,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F188" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>686</v>
+        <v>594</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B189">
         <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="C189" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_28</v>
       </c>
-      <c r="E189" t="s">
-        <v>685</v>
+      <c r="E189" t="str">
+        <f>VLOOKUP(F189,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
       </c>
       <c r="F189" t="s">
-        <v>685</v>
+        <v>406</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B190">
         <f t="shared" si="16"/>
         <v>29</v>
       </c>
       <c r="C190" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_29</v>
       </c>
-      <c r="E190" t="s">
-        <v>685</v>
+      <c r="E190" t="str">
+        <f>VLOOKUP(F190,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangLiao</v>
       </c>
       <c r="F190" t="s">
-        <v>685</v>
+        <v>591</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B191">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="C191" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_30</v>
       </c>
-      <c r="E191" t="str">
-        <f>VLOOKUP(F191,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+      <c r="E191" t="s">
+        <v>679</v>
+      </c>
+      <c r="F191" t="s">
+        <v>679</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>681</v>
+      </c>
+      <c r="B192">
+        <f t="shared" si="16"/>
+        <v>31</v>
+      </c>
+      <c r="C192" t="str">
+        <f t="shared" si="18"/>
+        <v>NODE_28_31</v>
+      </c>
+      <c r="E192" t="str">
+        <f>VLOOKUP(F192,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>GuanYu</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F192" t="s">
         <v>7</v>
       </c>
-      <c r="G191" s="3" t="s">
-        <v>597</v>
+      <c r="G192" s="3" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <f t="shared" si="16"/>
+        <v>32</v>
       </c>
       <c r="C193" t="str">
-        <f t="shared" ref="C193:C194" si="20">CONCATENATE(A193, "_", B193, IF(D193&lt;&gt;"", "_"&amp;D193, ""))</f>
-        <v>NODE_29_0</v>
+        <f t="shared" si="18"/>
+        <v>NODE_28_32</v>
       </c>
       <c r="E193" t="str">
         <f>VLOOKUP(F193,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F193" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B194">
-        <f>B193+1</f>
-        <v>1</v>
+        <f t="shared" si="16"/>
+        <v>33</v>
       </c>
       <c r="C194" t="str">
-        <f t="shared" si="20"/>
-        <v>NODE_29_1</v>
-      </c>
-      <c r="E194" t="str">
-        <f>VLOOKUP(F194,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <f t="shared" ref="C194:C196" si="19">CONCATENATE(A194, "_", B194, IF(D194&lt;&gt;"", "_"&amp;D194, ""))</f>
+        <v>NODE_28_33</v>
+      </c>
+      <c r="E194" t="s">
+        <v>679</v>
       </c>
       <c r="F194" t="s">
-        <v>406</v>
+        <v>679</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B195">
-        <f t="shared" ref="B195:B232" si="21">B194+1</f>
-        <v>2</v>
+        <f t="shared" si="16"/>
+        <v>34</v>
       </c>
       <c r="C195" t="str">
-        <f t="shared" ref="C195:C232" si="22">CONCATENATE(A195, "_", B195, IF(D195&lt;&gt;"", "_"&amp;D195, ""))</f>
-        <v>NODE_29_2</v>
-      </c>
-      <c r="E195" t="str">
-        <f>VLOOKUP(F195,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_34</v>
+      </c>
+      <c r="E195" t="s">
+        <v>679</v>
       </c>
       <c r="F195" t="s">
-        <v>7</v>
+        <v>679</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>691</v>
+        <v>771</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B196">
-        <f t="shared" si="21"/>
-        <v>3</v>
+        <f t="shared" si="16"/>
+        <v>35</v>
       </c>
       <c r="C196" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_3</v>
-      </c>
-      <c r="E196" t="str">
-        <f>VLOOKUP(F196,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <f t="shared" si="19"/>
+        <v>NODE_28_35</v>
+      </c>
+      <c r="E196" t="s">
+        <v>679</v>
       </c>
       <c r="F196" t="s">
-        <v>406</v>
+        <v>679</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>692</v>
+        <v>764</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B197">
-        <f t="shared" si="21"/>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>36</v>
       </c>
       <c r="C197" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_4</v>
-      </c>
-      <c r="E197" t="str">
-        <f>VLOOKUP(F197,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <f t="shared" ref="C197:C199" si="20">CONCATENATE(A197, "_", B197, IF(D197&lt;&gt;"", "_"&amp;D197, ""))</f>
+        <v>NODE_28_36</v>
+      </c>
+      <c r="E197" t="s">
+        <v>679</v>
       </c>
       <c r="F197" t="s">
-        <v>591</v>
+        <v>679</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>693</v>
+        <v>805</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B198">
-        <f t="shared" si="21"/>
-        <v>5</v>
+        <f t="shared" si="16"/>
+        <v>37</v>
       </c>
       <c r="C198" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_5</v>
+        <f t="shared" si="20"/>
+        <v>NODE_28_37</v>
       </c>
       <c r="E198" t="str">
         <f>VLOOKUP(F198,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F198" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B199">
-        <f t="shared" si="21"/>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>38</v>
       </c>
       <c r="C199" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_6</v>
+        <f t="shared" si="20"/>
+        <v>NODE_28_38</v>
       </c>
       <c r="E199" t="str">
         <f>VLOOKUP(F199,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F199" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>689</v>
-      </c>
-      <c r="B200">
-        <f t="shared" si="21"/>
-        <v>7</v>
-      </c>
-      <c r="C200" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_7</v>
-      </c>
-      <c r="E200" t="str">
-        <f>VLOOKUP(F200,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F200" t="s">
-        <v>7</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B201">
-        <f t="shared" si="21"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C201" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_8</v>
+        <f t="shared" ref="C201:C202" si="21">CONCATENATE(A201, "_", B201, IF(D201&lt;&gt;"", "_"&amp;D201, ""))</f>
+        <v>NODE_29_0</v>
       </c>
       <c r="E201" t="str">
         <f>VLOOKUP(F201,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F201" t="s">
-        <v>11</v>
+        <v>406</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>696</v>
+        <v>772</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B202">
+        <f>B201+1</f>
+        <v>1</v>
+      </c>
+      <c r="C202" t="str">
         <f t="shared" si="21"/>
-        <v>9</v>
-      </c>
-      <c r="C202" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_9</v>
+        <v>NODE_29_1</v>
       </c>
       <c r="E202" t="str">
         <f>VLOOKUP(F202,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F202" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B203">
-        <f t="shared" si="21"/>
-        <v>10</v>
+        <f t="shared" ref="B203:B235" si="22">B202+1</f>
+        <v>2</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_10</v>
+        <f t="shared" ref="C203" si="23">CONCATENATE(A203, "_", B203, IF(D203&lt;&gt;"", "_"&amp;D203, ""))</f>
+        <v>NODE_29_2</v>
       </c>
       <c r="E203" t="str">
         <f>VLOOKUP(F203,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F203" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B204">
-        <f t="shared" si="21"/>
-        <v>11</v>
+        <f t="shared" si="22"/>
+        <v>3</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_11</v>
+        <f t="shared" ref="C204:C208" si="24">CONCATENATE(A204, "_", B204, IF(D204&lt;&gt;"", "_"&amp;D204, ""))</f>
+        <v>NODE_29_3</v>
       </c>
       <c r="E204" t="str">
         <f>VLOOKUP(F204,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12205,135 +12234,135 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B205">
-        <f t="shared" si="21"/>
-        <v>12</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_12</v>
+        <f t="shared" si="24"/>
+        <v>NODE_29_4</v>
       </c>
       <c r="E205" t="str">
         <f>VLOOKUP(F205,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F205" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B206">
-        <f t="shared" si="21"/>
-        <v>13</v>
+        <f t="shared" si="22"/>
+        <v>5</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_13</v>
+        <f t="shared" si="24"/>
+        <v>NODE_29_5</v>
       </c>
       <c r="E206" t="str">
         <f>VLOOKUP(F206,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F206" t="s">
-        <v>7</v>
+        <v>406</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>700</v>
+        <v>791</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B207">
-        <f t="shared" si="21"/>
-        <v>14</v>
+        <f t="shared" si="22"/>
+        <v>6</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_14</v>
+        <f t="shared" si="24"/>
+        <v>NODE_29_6</v>
       </c>
       <c r="E207" t="str">
         <f>VLOOKUP(F207,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>XiahouYuan</v>
       </c>
       <c r="F207" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>701</v>
+        <v>773</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B208">
-        <f t="shared" si="21"/>
-        <v>15</v>
+        <f t="shared" si="22"/>
+        <v>7</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_15</v>
+        <f t="shared" si="24"/>
+        <v>NODE_29_7</v>
       </c>
       <c r="E208" t="str">
         <f>VLOOKUP(F208,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouYuan</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F208" t="s">
-        <v>407</v>
+        <v>591</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>702</v>
+        <v>610</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B209">
-        <f t="shared" si="21"/>
-        <v>16</v>
+        <f t="shared" si="22"/>
+        <v>8</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_16</v>
+        <f t="shared" ref="C209:C232" si="25">CONCATENATE(A209, "_", B209, IF(D209&lt;&gt;"", "_"&amp;D209, ""))</f>
+        <v>NODE_29_8</v>
       </c>
       <c r="E209" t="str">
         <f>VLOOKUP(F209,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F209" t="s">
-        <v>406</v>
+        <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>597</v>
+        <v>821</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B210">
-        <f t="shared" si="21"/>
-        <v>17</v>
+        <f t="shared" si="22"/>
+        <v>9</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_17</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_9</v>
       </c>
       <c r="E210" t="str">
         <f>VLOOKUP(F210,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12343,20 +12372,20 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>703</v>
+        <v>822</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B211">
-        <f t="shared" si="21"/>
-        <v>18</v>
+        <f t="shared" si="22"/>
+        <v>10</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_18</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_10</v>
       </c>
       <c r="E211" t="str">
         <f>VLOOKUP(F211,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12366,20 +12395,20 @@
         <v>11</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>705</v>
+        <v>685</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B212">
-        <f t="shared" si="21"/>
-        <v>19</v>
+        <f t="shared" si="22"/>
+        <v>11</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_19</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_11</v>
       </c>
       <c r="E212" t="str">
         <f>VLOOKUP(F212,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12389,20 +12418,20 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>597</v>
+        <v>825</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B213">
-        <f t="shared" si="21"/>
-        <v>20</v>
+        <f t="shared" si="22"/>
+        <v>12</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_20</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_12</v>
       </c>
       <c r="E213" t="str">
         <f>VLOOKUP(F213,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12412,43 +12441,43 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B214">
-        <f t="shared" si="21"/>
-        <v>21</v>
+        <f t="shared" si="22"/>
+        <v>13</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_21</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_13</v>
       </c>
       <c r="E214" t="str">
         <f>VLOOKUP(F214,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F214" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B215">
-        <f t="shared" si="21"/>
-        <v>22</v>
+        <f t="shared" si="22"/>
+        <v>14</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_22</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_14</v>
       </c>
       <c r="E215" t="str">
         <f>VLOOKUP(F215,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12458,20 +12487,20 @@
         <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B216">
-        <f t="shared" si="21"/>
-        <v>23</v>
+        <f t="shared" si="22"/>
+        <v>15</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_23</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_15</v>
       </c>
       <c r="E216" t="str">
         <f>VLOOKUP(F216,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12481,20 +12510,20 @@
         <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B217">
-        <f t="shared" si="21"/>
-        <v>24</v>
+        <f t="shared" si="22"/>
+        <v>16</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_24</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_16</v>
       </c>
       <c r="E217" t="str">
         <f>VLOOKUP(F217,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12504,20 +12533,20 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>718</v>
+        <v>823</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B218">
-        <f t="shared" si="21"/>
-        <v>25</v>
+        <f t="shared" si="22"/>
+        <v>17</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_25</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_17</v>
       </c>
       <c r="E218" t="str">
         <f>VLOOKUP(F218,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12527,20 +12556,20 @@
         <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>597</v>
+        <v>792</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B219">
-        <f t="shared" si="21"/>
-        <v>26</v>
+        <f t="shared" si="22"/>
+        <v>18</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_26</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_18</v>
       </c>
       <c r="E219" t="str">
         <f>VLOOKUP(F219,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12550,20 +12579,20 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>719</v>
+        <v>824</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B220">
-        <f t="shared" si="21"/>
-        <v>27</v>
+        <f t="shared" si="22"/>
+        <v>19</v>
       </c>
       <c r="C220" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_27</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_19</v>
       </c>
       <c r="E220" t="str">
         <f>VLOOKUP(F220,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12578,15 +12607,15 @@
     </row>
     <row r="221" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B221">
-        <f t="shared" si="21"/>
-        <v>28</v>
+        <f t="shared" si="22"/>
+        <v>20</v>
       </c>
       <c r="C221" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_28</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_20</v>
       </c>
       <c r="E221" t="str">
         <f>VLOOKUP(F221,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12596,20 +12625,20 @@
         <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B222">
-        <f t="shared" si="21"/>
-        <v>29</v>
+        <f t="shared" si="22"/>
+        <v>21</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_29</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_21</v>
       </c>
       <c r="E222" t="str">
         <f>VLOOKUP(F222,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12619,43 +12648,43 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>709</v>
+        <v>826</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B223">
-        <f t="shared" si="21"/>
-        <v>30</v>
+        <f t="shared" si="22"/>
+        <v>22</v>
       </c>
       <c r="C223" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_30</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_22</v>
       </c>
       <c r="E223" t="str">
         <f>VLOOKUP(F223,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F223" t="s">
-        <v>406</v>
+        <v>591</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B224">
-        <f t="shared" si="21"/>
-        <v>31</v>
+        <f t="shared" si="22"/>
+        <v>23</v>
       </c>
       <c r="C224" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_31</v>
+        <f t="shared" si="25"/>
+        <v>NODE_29_23</v>
       </c>
       <c r="E224" t="str">
         <f>VLOOKUP(F224,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12665,181 +12694,181 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B225">
-        <f t="shared" si="21"/>
-        <v>32</v>
+        <f t="shared" si="22"/>
+        <v>24</v>
       </c>
       <c r="C225" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_32</v>
+        <f t="shared" ref="C225:C235" si="26">CONCATENATE(A225, "_", B225, IF(D225&lt;&gt;"", "_"&amp;D225, ""))</f>
+        <v>NODE_29_24</v>
       </c>
       <c r="E225" t="str">
         <f>VLOOKUP(F225,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F225" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B226">
-        <f t="shared" si="21"/>
-        <v>33</v>
+        <f t="shared" si="22"/>
+        <v>25</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_33</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_25</v>
       </c>
       <c r="E226" t="str">
         <f>VLOOKUP(F226,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F226" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B227">
-        <f t="shared" si="21"/>
-        <v>34</v>
+        <f t="shared" si="22"/>
+        <v>26</v>
       </c>
       <c r="C227" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_34</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_26</v>
       </c>
       <c r="E227" t="str">
         <f>VLOOKUP(F227,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F227" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B228">
-        <f t="shared" si="21"/>
-        <v>35</v>
+        <f t="shared" si="22"/>
+        <v>27</v>
       </c>
       <c r="C228" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_35</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_27</v>
       </c>
       <c r="E228" t="str">
         <f>VLOOKUP(F228,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F228" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B229">
-        <f t="shared" si="21"/>
-        <v>36</v>
+        <f t="shared" si="22"/>
+        <v>28</v>
       </c>
       <c r="C229" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_36</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_28</v>
       </c>
       <c r="E229" t="str">
         <f>VLOOKUP(F229,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F229" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B230">
-        <f t="shared" si="21"/>
-        <v>37</v>
+        <f t="shared" si="22"/>
+        <v>29</v>
       </c>
       <c r="C230" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_37</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_29</v>
       </c>
       <c r="E230" t="str">
         <f>VLOOKUP(F230,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F230" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>716</v>
+        <v>781</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B231">
-        <f t="shared" si="21"/>
-        <v>38</v>
+        <f t="shared" si="22"/>
+        <v>30</v>
       </c>
       <c r="C231" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_38</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_30</v>
       </c>
       <c r="E231" t="str">
         <f>VLOOKUP(F231,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F231" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>720</v>
+        <v>782</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B232">
-        <f t="shared" si="21"/>
-        <v>39</v>
+        <f t="shared" si="22"/>
+        <v>31</v>
       </c>
       <c r="C232" t="str">
-        <f t="shared" si="22"/>
-        <v>NODE_29_39</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_31</v>
       </c>
       <c r="E232" t="str">
         <f>VLOOKUP(F232,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12849,111 +12878,111 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>683</v>
+      </c>
+      <c r="B233">
+        <f t="shared" si="22"/>
+        <v>32</v>
+      </c>
+      <c r="C233" t="str">
+        <f t="shared" si="26"/>
+        <v>NODE_29_32</v>
+      </c>
+      <c r="E233" t="str">
+        <f>VLOOKUP(F233,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>XiahouDun</v>
+      </c>
+      <c r="F233" t="s">
+        <v>406</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>748</v>
+        <v>683</v>
       </c>
       <c r="B234">
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>33</v>
       </c>
       <c r="C234" t="str">
-        <f>CONCATENATE(A234, "_", B234, IF(D234&lt;&gt;"", "_"&amp;D234, ""))</f>
-        <v>NODE_31_0</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_33</v>
       </c>
       <c r="E234" t="str">
         <f>VLOOKUP(F234,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F234" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>748</v>
+        <v>683</v>
       </c>
       <c r="B235">
-        <f t="shared" ref="B235:B271" si="23">B234+1</f>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>34</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" ref="C235" si="24">CONCATENATE(A235, "_", B235, IF(D235&lt;&gt;"", "_"&amp;D235, ""))</f>
-        <v>NODE_31_1</v>
+        <f t="shared" si="26"/>
+        <v>NODE_29_34</v>
       </c>
       <c r="E235" t="str">
         <f>VLOOKUP(F235,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F235" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>748</v>
-      </c>
-      <c r="B236">
-        <f t="shared" si="23"/>
-        <v>2</v>
-      </c>
-      <c r="C236" t="str">
-        <f t="shared" ref="C236:C271" si="25">CONCATENATE(A236, "_", B236, IF(D236&lt;&gt;"", "_"&amp;D236, ""))</f>
-        <v>NODE_31_2</v>
-      </c>
-      <c r="E236" t="str">
-        <f>VLOOKUP(F236,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F236" t="s">
-        <v>7</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>597</v>
+        <v>784</v>
       </c>
     </row>
     <row r="237" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B237">
-        <f t="shared" si="23"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C237" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_3</v>
+        <f>CONCATENATE(A237, "_", B237, IF(D237&lt;&gt;"", "_"&amp;D237, ""))</f>
+        <v>NODE_31_0</v>
       </c>
       <c r="E237" t="str">
         <f>VLOOKUP(F237,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F237" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B238">
-        <f t="shared" si="23"/>
-        <v>4</v>
+        <f t="shared" ref="B238:B281" si="27">B237+1</f>
+        <v>1</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_4</v>
+        <f t="shared" ref="C238" si="28">CONCATENATE(A238, "_", B238, IF(D238&lt;&gt;"", "_"&amp;D238, ""))</f>
+        <v>NODE_31_1</v>
       </c>
       <c r="E238" t="str">
         <f>VLOOKUP(F238,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -12963,43 +12992,43 @@
         <v>9</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>747</v>
+        <v>795</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B239">
-        <f t="shared" si="23"/>
-        <v>5</v>
+        <f t="shared" si="27"/>
+        <v>2</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_5</v>
+        <f t="shared" ref="C239:C281" si="29">CONCATENATE(A239, "_", B239, IF(D239&lt;&gt;"", "_"&amp;D239, ""))</f>
+        <v>NODE_31_2</v>
       </c>
       <c r="E239" t="str">
         <f>VLOOKUP(F239,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F239" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>721</v>
+        <v>796</v>
       </c>
     </row>
     <row r="240" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B240">
-        <f t="shared" si="23"/>
-        <v>6</v>
+        <f t="shared" si="27"/>
+        <v>3</v>
       </c>
       <c r="C240" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_6</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_3</v>
       </c>
       <c r="E240" t="str">
         <f>VLOOKUP(F240,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13009,43 +13038,43 @@
         <v>9</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B241">
-        <f t="shared" si="23"/>
-        <v>7</v>
+        <f t="shared" si="27"/>
+        <v>4</v>
       </c>
       <c r="C241" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_7</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_4</v>
       </c>
       <c r="E241" t="str">
         <f>VLOOKUP(F241,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F241" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B242">
-        <f t="shared" si="23"/>
-        <v>8</v>
+        <f t="shared" si="27"/>
+        <v>5</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_8</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_5</v>
       </c>
       <c r="E242" t="str">
         <f>VLOOKUP(F242,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13055,20 +13084,20 @@
         <v>7</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B243">
-        <f t="shared" si="23"/>
-        <v>9</v>
+        <f t="shared" si="27"/>
+        <v>6</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_9</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_6</v>
       </c>
       <c r="E243" t="str">
         <f>VLOOKUP(F243,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13078,66 +13107,66 @@
         <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>724</v>
+        <v>817</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B244">
-        <f t="shared" si="23"/>
-        <v>10</v>
+        <f t="shared" si="27"/>
+        <v>7</v>
       </c>
       <c r="C244" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_10</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_7</v>
       </c>
       <c r="E244" t="str">
         <f>VLOOKUP(F244,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F244" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B245">
-        <f t="shared" si="23"/>
-        <v>11</v>
+        <f t="shared" si="27"/>
+        <v>8</v>
       </c>
       <c r="C245" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_11</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_8</v>
       </c>
       <c r="E245" t="str">
         <f>VLOOKUP(F245,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F245" t="s">
+        <v>51</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>704</v>
+      </c>
+      <c r="B246">
+        <f t="shared" si="27"/>
         <v>9</v>
       </c>
-      <c r="G245" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>748</v>
-      </c>
-      <c r="B246">
-        <f t="shared" si="23"/>
-        <v>12</v>
-      </c>
       <c r="C246" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_12</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_9</v>
       </c>
       <c r="E246" t="str">
         <f>VLOOKUP(F246,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13147,158 +13176,158 @@
         <v>7</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B247">
-        <f t="shared" si="23"/>
-        <v>13</v>
+        <f t="shared" si="27"/>
+        <v>10</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_13</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_10</v>
       </c>
       <c r="E247" t="str">
         <f>VLOOKUP(F247,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F247" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>728</v>
+        <v>679</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B248">
-        <f t="shared" si="23"/>
-        <v>14</v>
+        <f t="shared" si="27"/>
+        <v>11</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_14</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_11</v>
       </c>
       <c r="E248" t="str">
         <f>VLOOKUP(F248,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F248" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>658</v>
+        <v>804</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B249">
-        <f t="shared" si="23"/>
-        <v>15</v>
+        <f t="shared" si="27"/>
+        <v>12</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_15</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_12</v>
       </c>
       <c r="E249" t="str">
         <f>VLOOKUP(F249,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F249" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B250">
-        <f t="shared" si="23"/>
-        <v>16</v>
+        <f t="shared" si="27"/>
+        <v>13</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_16</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_13</v>
       </c>
       <c r="E250" t="str">
         <f>VLOOKUP(F250,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F250" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B251">
-        <f t="shared" si="23"/>
-        <v>17</v>
+        <f t="shared" si="27"/>
+        <v>14</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_17</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_14</v>
       </c>
       <c r="E251" t="str">
         <f>VLOOKUP(F251,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F251" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>730</v>
+        <v>686</v>
       </c>
     </row>
     <row r="252" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B252">
-        <f t="shared" si="23"/>
-        <v>18</v>
+        <f t="shared" si="27"/>
+        <v>15</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_18</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_15</v>
       </c>
       <c r="E252" t="str">
         <f>VLOOKUP(F252,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F252" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B253">
-        <f t="shared" si="23"/>
-        <v>19</v>
+        <f t="shared" si="27"/>
+        <v>16</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_19</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_16</v>
       </c>
       <c r="E253" t="str">
         <f>VLOOKUP(F253,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13308,20 +13337,20 @@
         <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>773</v>
+        <v>688</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B254">
-        <f t="shared" si="23"/>
-        <v>20</v>
+        <f t="shared" si="27"/>
+        <v>17</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_20</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_17</v>
       </c>
       <c r="E254" t="str">
         <f>VLOOKUP(F254,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13331,20 +13360,20 @@
         <v>9</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B255">
-        <f t="shared" si="23"/>
-        <v>21</v>
+        <f t="shared" si="27"/>
+        <v>18</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_21</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_18</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13354,135 +13383,135 @@
         <v>7</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>774</v>
+        <v>807</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B256">
-        <f t="shared" si="23"/>
-        <v>22</v>
+        <f t="shared" si="27"/>
+        <v>19</v>
       </c>
       <c r="C256" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_22</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_19</v>
       </c>
       <c r="E256" t="str">
         <f>VLOOKUP(F256,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F256" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B257">
-        <f t="shared" si="23"/>
-        <v>23</v>
+        <f t="shared" si="27"/>
+        <v>20</v>
       </c>
       <c r="C257" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_23</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_20</v>
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F257" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>733</v>
+        <v>804</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B258">
-        <f t="shared" si="23"/>
-        <v>24</v>
+        <f t="shared" si="27"/>
+        <v>21</v>
       </c>
       <c r="C258" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_24</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_21</v>
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F258" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B259">
-        <f t="shared" si="23"/>
-        <v>25</v>
+        <f t="shared" si="27"/>
+        <v>22</v>
       </c>
       <c r="C259" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_25</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_22</v>
       </c>
       <c r="E259" t="str">
         <f>VLOOKUP(F259,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F259" t="s">
-        <v>744</v>
+        <v>9</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>734</v>
+        <v>690</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B260">
-        <f t="shared" si="23"/>
-        <v>26</v>
+        <f t="shared" si="27"/>
+        <v>23</v>
       </c>
       <c r="C260" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_26</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_23</v>
       </c>
       <c r="E260" t="str">
         <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>GuanYu</v>
       </c>
       <c r="F260" t="s">
-        <v>745</v>
+        <v>7</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>735</v>
+        <v>810</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B261">
-        <f t="shared" si="23"/>
-        <v>27</v>
+        <f t="shared" si="27"/>
+        <v>24</v>
       </c>
       <c r="C261" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_27</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_24</v>
       </c>
       <c r="E261" t="str">
         <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13492,20 +13521,20 @@
         <v>9</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B262">
-        <f t="shared" si="23"/>
-        <v>28</v>
+        <f t="shared" si="27"/>
+        <v>25</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_28</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_25</v>
       </c>
       <c r="E262" t="str">
         <f>VLOOKUP(F262,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13515,214 +13544,444 @@
         <v>7</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B263">
-        <f t="shared" si="23"/>
-        <v>29</v>
+        <f t="shared" si="27"/>
+        <v>26</v>
       </c>
       <c r="C263" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_29</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_26</v>
       </c>
       <c r="E263" t="str">
         <f>VLOOKUP(F263,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F263" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>738</v>
+        <v>811</v>
       </c>
     </row>
     <row r="264" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B264">
-        <f t="shared" si="23"/>
-        <v>30</v>
+        <f t="shared" si="27"/>
+        <v>27</v>
       </c>
       <c r="C264" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_30</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_27</v>
       </c>
       <c r="E264" t="str">
         <f>VLOOKUP(F264,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F264" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B265">
-        <f t="shared" si="23"/>
-        <v>31</v>
+        <f t="shared" si="27"/>
+        <v>28</v>
       </c>
       <c r="C265" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_31</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_28</v>
       </c>
       <c r="E265" t="str">
         <f>VLOOKUP(F265,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F265" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B266">
-        <f t="shared" si="23"/>
-        <v>32</v>
+        <f t="shared" si="27"/>
+        <v>29</v>
       </c>
       <c r="C266" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_32</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_29</v>
       </c>
       <c r="E266" t="str">
         <f>VLOOKUP(F266,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F266" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>740</v>
+        <v>693</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B267">
-        <f t="shared" si="23"/>
-        <v>33</v>
+        <f t="shared" si="27"/>
+        <v>30</v>
       </c>
       <c r="C267" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_33</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_30</v>
       </c>
       <c r="E267" t="str">
         <f>VLOOKUP(F267,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F267" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B268">
-        <f t="shared" si="23"/>
-        <v>34</v>
+        <f t="shared" si="27"/>
+        <v>31</v>
       </c>
       <c r="C268" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_34</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_31</v>
       </c>
       <c r="E268" t="str">
         <f>VLOOKUP(F268,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F268" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B269">
-        <f t="shared" si="23"/>
-        <v>35</v>
+        <f t="shared" si="27"/>
+        <v>32</v>
       </c>
       <c r="C269" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_35</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_32</v>
       </c>
       <c r="E269" t="str">
         <f>VLOOKUP(F269,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>FanJiang</v>
       </c>
       <c r="F269" t="s">
-        <v>5</v>
+        <v>702</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>742</v>
+        <v>695</v>
       </c>
     </row>
     <row r="270" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B270">
-        <f t="shared" si="23"/>
-        <v>36</v>
+        <f t="shared" si="27"/>
+        <v>33</v>
       </c>
       <c r="C270" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_36</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_33</v>
       </c>
       <c r="E270" t="str">
         <f>VLOOKUP(F270,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F270" t="s">
-        <v>5</v>
+        <v>703</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>743</v>
+        <v>812</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>748</v>
+        <v>704</v>
       </c>
       <c r="B271">
-        <f t="shared" si="23"/>
-        <v>37</v>
+        <f t="shared" si="27"/>
+        <v>34</v>
       </c>
       <c r="C271" t="str">
-        <f t="shared" si="25"/>
-        <v>NODE_31_37</v>
+        <f t="shared" si="29"/>
+        <v>NODE_31_34</v>
       </c>
       <c r="E271" t="str">
         <f>VLOOKUP(F271,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F271" t="s">
+        <v>9</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>704</v>
+      </c>
+      <c r="B272">
+        <f t="shared" si="27"/>
+        <v>35</v>
+      </c>
+      <c r="C272" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_35</v>
+      </c>
+      <c r="E272" t="str">
+        <f>VLOOKUP(F272,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F272" t="s">
+        <v>7</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>704</v>
+      </c>
+      <c r="B273">
+        <f t="shared" si="27"/>
+        <v>36</v>
+      </c>
+      <c r="C273" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_36</v>
+      </c>
+      <c r="E273" t="str">
+        <f>VLOOKUP(F273,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F273" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>704</v>
+      </c>
+      <c r="B274">
+        <f t="shared" si="27"/>
+        <v>37</v>
+      </c>
+      <c r="C274" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_37</v>
+      </c>
+      <c r="E274" t="str">
+        <f>VLOOKUP(F274,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F274" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>704</v>
+      </c>
+      <c r="B275">
+        <f t="shared" si="27"/>
+        <v>38</v>
+      </c>
+      <c r="C275" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_38</v>
+      </c>
+      <c r="E275" t="str">
+        <f>VLOOKUP(F275,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F275" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>704</v>
+      </c>
+      <c r="B276">
+        <f t="shared" si="27"/>
+        <v>39</v>
+      </c>
+      <c r="C276" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_39</v>
+      </c>
+      <c r="E276" t="str">
+        <f>VLOOKUP(F276,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>LiuBei</v>
       </c>
-      <c r="F271" t="s">
+      <c r="F276" t="s">
         <v>5</v>
       </c>
-      <c r="G271" s="3" t="s">
-        <v>776</v>
+      <c r="G276" s="3" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>704</v>
+      </c>
+      <c r="B277">
+        <f t="shared" si="27"/>
+        <v>40</v>
+      </c>
+      <c r="C277" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_40</v>
+      </c>
+      <c r="E277" t="str">
+        <f>VLOOKUP(F277,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F277" t="s">
+        <v>5</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>704</v>
+      </c>
+      <c r="B278">
+        <f t="shared" si="27"/>
+        <v>41</v>
+      </c>
+      <c r="C278" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_41</v>
+      </c>
+      <c r="E278" t="str">
+        <f>VLOOKUP(F278,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F278" t="s">
+        <v>5</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>704</v>
+      </c>
+      <c r="B279">
+        <f t="shared" si="27"/>
+        <v>42</v>
+      </c>
+      <c r="C279" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_42</v>
+      </c>
+      <c r="E279" t="str">
+        <f>VLOOKUP(F279,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F279" t="s">
+        <v>5</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>704</v>
+      </c>
+      <c r="B280">
+        <f t="shared" si="27"/>
+        <v>43</v>
+      </c>
+      <c r="C280" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_43</v>
+      </c>
+      <c r="E280" t="str">
+        <f>VLOOKUP(F280,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F280" t="s">
+        <v>5</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>704</v>
+      </c>
+      <c r="B281">
+        <f t="shared" si="27"/>
+        <v>44</v>
+      </c>
+      <c r="C281" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31_44</v>
+      </c>
+      <c r="E281" t="str">
+        <f>VLOOKUP(F281,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F281" t="s">
+        <v>5</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -14330,7 +14589,7 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>750</v>
+        <v>706</v>
       </c>
       <c r="F34" s="21"/>
     </row>
@@ -14347,7 +14606,7 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>751</v>
+        <v>707</v>
       </c>
       <c r="F35" s="24"/>
     </row>
@@ -14364,7 +14623,7 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>752</v>
+        <v>708</v>
       </c>
       <c r="F36" s="21"/>
     </row>
@@ -14424,7 +14683,7 @@
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>749</v>
+        <v>705</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -14432,7 +14691,7 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>753</v>
+        <v>709</v>
       </c>
       <c r="F40" s="21"/>
     </row>
@@ -14993,7 +15252,7 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>754</v>
+        <v>710</v>
       </c>
       <c r="F72" s="21"/>
     </row>
@@ -15010,7 +15269,7 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>755</v>
+        <v>711</v>
       </c>
       <c r="F73" s="24"/>
     </row>
@@ -15027,7 +15286,7 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>819</v>
+        <v>758</v>
       </c>
       <c r="F74" s="21"/>
     </row>
@@ -15087,7 +15346,7 @@
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>749</v>
+        <v>705</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -15095,7 +15354,7 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>756</v>
+        <v>712</v>
       </c>
       <c r="F78" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8418DF0-241E-4B9E-AF1A-3D7F70F64723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF147D-57C5-464B-8439-04821376B7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="833">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2989,11 +2989,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>뭐하는거요, 장군.
-그자는 그저 농사꾼이지 않소.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>뭐!? 그만두라고 이 자식아!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3084,10 +3079,6 @@
     <t>과연 대단하십니다, 관 장군.</t>
   </si>
   <si>
-    <t>하하하. 역시 관 장군이오.
-대단하십니다!</t>
-  </si>
-  <si>
     <t>ㅋㅋ 늦으시면 승상께서 내리신 술은
 내가 다 마셔버릴 거요! 캬캬캬</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3125,14 +3116,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>으읔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>..? 관 장군?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이번에는 번개가 안치는군요, 승상.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3199,16 +3182,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>크..큰일났다!!
-아수라가.. 소환된다..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>곧 죽을 놈이 말이 많구나!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>역시 전장의 귀신! 관 장군이오!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3246,21 +3220,57 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>괴물치고는..
-급소는 모두 피했군.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>으으.. 관 장군..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>.. 전 이만 가보겠습니다.
 늦기 전에 찾아뵙지요.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>음.. 알겠네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급소는 모두 빗겨갔군.
+괴물치고는..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸을 추스리시오.
+다녀와서 그대의 술잔을 받도록 하지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캬캬캬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>으으.. 관형..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하. 역시 관형이오.
+대단하십니다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐하는거요, 관형.
+그자는 그저 농사꾼이지 않소.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역시 전장의 귀신이오!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이야앗!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>..? 관공?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크..큰일났다!!
+아수라가.. 현현한다..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7500,7 +7510,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J281"/>
+  <dimension ref="A1:J285"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -8992,7 +9002,7 @@
         <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9016,7 +9026,7 @@
         <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -10509,7 +10519,7 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
@@ -10739,7 +10749,7 @@
         <v>662</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -11290,7 +11300,7 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -11359,7 +11369,7 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -11736,7 +11746,7 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>768</v>
+        <v>828</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -11782,7 +11792,7 @@
         <v>406</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -11963,7 +11973,7 @@
         <v>679</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12053,7 +12063,7 @@
         <v>679</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12097,7 +12107,7 @@
         <v>679</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,7 +12175,7 @@
         <v>406</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,7 +12198,7 @@
         <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -12196,11 +12206,11 @@
         <v>683</v>
       </c>
       <c r="B203">
-        <f t="shared" ref="B203:B235" si="22">B202+1</f>
+        <f t="shared" ref="B203:B239" si="22">B202+1</f>
         <v>2</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" ref="C203" si="23">CONCATENATE(A203, "_", B203, IF(D203&lt;&gt;"", "_"&amp;D203, ""))</f>
+        <f t="shared" ref="C203:C239" si="23">CONCATENATE(A203, "_", B203, IF(D203&lt;&gt;"", "_"&amp;D203, ""))</f>
         <v>NODE_29_2</v>
       </c>
       <c r="E203" t="str">
@@ -12223,7 +12233,7 @@
         <v>3</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" ref="C204:C208" si="24">CONCATENATE(A204, "_", B204, IF(D204&lt;&gt;"", "_"&amp;D204, ""))</f>
+        <f t="shared" si="23"/>
         <v>NODE_29_3</v>
       </c>
       <c r="E204" t="str">
@@ -12234,7 +12244,7 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12246,7 +12256,7 @@
         <v>4</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_4</v>
       </c>
       <c r="E205" t="str">
@@ -12257,7 +12267,7 @@
         <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12269,7 +12279,7 @@
         <v>5</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_5</v>
       </c>
       <c r="E206" t="str">
@@ -12280,7 +12290,7 @@
         <v>406</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -12292,7 +12302,7 @@
         <v>6</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_6</v>
       </c>
       <c r="E207" t="str">
@@ -12303,7 +12313,7 @@
         <v>407</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
@@ -12315,7 +12325,7 @@
         <v>7</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_7</v>
       </c>
       <c r="E208" t="str">
@@ -12338,7 +12348,7 @@
         <v>8</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" ref="C209:C232" si="25">CONCATENATE(A209, "_", B209, IF(D209&lt;&gt;"", "_"&amp;D209, ""))</f>
+        <f t="shared" si="23"/>
         <v>NODE_29_8</v>
       </c>
       <c r="E209" t="str">
@@ -12349,7 +12359,7 @@
         <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -12361,7 +12371,7 @@
         <v>9</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_9</v>
       </c>
       <c r="E210" t="str">
@@ -12372,7 +12382,7 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12384,7 +12394,7 @@
         <v>10</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_10</v>
       </c>
       <c r="E211" t="str">
@@ -12407,7 +12417,7 @@
         <v>11</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_11</v>
       </c>
       <c r="E212" t="str">
@@ -12418,7 +12428,7 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12430,7 +12440,7 @@
         <v>12</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_12</v>
       </c>
       <c r="E213" t="str">
@@ -12441,7 +12451,7 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12453,7 +12463,7 @@
         <v>13</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_13</v>
       </c>
       <c r="E214" t="str">
@@ -12464,7 +12474,7 @@
         <v>7</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12476,7 +12486,7 @@
         <v>14</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_14</v>
       </c>
       <c r="E215" t="str">
@@ -12487,7 +12497,7 @@
         <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -12499,7 +12509,7 @@
         <v>15</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_15</v>
       </c>
       <c r="E216" t="str">
@@ -12510,7 +12520,7 @@
         <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -12522,7 +12532,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_16</v>
       </c>
       <c r="E217" t="str">
@@ -12533,7 +12543,7 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -12545,7 +12555,7 @@
         <v>17</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_17</v>
       </c>
       <c r="E218" t="str">
@@ -12556,7 +12566,7 @@
         <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -12568,7 +12578,7 @@
         <v>18</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_18</v>
       </c>
       <c r="E219" t="str">
@@ -12579,7 +12589,7 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -12591,7 +12601,7 @@
         <v>19</v>
       </c>
       <c r="C220" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_19</v>
       </c>
       <c r="E220" t="str">
@@ -12614,7 +12624,7 @@
         <v>20</v>
       </c>
       <c r="C221" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_20</v>
       </c>
       <c r="E221" t="str">
@@ -12625,7 +12635,7 @@
         <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12637,7 +12647,7 @@
         <v>21</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_21</v>
       </c>
       <c r="E222" t="str">
@@ -12648,7 +12658,7 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -12660,7 +12670,7 @@
         <v>22</v>
       </c>
       <c r="C223" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_22</v>
       </c>
       <c r="E223" t="str">
@@ -12683,7 +12693,7 @@
         <v>23</v>
       </c>
       <c r="C224" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_23</v>
       </c>
       <c r="E224" t="str">
@@ -12694,7 +12704,7 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -12706,7 +12716,7 @@
         <v>24</v>
       </c>
       <c r="C225" t="str">
-        <f t="shared" ref="C225:C235" si="26">CONCATENATE(A225, "_", B225, IF(D225&lt;&gt;"", "_"&amp;D225, ""))</f>
+        <f t="shared" si="23"/>
         <v>NODE_29_24</v>
       </c>
       <c r="E225" t="str">
@@ -12717,7 +12727,7 @@
         <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12729,7 +12739,7 @@
         <v>25</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_25</v>
       </c>
       <c r="E226" t="str">
@@ -12740,7 +12750,7 @@
         <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -12752,7 +12762,7 @@
         <v>26</v>
       </c>
       <c r="C227" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_26</v>
       </c>
       <c r="E227" t="str">
@@ -12763,7 +12773,7 @@
         <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12775,7 +12785,7 @@
         <v>27</v>
       </c>
       <c r="C228" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_27</v>
       </c>
       <c r="E228" t="str">
@@ -12786,7 +12796,7 @@
         <v>591</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -12798,7 +12808,7 @@
         <v>28</v>
       </c>
       <c r="C229" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_28</v>
       </c>
       <c r="E229" t="str">
@@ -12809,7 +12819,7 @@
         <v>7</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12821,7 +12831,7 @@
         <v>29</v>
       </c>
       <c r="C230" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_29</v>
       </c>
       <c r="E230" t="str">
@@ -12832,7 +12842,7 @@
         <v>591</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12844,7 +12854,7 @@
         <v>30</v>
       </c>
       <c r="C231" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_30</v>
       </c>
       <c r="E231" t="str">
@@ -12855,7 +12865,7 @@
         <v>591</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -12867,7 +12877,7 @@
         <v>31</v>
       </c>
       <c r="C232" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_31</v>
       </c>
       <c r="E232" t="str">
@@ -12878,7 +12888,7 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -12890,21 +12900,11 @@
         <v>32</v>
       </c>
       <c r="C233" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_32</v>
       </c>
-      <c r="E233" t="str">
-        <f>VLOOKUP(F233,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>XiahouDun</v>
-      </c>
-      <c r="F233" t="s">
-        <v>406</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>683</v>
       </c>
@@ -12913,7 +12913,7 @@
         <v>33</v>
       </c>
       <c r="C234" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_33</v>
       </c>
       <c r="E234" t="str">
@@ -12924,10 +12924,10 @@
         <v>7</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>683</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v>34</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>NODE_29_34</v>
       </c>
       <c r="E235" t="str">
@@ -12947,98 +12947,99 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>683</v>
+      </c>
+      <c r="B236">
+        <f t="shared" si="22"/>
+        <v>35</v>
+      </c>
+      <c r="C236" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29_35</v>
+      </c>
+      <c r="E236" t="str">
+        <f>VLOOKUP(F236,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F236" t="s">
+        <v>7</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="B237">
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>36</v>
       </c>
       <c r="C237" t="str">
-        <f>CONCATENATE(A237, "_", B237, IF(D237&lt;&gt;"", "_"&amp;D237, ""))</f>
-        <v>NODE_31_0</v>
+        <f t="shared" si="23"/>
+        <v>NODE_29_36</v>
       </c>
       <c r="E237" t="str">
         <f>VLOOKUP(F237,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F237" t="s">
-        <v>51</v>
+        <v>406</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>794</v>
+        <v>826</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="B238">
-        <f t="shared" ref="B238:B281" si="27">B237+1</f>
-        <v>1</v>
+        <f t="shared" si="22"/>
+        <v>37</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" ref="C238" si="28">CONCATENATE(A238, "_", B238, IF(D238&lt;&gt;"", "_"&amp;D238, ""))</f>
-        <v>NODE_31_1</v>
+        <f t="shared" ref="C238:C239" si="24">CONCATENATE(A238, "_", B238, IF(D238&lt;&gt;"", "_"&amp;D238, ""))</f>
+        <v>NODE_29_37</v>
       </c>
       <c r="E238" t="str">
         <f>VLOOKUP(F238,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F238" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>795</v>
+        <v>824</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="B239">
-        <f t="shared" si="27"/>
-        <v>2</v>
+        <f t="shared" si="22"/>
+        <v>38</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" ref="C239:C281" si="29">CONCATENATE(A239, "_", B239, IF(D239&lt;&gt;"", "_"&amp;D239, ""))</f>
-        <v>NODE_31_2</v>
+        <f t="shared" si="24"/>
+        <v>NODE_29_38</v>
       </c>
       <c r="E239" t="str">
         <f>VLOOKUP(F239,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>XiahouDun</v>
       </c>
       <c r="F239" t="s">
-        <v>51</v>
+        <v>406</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>704</v>
-      </c>
-      <c r="B240">
-        <f t="shared" si="27"/>
-        <v>3</v>
-      </c>
-      <c r="C240" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_3</v>
-      </c>
-      <c r="E240" t="str">
-        <f>VLOOKUP(F240,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
-      </c>
-      <c r="F240" t="s">
-        <v>9</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
     </row>
     <row r="241" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13046,12 +13047,11 @@
         <v>704</v>
       </c>
       <c r="B241">
-        <f t="shared" si="27"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C241" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_4</v>
+        <f>CONCATENATE(A241, "_", B241, IF(D241&lt;&gt;"", "_"&amp;D241, ""))</f>
+        <v>NODE_31_0</v>
       </c>
       <c r="E241" t="str">
         <f>VLOOKUP(F241,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13061,30 +13061,30 @@
         <v>51</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>704</v>
       </c>
       <c r="B242">
-        <f t="shared" si="27"/>
-        <v>5</v>
+        <f t="shared" ref="B242:B285" si="25">B241+1</f>
+        <v>1</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_5</v>
+        <f t="shared" ref="C242" si="26">CONCATENATE(A242, "_", B242, IF(D242&lt;&gt;"", "_"&amp;D242, ""))</f>
+        <v>NODE_31_1</v>
       </c>
       <c r="E242" t="str">
         <f>VLOOKUP(F242,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F242" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>597</v>
+        <v>793</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -13092,58 +13092,58 @@
         <v>704</v>
       </c>
       <c r="B243">
-        <f t="shared" si="27"/>
-        <v>6</v>
+        <f t="shared" si="25"/>
+        <v>2</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_6</v>
+        <f t="shared" ref="C243:C285" si="27">CONCATENATE(A243, "_", B243, IF(D243&lt;&gt;"", "_"&amp;D243, ""))</f>
+        <v>NODE_31_2</v>
       </c>
       <c r="E243" t="str">
         <f>VLOOKUP(F243,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F243" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>704</v>
       </c>
       <c r="B244">
+        <f t="shared" si="25"/>
+        <v>3</v>
+      </c>
+      <c r="C244" t="str">
         <f t="shared" si="27"/>
-        <v>7</v>
-      </c>
-      <c r="C244" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_7</v>
+        <v>NODE_31_3</v>
       </c>
       <c r="E244" t="str">
         <f>VLOOKUP(F244,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F244" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>704</v>
       </c>
       <c r="B245">
+        <f t="shared" si="25"/>
+        <v>4</v>
+      </c>
+      <c r="C245" t="str">
         <f t="shared" si="27"/>
-        <v>8</v>
-      </c>
-      <c r="C245" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_8</v>
+        <v>NODE_31_4</v>
       </c>
       <c r="E245" t="str">
         <f>VLOOKUP(F245,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13153,7 +13153,7 @@
         <v>51</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -13161,12 +13161,12 @@
         <v>704</v>
       </c>
       <c r="B246">
+        <f t="shared" si="25"/>
+        <v>5</v>
+      </c>
+      <c r="C246" t="str">
         <f t="shared" si="27"/>
-        <v>9</v>
-      </c>
-      <c r="C246" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_9</v>
+        <v>NODE_31_5</v>
       </c>
       <c r="E246" t="str">
         <f>VLOOKUP(F246,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13176,7 +13176,7 @@
         <v>7</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>801</v>
+        <v>597</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -13184,22 +13184,22 @@
         <v>704</v>
       </c>
       <c r="B247">
+        <f t="shared" si="25"/>
+        <v>6</v>
+      </c>
+      <c r="C247" t="str">
         <f t="shared" si="27"/>
-        <v>10</v>
-      </c>
-      <c r="C247" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_10</v>
+        <v>NODE_31_6</v>
       </c>
       <c r="E247" t="str">
         <f>VLOOKUP(F247,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F247" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>679</v>
+        <v>812</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -13207,45 +13207,45 @@
         <v>704</v>
       </c>
       <c r="B248">
+        <f t="shared" si="25"/>
+        <v>7</v>
+      </c>
+      <c r="C248" t="str">
         <f t="shared" si="27"/>
-        <v>11</v>
-      </c>
-      <c r="C248" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_11</v>
+        <v>NODE_31_7</v>
       </c>
       <c r="E248" t="str">
         <f>VLOOKUP(F248,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F248" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>704</v>
       </c>
       <c r="B249">
+        <f t="shared" si="25"/>
+        <v>8</v>
+      </c>
+      <c r="C249" t="str">
         <f t="shared" si="27"/>
-        <v>12</v>
-      </c>
-      <c r="C249" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_12</v>
+        <v>NODE_31_8</v>
       </c>
       <c r="E249" t="str">
         <f>VLOOKUP(F249,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F249" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>802</v>
+        <v>831</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -13253,58 +13253,58 @@
         <v>704</v>
       </c>
       <c r="B250">
+        <f t="shared" si="25"/>
+        <v>9</v>
+      </c>
+      <c r="C250" t="str">
         <f t="shared" si="27"/>
-        <v>13</v>
-      </c>
-      <c r="C250" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_13</v>
+        <v>NODE_31_9</v>
       </c>
       <c r="E250" t="str">
         <f>VLOOKUP(F250,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F250" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>704</v>
       </c>
       <c r="B251">
+        <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+      <c r="C251" t="str">
         <f t="shared" si="27"/>
-        <v>14</v>
-      </c>
-      <c r="C251" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_14</v>
+        <v>NODE_31_10</v>
       </c>
       <c r="E251" t="str">
         <f>VLOOKUP(F251,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F251" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>704</v>
       </c>
       <c r="B252">
+        <f t="shared" si="25"/>
+        <v>11</v>
+      </c>
+      <c r="C252" t="str">
         <f t="shared" si="27"/>
-        <v>15</v>
-      </c>
-      <c r="C252" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_15</v>
+        <v>NODE_31_11</v>
       </c>
       <c r="E252" t="str">
         <f>VLOOKUP(F252,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13314,20 +13314,20 @@
         <v>9</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>704</v>
       </c>
       <c r="B253">
+        <f t="shared" si="25"/>
+        <v>12</v>
+      </c>
+      <c r="C253" t="str">
         <f t="shared" si="27"/>
-        <v>16</v>
-      </c>
-      <c r="C253" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_16</v>
+        <v>NODE_31_12</v>
       </c>
       <c r="E253" t="str">
         <f>VLOOKUP(F253,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13337,20 +13337,20 @@
         <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>704</v>
       </c>
       <c r="B254">
+        <f t="shared" si="25"/>
+        <v>13</v>
+      </c>
+      <c r="C254" t="str">
         <f t="shared" si="27"/>
-        <v>17</v>
-      </c>
-      <c r="C254" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_17</v>
+        <v>NODE_31_13</v>
       </c>
       <c r="E254" t="str">
         <f>VLOOKUP(F254,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13360,7 +13360,7 @@
         <v>9</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>689</v>
+        <v>799</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13368,12 +13368,12 @@
         <v>704</v>
       </c>
       <c r="B255">
+        <f t="shared" si="25"/>
+        <v>14</v>
+      </c>
+      <c r="C255" t="str">
         <f t="shared" si="27"/>
-        <v>18</v>
-      </c>
-      <c r="C255" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_18</v>
+        <v>NODE_31_14</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13383,30 +13383,30 @@
         <v>7</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>704</v>
       </c>
       <c r="B256">
+        <f t="shared" si="25"/>
+        <v>15</v>
+      </c>
+      <c r="C256" t="str">
         <f t="shared" si="27"/>
-        <v>19</v>
-      </c>
-      <c r="C256" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_19</v>
+        <v>NODE_31_15</v>
       </c>
       <c r="E256" t="str">
         <f>VLOOKUP(F256,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F256" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>808</v>
+        <v>687</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -13414,45 +13414,45 @@
         <v>704</v>
       </c>
       <c r="B257">
+        <f t="shared" si="25"/>
+        <v>16</v>
+      </c>
+      <c r="C257" t="str">
         <f t="shared" si="27"/>
-        <v>20</v>
-      </c>
-      <c r="C257" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_20</v>
+        <v>NODE_31_16</v>
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F257" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>704</v>
       </c>
       <c r="B258">
+        <f t="shared" si="25"/>
+        <v>17</v>
+      </c>
+      <c r="C258" t="str">
         <f t="shared" si="27"/>
-        <v>21</v>
-      </c>
-      <c r="C258" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_21</v>
+        <v>NODE_31_17</v>
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F258" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>809</v>
+        <v>689</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13460,22 +13460,22 @@
         <v>704</v>
       </c>
       <c r="B259">
+        <f t="shared" si="25"/>
+        <v>18</v>
+      </c>
+      <c r="C259" t="str">
         <f t="shared" si="27"/>
-        <v>22</v>
-      </c>
-      <c r="C259" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_22</v>
+        <v>NODE_31_18</v>
       </c>
       <c r="E259" t="str">
         <f>VLOOKUP(F259,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F259" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>690</v>
+        <v>803</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -13483,12 +13483,12 @@
         <v>704</v>
       </c>
       <c r="B260">
+        <f t="shared" si="25"/>
+        <v>19</v>
+      </c>
+      <c r="C260" t="str">
         <f t="shared" si="27"/>
-        <v>23</v>
-      </c>
-      <c r="C260" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_23</v>
+        <v>NODE_31_19</v>
       </c>
       <c r="E260" t="str">
         <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13498,7 +13498,7 @@
         <v>7</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -13506,12 +13506,12 @@
         <v>704</v>
       </c>
       <c r="B261">
+        <f t="shared" si="25"/>
+        <v>20</v>
+      </c>
+      <c r="C261" t="str">
         <f t="shared" si="27"/>
-        <v>24</v>
-      </c>
-      <c r="C261" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_24</v>
+        <v>NODE_31_20</v>
       </c>
       <c r="E261" t="str">
         <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13521,20 +13521,20 @@
         <v>9</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>704</v>
       </c>
       <c r="B262">
+        <f t="shared" si="25"/>
+        <v>21</v>
+      </c>
+      <c r="C262" t="str">
         <f t="shared" si="27"/>
-        <v>25</v>
-      </c>
-      <c r="C262" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_25</v>
+        <v>NODE_31_21</v>
       </c>
       <c r="E262" t="str">
         <f>VLOOKUP(F262,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13544,7 +13544,7 @@
         <v>7</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13552,91 +13552,91 @@
         <v>704</v>
       </c>
       <c r="B263">
+        <f t="shared" si="25"/>
+        <v>22</v>
+      </c>
+      <c r="C263" t="str">
         <f t="shared" si="27"/>
-        <v>26</v>
-      </c>
-      <c r="C263" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_26</v>
+        <v>NODE_31_22</v>
       </c>
       <c r="E263" t="str">
         <f>VLOOKUP(F263,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F263" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>704</v>
       </c>
       <c r="B264">
+        <f t="shared" si="25"/>
+        <v>23</v>
+      </c>
+      <c r="C264" t="str">
         <f t="shared" si="27"/>
-        <v>27</v>
-      </c>
-      <c r="C264" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_27</v>
+        <v>NODE_31_23</v>
       </c>
       <c r="E264" t="str">
         <f>VLOOKUP(F264,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F264" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>704</v>
       </c>
       <c r="B265">
+        <f t="shared" si="25"/>
+        <v>24</v>
+      </c>
+      <c r="C265" t="str">
         <f t="shared" si="27"/>
-        <v>28</v>
-      </c>
-      <c r="C265" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_28</v>
+        <v>NODE_31_24</v>
       </c>
       <c r="E265" t="str">
         <f>VLOOKUP(F265,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F265" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>704</v>
       </c>
       <c r="B266">
+        <f t="shared" si="25"/>
+        <v>25</v>
+      </c>
+      <c r="C266" t="str">
         <f t="shared" si="27"/>
-        <v>29</v>
-      </c>
-      <c r="C266" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_29</v>
+        <v>NODE_31_25</v>
       </c>
       <c r="E266" t="str">
         <f>VLOOKUP(F266,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F266" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>693</v>
+        <v>802</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13644,12 +13644,12 @@
         <v>704</v>
       </c>
       <c r="B267">
+        <f t="shared" si="25"/>
+        <v>26</v>
+      </c>
+      <c r="C267" t="str">
         <f t="shared" si="27"/>
-        <v>30</v>
-      </c>
-      <c r="C267" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_30</v>
+        <v>NODE_31_26</v>
       </c>
       <c r="E267" t="str">
         <f>VLOOKUP(F267,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13659,20 +13659,20 @@
         <v>7</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>704</v>
       </c>
       <c r="B268">
+        <f t="shared" si="25"/>
+        <v>27</v>
+      </c>
+      <c r="C268" t="str">
         <f t="shared" si="27"/>
-        <v>31</v>
-      </c>
-      <c r="C268" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_31</v>
+        <v>NODE_31_27</v>
       </c>
       <c r="E268" t="str">
         <f>VLOOKUP(F268,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13682,76 +13682,76 @@
         <v>9</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>704</v>
       </c>
       <c r="B269">
+        <f t="shared" si="25"/>
+        <v>28</v>
+      </c>
+      <c r="C269" t="str">
         <f t="shared" si="27"/>
-        <v>32</v>
-      </c>
-      <c r="C269" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_32</v>
+        <v>NODE_31_28</v>
       </c>
       <c r="E269" t="str">
         <f>VLOOKUP(F269,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>GuanYu</v>
       </c>
       <c r="F269" t="s">
-        <v>702</v>
+        <v>7</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>704</v>
       </c>
       <c r="B270">
+        <f t="shared" si="25"/>
+        <v>29</v>
+      </c>
+      <c r="C270" t="str">
         <f t="shared" si="27"/>
-        <v>33</v>
-      </c>
-      <c r="C270" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_33</v>
+        <v>NODE_31_29</v>
       </c>
       <c r="E270" t="str">
         <f>VLOOKUP(F270,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F270" t="s">
-        <v>703</v>
+        <v>9</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>704</v>
       </c>
       <c r="B271">
+        <f t="shared" si="25"/>
+        <v>30</v>
+      </c>
+      <c r="C271" t="str">
         <f t="shared" si="27"/>
-        <v>34</v>
-      </c>
-      <c r="C271" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_34</v>
+        <v>NODE_31_30</v>
       </c>
       <c r="E271" t="str">
         <f>VLOOKUP(F271,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F271" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>813</v>
+        <v>694</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -13759,22 +13759,22 @@
         <v>704</v>
       </c>
       <c r="B272">
+        <f t="shared" si="25"/>
+        <v>31</v>
+      </c>
+      <c r="C272" t="str">
         <f t="shared" si="27"/>
-        <v>35</v>
-      </c>
-      <c r="C272" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_35</v>
+        <v>NODE_31_31</v>
       </c>
       <c r="E272" t="str">
         <f>VLOOKUP(F272,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F272" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>696</v>
+        <v>594</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -13782,22 +13782,22 @@
         <v>704</v>
       </c>
       <c r="B273">
+        <f t="shared" si="25"/>
+        <v>32</v>
+      </c>
+      <c r="C273" t="str">
         <f t="shared" si="27"/>
-        <v>36</v>
-      </c>
-      <c r="C273" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_36</v>
+        <v>NODE_31_32</v>
       </c>
       <c r="E273" t="str">
         <f>VLOOKUP(F273,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>FanJiang</v>
       </c>
       <c r="F273" t="s">
-        <v>11</v>
+        <v>702</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13805,22 +13805,22 @@
         <v>704</v>
       </c>
       <c r="B274">
+        <f t="shared" si="25"/>
+        <v>33</v>
+      </c>
+      <c r="C274" t="str">
         <f t="shared" si="27"/>
-        <v>37</v>
-      </c>
-      <c r="C274" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_37</v>
+        <v>NODE_31_33</v>
       </c>
       <c r="E274" t="str">
         <f>VLOOKUP(F274,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F274" t="s">
-        <v>11</v>
+        <v>703</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -13828,22 +13828,22 @@
         <v>704</v>
       </c>
       <c r="B275">
+        <f t="shared" si="25"/>
+        <v>34</v>
+      </c>
+      <c r="C275" t="str">
         <f t="shared" si="27"/>
-        <v>38</v>
-      </c>
-      <c r="C275" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_38</v>
+        <v>NODE_31_34</v>
       </c>
       <c r="E275" t="str">
         <f>VLOOKUP(F275,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F275" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -13851,45 +13851,45 @@
         <v>704</v>
       </c>
       <c r="B276">
+        <f t="shared" si="25"/>
+        <v>35</v>
+      </c>
+      <c r="C276" t="str">
         <f t="shared" si="27"/>
-        <v>39</v>
-      </c>
-      <c r="C276" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_39</v>
+        <v>NODE_31_35</v>
       </c>
       <c r="E276" t="str">
         <f>VLOOKUP(F276,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F276" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>704</v>
       </c>
       <c r="B277">
+        <f t="shared" si="25"/>
+        <v>36</v>
+      </c>
+      <c r="C277" t="str">
         <f t="shared" si="27"/>
-        <v>40</v>
-      </c>
-      <c r="C277" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_40</v>
+        <v>NODE_31_36</v>
       </c>
       <c r="E277" t="str">
         <f>VLOOKUP(F277,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F277" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13897,58 +13897,58 @@
         <v>704</v>
       </c>
       <c r="B278">
+        <f t="shared" si="25"/>
+        <v>37</v>
+      </c>
+      <c r="C278" t="str">
         <f t="shared" si="27"/>
-        <v>41</v>
-      </c>
-      <c r="C278" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_41</v>
+        <v>NODE_31_37</v>
       </c>
       <c r="E278" t="str">
         <f>VLOOKUP(F278,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F278" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>704</v>
       </c>
       <c r="B279">
+        <f t="shared" si="25"/>
+        <v>38</v>
+      </c>
+      <c r="C279" t="str">
         <f t="shared" si="27"/>
-        <v>42</v>
-      </c>
-      <c r="C279" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_42</v>
+        <v>NODE_31_38</v>
       </c>
       <c r="E279" t="str">
         <f>VLOOKUP(F279,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F279" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>704</v>
       </c>
       <c r="B280">
+        <f t="shared" si="25"/>
+        <v>39</v>
+      </c>
+      <c r="C280" t="str">
         <f t="shared" si="27"/>
-        <v>43</v>
-      </c>
-      <c r="C280" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_43</v>
+        <v>NODE_31_39</v>
       </c>
       <c r="E280" t="str">
         <f>VLOOKUP(F280,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13958,20 +13958,20 @@
         <v>5</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>704</v>
       </c>
       <c r="B281">
+        <f t="shared" si="25"/>
+        <v>40</v>
+      </c>
+      <c r="C281" t="str">
         <f t="shared" si="27"/>
-        <v>44</v>
-      </c>
-      <c r="C281" t="str">
-        <f t="shared" si="29"/>
-        <v>NODE_31_44</v>
+        <v>NODE_31_40</v>
       </c>
       <c r="E281" t="str">
         <f>VLOOKUP(F281,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
@@ -13981,6 +13981,98 @@
         <v>5</v>
       </c>
       <c r="G281" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>704</v>
+      </c>
+      <c r="B282">
+        <f t="shared" si="25"/>
+        <v>41</v>
+      </c>
+      <c r="C282" t="str">
+        <f t="shared" si="27"/>
+        <v>NODE_31_41</v>
+      </c>
+      <c r="E282" t="str">
+        <f>VLOOKUP(F282,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F282" t="s">
+        <v>5</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>704</v>
+      </c>
+      <c r="B283">
+        <f t="shared" si="25"/>
+        <v>42</v>
+      </c>
+      <c r="C283" t="str">
+        <f t="shared" si="27"/>
+        <v>NODE_31_42</v>
+      </c>
+      <c r="E283" t="str">
+        <f>VLOOKUP(F283,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F283" t="s">
+        <v>5</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>704</v>
+      </c>
+      <c r="B284">
+        <f t="shared" si="25"/>
+        <v>43</v>
+      </c>
+      <c r="C284" t="str">
+        <f t="shared" si="27"/>
+        <v>NODE_31_43</v>
+      </c>
+      <c r="E284" t="str">
+        <f>VLOOKUP(F284,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F284" t="s">
+        <v>5</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>704</v>
+      </c>
+      <c r="B285">
+        <f t="shared" si="25"/>
+        <v>44</v>
+      </c>
+      <c r="C285" t="str">
+        <f t="shared" si="27"/>
+        <v>NODE_31_44</v>
+      </c>
+      <c r="E285" t="str">
+        <f>VLOOKUP(F285,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F285" t="s">
+        <v>5</v>
+      </c>
+      <c r="G285" s="3" t="s">
         <v>723</v>
       </c>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DF147D-57C5-464B-8439-04821376B7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AD3BC1-1DFB-42A7-A16D-DD08348502CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="843">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2633,15 +2633,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시끄럽다!! 첫째 형님을 죽음으로 몰고,
-역적 조조에게 붙어버린 배신자놈!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅋㅋㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>뭐냐!? 어찌하여 공격을
 하지 않는 것이냐!?</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2665,29 +2656,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>백성들에게는 그런 신의 존재가 필요하다.
-그러니 네가..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하하.. 잡았다..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.. 막내야??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이..이런!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>아으.. 바쁘다 바빠!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>신선이 되자마자
-무르게 생겼네..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2796,11 +2769,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일단 악귀가 소환되는
-것은 막아야지..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그대는 그대의 일을 하시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3092,40 +3060,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>멈추어라! 폐하가 머무는
-곳에서 살육이라니!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흥! 역적 놈이 어디서
-폐하 운운하느냐!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>역적이라고??</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>동소라고 했던가? 네놈을 위왕에
-봉하라는 상소를 올렸다지?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>흥, 난 한 나라의 신하일 뿐,
-천하를 편안하게 하는 것 외엔 관심없다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 번개가 안치는군요, 승상.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3년동안 제삿밥만 먹더니
-살이 많이 빠졌구나, 막내야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>!? 어..어떻게 안 것이냐!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3147,10 +3082,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>겨우 이정도가 장익덕의 힘이더냐?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>크윽..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3164,15 +3095,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>내가 이 괴물같은 녀석의
-심장을 뚫었다!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>크읔.. 혀..형님..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이제 이 세계는 끝이야..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3182,10 +3104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>곧 죽을 놈이 말이 많구나!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>캬캬! 또 말이 없으시군ㅋㅋ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3239,10 +3157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>캬캬캬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>으으.. 관형..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3271,6 +3185,138 @@
   <si>
     <t>크..큰일났다!!
 아수라가.. 현현한다..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멈추어라!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 역적 놈이 
+명을 재촉하는군ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋ 악귀놈, 이제야 온 것이냐ㅋ
+어차피 네놈 또한..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고생하긴 했지.. 음??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭐야!! 어떻게 안것이냐, 네놈!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3년동안 제삿밥만 먹더니
+살이 좀 빠졌구나, 막내야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아깝군. 이대로만 갔어도 
+좋은 흐름이었는데..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 두 놈은 어느 시간선에서든
+문제만 일으키는군 - -+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 아수라가 현현하는 건
+막아야한다.. 시간을 되돌릴 수 밖에..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 괴물같은 넘..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어휴.. 죽이지 않고 패는게
+더 힘들구만..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> '동소'라고 했던가? 네 놈을 위왕에
+봉하라는 상소를 올렸다지?ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어리석은!! 난 한 나라의 신하일 뿐,
+천하를 편안하게 하는 것 외엔 관심없다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋ 곧 죽을 놈이 말이 많구나!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>..번개?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋㅋ 오거라ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시끄럽다!! 큰 형님을 죽음으로 몰고,
+역적 조조에게 붙어버린 배신자놈!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 번개가
+안치는군요, 승상.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주공, 일단 자리를
+피하시지요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캬캬. 술이 식기
+전엔 돌아오쇼ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋㅋ 겨우 이정도가
+장익덕의 힘이더냐?ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백성들에게는 그런 신의 존재가
+필요하다. 그러니 네가..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크읔..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이..이 버러지같은 것들이!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마..막내야??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크윽.. 크아아아아ㅏㅏ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잡았다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하하하!! 내가 이 괴물같은
+녀석의 심장을 뚫었다!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3407,7 +3453,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3523,6 +3569,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6631,17 +6680,17 @@
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D93" s="27" t="str">
         <f t="shared" si="2"/>
-        <v>NAME_ETC_FANJIANG</v>
+        <v>NAME_WEI_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F93" s="38"/>
     </row>
@@ -6650,17 +6699,17 @@
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D94" s="27" t="str">
         <f t="shared" si="2"/>
-        <v>NAME_ETC_ZHANGDA</v>
+        <v>NAME_WEI_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F94" s="38"/>
     </row>
@@ -7510,7 +7559,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J285"/>
+  <dimension ref="A1:J296"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -8485,7 +8534,7 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -8978,7 +9027,7 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -9002,7 +9051,7 @@
         <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9026,7 +9075,7 @@
         <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
@@ -9170,7 +9219,7 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -9194,7 +9243,7 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
@@ -9652,7 +9701,7 @@
         <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -9748,7 +9797,7 @@
         <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10273,7 +10322,7 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10327,7 +10376,7 @@
         <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
@@ -10354,7 +10403,7 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
@@ -10403,7 +10452,7 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10426,7 +10475,7 @@
         <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10449,7 +10498,7 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
@@ -10472,7 +10521,7 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10495,7 +10544,7 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="J125" s="3"/>
     </row>
@@ -10519,7 +10568,7 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
@@ -10588,7 +10637,7 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -10611,7 +10660,7 @@
         <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -10657,7 +10706,7 @@
         <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10680,7 +10729,7 @@
         <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10703,7 +10752,7 @@
         <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -10749,7 +10798,7 @@
         <v>662</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10772,7 +10821,7 @@
         <v>662</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -10795,7 +10844,7 @@
         <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -10818,7 +10867,7 @@
         <v>662</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -10887,7 +10936,7 @@
         <v>662</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10979,7 +11028,7 @@
         <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -11002,7 +11051,7 @@
         <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -11071,7 +11120,7 @@
         <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -11094,7 +11143,7 @@
         <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -11117,7 +11166,7 @@
         <v>662</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -11140,7 +11189,7 @@
         <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -11186,7 +11235,7 @@
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -11232,7 +11281,7 @@
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -11300,12 +11349,13 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>681</v>
+      <c r="A162" t="str">
+        <f>A161</f>
+        <v>NODE_28</v>
       </c>
       <c r="B162">
         <f t="shared" ref="B162:B199" si="16">B161+1</f>
@@ -11327,15 +11377,16 @@
       </c>
     </row>
     <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>681</v>
+      <c r="A163" t="str">
+        <f t="shared" ref="A163:A199" si="17">A162</f>
+        <v>NODE_28</v>
       </c>
       <c r="B163">
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="C163" t="str">
-        <f t="shared" ref="C163:C169" si="17">CONCATENATE(A163, "_", B163, IF(D163&lt;&gt;"", "_"&amp;D163, ""))</f>
+        <f t="shared" ref="C163:C169" si="18">CONCATENATE(A163, "_", B163, IF(D163&lt;&gt;"", "_"&amp;D163, ""))</f>
         <v>NODE_28_2</v>
       </c>
       <c r="E163" t="str">
@@ -11350,15 +11401,16 @@
       </c>
     </row>
     <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>681</v>
+      <c r="A164" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B164">
         <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="C164" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_3</v>
       </c>
       <c r="E164" t="str">
@@ -11369,19 +11421,20 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>681</v>
+      <c r="A165" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B165">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="C165" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_4</v>
       </c>
       <c r="E165" t="str">
@@ -11396,15 +11449,16 @@
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>681</v>
+      <c r="A166" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B166">
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="C166" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_5</v>
       </c>
       <c r="E166" t="str">
@@ -11419,15 +11473,16 @@
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>681</v>
+      <c r="A167" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B167">
         <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="C167" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_6</v>
       </c>
       <c r="E167" t="str">
@@ -11438,19 +11493,20 @@
         <v>406</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>681</v>
+      <c r="A168" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B168">
         <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="C168" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_7</v>
       </c>
       <c r="E168" t="str">
@@ -11461,19 +11517,20 @@
         <v>407</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>681</v>
+      <c r="A169" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B169">
         <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="C169" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>NODE_28_8</v>
       </c>
       <c r="E169" t="str">
@@ -11488,15 +11545,16 @@
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>681</v>
+      <c r="A170" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B170">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="C170" t="str">
-        <f t="shared" ref="C170:C193" si="18">CONCATENATE(A170, "_", B170, IF(D170&lt;&gt;"", "_"&amp;D170, ""))</f>
+        <f t="shared" ref="C170:C193" si="19">CONCATENATE(A170, "_", B170, IF(D170&lt;&gt;"", "_"&amp;D170, ""))</f>
         <v>NODE_28_9</v>
       </c>
       <c r="E170" t="str">
@@ -11507,19 +11565,20 @@
         <v>591</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>681</v>
+      <c r="A171" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B171">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="C171" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_10</v>
       </c>
       <c r="E171" t="str">
@@ -11534,94 +11593,99 @@
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>681</v>
+      <c r="A172" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B172">
         <f t="shared" si="16"/>
         <v>11</v>
       </c>
       <c r="C172" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_11</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>681</v>
+      <c r="A173" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B173">
         <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="C173" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_12</v>
       </c>
       <c r="E173" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="F173" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>681</v>
+      <c r="A174" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B174">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
       <c r="C174" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_13</v>
       </c>
       <c r="E174" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="F174" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>681</v>
+      <c r="A175" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B175">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="C175" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_14</v>
       </c>
       <c r="E175" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="F175" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>681</v>
+      <c r="A176" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B176">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="C176" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_15</v>
       </c>
       <c r="E176" t="str">
@@ -11632,19 +11696,20 @@
         <v>7</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>681</v>
+      <c r="A177" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B177">
         <f t="shared" si="16"/>
         <v>16</v>
       </c>
       <c r="C177" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_16</v>
       </c>
       <c r="E177" t="str">
@@ -11655,19 +11720,20 @@
         <v>591</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>681</v>
+      <c r="A178" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B178">
         <f t="shared" si="16"/>
         <v>17</v>
       </c>
       <c r="C178" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_17</v>
       </c>
       <c r="E178" t="str">
@@ -11682,15 +11748,16 @@
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>681</v>
+      <c r="A179" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B179">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="C179" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_18</v>
       </c>
       <c r="E179" t="str">
@@ -11701,19 +11768,20 @@
         <v>591</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>681</v>
+      <c r="A180" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B180">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
       <c r="C180" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_19</v>
       </c>
       <c r="E180" t="s">
@@ -11723,19 +11791,20 @@
         <v>415</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>681</v>
+      <c r="A181" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B181">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="C181" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_20</v>
       </c>
       <c r="E181" t="str">
@@ -11746,19 +11815,20 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>681</v>
+      <c r="A182" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B182">
         <f t="shared" si="16"/>
         <v>21</v>
       </c>
       <c r="C182" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_21</v>
       </c>
       <c r="E182" t="str">
@@ -11769,19 +11839,20 @@
         <v>7</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>681</v>
+      <c r="A183" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B183">
         <f t="shared" si="16"/>
         <v>22</v>
       </c>
       <c r="C183" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_22</v>
       </c>
       <c r="E183" t="str">
@@ -11792,19 +11863,20 @@
         <v>406</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>681</v>
+      <c r="A184" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B184">
         <f t="shared" si="16"/>
         <v>23</v>
       </c>
       <c r="C184" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_23</v>
       </c>
       <c r="E184" t="str">
@@ -11815,19 +11887,20 @@
         <v>591</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>681</v>
+      <c r="A185" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B185">
         <f t="shared" si="16"/>
         <v>24</v>
       </c>
       <c r="C185" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_24</v>
       </c>
       <c r="E185" t="str">
@@ -11842,15 +11915,16 @@
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>681</v>
+      <c r="A186" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B186">
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
       <c r="C186" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_25</v>
       </c>
       <c r="E186" t="s">
@@ -11860,19 +11934,20 @@
         <v>679</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>681</v>
+      <c r="A187" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B187">
         <f t="shared" si="16"/>
         <v>26</v>
       </c>
       <c r="C187" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_26</v>
       </c>
       <c r="E187" t="s">
@@ -11882,19 +11957,20 @@
         <v>679</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>681</v>
+      <c r="A188" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B188">
         <f t="shared" si="16"/>
         <v>27</v>
       </c>
       <c r="C188" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_27</v>
       </c>
       <c r="E188" t="str">
@@ -11909,15 +11985,16 @@
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>681</v>
+      <c r="A189" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B189">
         <f t="shared" si="16"/>
         <v>28</v>
       </c>
       <c r="C189" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_28</v>
       </c>
       <c r="E189" t="str">
@@ -11932,15 +12009,16 @@
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>681</v>
+      <c r="A190" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B190">
         <f t="shared" si="16"/>
         <v>29</v>
       </c>
       <c r="C190" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_29</v>
       </c>
       <c r="E190" t="str">
@@ -11955,15 +12033,16 @@
       </c>
     </row>
     <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>681</v>
+      <c r="A191" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B191">
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="C191" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_30</v>
       </c>
       <c r="E191" t="s">
@@ -11973,19 +12052,20 @@
         <v>679</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>681</v>
+      <c r="A192" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B192">
         <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="C192" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_31</v>
       </c>
       <c r="E192" t="str">
@@ -11996,19 +12076,20 @@
         <v>7</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>681</v>
+      <c r="A193" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B193">
         <f t="shared" si="16"/>
         <v>32</v>
       </c>
       <c r="C193" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>NODE_28_32</v>
       </c>
       <c r="E193" t="str">
@@ -12019,19 +12100,20 @@
         <v>7</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>681</v>
+      <c r="A194" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B194">
         <f t="shared" si="16"/>
         <v>33</v>
       </c>
       <c r="C194" t="str">
-        <f t="shared" ref="C194:C196" si="19">CONCATENATE(A194, "_", B194, IF(D194&lt;&gt;"", "_"&amp;D194, ""))</f>
+        <f t="shared" ref="C194:C196" si="20">CONCATENATE(A194, "_", B194, IF(D194&lt;&gt;"", "_"&amp;D194, ""))</f>
         <v>NODE_28_33</v>
       </c>
       <c r="E194" t="s">
@@ -12045,15 +12127,16 @@
       </c>
     </row>
     <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>681</v>
+      <c r="A195" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B195">
         <f t="shared" si="16"/>
         <v>34</v>
       </c>
       <c r="C195" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>NODE_28_34</v>
       </c>
       <c r="E195" t="s">
@@ -12063,19 +12146,20 @@
         <v>679</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>681</v>
+      <c r="A196" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B196">
         <f t="shared" si="16"/>
         <v>35</v>
       </c>
       <c r="C196" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>NODE_28_35</v>
       </c>
       <c r="E196" t="s">
@@ -12085,19 +12169,20 @@
         <v>679</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>681</v>
+      <c r="A197" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B197">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="C197" t="str">
-        <f t="shared" ref="C197:C199" si="20">CONCATENATE(A197, "_", B197, IF(D197&lt;&gt;"", "_"&amp;D197, ""))</f>
+        <f t="shared" ref="C197:C199" si="21">CONCATENATE(A197, "_", B197, IF(D197&lt;&gt;"", "_"&amp;D197, ""))</f>
         <v>NODE_28_36</v>
       </c>
       <c r="E197" t="s">
@@ -12107,19 +12192,20 @@
         <v>679</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>801</v>
+        <v>787</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>681</v>
+      <c r="A198" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B198">
         <f t="shared" si="16"/>
         <v>37</v>
       </c>
       <c r="C198" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>NODE_28_37</v>
       </c>
       <c r="E198" t="str">
@@ -12134,15 +12220,16 @@
       </c>
     </row>
     <row r="199" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>681</v>
+      <c r="A199" t="str">
+        <f t="shared" si="17"/>
+        <v>NODE_28</v>
       </c>
       <c r="B199">
         <f t="shared" si="16"/>
         <v>38</v>
       </c>
       <c r="C199" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>NODE_28_38</v>
       </c>
       <c r="E199" t="str">
@@ -12153,7 +12240,7 @@
         <v>406</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12164,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="str">
-        <f t="shared" ref="C201:C202" si="21">CONCATENATE(A201, "_", B201, IF(D201&lt;&gt;"", "_"&amp;D201, ""))</f>
+        <f t="shared" ref="C201:C202" si="22">CONCATENATE(A201, "_", B201, IF(D201&lt;&gt;"", "_"&amp;D201, ""))</f>
         <v>NODE_29_0</v>
       </c>
       <c r="E201" t="str">
@@ -12175,19 +12262,20 @@
         <v>406</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>683</v>
+      <c r="A202" t="str">
+        <f>A201</f>
+        <v>NODE_29</v>
       </c>
       <c r="B202">
         <f>B201+1</f>
         <v>1</v>
       </c>
       <c r="C202" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>NODE_29_1</v>
       </c>
       <c r="E202" t="str">
@@ -12198,19 +12286,20 @@
         <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>683</v>
+      <c r="A203" t="str">
+        <f t="shared" ref="A203:A239" si="23">A202</f>
+        <v>NODE_29</v>
       </c>
       <c r="B203">
-        <f t="shared" ref="B203:B239" si="22">B202+1</f>
+        <f t="shared" ref="B203:B239" si="24">B202+1</f>
         <v>2</v>
       </c>
       <c r="C203" t="str">
-        <f t="shared" ref="C203:C239" si="23">CONCATENATE(A203, "_", B203, IF(D203&lt;&gt;"", "_"&amp;D203, ""))</f>
+        <f t="shared" ref="C203:C237" si="25">CONCATENATE(A203, "_", B203, IF(D203&lt;&gt;"", "_"&amp;D203, ""))</f>
         <v>NODE_29_2</v>
       </c>
       <c r="E203" t="str">
@@ -12225,15 +12314,16 @@
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>683</v>
+      <c r="A204" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B204">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="C204" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_3</v>
       </c>
       <c r="E204" t="str">
@@ -12244,19 +12334,20 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>683</v>
+      <c r="A205" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B205">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>4</v>
       </c>
       <c r="C205" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_4</v>
       </c>
       <c r="E205" t="str">
@@ -12267,19 +12358,20 @@
         <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>683</v>
+      <c r="A206" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B206">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
       <c r="C206" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_5</v>
       </c>
       <c r="E206" t="str">
@@ -12290,19 +12382,20 @@
         <v>406</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>683</v>
+      <c r="A207" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B207">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
       <c r="C207" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_6</v>
       </c>
       <c r="E207" t="str">
@@ -12313,19 +12406,20 @@
         <v>407</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>683</v>
+      <c r="A208" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B208">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>7</v>
       </c>
       <c r="C208" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_7</v>
       </c>
       <c r="E208" t="str">
@@ -12340,15 +12434,16 @@
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>683</v>
+      <c r="A209" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B209">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>8</v>
       </c>
       <c r="C209" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_8</v>
       </c>
       <c r="E209" t="str">
@@ -12359,19 +12454,20 @@
         <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>683</v>
+      <c r="A210" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B210">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
       <c r="C210" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_9</v>
       </c>
       <c r="E210" t="str">
@@ -12382,19 +12478,20 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>683</v>
+      <c r="A211" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B211">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="C211" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_10</v>
       </c>
       <c r="E211" t="str">
@@ -12409,15 +12506,16 @@
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>683</v>
+      <c r="A212" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B212">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>11</v>
       </c>
       <c r="C212" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_11</v>
       </c>
       <c r="E212" t="str">
@@ -12428,19 +12526,20 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>819</v>
+        <v>801</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>683</v>
+      <c r="A213" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B213">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
       <c r="C213" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_12</v>
       </c>
       <c r="E213" t="str">
@@ -12451,19 +12550,20 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>811</v>
+        <v>794</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>683</v>
+      <c r="A214" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B214">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>13</v>
       </c>
       <c r="C214" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_13</v>
       </c>
       <c r="E214" t="str">
@@ -12474,19 +12574,20 @@
         <v>7</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>683</v>
+      <c r="A215" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B215">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>14</v>
       </c>
       <c r="C215" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_14</v>
       </c>
       <c r="E215" t="str">
@@ -12497,19 +12598,20 @@
         <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>683</v>
+      <c r="A216" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B216">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>15</v>
       </c>
       <c r="C216" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_15</v>
       </c>
       <c r="E216" t="str">
@@ -12520,19 +12622,20 @@
         <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>683</v>
+      <c r="A217" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B217">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>16</v>
       </c>
       <c r="C217" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_16</v>
       </c>
       <c r="E217" t="str">
@@ -12543,19 +12646,20 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>817</v>
+        <v>799</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>683</v>
+      <c r="A218" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B218">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>17</v>
       </c>
       <c r="C218" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_17</v>
       </c>
       <c r="E218" t="str">
@@ -12566,19 +12670,20 @@
         <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>683</v>
+      <c r="A219" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B219">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>18</v>
       </c>
       <c r="C219" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_18</v>
       </c>
       <c r="E219" t="str">
@@ -12589,19 +12694,20 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>818</v>
+        <v>800</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>683</v>
+      <c r="A220" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B220">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>19</v>
       </c>
       <c r="C220" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_19</v>
       </c>
       <c r="E220" t="str">
@@ -12616,15 +12722,16 @@
       </c>
     </row>
     <row r="221" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>683</v>
+      <c r="A221" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B221">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>20</v>
       </c>
       <c r="C221" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_20</v>
       </c>
       <c r="E221" t="str">
@@ -12635,19 +12742,20 @@
         <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
     </row>
     <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>683</v>
+      <c r="A222" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B222">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>21</v>
       </c>
       <c r="C222" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_21</v>
       </c>
       <c r="E222" t="str">
@@ -12658,19 +12766,20 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>683</v>
+      <c r="A223" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B223">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="C223" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_22</v>
       </c>
       <c r="E223" t="str">
@@ -12685,15 +12794,16 @@
       </c>
     </row>
     <row r="224" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>683</v>
+      <c r="A224" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B224">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>23</v>
       </c>
       <c r="C224" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_23</v>
       </c>
       <c r="E224" t="str">
@@ -12704,19 +12814,20 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>683</v>
+      <c r="A225" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B225">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>24</v>
       </c>
       <c r="C225" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_24</v>
       </c>
       <c r="E225" t="str">
@@ -12727,19 +12838,20 @@
         <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>822</v>
+        <v>804</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>683</v>
+      <c r="A226" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B226">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>25</v>
       </c>
       <c r="C226" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_25</v>
       </c>
       <c r="E226" t="str">
@@ -12750,19 +12862,20 @@
         <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>683</v>
+      <c r="A227" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B227">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>26</v>
       </c>
       <c r="C227" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_26</v>
       </c>
       <c r="E227" t="str">
@@ -12773,19 +12886,20 @@
         <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>683</v>
+      <c r="A228" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B228">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>27</v>
       </c>
       <c r="C228" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_27</v>
       </c>
       <c r="E228" t="str">
@@ -12796,19 +12910,20 @@
         <v>591</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>683</v>
+      <c r="A229" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B229">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
       <c r="C229" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_28</v>
       </c>
       <c r="E229" t="str">
@@ -12819,19 +12934,20 @@
         <v>7</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>683</v>
+      <c r="A230" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B230">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>29</v>
       </c>
       <c r="C230" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_29</v>
       </c>
       <c r="E230" t="str">
@@ -12842,19 +12958,20 @@
         <v>591</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
     </row>
     <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>683</v>
+      <c r="A231" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B231">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>30</v>
       </c>
       <c r="C231" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_30</v>
       </c>
       <c r="E231" t="str">
@@ -12865,19 +12982,20 @@
         <v>591</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>683</v>
+      <c r="A232" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B232">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>31</v>
       </c>
       <c r="C232" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_31</v>
       </c>
       <c r="E232" t="str">
@@ -12888,32 +13006,34 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>683</v>
+      <c r="A233" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B233">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>32</v>
       </c>
       <c r="C233" t="str">
+        <f t="shared" si="25"/>
+        <v>NODE_29_32</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234" t="str">
         <f t="shared" si="23"/>
-        <v>NODE_29_32</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>683</v>
+        <v>NODE_29</v>
       </c>
       <c r="B234">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
       <c r="C234" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_33</v>
       </c>
       <c r="E234" t="str">
@@ -12928,15 +13048,16 @@
       </c>
     </row>
     <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>683</v>
+      <c r="A235" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B235">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>34</v>
       </c>
       <c r="C235" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_34</v>
       </c>
       <c r="E235" t="str">
@@ -12947,19 +13068,20 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>683</v>
+      <c r="A236" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B236">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>35</v>
       </c>
       <c r="C236" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_35</v>
       </c>
       <c r="E236" t="str">
@@ -12970,19 +13092,20 @@
         <v>7</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>683</v>
+      <c r="A237" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B237">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>36</v>
       </c>
       <c r="C237" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>NODE_29_36</v>
       </c>
       <c r="E237" t="str">
@@ -12993,19 +13116,20 @@
         <v>406</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>683</v>
+      <c r="A238" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B238">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>37</v>
       </c>
       <c r="C238" t="str">
-        <f t="shared" ref="C238:C239" si="24">CONCATENATE(A238, "_", B238, IF(D238&lt;&gt;"", "_"&amp;D238, ""))</f>
+        <f t="shared" ref="C238:C239" si="26">CONCATENATE(A238, "_", B238, IF(D238&lt;&gt;"", "_"&amp;D238, ""))</f>
         <v>NODE_29_37</v>
       </c>
       <c r="E238" t="str">
@@ -13016,19 +13140,20 @@
         <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>683</v>
+        <v>806</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A239" t="str">
+        <f t="shared" si="23"/>
+        <v>NODE_29</v>
       </c>
       <c r="B239">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>38</v>
       </c>
       <c r="C239" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>NODE_29_38</v>
       </c>
       <c r="E239" t="str">
@@ -13039,12 +13164,12 @@
         <v>406</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -13055,140 +13180,146 @@
       </c>
       <c r="E241" t="str">
         <f>VLOOKUP(F241,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>CaoRen</v>
       </c>
       <c r="F241" t="s">
-        <v>51</v>
+        <v>403</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>704</v>
+        <v>823</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A242" t="str">
+        <f>A241</f>
+        <v>NODE_31</v>
       </c>
       <c r="B242">
-        <f t="shared" ref="B242:B285" si="25">B241+1</f>
+        <f t="shared" ref="B242:B296" si="27">B241+1</f>
         <v>1</v>
       </c>
       <c r="C242" t="str">
-        <f t="shared" ref="C242" si="26">CONCATENATE(A242, "_", B242, IF(D242&lt;&gt;"", "_"&amp;D242, ""))</f>
+        <f t="shared" ref="C242" si="28">CONCATENATE(A242, "_", B242, IF(D242&lt;&gt;"", "_"&amp;D242, ""))</f>
         <v>NODE_31_1</v>
       </c>
       <c r="E242" t="str">
         <f>VLOOKUP(F242,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoRen</v>
       </c>
       <c r="F242" t="s">
-        <v>9</v>
+        <v>403</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>704</v>
+        <v>824</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A243" t="str">
+        <f t="shared" ref="A243:A261" si="29">A242</f>
+        <v>NODE_31</v>
       </c>
       <c r="B243">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" ref="C243:C285" si="27">CONCATENATE(A243, "_", B243, IF(D243&lt;&gt;"", "_"&amp;D243, ""))</f>
+        <f t="shared" ref="C243:C250" si="30">CONCATENATE(A243, "_", B243, IF(D243&lt;&gt;"", "_"&amp;D243, ""))</f>
         <v>NODE_31_2</v>
       </c>
       <c r="E243" t="str">
         <f>VLOOKUP(F243,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F243" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>704</v>
+        <v>825</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A244" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B244">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>3</v>
       </c>
       <c r="C244" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_3</v>
       </c>
       <c r="E244" t="str">
         <f>VLOOKUP(F244,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F244" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>795</v>
+        <v>814</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>704</v>
+      <c r="A245" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B245">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>4</v>
       </c>
       <c r="C245" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_4</v>
       </c>
       <c r="E245" t="str">
         <f>VLOOKUP(F245,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F245" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>796</v>
+        <v>815</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>704</v>
+      <c r="A246" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B246">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>5</v>
       </c>
       <c r="C246" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_5</v>
       </c>
       <c r="E246" t="str">
         <f>VLOOKUP(F246,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F246" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>704</v>
+        <v>785</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A247" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B247">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_6</v>
       </c>
       <c r="E247" t="str">
@@ -13198,20 +13329,21 @@
       <c r="F247" t="s">
         <v>9</v>
       </c>
-      <c r="G247" s="3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>704</v>
+      <c r="G247" s="39" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A248" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B248">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_7</v>
       </c>
       <c r="E248" t="str">
@@ -13222,111 +13354,116 @@
         <v>51</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>704</v>
+      <c r="A249" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B249">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_8</v>
       </c>
       <c r="E249" t="str">
         <f>VLOOKUP(F249,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F249" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>704</v>
+      <c r="A250" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B250">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>NODE_31_9</v>
       </c>
       <c r="E250" t="str">
         <f>VLOOKUP(F250,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F250" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>704</v>
+      <c r="A251" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B251">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>10</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="C251:C254" si="31">CONCATENATE(A251, "_", B251, IF(D251&lt;&gt;"", "_"&amp;D251, ""))</f>
         <v>NODE_31_10</v>
       </c>
       <c r="E251" t="str">
         <f>VLOOKUP(F251,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>CaoCao</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F251" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>679</v>
+        <v>797</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>704</v>
+      <c r="A252" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B252">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>11</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>NODE_31_11</v>
       </c>
       <c r="E252" t="str">
         <f>VLOOKUP(F252,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F252" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>704</v>
+      <c r="A253" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B253">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>NODE_31_12</v>
       </c>
       <c r="E253" t="str">
@@ -13337,272 +13474,274 @@
         <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>798</v>
+        <v>832</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>704</v>
+      <c r="A254" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B254">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>13</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>NODE_31_13</v>
       </c>
       <c r="E254" t="str">
         <f>VLOOKUP(F254,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F254" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>799</v>
+        <v>679</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>704</v>
+      <c r="A255" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B255">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>14</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="C255:C261" si="32">CONCATENATE(A255, "_", B255, IF(D255&lt;&gt;"", "_"&amp;D255, ""))</f>
         <v>NODE_31_14</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F255" t="s">
-        <v>7</v>
+        <v>591</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>704</v>
+        <v>833</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A256" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B256">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>15</v>
       </c>
       <c r="C256" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_15</v>
       </c>
       <c r="E256" t="str">
         <f>VLOOKUP(F256,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>CaoCao</v>
       </c>
       <c r="F256" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>704</v>
+        <v>829</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A257" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B257">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>16</v>
       </c>
       <c r="C257" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_16</v>
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F257" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>688</v>
+        <v>816</v>
       </c>
     </row>
     <row r="258" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>704</v>
+      <c r="A258" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B258">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>17</v>
       </c>
       <c r="C258" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_17</v>
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F258" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>704</v>
+        <v>819</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A259" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B259">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>18</v>
       </c>
       <c r="C259" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_18</v>
       </c>
       <c r="E259" t="str">
         <f>VLOOKUP(F259,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F259" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
-        <v>704</v>
+      <c r="A260" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B260">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>19</v>
       </c>
       <c r="C260" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_19</v>
       </c>
       <c r="E260" t="str">
         <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F260" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
-        <v>704</v>
+        <v>818</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A261" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
       </c>
       <c r="B261">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
       <c r="C261" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_20</v>
       </c>
       <c r="E261" t="str">
         <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F261" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
-        <v>704</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A262" t="str">
+        <f t="shared" ref="A262" si="33">A261</f>
+        <v>NODE_31</v>
       </c>
       <c r="B262">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>21</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="C262:C282" si="34">CONCATENATE(A262, "_", B262, IF(D262&lt;&gt;"", "_"&amp;D262, ""))</f>
         <v>NODE_31_21</v>
       </c>
       <c r="E262" t="str">
         <f>VLOOKUP(F262,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F262" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
-        <v>704</v>
+        <v>831</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263" t="str">
+        <f t="shared" ref="A263" si="35">A262</f>
+        <v>NODE_31</v>
       </c>
       <c r="B263">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>22</v>
       </c>
       <c r="C263" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_22</v>
       </c>
       <c r="E263" t="str">
         <f>VLOOKUP(F263,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F263" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>690</v>
+        <v>830</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
-        <v>704</v>
+      <c r="A264" t="str">
+        <f t="shared" ref="A264" si="36">A263</f>
+        <v>NODE_31</v>
       </c>
       <c r="B264">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>23</v>
       </c>
       <c r="C264" t="str">
+        <f t="shared" si="34"/>
+        <v>NODE_31_23</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265" t="str">
+        <f t="shared" ref="A265" si="37">A264</f>
+        <v>NODE_31</v>
+      </c>
+      <c r="B265">
         <f t="shared" si="27"/>
-        <v>NODE_31_23</v>
-      </c>
-      <c r="E264" t="str">
-        <f>VLOOKUP(F264,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
-      </c>
-      <c r="F264" t="s">
-        <v>7</v>
-      </c>
-      <c r="G264" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
-        <v>704</v>
-      </c>
-      <c r="B265">
-        <f t="shared" si="25"/>
         <v>24</v>
       </c>
       <c r="C265" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_24</v>
       </c>
       <c r="E265" t="str">
@@ -13613,42 +13752,44 @@
         <v>9</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
     </row>
     <row r="266" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>704</v>
+      <c r="A266" t="str">
+        <f t="shared" ref="A266" si="38">A265</f>
+        <v>NODE_31</v>
       </c>
       <c r="B266">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>25</v>
       </c>
       <c r="C266" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_25</v>
       </c>
       <c r="E266" t="str">
         <f>VLOOKUP(F266,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F266" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>802</v>
+        <v>687</v>
       </c>
     </row>
     <row r="267" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>704</v>
+      <c r="A267" t="str">
+        <f t="shared" ref="A267" si="39">A266</f>
+        <v>NODE_31</v>
       </c>
       <c r="B267">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>26</v>
       </c>
       <c r="C267" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_26</v>
       </c>
       <c r="E267" t="str">
@@ -13659,421 +13800,703 @@
         <v>7</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
     </row>
     <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>704</v>
+      <c r="A268" t="str">
+        <f t="shared" ref="A268" si="40">A267</f>
+        <v>NODE_31</v>
       </c>
       <c r="B268">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>27</v>
       </c>
       <c r="C268" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_27</v>
       </c>
       <c r="E268" t="str">
         <f>VLOOKUP(F268,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F268" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>704</v>
+        <v>835</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269" t="str">
+        <f t="shared" ref="A269" si="41">A268</f>
+        <v>NODE_31</v>
       </c>
       <c r="B269">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>28</v>
       </c>
       <c r="C269" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_28</v>
       </c>
       <c r="E269" t="str">
         <f>VLOOKUP(F269,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F269" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>722</v>
+        <v>786</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>704</v>
+      <c r="A270" t="str">
+        <f t="shared" ref="A270" si="42">A269</f>
+        <v>NODE_31</v>
       </c>
       <c r="B270">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>29</v>
       </c>
       <c r="C270" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_29</v>
       </c>
       <c r="E270" t="str">
         <f>VLOOKUP(F270,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F270" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>693</v>
+        <v>790</v>
       </c>
     </row>
     <row r="271" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>704</v>
+      <c r="A271" t="str">
+        <f t="shared" ref="A271" si="43">A270</f>
+        <v>NODE_31</v>
       </c>
       <c r="B271">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>30</v>
       </c>
       <c r="C271" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_30</v>
       </c>
       <c r="E271" t="str">
         <f>VLOOKUP(F271,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F271" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>704</v>
+      <c r="A272" t="str">
+        <f t="shared" ref="A272" si="44">A271</f>
+        <v>NODE_31</v>
       </c>
       <c r="B272">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="C272" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_31</v>
       </c>
       <c r="E272" t="str">
         <f>VLOOKUP(F272,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F272" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>594</v>
+        <v>791</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>704</v>
+      <c r="A273" t="str">
+        <f t="shared" ref="A273" si="45">A272</f>
+        <v>NODE_31</v>
       </c>
       <c r="B273">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>32</v>
       </c>
       <c r="C273" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_32</v>
       </c>
       <c r="E273" t="str">
         <f>VLOOKUP(F273,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F273" t="s">
-        <v>702</v>
+        <v>9</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="274" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>704</v>
+      <c r="A274" t="str">
+        <f t="shared" ref="A274" si="46">A273</f>
+        <v>NODE_31</v>
       </c>
       <c r="B274">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>33</v>
       </c>
       <c r="C274" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_33</v>
       </c>
       <c r="E274" t="str">
         <f>VLOOKUP(F274,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>GuanYu</v>
       </c>
       <c r="F274" t="s">
-        <v>703</v>
+        <v>7</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>704</v>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A275" t="str">
+        <f t="shared" ref="A275" si="47">A274</f>
+        <v>NODE_31</v>
       </c>
       <c r="B275">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>34</v>
       </c>
       <c r="C275" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_34</v>
       </c>
       <c r="E275" t="str">
         <f>VLOOKUP(F275,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F275" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>704</v>
+        <v>792</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A276" t="str">
+        <f t="shared" ref="A276" si="48">A275</f>
+        <v>NODE_31</v>
       </c>
       <c r="B276">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>35</v>
       </c>
       <c r="C276" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_35</v>
       </c>
       <c r="E276" t="str">
         <f>VLOOKUP(F276,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F276" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>704</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A277" t="str">
+        <f t="shared" ref="A277" si="49">A276</f>
+        <v>NODE_31</v>
       </c>
       <c r="B277">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>36</v>
       </c>
       <c r="C277" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_36</v>
       </c>
       <c r="E277" t="str">
         <f>VLOOKUP(F277,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F277" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>704</v>
+        <v>716</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" t="str">
+        <f t="shared" ref="A278" si="50">A277</f>
+        <v>NODE_31</v>
       </c>
       <c r="B278">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>37</v>
       </c>
       <c r="C278" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_37</v>
       </c>
       <c r="E278" t="str">
         <f>VLOOKUP(F278,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F278" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>704</v>
+        <v>691</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A279" t="str">
+        <f t="shared" ref="A279" si="51">A278</f>
+        <v>NODE_31</v>
       </c>
       <c r="B279">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>38</v>
       </c>
       <c r="C279" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_38</v>
       </c>
       <c r="E279" t="str">
         <f>VLOOKUP(F279,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F279" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>810</v>
+        <v>836</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>704</v>
+      <c r="A280" t="str">
+        <f t="shared" ref="A280" si="52">A279</f>
+        <v>NODE_31</v>
       </c>
       <c r="B280">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>39</v>
       </c>
       <c r="C280" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_39</v>
       </c>
       <c r="E280" t="str">
         <f>VLOOKUP(F280,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F280" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>704</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A281" t="str">
+        <f t="shared" ref="A281" si="53">A280</f>
+        <v>NODE_31</v>
       </c>
       <c r="B281">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>40</v>
       </c>
       <c r="C281" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_40</v>
       </c>
       <c r="E281" t="str">
         <f>VLOOKUP(F281,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>FanJiang</v>
       </c>
       <c r="F281" t="s">
-        <v>5</v>
+        <v>696</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>699</v>
+        <v>841</v>
       </c>
     </row>
     <row r="282" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>704</v>
+      <c r="A282" t="str">
+        <f t="shared" ref="A282:A296" si="54">A281</f>
+        <v>NODE_31</v>
       </c>
       <c r="B282">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>41</v>
       </c>
       <c r="C282" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NODE_31_41</v>
       </c>
       <c r="E282" t="str">
         <f>VLOOKUP(F282,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F282" t="s">
-        <v>5</v>
+        <v>697</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A283" t="s">
-        <v>704</v>
+        <v>842</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A283" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
       </c>
       <c r="B283">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>42</v>
       </c>
       <c r="C283" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="C283:C296" si="55">CONCATENATE(A283, "_", B283, IF(D283&lt;&gt;"", "_"&amp;D283, ""))</f>
         <v>NODE_31_42</v>
       </c>
       <c r="E283" t="str">
         <f>VLOOKUP(F283,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F283" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A284" t="s">
-        <v>704</v>
+        <v>837</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A284" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
       </c>
       <c r="B284">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>43</v>
       </c>
       <c r="C284" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="55"/>
         <v>NODE_31_43</v>
       </c>
       <c r="E284" t="str">
         <f>VLOOKUP(F284,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F284" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>701</v>
+        <v>838</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" t="s">
-        <v>704</v>
+      <c r="A285" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
       </c>
       <c r="B285">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>44</v>
       </c>
       <c r="C285" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="55"/>
         <v>NODE_31_44</v>
       </c>
       <c r="E285" t="str">
         <f>VLOOKUP(F285,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F285" t="s">
+        <v>7</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A286" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B286">
+        <f t="shared" si="27"/>
+        <v>45</v>
+      </c>
+      <c r="C286" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_45</v>
+      </c>
+      <c r="E286" t="str">
+        <f>VLOOKUP(F286,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>GuanYu</v>
+      </c>
+      <c r="F286" t="s">
+        <v>7</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A287" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B287">
+        <f t="shared" si="27"/>
+        <v>46</v>
+      </c>
+      <c r="C287" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_46</v>
+      </c>
+      <c r="E287" t="str">
+        <f>VLOOKUP(F287,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F287" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A288" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B288">
+        <f t="shared" si="27"/>
+        <v>47</v>
+      </c>
+      <c r="C288" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_47</v>
+      </c>
+      <c r="E288" t="str">
+        <f>VLOOKUP(F288,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F288" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A289" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B289">
+        <f t="shared" si="27"/>
+        <v>48</v>
+      </c>
+      <c r="C289" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_48</v>
+      </c>
+      <c r="E289" t="str">
+        <f>VLOOKUP(F289,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhaoYun</v>
+      </c>
+      <c r="F289" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B290">
+        <f t="shared" si="27"/>
+        <v>49</v>
+      </c>
+      <c r="C290" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_49</v>
+      </c>
+      <c r="E290" t="str">
+        <f>VLOOKUP(F290,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
         <v>LiuBei</v>
       </c>
-      <c r="F285" t="s">
+      <c r="F290" t="s">
         <v>5</v>
       </c>
-      <c r="G285" s="3" t="s">
-        <v>723</v>
+      <c r="G290" s="3" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A291" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B291">
+        <f t="shared" si="27"/>
+        <v>50</v>
+      </c>
+      <c r="C291" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_50</v>
+      </c>
+      <c r="E291" t="str">
+        <f>VLOOKUP(F291,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F291" t="s">
+        <v>5</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A292" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B292">
+        <f t="shared" si="27"/>
+        <v>51</v>
+      </c>
+      <c r="C292" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_51</v>
+      </c>
+      <c r="E292" t="str">
+        <f>VLOOKUP(F292,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F292" t="s">
+        <v>5</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A293" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B293">
+        <f t="shared" si="27"/>
+        <v>52</v>
+      </c>
+      <c r="C293" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_52</v>
+      </c>
+      <c r="E293" t="str">
+        <f>VLOOKUP(F293,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F293" t="s">
+        <v>5</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A294" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B294">
+        <f t="shared" si="27"/>
+        <v>53</v>
+      </c>
+      <c r="C294" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_53</v>
+      </c>
+      <c r="E294" t="str">
+        <f>VLOOKUP(F294,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F294" t="s">
+        <v>5</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A295" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B295">
+        <f t="shared" si="27"/>
+        <v>54</v>
+      </c>
+      <c r="C295" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_54</v>
+      </c>
+      <c r="E295" t="str">
+        <f>VLOOKUP(F295,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F295" t="s">
+        <v>5</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A296" t="str">
+        <f t="shared" si="54"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B296">
+        <f t="shared" si="27"/>
+        <v>55</v>
+      </c>
+      <c r="C296" t="str">
+        <f t="shared" si="55"/>
+        <v>NODE_31_55</v>
+      </c>
+      <c r="E296" t="str">
+        <f>VLOOKUP(F296,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F296" t="s">
+        <v>5</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -14681,7 +15104,7 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="F34" s="21"/>
     </row>
@@ -14698,7 +15121,7 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="F35" s="24"/>
     </row>
@@ -14715,7 +15138,7 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="F36" s="21"/>
     </row>
@@ -14775,7 +15198,7 @@
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -14783,7 +15206,7 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="F40" s="21"/>
     </row>
@@ -15344,7 +15767,7 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F72" s="21"/>
     </row>
@@ -15361,7 +15784,7 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="F73" s="24"/>
     </row>
@@ -15378,7 +15801,7 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="F74" s="21"/>
     </row>
@@ -15438,7 +15861,7 @@
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -15446,7 +15869,7 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="F78" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33AD3BC1-1DFB-42A7-A16D-DD08348502CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1400" windowWidth="25820" windowHeight="16220" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -19,7 +18,7 @@
   <externalReferences>
     <externalReference r:id="rId8"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2253,10 +2252,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>흥! 대체 안량이 어떻게..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2274,11 +2269,6 @@
   </si>
   <si>
     <t>으아!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>명공! 조조는 원래 저를 시기하여
-명공의 손을 빌려 저를 죽이려는 것입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2323,11 +2313,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>유비.. 네 놈 때문에 내가 제일 아끼는
-장수 두명을 잃었다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아니 죽인 것은 관우인데요?
 그게 아니라. 제가 지금 당장 밀서를..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2337,11 +2322,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안량, 문추를 잃은 것은 
-안타까운..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>저를 살려주시면
 관우를 얻게 될 것입니다!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2464,11 +2444,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안량을 벤 자가 누구더냐!
-분명 무슨 암수를 썻을테지!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관우는 아닐것입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2746,11 +2721,6 @@
   <si>
     <t>우리 주군께선 그런
 파렴치한 자가 아니오!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>네 놈의 목을 쳐그들의
-원한을 풀어주겠다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2999,11 +2969,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(누구였지? 아무런 기척도
-못 느꼈었는데..)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아!! 큰일났습니다. 지금 허도에 괴물같은
 자가 나타나 궁으로 돌격하고 있습니다!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3095,10 +3060,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이제 이 세계는 끝이야..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>관우님도 느끼고 있으실 것입니다.
 아수라의 기운을..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3129,10 +3090,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>그럴 수만은 없다네..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>알고 있네. 혹시..
 만약에 말일세..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3147,16 +3104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>급소는 모두 빗겨갔군.
-괴물치고는..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몸을 추스리시오.
-다녀와서 그대의 술잔을 받도록 하지.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>으으.. 관형..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3183,11 +3130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>크..큰일났다!!
-아수라가.. 현현한다..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>멈추어라!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3220,16 +3162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이 두 놈은 어느 시간선에서든
-문제만 일으키는군 - -+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선 아수라가 현현하는 건
-막아야한다.. 시간을 되돌릴 수 밖에..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이 괴물같은 넘..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3317,14 +3249,81 @@
   <si>
     <t>하하하!! 내가 이 괴물같은
 녀석의 심장을 뚫었다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸을 추스리게. 다녀와서
+그대의 술잔을 받도록 하지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 놈의 목을 쳐 그들의
+원한을 풀어주겠다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안량, 문추를 잃은 것은 
+안타까우나..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유비.. 네 놈 때문에 내가 제일
+아끼는 장수 두명을 잃었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명공! 조조는 원래 저를 시기하여 명공의
+손을 빌려 저를 죽이려는 것입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안량을 벤 자가 누구더냐!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흥! 대체 안량이 어떻게..
+분명 무슨 암수를 썻을테지!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럴 순 없다네..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(누구지? 아무런 기척도
+못 느꼈었는데..)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급소는 모두 빗겨갔군.
+괴물이라 하기엔..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크..큰일났다!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아수라가.. 현현한다..
+이제 이 세계는 끝이야..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범강, 장달.. 으으 저 두 놈은 어느
+시간선에서든 문제를 일으키는군 - -+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 아수라가 현현하는 건 막아야한다..
+시간을 되돌릴 수 밖에..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3592,7 +3591,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Overview"/>
@@ -3886,7 +3885,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3918,27 +3917,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3970,24 +3951,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4163,9 +4126,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4174,15 +4137,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D68"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="38.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="40.875" customWidth="1"/>
+    <col min="2" max="2" width="38.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>384</v>
       </c>
@@ -4196,7 +4159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4210,7 +4173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="B3" t="s">
         <v>83</v>
       </c>
@@ -4218,7 +4181,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="B4" t="s">
         <v>86</v>
       </c>
@@ -4226,7 +4189,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="B5" t="s">
         <v>93</v>
       </c>
@@ -4234,7 +4197,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="B6" t="s">
         <v>91</v>
       </c>
@@ -4242,7 +4205,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="B7" t="s">
         <v>92</v>
       </c>
@@ -4250,7 +4213,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="B8" t="s">
         <v>90</v>
       </c>
@@ -4258,7 +4221,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="B9" t="s">
         <v>85</v>
       </c>
@@ -4266,7 +4229,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="B10" t="s">
         <v>87</v>
       </c>
@@ -4274,7 +4237,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="B11" t="s">
         <v>89</v>
       </c>
@@ -4282,7 +4245,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>88</v>
       </c>
@@ -4290,7 +4253,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>114</v>
       </c>
@@ -4298,7 +4261,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -4306,7 +4269,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>115</v>
       </c>
@@ -4314,7 +4277,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>117</v>
       </c>
@@ -4322,7 +4285,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3">
       <c r="B17" t="s">
         <v>116</v>
       </c>
@@ -4330,7 +4293,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>113</v>
       </c>
@@ -4338,7 +4301,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3">
       <c r="B19" t="s">
         <v>106</v>
       </c>
@@ -4346,7 +4309,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3">
       <c r="B20" t="s">
         <v>112</v>
       </c>
@@ -4354,7 +4317,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3">
       <c r="B21" t="s">
         <v>103</v>
       </c>
@@ -4362,7 +4325,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3">
       <c r="B22" t="s">
         <v>105</v>
       </c>
@@ -4370,7 +4333,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3">
       <c r="B23" t="s">
         <v>104</v>
       </c>
@@ -4378,7 +4341,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3">
       <c r="B24" s="17" t="s">
         <v>154</v>
       </c>
@@ -4386,7 +4349,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3">
       <c r="B25" s="17" t="s">
         <v>155</v>
       </c>
@@ -4394,7 +4357,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:3">
       <c r="B26" s="17" t="s">
         <v>156</v>
       </c>
@@ -4402,7 +4365,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:3">
       <c r="B27" s="17" t="s">
         <v>157</v>
       </c>
@@ -4410,7 +4373,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:3">
       <c r="B28" s="17" t="s">
         <v>153</v>
       </c>
@@ -4418,7 +4381,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:3">
       <c r="B29" t="s">
         <v>63</v>
       </c>
@@ -4426,7 +4389,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:3">
       <c r="B30" t="s">
         <v>65</v>
       </c>
@@ -4434,7 +4397,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:3">
       <c r="B31" t="s">
         <v>66</v>
       </c>
@@ -4442,7 +4405,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:3">
       <c r="B32" t="s">
         <v>69</v>
       </c>
@@ -4450,7 +4413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4">
       <c r="B33" t="s">
         <v>61</v>
       </c>
@@ -4458,7 +4421,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4">
       <c r="B34" t="s">
         <v>151</v>
       </c>
@@ -4466,7 +4429,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4">
       <c r="B35" t="s">
         <v>74</v>
       </c>
@@ -4474,7 +4437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4">
       <c r="B36" t="s">
         <v>150</v>
       </c>
@@ -4482,7 +4445,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4">
       <c r="B37" t="s">
         <v>80</v>
       </c>
@@ -4490,7 +4453,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4">
       <c r="B38" t="s">
         <v>152</v>
       </c>
@@ -4498,7 +4461,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4">
       <c r="B39" t="s">
         <v>53</v>
       </c>
@@ -4507,7 +4470,7 @@
       </c>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4">
       <c r="B40" t="s">
         <v>164</v>
       </c>
@@ -4515,7 +4478,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4">
       <c r="B41" t="s">
         <v>267</v>
       </c>
@@ -4523,7 +4486,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4">
       <c r="B42" t="s">
         <v>265</v>
       </c>
@@ -4531,7 +4494,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4">
       <c r="B43" t="s">
         <v>264</v>
       </c>
@@ -4539,7 +4502,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4">
       <c r="B44" t="s">
         <v>266</v>
       </c>
@@ -4547,7 +4510,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4">
       <c r="B45" t="s">
         <v>163</v>
       </c>
@@ -4555,7 +4518,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4">
       <c r="B46" t="s">
         <v>161</v>
       </c>
@@ -4563,7 +4526,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4">
       <c r="B47" t="s">
         <v>162</v>
       </c>
@@ -4571,7 +4534,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>543</v>
       </c>
@@ -4583,7 +4546,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>544</v>
       </c>
@@ -4595,7 +4558,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>545</v>
       </c>
@@ -4607,7 +4570,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>546</v>
       </c>
@@ -4619,7 +4582,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>542</v>
       </c>
@@ -4631,7 +4594,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4">
       <c r="B53" t="s">
         <v>552</v>
       </c>
@@ -4639,7 +4602,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4">
       <c r="B54" t="s">
         <v>520</v>
       </c>
@@ -4647,7 +4610,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="B55" t="s">
         <v>516</v>
       </c>
@@ -4655,7 +4618,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="B56" t="s">
         <v>521</v>
       </c>
@@ -4663,7 +4626,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="B57" t="s">
         <v>517</v>
       </c>
@@ -4671,7 +4634,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="B58" t="s">
         <v>519</v>
       </c>
@@ -4679,7 +4642,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="B59" t="s">
         <v>515</v>
       </c>
@@ -4687,7 +4650,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4">
       <c r="B60" t="s">
         <v>522</v>
       </c>
@@ -4695,7 +4658,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4">
       <c r="B61" t="s">
         <v>518</v>
       </c>
@@ -4703,7 +4666,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4">
       <c r="B62" t="s">
         <v>286</v>
       </c>
@@ -4714,7 +4677,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4">
       <c r="B63" t="s">
         <v>282</v>
       </c>
@@ -4725,7 +4688,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4">
       <c r="B64" t="s">
         <v>287</v>
       </c>
@@ -4736,7 +4699,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4">
       <c r="B65" t="s">
         <v>288</v>
       </c>
@@ -4747,7 +4710,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4">
       <c r="B66" t="s">
         <v>285</v>
       </c>
@@ -4758,7 +4721,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4">
       <c r="B67" t="s">
         <v>283</v>
       </c>
@@ -4769,7 +4732,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:4">
       <c r="B68" t="s">
         <v>284</v>
       </c>
@@ -4781,7 +4744,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
+  <sortState ref="A3:D68">
     <sortCondition ref="B3:B68"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4791,16 +4754,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE1FA765-18DF-4AAD-91B0-AAB6166EA35D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="28.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
         <v>125</v>
       </c>
@@ -4814,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
@@ -4828,7 +4791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="16" t="s">
         <v>126</v>
       </c>
@@ -4841,7 +4804,7 @@
       </c>
       <c r="D3" s="18"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="16" t="s">
         <v>127</v>
       </c>
@@ -4854,7 +4817,7 @@
       </c>
       <c r="D4" s="18"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="16" t="s">
         <v>128</v>
       </c>
@@ -4867,7 +4830,7 @@
       </c>
       <c r="D5" s="18"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="16" t="s">
         <v>129</v>
       </c>
@@ -4880,7 +4843,7 @@
       </c>
       <c r="D6" s="18"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="16" t="s">
         <v>130</v>
       </c>
@@ -4893,7 +4856,7 @@
       </c>
       <c r="D7" s="18"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="16" t="s">
         <v>131</v>
       </c>
@@ -4906,7 +4869,7 @@
       </c>
       <c r="D8" s="18"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="16" t="s">
         <v>132</v>
       </c>
@@ -4919,7 +4882,7 @@
       </c>
       <c r="D9" s="18"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="16" t="s">
         <v>133</v>
       </c>
@@ -4932,7 +4895,7 @@
       </c>
       <c r="D10" s="18"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="16" t="s">
         <v>134</v>
       </c>
@@ -4945,7 +4908,7 @@
       </c>
       <c r="D11" s="18"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="16" t="s">
         <v>135</v>
       </c>
@@ -4958,23 +4921,23 @@
       </c>
       <c r="D12" s="18"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="17"/>
       <c r="D13" s="18"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="17"/>
       <c r="D14" s="18"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="17"/>
       <c r="D15" s="18"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="17"/>
       <c r="D16" s="18"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="17"/>
       <c r="D17" s="18"/>
     </row>
@@ -4986,18 +4949,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G102"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="50.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="50.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>450</v>
       </c>
@@ -5020,7 +4983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -5041,7 +5004,7 @@
       </c>
       <c r="G2" s="37"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -5055,7 +5018,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="27"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -5069,7 +5032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
       <c r="C5" s="27"/>
@@ -5083,7 +5046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -5097,7 +5060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -5111,7 +5074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -5125,7 +5088,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="27" t="s">
         <v>479</v>
       </c>
@@ -5146,7 +5109,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="27" t="s">
         <v>479</v>
       </c>
@@ -5167,7 +5130,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="27" t="s">
         <v>479</v>
       </c>
@@ -5188,7 +5151,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="27" t="s">
         <v>479</v>
       </c>
@@ -5209,7 +5172,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="27" t="s">
         <v>479</v>
       </c>
@@ -5230,7 +5193,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="27" t="s">
         <v>479</v>
       </c>
@@ -5251,7 +5214,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="27" t="s">
         <v>479</v>
       </c>
@@ -5272,7 +5235,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="27" t="s">
         <v>479</v>
       </c>
@@ -5293,7 +5256,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="27" t="s">
         <v>479</v>
       </c>
@@ -5314,7 +5277,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="27" t="s">
         <v>479</v>
       </c>
@@ -5335,7 +5298,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="27" t="s">
         <v>479</v>
       </c>
@@ -5356,7 +5319,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="27" t="s">
         <v>479</v>
       </c>
@@ -5377,7 +5340,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="27" t="s">
         <v>479</v>
       </c>
@@ -5398,7 +5361,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="27" t="s">
         <v>479</v>
       </c>
@@ -5419,7 +5382,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="27" t="s">
         <v>479</v>
       </c>
@@ -5440,7 +5403,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="27" t="s">
         <v>479</v>
       </c>
@@ -5461,7 +5424,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="27" t="s">
         <v>479</v>
       </c>
@@ -5482,7 +5445,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="27" t="s">
         <v>479</v>
       </c>
@@ -5503,7 +5466,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="27" t="s">
         <v>479</v>
       </c>
@@ -5524,7 +5487,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="27" t="s">
         <v>479</v>
       </c>
@@ -5545,7 +5508,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="34">
       <c r="A29" s="27" t="s">
         <v>464</v>
       </c>
@@ -5564,7 +5527,7 @@
       </c>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="34">
       <c r="A30" s="27" t="s">
         <v>464</v>
       </c>
@@ -5583,7 +5546,7 @@
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="34">
       <c r="A31" s="27" t="s">
         <v>464</v>
       </c>
@@ -5602,7 +5565,7 @@
       </c>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="34">
       <c r="A32" s="27" t="s">
         <v>464</v>
       </c>
@@ -5621,7 +5584,7 @@
       </c>
       <c r="F32" s="38"/>
     </row>
-    <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="34">
       <c r="A33" s="27" t="s">
         <v>464</v>
       </c>
@@ -5640,7 +5603,7 @@
       </c>
       <c r="F33" s="38"/>
     </row>
-    <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="34">
       <c r="A34" s="27" t="s">
         <v>464</v>
       </c>
@@ -5659,7 +5622,7 @@
       </c>
       <c r="F34" s="38"/>
     </row>
-    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="34">
       <c r="A35" s="27" t="s">
         <v>464</v>
       </c>
@@ -5678,7 +5641,7 @@
       </c>
       <c r="F35" s="38"/>
     </row>
-    <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="34">
       <c r="A36" s="27" t="s">
         <v>464</v>
       </c>
@@ -5697,7 +5660,7 @@
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="34">
       <c r="A37" s="27" t="s">
         <v>464</v>
       </c>
@@ -5716,7 +5679,7 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="34">
       <c r="A38" s="27" t="s">
         <v>464</v>
       </c>
@@ -5735,7 +5698,7 @@
       </c>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="34">
       <c r="A39" s="27" t="s">
         <v>464</v>
       </c>
@@ -5754,7 +5717,7 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="34">
       <c r="A40" s="27" t="s">
         <v>464</v>
       </c>
@@ -5773,7 +5736,7 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="27" t="s">
         <v>464</v>
       </c>
@@ -5794,7 +5757,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="34">
       <c r="A42" s="27" t="s">
         <v>464</v>
       </c>
@@ -5815,7 +5778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="34">
       <c r="A43" s="27" t="s">
         <v>464</v>
       </c>
@@ -5836,7 +5799,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="34">
       <c r="A44" s="27" t="s">
         <v>464</v>
       </c>
@@ -5857,7 +5820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" s="27" t="s">
         <v>464</v>
       </c>
@@ -5878,7 +5841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="34">
       <c r="A46" s="27" t="s">
         <v>464</v>
       </c>
@@ -5899,7 +5862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="34">
       <c r="A47" s="27" t="s">
         <v>464</v>
       </c>
@@ -5920,7 +5883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="34">
       <c r="A48" s="27" t="s">
         <v>464</v>
       </c>
@@ -5941,7 +5904,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" s="27"/>
       <c r="B49" s="27"/>
       <c r="C49" s="27"/>
@@ -5955,7 +5918,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" s="27"/>
       <c r="B50" s="27"/>
       <c r="C50" s="27"/>
@@ -5969,7 +5932,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" s="27"/>
       <c r="B51" s="27"/>
       <c r="C51" s="27"/>
@@ -5983,7 +5946,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" s="27"/>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
@@ -5997,7 +5960,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" s="27"/>
       <c r="B53" s="27"/>
       <c r="C53" s="27"/>
@@ -6011,7 +5974,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" s="27"/>
       <c r="B54" s="27"/>
       <c r="C54" s="27"/>
@@ -6025,7 +5988,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" s="27"/>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
@@ -6039,7 +6002,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" s="27"/>
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
@@ -6053,7 +6016,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" s="27"/>
       <c r="B57" s="27"/>
       <c r="C57" s="27"/>
@@ -6067,7 +6030,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" s="27"/>
       <c r="B58" s="27"/>
       <c r="C58" s="27"/>
@@ -6081,7 +6044,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" s="27"/>
       <c r="B59" s="27"/>
       <c r="C59" s="27"/>
@@ -6095,7 +6058,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" s="27"/>
       <c r="B60" s="27"/>
       <c r="C60" s="27"/>
@@ -6109,7 +6072,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" s="27" t="s">
         <v>451</v>
       </c>
@@ -6128,7 +6091,7 @@
       </c>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" s="27" t="s">
         <v>451</v>
       </c>
@@ -6147,7 +6110,7 @@
       </c>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" s="27" t="s">
         <v>451</v>
       </c>
@@ -6166,7 +6129,7 @@
       </c>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" s="27" t="s">
         <v>451</v>
       </c>
@@ -6185,7 +6148,7 @@
       </c>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" s="27" t="s">
         <v>451</v>
       </c>
@@ -6204,7 +6167,7 @@
       </c>
       <c r="F65" s="38"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" s="27" t="s">
         <v>451</v>
       </c>
@@ -6223,7 +6186,7 @@
       </c>
       <c r="F66" s="38"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" s="27" t="s">
         <v>451</v>
       </c>
@@ -6242,7 +6205,7 @@
       </c>
       <c r="F67" s="38"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" s="27" t="s">
         <v>451</v>
       </c>
@@ -6261,7 +6224,7 @@
       </c>
       <c r="F68" s="38"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" s="27" t="s">
         <v>451</v>
       </c>
@@ -6280,7 +6243,7 @@
       </c>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" s="27" t="s">
         <v>451</v>
       </c>
@@ -6299,7 +6262,7 @@
       </c>
       <c r="F70" s="38"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" s="27" t="s">
         <v>451</v>
       </c>
@@ -6318,7 +6281,7 @@
       </c>
       <c r="F71" s="38"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" s="27" t="s">
         <v>451</v>
       </c>
@@ -6337,7 +6300,7 @@
       </c>
       <c r="F72" s="38"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" s="27" t="s">
         <v>451</v>
       </c>
@@ -6356,7 +6319,7 @@
       </c>
       <c r="F73" s="38"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" s="27" t="s">
         <v>451</v>
       </c>
@@ -6375,7 +6338,7 @@
       </c>
       <c r="F74" s="38"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" s="27" t="s">
         <v>451</v>
       </c>
@@ -6394,7 +6357,7 @@
       </c>
       <c r="F75" s="38"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" s="27" t="s">
         <v>451</v>
       </c>
@@ -6413,7 +6376,7 @@
       </c>
       <c r="F76" s="38"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" s="27" t="s">
         <v>451</v>
       </c>
@@ -6432,7 +6395,7 @@
       </c>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" s="27" t="s">
         <v>451</v>
       </c>
@@ -6451,7 +6414,7 @@
       </c>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" s="27" t="s">
         <v>451</v>
       </c>
@@ -6470,7 +6433,7 @@
       </c>
       <c r="F79" s="38"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" s="27" t="s">
         <v>451</v>
       </c>
@@ -6489,7 +6452,7 @@
       </c>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" s="27"/>
       <c r="B81" s="27"/>
       <c r="C81" s="27"/>
@@ -6501,7 +6464,7 @@
       </c>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" s="27"/>
       <c r="B82" s="27"/>
       <c r="C82" s="27"/>
@@ -6513,7 +6476,7 @@
       </c>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" s="27"/>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -6525,7 +6488,7 @@
       </c>
       <c r="F83" s="38"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" s="27"/>
       <c r="B84" s="27"/>
       <c r="C84" s="27"/>
@@ -6537,7 +6500,7 @@
       </c>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" s="27"/>
       <c r="B85" s="27"/>
       <c r="C85" s="27"/>
@@ -6549,7 +6512,7 @@
       </c>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" s="27"/>
       <c r="B86" s="27"/>
       <c r="C86" s="27"/>
@@ -6561,12 +6524,12 @@
       </c>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C87" s="27" t="s">
         <v>449</v>
@@ -6580,12 +6543,12 @@
       </c>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C88" s="27" t="s">
         <v>449</v>
@@ -6599,12 +6562,12 @@
       </c>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C89" s="27" t="s">
         <v>449</v>
@@ -6618,12 +6581,12 @@
       </c>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C90" s="27" t="s">
         <v>449</v>
@@ -6633,16 +6596,16 @@
         <v>NAME_ETC_SONGXIAN</v>
       </c>
       <c r="E90" s="27" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C91" s="27" t="s">
         <v>449</v>
@@ -6652,16 +6615,16 @@
         <v>NAME_ETC_WEIXU</v>
       </c>
       <c r="E91" s="27" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C92" s="27" t="s">
         <v>447</v>
@@ -6671,16 +6634,16 @@
         <v>NAME_WEI_XUHUANG</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C93" s="27" t="s">
         <v>447</v>
@@ -6690,16 +6653,16 @@
         <v>NAME_WEI_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C94" s="27" t="s">
         <v>447</v>
@@ -6709,16 +6672,16 @@
         <v>NAME_WEI_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" s="27" t="s">
         <v>479</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C95" s="27" t="s">
         <v>449</v>
@@ -6728,16 +6691,16 @@
         <v>COURTESY_ETC_YUANSHAO</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" s="27" t="s">
         <v>479</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C96" s="27" t="s">
         <v>449</v>
@@ -6751,12 +6714,12 @@
       </c>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" s="27" t="s">
         <v>479</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C97" s="27" t="s">
         <v>449</v>
@@ -6770,12 +6733,12 @@
       </c>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" s="27" t="s">
         <v>479</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C98" s="27" t="s">
         <v>447</v>
@@ -6789,12 +6752,12 @@
       </c>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="34">
       <c r="A99" s="27" t="s">
         <v>464</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C99" s="27" t="s">
         <v>449</v>
@@ -6804,16 +6767,16 @@
         <v>DESC_TALK_ETC_YUANSHAO</v>
       </c>
       <c r="E99" s="38" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="34">
       <c r="A100" s="27" t="s">
         <v>464</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C100" s="27" t="s">
         <v>449</v>
@@ -6823,16 +6786,16 @@
         <v>DESC_TALK_ETC_YANLIANG</v>
       </c>
       <c r="E100" s="38" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="F100" s="38"/>
     </row>
-    <row r="101" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="34">
       <c r="A101" s="27" t="s">
         <v>464</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C101" s="27" t="s">
         <v>449</v>
@@ -6842,16 +6805,16 @@
         <v>DESC_TALK_ETC_WENCHOU</v>
       </c>
       <c r="E101" s="38" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="34">
       <c r="A102" s="27" t="s">
         <v>464</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C102" s="27" t="s">
         <v>447</v>
@@ -6861,12 +6824,12 @@
         <v>DESC_TALK_WEI_XUHUANG</v>
       </c>
       <c r="E102" s="38" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="F102" s="38"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G66">
+  <sortState ref="A3:G66">
     <sortCondition ref="D3:D66"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6876,19 +6839,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7EE6A7D-8E38-47C7-B564-D54B5D506D09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="29.25" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="6.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.58203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="6.08203125" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="7" t="s">
         <v>166</v>
       </c>
@@ -6905,7 +6868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -6920,7 +6883,7 @@
       </c>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" s="10" t="s">
         <v>168</v>
       </c>
@@ -6934,7 +6897,7 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" s="10" t="s">
         <v>169</v>
       </c>
@@ -6948,7 +6911,7 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
         <v>170</v>
       </c>
@@ -6962,7 +6925,7 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
         <v>171</v>
       </c>
@@ -6976,7 +6939,7 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
         <v>172</v>
       </c>
@@ -6990,7 +6953,7 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5">
       <c r="A8" s="10" t="s">
         <v>173</v>
       </c>
@@ -7004,7 +6967,7 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5">
       <c r="A9" s="10" t="s">
         <v>174</v>
       </c>
@@ -7018,7 +6981,7 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5">
       <c r="A10" s="10" t="s">
         <v>175</v>
       </c>
@@ -7032,7 +6995,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5">
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
@@ -7046,7 +7009,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5">
       <c r="A12" s="10" t="s">
         <v>177</v>
       </c>
@@ -7060,7 +7023,7 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5">
       <c r="A13" s="10" t="s">
         <v>167</v>
       </c>
@@ -7074,7 +7037,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5">
       <c r="A14" s="10" t="s">
         <v>178</v>
       </c>
@@ -7088,7 +7051,7 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
         <v>179</v>
       </c>
@@ -7102,7 +7065,7 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5">
       <c r="A16" s="10" t="s">
         <v>180</v>
       </c>
@@ -7116,7 +7079,7 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
         <v>181</v>
       </c>
@@ -7130,7 +7093,7 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="10" t="s">
         <v>182</v>
       </c>
@@ -7144,7 +7107,7 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="10" t="s">
         <v>183</v>
       </c>
@@ -7158,7 +7121,7 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="10" t="s">
         <v>184</v>
       </c>
@@ -7172,7 +7135,7 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="10" t="s">
         <v>185</v>
       </c>
@@ -7186,7 +7149,7 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="10" t="s">
         <v>186</v>
       </c>
@@ -7200,7 +7163,7 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="10" t="s">
         <v>187</v>
       </c>
@@ -7214,7 +7177,7 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="10" t="s">
         <v>188</v>
       </c>
@@ -7228,7 +7191,7 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="10" t="s">
         <v>189</v>
       </c>
@@ -7242,7 +7205,7 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="10" t="s">
         <v>190</v>
       </c>
@@ -7256,7 +7219,7 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="10" t="s">
         <v>191</v>
       </c>
@@ -7270,7 +7233,7 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="10" t="s">
         <v>192</v>
       </c>
@@ -7284,7 +7247,7 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="10" t="s">
         <v>193</v>
       </c>
@@ -7298,7 +7261,7 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="10" t="s">
         <v>194</v>
       </c>
@@ -7312,7 +7275,7 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="10" t="s">
         <v>195</v>
       </c>
@@ -7326,7 +7289,7 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="10" t="s">
         <v>196</v>
       </c>
@@ -7340,7 +7303,7 @@
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="10" t="s">
         <v>197</v>
       </c>
@@ -7354,7 +7317,7 @@
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="10" t="s">
         <v>198</v>
       </c>
@@ -7368,7 +7331,7 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="10" t="s">
         <v>199</v>
       </c>
@@ -7382,7 +7345,7 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="10" t="s">
         <v>200</v>
       </c>
@@ -7396,7 +7359,7 @@
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="10" t="s">
         <v>201</v>
       </c>
@@ -7410,7 +7373,7 @@
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="10" t="s">
         <v>202</v>
       </c>
@@ -7424,7 +7387,7 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="10" t="s">
         <v>203</v>
       </c>
@@ -7438,7 +7401,7 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="10" t="s">
         <v>204</v>
       </c>
@@ -7452,7 +7415,7 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="10" t="s">
         <v>205</v>
       </c>
@@ -7466,7 +7429,7 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="10" t="s">
         <v>206</v>
       </c>
@@ -7480,7 +7443,7 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="10" t="s">
         <v>207</v>
       </c>
@@ -7494,7 +7457,7 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="10" t="s">
         <v>208</v>
       </c>
@@ -7508,7 +7471,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5">
       <c r="A45" s="10" t="s">
         <v>209</v>
       </c>
@@ -7522,7 +7485,7 @@
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5">
       <c r="A46" s="10" t="s">
         <v>210</v>
       </c>
@@ -7536,7 +7499,7 @@
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" s="10" t="s">
         <v>211</v>
       </c>
@@ -7558,22 +7521,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J296"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="5" max="5" width="9.58203125" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="50.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="50.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -7602,7 +7565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -7629,7 +7592,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>411</v>
       </c>
@@ -7651,7 +7614,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" t="str">
         <f t="shared" ref="A4:A26" si="1">A3</f>
         <v>NODE_2</v>
@@ -7675,7 +7638,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7689,7 +7652,7 @@
         <v>NODE_2_2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7713,7 +7676,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="34">
       <c r="A7" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7733,7 +7696,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7757,7 +7720,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="34">
       <c r="A9" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7781,7 +7744,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7795,7 +7758,7 @@
         <v>NODE_2_7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="34">
       <c r="A11" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7819,7 +7782,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="34">
       <c r="A12" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7843,7 +7806,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="34">
       <c r="A13" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7867,7 +7830,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="34">
       <c r="A14" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7891,7 +7854,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="34">
       <c r="A15" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7915,7 +7878,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="51">
       <c r="A16" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7935,7 +7898,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7959,7 +7922,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7983,7 +7946,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7997,7 +7960,7 @@
         <v>NODE_2_16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="34">
       <c r="A20" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8018,10 +7981,10 @@
         <v>403</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8045,7 +8008,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="34">
       <c r="A22" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8066,10 +8029,10 @@
         <v>51</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8093,7 +8056,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="34">
       <c r="A24" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8117,7 +8080,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="51">
       <c r="A25" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8141,7 +8104,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8165,7 +8128,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="34">
       <c r="A27" t="s">
         <v>561</v>
       </c>
@@ -8187,7 +8150,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="str">
         <f t="shared" ref="A28:A52" si="3">A27</f>
         <v>NODE_30B</v>
@@ -8211,7 +8174,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="34">
       <c r="A29" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8235,7 +8198,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="34">
       <c r="A30" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8259,7 +8222,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8283,7 +8246,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="34">
       <c r="A32" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8307,7 +8270,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="34">
       <c r="A33" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8331,7 +8294,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8355,7 +8318,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="34">
       <c r="A35" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8379,7 +8342,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="34">
       <c r="A36" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8400,10 +8363,10 @@
         <v>5</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8427,7 +8390,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8441,7 +8404,7 @@
         <v>NODE_30B_11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="34">
       <c r="A39" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8465,7 +8428,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="34">
       <c r="A40" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8489,7 +8452,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8513,7 +8476,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="34">
       <c r="A42" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8534,10 +8497,10 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="34">
       <c r="A43" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8561,7 +8524,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8588,7 +8551,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="34">
       <c r="A45" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8615,7 +8578,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="34">
       <c r="A46" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8642,7 +8605,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8669,7 +8632,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="34">
       <c r="A48" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8696,7 +8659,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="34">
       <c r="A49" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8720,7 +8683,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8744,7 +8707,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="34">
       <c r="A51" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8765,10 +8728,10 @@
         <v>7</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8792,7 +8755,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>587</v>
       </c>
@@ -8814,7 +8777,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="34">
       <c r="A55" t="str">
         <f>A54</f>
         <v>NODE_16</v>
@@ -8835,10 +8798,10 @@
         <v>51</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="34">
       <c r="A56" t="str">
         <f>A55</f>
         <v>NODE_16</v>
@@ -8862,7 +8825,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="str">
         <f t="shared" ref="A57:A115" si="7">A56</f>
         <v>NODE_16</v>
@@ -8883,10 +8846,10 @@
         <v>406</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="34">
       <c r="A58" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8907,10 +8870,10 @@
         <v>406</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="34">
       <c r="A59" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8931,10 +8894,10 @@
         <v>407</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="34">
       <c r="A60" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8955,10 +8918,10 @@
         <v>406</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8979,10 +8942,10 @@
         <v>406</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9006,7 +8969,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9027,10 +8990,10 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9051,10 +9014,10 @@
         <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="34">
       <c r="A65" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9075,10 +9038,10 @@
         <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9102,7 +9065,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="34">
       <c r="A67" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9123,10 +9086,10 @@
         <v>51</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9150,7 +9113,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="34">
       <c r="A69" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9171,10 +9134,10 @@
         <v>7</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="34">
       <c r="A70" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9195,10 +9158,10 @@
         <v>51</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="34">
       <c r="A71" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9219,10 +9182,10 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="34">
       <c r="A72" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9243,12 +9206,12 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="34">
       <c r="A73" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9269,10 +9232,10 @@
         <v>591</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="34">
       <c r="A74" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9293,10 +9256,10 @@
         <v>589</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9320,7 +9283,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9341,10 +9304,10 @@
         <v>591</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="34">
       <c r="A77" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9365,10 +9328,10 @@
         <v>51</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
       <c r="A78" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9392,7 +9355,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9413,10 +9376,10 @@
         <v>406</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9440,7 +9403,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7">
       <c r="A81" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9464,7 +9427,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="34">
       <c r="A82" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9488,7 +9451,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7">
       <c r="A83" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9509,10 +9472,10 @@
         <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9536,7 +9499,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7">
       <c r="A85" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9557,10 +9520,10 @@
         <v>5</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9584,7 +9547,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="34">
       <c r="A87" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9605,10 +9568,10 @@
         <v>599</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9629,10 +9592,10 @@
         <v>599</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9653,10 +9616,10 @@
         <v>599</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9680,7 +9643,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="34">
       <c r="A91" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9701,10 +9664,10 @@
         <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9725,10 +9688,10 @@
         <v>599</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9749,10 +9712,10 @@
         <v>7</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9773,10 +9736,10 @@
         <v>599</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="34">
       <c r="A95" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9797,10 +9760,10 @@
         <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="34">
       <c r="A96" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9821,10 +9784,10 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9845,10 +9808,10 @@
         <v>600</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9869,10 +9832,10 @@
         <v>7</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="34">
       <c r="A99" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9893,10 +9856,10 @@
         <v>7</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="34">
       <c r="A100" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9917,10 +9880,10 @@
         <v>7</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="34">
       <c r="A101" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9944,10 +9907,10 @@
         <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="34">
       <c r="A102" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9971,10 +9934,10 @@
         <v>5</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10001,7 +9964,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="34">
       <c r="A104" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10025,10 +9988,10 @@
         <v>5</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="34">
       <c r="A105" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10052,10 +10015,10 @@
         <v>5</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="34">
       <c r="A106" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10079,10 +10042,10 @@
         <v>600</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="34">
       <c r="A107" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10106,10 +10069,10 @@
         <v>600</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10133,10 +10096,10 @@
         <v>5</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10163,7 +10126,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10187,10 +10150,10 @@
         <v>5</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="34">
       <c r="A111" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10214,10 +10177,10 @@
         <v>600</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="34">
       <c r="A112" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10241,10 +10204,10 @@
         <v>5</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10268,10 +10231,10 @@
         <v>600</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="34">
       <c r="A114" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10295,10 +10258,10 @@
         <v>5</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="34">
       <c r="A115" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10322,10 +10285,10 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="34">
       <c r="A116" t="str">
         <f t="shared" ref="A116:A119" si="10">A115</f>
         <v>NODE_16</v>
@@ -10349,10 +10312,10 @@
         <v>5</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="34">
       <c r="A117" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10376,10 +10339,10 @@
         <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10403,10 +10366,10 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10430,12 +10393,12 @@
         <v>7</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -10452,12 +10415,12 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="34">
       <c r="A122" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B122">
         <f t="shared" ref="B122:B159" si="13">B121+1</f>
@@ -10475,12 +10438,12 @@
         <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="34">
       <c r="A123" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B123">
         <f t="shared" si="13"/>
@@ -10498,12 +10461,12 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B124">
         <f t="shared" si="13"/>
@@ -10521,12 +10484,12 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="34">
       <c r="A125" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B125">
         <f t="shared" si="13"/>
@@ -10544,13 +10507,13 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B126">
         <f t="shared" si="13"/>
@@ -10568,12 +10531,12 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B127">
         <f t="shared" si="13"/>
@@ -10591,12 +10554,12 @@
         <v>51</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B128">
         <f t="shared" si="13"/>
@@ -10614,12 +10577,12 @@
         <v>51</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="34">
       <c r="A129" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B129">
         <f t="shared" si="13"/>
@@ -10637,12 +10600,12 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B130">
         <f t="shared" si="13"/>
@@ -10660,12 +10623,12 @@
         <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B131">
         <f t="shared" si="13"/>
@@ -10683,12 +10646,12 @@
         <v>51</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="34">
       <c r="A132" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B132">
         <f t="shared" si="13"/>
@@ -10706,12 +10669,12 @@
         <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="34">
       <c r="A133" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B133">
         <f t="shared" si="13"/>
@@ -10729,12 +10692,12 @@
         <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="34">
       <c r="A134" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B134">
         <f t="shared" si="13"/>
@@ -10752,12 +10715,12 @@
         <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B135">
         <f t="shared" si="13"/>
@@ -10775,12 +10738,12 @@
         <v>51</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B136">
         <f t="shared" si="13"/>
@@ -10795,15 +10758,15 @@
         <v>XunYu</v>
       </c>
       <c r="F136" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="34">
       <c r="A137" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B137">
         <f t="shared" si="13"/>
@@ -10818,15 +10781,15 @@
         <v>XunYu</v>
       </c>
       <c r="F137" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B138">
         <f t="shared" si="13"/>
@@ -10844,12 +10807,12 @@
         <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="51">
       <c r="A139" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B139">
         <f t="shared" si="13"/>
@@ -10864,15 +10827,15 @@
         <v>XunYu</v>
       </c>
       <c r="F139" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B140">
         <f t="shared" si="13"/>
@@ -10887,15 +10850,15 @@
         <v>XunYu</v>
       </c>
       <c r="F140" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B141">
         <f t="shared" si="13"/>
@@ -10913,12 +10876,12 @@
         <v>51</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B142">
         <f t="shared" si="13"/>
@@ -10933,15 +10896,15 @@
         <v>XunYu</v>
       </c>
       <c r="F142" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="34">
       <c r="A143" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B143">
         <f t="shared" si="13"/>
@@ -10959,12 +10922,12 @@
         <v>51</v>
       </c>
       <c r="G143" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
         <v>666</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>671</v>
       </c>
       <c r="B144">
         <f t="shared" si="13"/>
@@ -10985,9 +10948,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="34">
       <c r="A145" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B145">
         <f t="shared" si="13"/>
@@ -11005,12 +10968,12 @@
         <v>51</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="34">
       <c r="A146" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B146">
         <f t="shared" si="13"/>
@@ -11028,12 +10991,12 @@
         <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B147">
         <f t="shared" si="13"/>
@@ -11051,12 +11014,12 @@
         <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="34">
       <c r="A148" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B148">
         <f t="shared" si="13"/>
@@ -11074,12 +11037,12 @@
         <v>7</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="34">
       <c r="A149" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B149">
         <f t="shared" si="13"/>
@@ -11097,12 +11060,12 @@
         <v>7</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="34">
       <c r="A150" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B150">
         <f t="shared" si="13"/>
@@ -11120,12 +11083,12 @@
         <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="34">
       <c r="A151" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B151">
         <f t="shared" si="13"/>
@@ -11143,12 +11106,12 @@
         <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B152">
         <f t="shared" si="13"/>
@@ -11163,15 +11126,15 @@
         <v>XunYu</v>
       </c>
       <c r="F152" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B153">
         <f t="shared" si="13"/>
@@ -11189,12 +11152,12 @@
         <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B154">
         <f t="shared" si="13"/>
@@ -11215,9 +11178,9 @@
         <v>597</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="34">
       <c r="A155" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B155">
         <f t="shared" si="13"/>
@@ -11235,12 +11198,12 @@
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B156">
         <f t="shared" si="13"/>
@@ -11258,12 +11221,12 @@
         <v>51</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="34">
       <c r="A157" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B157">
         <f t="shared" si="13"/>
@@ -11281,12 +11244,12 @@
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B158">
         <f t="shared" si="13"/>
@@ -11304,12 +11267,12 @@
         <v>591</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B159">
         <f t="shared" si="13"/>
@@ -11327,12 +11290,12 @@
         <v>51</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -11349,10 +11312,10 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="34">
       <c r="A162" t="str">
         <f>A161</f>
         <v>NODE_28</v>
@@ -11373,10 +11336,10 @@
         <v>591</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="34">
       <c r="A163" t="str">
         <f t="shared" ref="A163:A199" si="17">A162</f>
         <v>NODE_28</v>
@@ -11397,10 +11360,10 @@
         <v>7</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="34">
       <c r="A164" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11421,10 +11384,10 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
       <c r="A165" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11448,7 +11411,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7">
       <c r="A166" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11469,10 +11432,10 @@
         <v>406</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
       <c r="A167" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11493,10 +11456,10 @@
         <v>406</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="34">
       <c r="A168" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11517,10 +11480,10 @@
         <v>407</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="34">
       <c r="A169" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11541,10 +11504,10 @@
         <v>7</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
       <c r="A170" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11565,10 +11528,10 @@
         <v>591</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
       <c r="A171" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11592,7 +11555,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7">
       <c r="A172" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11606,7 +11569,7 @@
         <v>NODE_28_11</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7">
       <c r="A173" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11620,16 +11583,16 @@
         <v>NODE_28_12</v>
       </c>
       <c r="E173" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="F173" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
       <c r="A174" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11643,16 +11606,16 @@
         <v>NODE_28_13</v>
       </c>
       <c r="E174" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="F174" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
       <c r="A175" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11666,16 +11629,16 @@
         <v>NODE_28_14</v>
       </c>
       <c r="E175" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="F175" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
       <c r="A176" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11696,10 +11659,10 @@
         <v>7</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="34">
       <c r="A177" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11720,10 +11683,10 @@
         <v>591</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
       <c r="A178" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11747,7 +11710,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7">
       <c r="A179" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11768,10 +11731,10 @@
         <v>591</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
       <c r="A180" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11791,10 +11754,10 @@
         <v>415</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="34">
       <c r="A181" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11815,10 +11778,10 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="34">
       <c r="A182" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11839,10 +11802,10 @@
         <v>7</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
       <c r="A183" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11863,10 +11826,10 @@
         <v>406</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
       <c r="A184" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11887,10 +11850,10 @@
         <v>591</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
       <c r="A185" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11914,7 +11877,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7">
       <c r="A186" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11928,16 +11891,16 @@
         <v>NODE_28_25</v>
       </c>
       <c r="E186" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F186" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
       <c r="A187" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11951,16 +11914,16 @@
         <v>NODE_28_26</v>
       </c>
       <c r="E187" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F187" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
       <c r="A188" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11984,7 +11947,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7">
       <c r="A189" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12008,7 +11971,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7">
       <c r="A190" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12029,10 +11992,10 @@
         <v>591</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="34">
       <c r="A191" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12046,16 +12009,16 @@
         <v>NODE_28_30</v>
       </c>
       <c r="E191" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F191" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="34">
       <c r="A192" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12076,10 +12039,10 @@
         <v>7</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="34">
       <c r="A193" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12100,10 +12063,10 @@
         <v>7</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
       <c r="A194" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12117,16 +12080,16 @@
         <v>NODE_28_33</v>
       </c>
       <c r="E194" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F194" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="34">
       <c r="A195" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12140,16 +12103,16 @@
         <v>NODE_28_34</v>
       </c>
       <c r="E195" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F195" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="34">
       <c r="A196" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12163,16 +12126,16 @@
         <v>NODE_28_35</v>
       </c>
       <c r="E196" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F196" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
       <c r="A197" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12186,16 +12149,16 @@
         <v>NODE_28_36</v>
       </c>
       <c r="E197" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F197" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
       <c r="A198" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12219,7 +12182,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="34">
       <c r="A199" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12240,12 +12203,12 @@
         <v>406</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="34">
       <c r="A201" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -12262,10 +12225,10 @@
         <v>406</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
       <c r="A202" t="str">
         <f>A201</f>
         <v>NODE_29</v>
@@ -12286,10 +12249,10 @@
         <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
       <c r="A203" t="str">
         <f t="shared" ref="A203:A239" si="23">A202</f>
         <v>NODE_29</v>
@@ -12313,7 +12276,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7">
       <c r="A204" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12334,10 +12297,10 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="34">
       <c r="A205" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12358,10 +12321,10 @@
         <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="34">
       <c r="A206" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12382,10 +12345,10 @@
         <v>406</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
       <c r="A207" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12406,10 +12369,10 @@
         <v>407</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
       <c r="A208" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12430,10 +12393,10 @@
         <v>591</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
       <c r="A209" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12454,10 +12417,10 @@
         <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
       <c r="A210" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12478,10 +12441,10 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="34">
       <c r="A211" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12502,10 +12465,10 @@
         <v>11</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
       <c r="A212" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12526,10 +12489,10 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="34">
       <c r="A213" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12550,10 +12513,10 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="34">
       <c r="A214" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12574,10 +12537,10 @@
         <v>7</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="34">
       <c r="A215" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12598,10 +12561,10 @@
         <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
       <c r="A216" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12622,10 +12585,10 @@
         <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
       <c r="A217" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12646,10 +12609,10 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
       <c r="A218" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12670,10 +12633,10 @@
         <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
       <c r="A219" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12694,10 +12657,10 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
       <c r="A220" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12721,7 +12684,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" ht="34">
       <c r="A221" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12742,10 +12705,10 @@
         <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="34">
       <c r="A222" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12766,10 +12729,10 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
       <c r="A223" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12790,10 +12753,10 @@
         <v>591</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="34">
       <c r="A224" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12814,10 +12777,10 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
       <c r="A225" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12838,10 +12801,10 @@
         <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="34">
       <c r="A226" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12862,10 +12825,10 @@
         <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
       <c r="A227" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12886,10 +12849,10 @@
         <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="34">
       <c r="A228" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12910,10 +12873,10 @@
         <v>591</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
       <c r="A229" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12934,10 +12897,10 @@
         <v>7</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="34">
       <c r="A230" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12958,10 +12921,10 @@
         <v>591</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="34">
       <c r="A231" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12982,10 +12945,10 @@
         <v>591</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
       <c r="A232" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13006,10 +12969,10 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
       <c r="A233" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13023,7 +12986,7 @@
         <v>NODE_29_32</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7">
       <c r="A234" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13047,7 +13010,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" ht="34">
       <c r="A235" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13068,10 +13031,10 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
       <c r="A236" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13092,10 +13055,10 @@
         <v>7</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
       <c r="A237" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13116,10 +13079,10 @@
         <v>406</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="34">
       <c r="A238" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13140,10 +13103,10 @@
         <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="34">
       <c r="A239" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13164,12 +13127,12 @@
         <v>406</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -13186,10 +13149,10 @@
         <v>403</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
       <c r="A242" t="str">
         <f>A241</f>
         <v>NODE_31</v>
@@ -13210,10 +13173,10 @@
         <v>403</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="34">
       <c r="A243" t="str">
         <f t="shared" ref="A243:A261" si="29">A242</f>
         <v>NODE_31</v>
@@ -13234,10 +13197,10 @@
         <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
       <c r="A244" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13258,10 +13221,10 @@
         <v>51</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="34">
       <c r="A245" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13282,10 +13245,10 @@
         <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
       <c r="A246" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13306,10 +13269,10 @@
         <v>51</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="34">
       <c r="A247" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13330,10 +13293,10 @@
         <v>9</v>
       </c>
       <c r="G247" s="39" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="34">
       <c r="A248" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13354,10 +13317,10 @@
         <v>51</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
       <c r="A249" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13378,10 +13341,10 @@
         <v>9</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
       <c r="A250" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13402,10 +13365,10 @@
         <v>51</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
       <c r="A251" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13426,10 +13389,10 @@
         <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
       <c r="A252" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13450,10 +13413,10 @@
         <v>51</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="34">
       <c r="A253" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13474,10 +13437,10 @@
         <v>7</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
       <c r="A254" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13498,10 +13461,10 @@
         <v>51</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="34">
       <c r="A255" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13522,10 +13485,10 @@
         <v>591</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
       <c r="A256" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13546,10 +13509,10 @@
         <v>51</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="34">
       <c r="A257" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13570,10 +13533,10 @@
         <v>9</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="34">
       <c r="A258" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13594,10 +13557,10 @@
         <v>7</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13618,10 +13581,10 @@
         <v>9</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13642,10 +13605,10 @@
         <v>9</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="34">
       <c r="A261" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13666,10 +13629,10 @@
         <v>7</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="34">
       <c r="A262" t="str">
         <f t="shared" ref="A262" si="33">A261</f>
         <v>NODE_31</v>
@@ -13690,10 +13653,10 @@
         <v>9</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="str">
         <f t="shared" ref="A263" si="35">A262</f>
         <v>NODE_31</v>
@@ -13714,10 +13677,10 @@
         <v>7</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="str">
         <f t="shared" ref="A264" si="36">A263</f>
         <v>NODE_31</v>
@@ -13731,7 +13694,7 @@
         <v>NODE_31_23</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7">
       <c r="A265" t="str">
         <f t="shared" ref="A265" si="37">A264</f>
         <v>NODE_31</v>
@@ -13752,10 +13715,10 @@
         <v>9</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="34">
       <c r="A266" t="str">
         <f t="shared" ref="A266" si="38">A265</f>
         <v>NODE_31</v>
@@ -13776,10 +13739,10 @@
         <v>9</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="34">
       <c r="A267" t="str">
         <f t="shared" ref="A267" si="39">A266</f>
         <v>NODE_31</v>
@@ -13800,10 +13763,10 @@
         <v>7</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="34">
       <c r="A268" t="str">
         <f t="shared" ref="A268" si="40">A267</f>
         <v>NODE_31</v>
@@ -13824,10 +13787,10 @@
         <v>7</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="str">
         <f t="shared" ref="A269" si="41">A268</f>
         <v>NODE_31</v>
@@ -13848,10 +13811,10 @@
         <v>9</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="str">
         <f t="shared" ref="A270" si="42">A269</f>
         <v>NODE_31</v>
@@ -13872,10 +13835,10 @@
         <v>7</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="34">
       <c r="A271" t="str">
         <f t="shared" ref="A271" si="43">A270</f>
         <v>NODE_31</v>
@@ -13896,10 +13859,10 @@
         <v>9</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="str">
         <f t="shared" ref="A272" si="44">A271</f>
         <v>NODE_31</v>
@@ -13920,10 +13883,10 @@
         <v>7</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" t="str">
         <f t="shared" ref="A273" si="45">A272</f>
         <v>NODE_31</v>
@@ -13944,10 +13907,10 @@
         <v>9</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="34">
       <c r="A274" t="str">
         <f t="shared" ref="A274" si="46">A273</f>
         <v>NODE_31</v>
@@ -13968,10 +13931,10 @@
         <v>7</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="34">
       <c r="A275" t="str">
         <f t="shared" ref="A275" si="47">A274</f>
         <v>NODE_31</v>
@@ -13992,10 +13955,10 @@
         <v>7</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="34">
       <c r="A276" t="str">
         <f t="shared" ref="A276" si="48">A275</f>
         <v>NODE_31</v>
@@ -14016,10 +13979,10 @@
         <v>9</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="51">
       <c r="A277" t="str">
         <f t="shared" ref="A277" si="49">A276</f>
         <v>NODE_31</v>
@@ -14040,10 +14003,10 @@
         <v>7</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="str">
         <f t="shared" ref="A278" si="50">A277</f>
         <v>NODE_31</v>
@@ -14064,10 +14027,10 @@
         <v>9</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="34">
       <c r="A279" t="str">
         <f t="shared" ref="A279" si="51">A278</f>
         <v>NODE_31</v>
@@ -14088,10 +14051,10 @@
         <v>7</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="str">
         <f t="shared" ref="A280" si="52">A279</f>
         <v>NODE_31</v>
@@ -14115,7 +14078,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7">
       <c r="A281" t="str">
         <f t="shared" ref="A281" si="53">A280</f>
         <v>NODE_31</v>
@@ -14133,13 +14096,13 @@
         <v>FanJiang</v>
       </c>
       <c r="F281" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="34">
       <c r="A282" t="str">
         <f t="shared" ref="A282:A296" si="54">A281</f>
         <v>NODE_31</v>
@@ -14157,13 +14120,13 @@
         <v>ZhangDa</v>
       </c>
       <c r="F282" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14184,10 +14147,10 @@
         <v>9</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14208,10 +14171,10 @@
         <v>7</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14232,10 +14195,10 @@
         <v>7</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14256,10 +14219,10 @@
         <v>7</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14280,10 +14243,10 @@
         <v>11</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14304,10 +14267,10 @@
         <v>11</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="34">
       <c r="A289" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14328,10 +14291,10 @@
         <v>11</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14352,10 +14315,10 @@
         <v>5</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="34">
       <c r="A291" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14376,10 +14339,10 @@
         <v>5</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="34">
       <c r="A292" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14400,10 +14363,10 @@
         <v>5</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="34">
       <c r="A293" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14424,10 +14387,10 @@
         <v>5</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="34">
       <c r="A294" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14448,10 +14411,10 @@
         <v>5</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="34">
       <c r="A295" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14472,10 +14435,10 @@
         <v>5</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="str">
         <f t="shared" si="54"/>
         <v>NODE_31</v>
@@ -14496,7 +14459,7 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -14507,18 +14470,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC39210-5BFC-4779-981A-9157C4AD45DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G126"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="65.75" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>363</v>
       </c>
@@ -14541,7 +14504,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -14564,7 +14527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="27" t="s">
         <v>364</v>
       </c>
@@ -14581,7 +14544,7 @@
       </c>
       <c r="F3" s="21"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="27" t="s">
         <v>364</v>
       </c>
@@ -14598,7 +14561,7 @@
       </c>
       <c r="F4" s="21"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="27" t="s">
         <v>364</v>
       </c>
@@ -14615,7 +14578,7 @@
       </c>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="27" t="s">
         <v>364</v>
       </c>
@@ -14632,7 +14595,7 @@
       </c>
       <c r="F6" s="21"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="27" t="s">
         <v>364</v>
       </c>
@@ -14649,7 +14612,7 @@
       </c>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="27" t="s">
         <v>364</v>
       </c>
@@ -14666,7 +14629,7 @@
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="27" t="s">
         <v>364</v>
       </c>
@@ -14683,7 +14646,7 @@
       </c>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="27" t="s">
         <v>364</v>
       </c>
@@ -14700,7 +14663,7 @@
       </c>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="27" t="s">
         <v>364</v>
       </c>
@@ -14717,7 +14680,7 @@
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="27" t="s">
         <v>364</v>
       </c>
@@ -14734,7 +14697,7 @@
       </c>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="27" t="s">
         <v>364</v>
       </c>
@@ -14751,7 +14714,7 @@
       </c>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="27" t="s">
         <v>364</v>
       </c>
@@ -14768,7 +14731,7 @@
       </c>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="27" t="s">
         <v>364</v>
       </c>
@@ -14785,7 +14748,7 @@
       </c>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="27" t="s">
         <v>364</v>
       </c>
@@ -14802,7 +14765,7 @@
       </c>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="27" t="s">
         <v>364</v>
       </c>
@@ -14819,7 +14782,7 @@
       </c>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="27" t="s">
         <v>364</v>
       </c>
@@ -14836,7 +14799,7 @@
       </c>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="27" t="s">
         <v>364</v>
       </c>
@@ -14853,7 +14816,7 @@
       </c>
       <c r="F19" s="21"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="27" t="s">
         <v>364</v>
       </c>
@@ -14870,7 +14833,7 @@
       </c>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="27" t="s">
         <v>364</v>
       </c>
@@ -14887,7 +14850,7 @@
       </c>
       <c r="F21" s="21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="27" t="s">
         <v>364</v>
       </c>
@@ -14904,7 +14867,7 @@
       </c>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="27" t="s">
         <v>364</v>
       </c>
@@ -14921,7 +14884,7 @@
       </c>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="27" t="s">
         <v>364</v>
       </c>
@@ -14938,7 +14901,7 @@
       </c>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="27" t="s">
         <v>364</v>
       </c>
@@ -14955,7 +14918,7 @@
       </c>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="27" t="s">
         <v>364</v>
       </c>
@@ -14972,7 +14935,7 @@
       </c>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="27" t="s">
         <v>364</v>
       </c>
@@ -14989,7 +14952,7 @@
       </c>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="27" t="s">
         <v>364</v>
       </c>
@@ -15006,7 +14969,7 @@
       </c>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="27" t="s">
         <v>364</v>
       </c>
@@ -15023,7 +14986,7 @@
       </c>
       <c r="F29" s="21"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="27" t="s">
         <v>364</v>
       </c>
@@ -15040,7 +15003,7 @@
       </c>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="27" t="s">
         <v>364</v>
       </c>
@@ -15057,7 +15020,7 @@
       </c>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="27" t="s">
         <v>364</v>
       </c>
@@ -15074,7 +15037,7 @@
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="27" t="s">
         <v>364</v>
       </c>
@@ -15091,7 +15054,7 @@
       </c>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="27" t="s">
         <v>364</v>
       </c>
@@ -15104,11 +15067,11 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="F34" s="21"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="27" t="s">
         <v>364</v>
       </c>
@@ -15121,11 +15084,11 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="F35" s="24"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" s="21" t="s">
         <v>364</v>
       </c>
@@ -15138,11 +15101,11 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" s="21" t="s">
         <v>364</v>
       </c>
@@ -15159,7 +15122,7 @@
       </c>
       <c r="F37" s="33"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" s="21" t="s">
         <v>364</v>
       </c>
@@ -15176,7 +15139,7 @@
       </c>
       <c r="F38" s="21"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="21" t="s">
         <v>364</v>
       </c>
@@ -15193,12 +15156,12 @@
       </c>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="21" t="s">
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -15206,11 +15169,11 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="27" t="s">
         <v>369</v>
       </c>
@@ -15227,7 +15190,7 @@
       </c>
       <c r="F41" s="21"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" s="27" t="s">
         <v>369</v>
       </c>
@@ -15244,7 +15207,7 @@
       </c>
       <c r="F42" s="21"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" s="27" t="s">
         <v>369</v>
       </c>
@@ -15261,7 +15224,7 @@
       </c>
       <c r="F43" s="21"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" s="27" t="s">
         <v>369</v>
       </c>
@@ -15278,7 +15241,7 @@
       </c>
       <c r="F44" s="21"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" s="27" t="s">
         <v>369</v>
       </c>
@@ -15295,7 +15258,7 @@
       </c>
       <c r="F45" s="21"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="27" t="s">
         <v>369</v>
       </c>
@@ -15312,7 +15275,7 @@
       </c>
       <c r="F46" s="21"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" s="27" t="s">
         <v>369</v>
       </c>
@@ -15329,7 +15292,7 @@
       </c>
       <c r="F47" s="21"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" s="27" t="s">
         <v>369</v>
       </c>
@@ -15346,7 +15309,7 @@
       </c>
       <c r="F48" s="21"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" s="27" t="s">
         <v>369</v>
       </c>
@@ -15363,7 +15326,7 @@
       </c>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="27" t="s">
         <v>369</v>
       </c>
@@ -15380,7 +15343,7 @@
       </c>
       <c r="F50" s="21"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="27" t="s">
         <v>369</v>
       </c>
@@ -15397,7 +15360,7 @@
       </c>
       <c r="F51" s="21"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="27" t="s">
         <v>369</v>
       </c>
@@ -15414,7 +15377,7 @@
       </c>
       <c r="F52" s="21"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="27" t="s">
         <v>369</v>
       </c>
@@ -15431,7 +15394,7 @@
       </c>
       <c r="F53" s="21"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" s="27" t="s">
         <v>369</v>
       </c>
@@ -15449,7 +15412,7 @@
       <c r="F54" s="21"/>
       <c r="G54" s="35"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="27" t="s">
         <v>369</v>
       </c>
@@ -15467,7 +15430,7 @@
       <c r="F55" s="21"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" s="27" t="s">
         <v>369</v>
       </c>
@@ -15485,7 +15448,7 @@
       <c r="F56" s="21"/>
       <c r="G56" s="35"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="27" t="s">
         <v>369</v>
       </c>
@@ -15503,7 +15466,7 @@
       <c r="F57" s="21"/>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" s="27" t="s">
         <v>369</v>
       </c>
@@ -15521,7 +15484,7 @@
       <c r="F58" s="21"/>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" s="27" t="s">
         <v>369</v>
       </c>
@@ -15539,7 +15502,7 @@
       <c r="F59" s="21"/>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="27" t="s">
         <v>369</v>
       </c>
@@ -15557,7 +15520,7 @@
       <c r="F60" s="21"/>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="A61" s="27" t="s">
         <v>369</v>
       </c>
@@ -15575,7 +15538,7 @@
       <c r="F61" s="21"/>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="27" t="s">
         <v>369</v>
       </c>
@@ -15593,7 +15556,7 @@
       <c r="F62" s="21"/>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" s="27" t="s">
         <v>369</v>
       </c>
@@ -15611,7 +15574,7 @@
       <c r="F63" s="21"/>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" s="27" t="s">
         <v>369</v>
       </c>
@@ -15629,7 +15592,7 @@
       <c r="F64" s="21"/>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="27" t="s">
         <v>369</v>
       </c>
@@ -15647,7 +15610,7 @@
       <c r="F65" s="21"/>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="A66" s="27" t="s">
         <v>369</v>
       </c>
@@ -15665,7 +15628,7 @@
       <c r="F66" s="21"/>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="A67" s="27" t="s">
         <v>369</v>
       </c>
@@ -15683,7 +15646,7 @@
       <c r="F67" s="21"/>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="A68" s="27" t="s">
         <v>369</v>
       </c>
@@ -15701,7 +15664,7 @@
       <c r="F68" s="21"/>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7">
       <c r="A69" s="27" t="s">
         <v>369</v>
       </c>
@@ -15719,7 +15682,7 @@
       <c r="F69" s="21"/>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="A70" s="27" t="s">
         <v>369</v>
       </c>
@@ -15737,7 +15700,7 @@
       <c r="F70" s="21"/>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="A71" s="27" t="s">
         <v>369</v>
       </c>
@@ -15754,7 +15717,7 @@
       </c>
       <c r="F71" s="21"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7">
       <c r="A72" s="27" t="s">
         <v>369</v>
       </c>
@@ -15767,11 +15730,11 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F72" s="21"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="A73" s="27" t="s">
         <v>369</v>
       </c>
@@ -15784,11 +15747,11 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F73" s="24"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7">
       <c r="A74" s="27" t="s">
         <v>369</v>
       </c>
@@ -15801,11 +15764,11 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="F74" s="21"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="A75" s="27" t="s">
         <v>369</v>
       </c>
@@ -15822,7 +15785,7 @@
       </c>
       <c r="F75" s="33"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="A76" s="27" t="s">
         <v>369</v>
       </c>
@@ -15839,7 +15802,7 @@
       </c>
       <c r="F76" s="24"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="A77" s="27" t="s">
         <v>369</v>
       </c>
@@ -15856,12 +15819,12 @@
       </c>
       <c r="F77" s="21"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7">
       <c r="A78" s="27" t="s">
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -15869,11 +15832,11 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F78" s="21"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="21" t="s">
         <v>365</v>
       </c>
@@ -15890,7 +15853,7 @@
       <c r="E79" s="29"/>
       <c r="F79" s="21"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="21" t="s">
         <v>365</v>
       </c>
@@ -15907,7 +15870,7 @@
       <c r="E80" s="29"/>
       <c r="F80" s="21"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="A81" s="21" t="s">
         <v>365</v>
       </c>
@@ -15924,7 +15887,7 @@
       <c r="E81" s="29"/>
       <c r="F81" s="21"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6">
       <c r="A82" s="21" t="s">
         <v>365</v>
       </c>
@@ -15941,7 +15904,7 @@
       <c r="E82" s="29"/>
       <c r="F82" s="21"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="A83" s="21" t="s">
         <v>365</v>
       </c>
@@ -15958,7 +15921,7 @@
       <c r="E83" s="29"/>
       <c r="F83" s="21"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="A84" s="21" t="s">
         <v>365</v>
       </c>
@@ -15975,7 +15938,7 @@
       <c r="E84" s="29"/>
       <c r="F84" s="21"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="A85" s="21" t="s">
         <v>365</v>
       </c>
@@ -15992,7 +15955,7 @@
       <c r="E85" s="29"/>
       <c r="F85" s="21"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="A86" s="21" t="s">
         <v>365</v>
       </c>
@@ -16009,7 +15972,7 @@
       <c r="E86" s="29"/>
       <c r="F86" s="21"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6">
       <c r="A87" s="21" t="s">
         <v>365</v>
       </c>
@@ -16026,7 +15989,7 @@
       <c r="E87" s="29"/>
       <c r="F87" s="21"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="A88" s="21" t="s">
         <v>365</v>
       </c>
@@ -16043,7 +16006,7 @@
       <c r="E88" s="29"/>
       <c r="F88" s="21"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="A89" s="21" t="s">
         <v>365</v>
       </c>
@@ -16060,7 +16023,7 @@
       <c r="E89" s="29"/>
       <c r="F89" s="21"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="A90" s="21" t="s">
         <v>365</v>
       </c>
@@ -16077,7 +16040,7 @@
       <c r="E90" s="29"/>
       <c r="F90" s="21"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6">
       <c r="A91" s="21" t="s">
         <v>365</v>
       </c>
@@ -16094,7 +16057,7 @@
       <c r="E91" s="29"/>
       <c r="F91" s="21"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="A92" s="21" t="s">
         <v>365</v>
       </c>
@@ -16111,7 +16074,7 @@
       <c r="E92" s="29"/>
       <c r="F92" s="21"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6">
       <c r="A93" s="21" t="s">
         <v>365</v>
       </c>
@@ -16128,7 +16091,7 @@
       <c r="E93" s="29"/>
       <c r="F93" s="21"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6">
       <c r="A94" s="21" t="s">
         <v>365</v>
       </c>
@@ -16145,7 +16108,7 @@
       <c r="E94" s="29"/>
       <c r="F94" s="21"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="21" t="s">
         <v>365</v>
       </c>
@@ -16162,7 +16125,7 @@
       <c r="E95" s="29"/>
       <c r="F95" s="21"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="21" t="s">
         <v>365</v>
       </c>
@@ -16179,7 +16142,7 @@
       <c r="E96" s="29"/>
       <c r="F96" s="21"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6">
       <c r="A97" s="21" t="s">
         <v>365</v>
       </c>
@@ -16196,7 +16159,7 @@
       <c r="E97" s="29"/>
       <c r="F97" s="21"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6">
       <c r="A98" s="21" t="s">
         <v>365</v>
       </c>
@@ -16213,7 +16176,7 @@
       <c r="E98" s="29"/>
       <c r="F98" s="21"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6">
       <c r="A99" s="21" t="s">
         <v>365</v>
       </c>
@@ -16230,7 +16193,7 @@
       <c r="E99" s="29"/>
       <c r="F99" s="21"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="21" t="s">
         <v>365</v>
       </c>
@@ -16247,7 +16210,7 @@
       <c r="E100" s="29"/>
       <c r="F100" s="21"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="21" t="s">
         <v>365</v>
       </c>
@@ -16264,7 +16227,7 @@
       <c r="E101" s="29"/>
       <c r="F101" s="21"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="21" t="s">
         <v>365</v>
       </c>
@@ -16281,7 +16244,7 @@
       <c r="E102" s="29"/>
       <c r="F102" s="21"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="21" t="s">
         <v>367</v>
       </c>
@@ -16301,7 +16264,7 @@
       </c>
       <c r="F103" s="21"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="21" t="s">
         <v>367</v>
       </c>
@@ -16321,7 +16284,7 @@
       </c>
       <c r="F104" s="21"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="21" t="s">
         <v>367</v>
       </c>
@@ -16341,7 +16304,7 @@
       </c>
       <c r="F105" s="21"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="21" t="s">
         <v>367</v>
       </c>
@@ -16361,7 +16324,7 @@
       </c>
       <c r="F106" s="21"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="21" t="s">
         <v>367</v>
       </c>
@@ -16381,7 +16344,7 @@
       </c>
       <c r="F107" s="21"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6">
       <c r="A108" s="21" t="s">
         <v>367</v>
       </c>
@@ -16401,7 +16364,7 @@
       </c>
       <c r="F108" s="21"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6">
       <c r="A109" s="21" t="s">
         <v>367</v>
       </c>
@@ -16421,7 +16384,7 @@
       </c>
       <c r="F109" s="21"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="21" t="s">
         <v>367</v>
       </c>
@@ -16441,7 +16404,7 @@
       </c>
       <c r="F110" s="21"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="21" t="s">
         <v>367</v>
       </c>
@@ -16461,7 +16424,7 @@
       </c>
       <c r="F111" s="21"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="21" t="s">
         <v>367</v>
       </c>
@@ -16481,7 +16444,7 @@
       </c>
       <c r="F112" s="21"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="21" t="s">
         <v>367</v>
       </c>
@@ -16501,7 +16464,7 @@
       </c>
       <c r="F113" s="21"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="21" t="s">
         <v>367</v>
       </c>
@@ -16521,7 +16484,7 @@
       </c>
       <c r="F114" s="21"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6">
       <c r="A115" s="21" t="s">
         <v>367</v>
       </c>
@@ -16541,7 +16504,7 @@
       </c>
       <c r="F115" s="21"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="21" t="s">
         <v>367</v>
       </c>
@@ -16561,7 +16524,7 @@
       </c>
       <c r="F116" s="21"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="21" t="s">
         <v>367</v>
       </c>
@@ -16581,7 +16544,7 @@
       </c>
       <c r="F117" s="21"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="21" t="s">
         <v>367</v>
       </c>
@@ -16601,7 +16564,7 @@
       </c>
       <c r="F118" s="21"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="21" t="s">
         <v>367</v>
       </c>
@@ -16621,7 +16584,7 @@
       </c>
       <c r="F119" s="21"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="A120" s="21" t="s">
         <v>367</v>
       </c>
@@ -16641,7 +16604,7 @@
       </c>
       <c r="F120" s="21"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="A121" s="21" t="s">
         <v>367</v>
       </c>
@@ -16661,7 +16624,7 @@
       </c>
       <c r="F121" s="21"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="A122" s="21" t="s">
         <v>367</v>
       </c>
@@ -16681,7 +16644,7 @@
       </c>
       <c r="F122" s="21"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6">
       <c r="A123" s="21" t="s">
         <v>367</v>
       </c>
@@ -16701,7 +16664,7 @@
       </c>
       <c r="F123" s="21"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="A124" s="21" t="s">
         <v>367</v>
       </c>
@@ -16721,7 +16684,7 @@
       </c>
       <c r="F124" s="21"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="A125" s="21" t="s">
         <v>367</v>
       </c>
@@ -16741,7 +16704,7 @@
       </c>
       <c r="F125" s="21"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6">
       <c r="A126" s="21" t="s">
         <v>367</v>
       </c>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1400" windowWidth="25820" windowHeight="16220" activeTab="5"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="845">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3316,6 +3316,14 @@
   <si>
     <t>우선 아수라가 현현하는 건 막아야한다..
 시간을 되돌릴 수 밖에..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸우욱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7522,7 +7530,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J296"/>
+  <dimension ref="A1:J298"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
@@ -13158,7 +13166,7 @@
         <v>NODE_31</v>
       </c>
       <c r="B242">
-        <f t="shared" ref="B242:B296" si="27">B241+1</f>
+        <f t="shared" ref="B242:B298" si="27">B241+1</f>
         <v>1</v>
       </c>
       <c r="C242" t="str">
@@ -13642,7 +13650,7 @@
         <v>21</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" ref="C262:C282" si="34">CONCATENATE(A262, "_", B262, IF(D262&lt;&gt;"", "_"&amp;D262, ""))</f>
+        <f t="shared" ref="C262:C280" si="34">CONCATENATE(A262, "_", B262, IF(D262&lt;&gt;"", "_"&amp;D262, ""))</f>
         <v>NODE_31_21</v>
       </c>
       <c r="E262" t="str">
@@ -13886,7 +13894,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:9">
       <c r="A273" t="str">
         <f t="shared" ref="A273" si="45">A272</f>
         <v>NODE_31</v>
@@ -13910,7 +13918,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="34">
+    <row r="274" spans="1:9" ht="34">
       <c r="A274" t="str">
         <f t="shared" ref="A274" si="46">A273</f>
         <v>NODE_31</v>
@@ -13934,7 +13942,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="34">
+    <row r="275" spans="1:9" ht="34">
       <c r="A275" t="str">
         <f t="shared" ref="A275" si="47">A274</f>
         <v>NODE_31</v>
@@ -13958,7 +13966,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="34">
+    <row r="276" spans="1:9" ht="34">
       <c r="A276" t="str">
         <f t="shared" ref="A276" si="48">A275</f>
         <v>NODE_31</v>
@@ -13982,7 +13990,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="51">
+    <row r="277" spans="1:9" ht="51">
       <c r="A277" t="str">
         <f t="shared" ref="A277" si="49">A276</f>
         <v>NODE_31</v>
@@ -14006,7 +14014,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:9">
       <c r="A278" t="str">
         <f t="shared" ref="A278" si="50">A277</f>
         <v>NODE_31</v>
@@ -14030,7 +14038,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="34">
+    <row r="279" spans="1:9" ht="34">
       <c r="A279" t="str">
         <f t="shared" ref="A279" si="51">A278</f>
         <v>NODE_31</v>
@@ -14054,9 +14062,9 @@
         <v>822</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:9">
       <c r="A280" t="str">
-        <f t="shared" ref="A280" si="52">A279</f>
+        <f t="shared" ref="A280:A298" si="52">A279</f>
         <v>NODE_31</v>
       </c>
       <c r="B280">
@@ -14069,18 +14077,20 @@
       </c>
       <c r="E280" t="str">
         <f>VLOOKUP(F280,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>FanJiang</v>
       </c>
       <c r="F280" t="s">
-        <v>9</v>
+        <v>691</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+        <v>843</v>
+      </c>
+      <c r="H280"/>
+      <c r="I280" s="3"/>
+    </row>
+    <row r="281" spans="1:9">
       <c r="A281" t="str">
-        <f t="shared" ref="A281" si="53">A280</f>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B281">
@@ -14088,23 +14098,23 @@
         <v>40</v>
       </c>
       <c r="C281" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="C281:C298" si="53">CONCATENATE(A281, "_", B281, IF(D281&lt;&gt;"", "_"&amp;D281, ""))</f>
         <v>NODE_31_40</v>
       </c>
       <c r="E281" t="str">
         <f>VLOOKUP(F281,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F281" t="s">
-        <v>691</v>
+        <v>9</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="34">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
       <c r="A282" t="str">
-        <f t="shared" ref="A282:A296" si="54">A281</f>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B282">
@@ -14112,23 +14122,23 @@
         <v>41</v>
       </c>
       <c r="C282" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_41</v>
       </c>
       <c r="E282" t="str">
         <f>VLOOKUP(F282,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>FanJiang</v>
       </c>
       <c r="F282" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
       <c r="A283" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B283">
@@ -14136,23 +14146,23 @@
         <v>42</v>
       </c>
       <c r="C283" t="str">
-        <f t="shared" ref="C283:C296" si="55">CONCATENATE(A283, "_", B283, IF(D283&lt;&gt;"", "_"&amp;D283, ""))</f>
+        <f t="shared" si="53"/>
         <v>NODE_31_42</v>
       </c>
       <c r="E283" t="str">
         <f>VLOOKUP(F283,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F283" t="s">
-        <v>9</v>
+        <v>692</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="34">
       <c r="A284" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B284">
@@ -14160,23 +14170,23 @@
         <v>43</v>
       </c>
       <c r="C284" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_43</v>
       </c>
       <c r="E284" t="str">
         <f>VLOOKUP(F284,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F284" t="s">
-        <v>7</v>
+        <v>692</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
       <c r="A285" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B285">
@@ -14184,23 +14194,23 @@
         <v>44</v>
       </c>
       <c r="C285" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_44</v>
       </c>
       <c r="E285" t="str">
         <f>VLOOKUP(F285,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F285" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
       <c r="A286" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B286">
@@ -14208,7 +14218,7 @@
         <v>45</v>
       </c>
       <c r="C286" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_45</v>
       </c>
       <c r="E286" t="str">
@@ -14219,12 +14229,12 @@
         <v>7</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
       <c r="A287" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B287">
@@ -14232,23 +14242,23 @@
         <v>46</v>
       </c>
       <c r="C287" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_46</v>
       </c>
       <c r="E287" t="str">
         <f>VLOOKUP(F287,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F287" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
       <c r="A288" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B288">
@@ -14256,23 +14266,23 @@
         <v>47</v>
       </c>
       <c r="C288" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_47</v>
       </c>
       <c r="E288" t="str">
         <f>VLOOKUP(F288,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F288" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" ht="34">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B289">
@@ -14280,7 +14290,7 @@
         <v>48</v>
       </c>
       <c r="C289" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_48</v>
       </c>
       <c r="E289" t="str">
@@ -14291,12 +14301,12 @@
         <v>11</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>840</v>
+        <v>687</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B290">
@@ -14304,23 +14314,23 @@
         <v>49</v>
       </c>
       <c r="C290" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_49</v>
       </c>
       <c r="E290" t="str">
         <f>VLOOKUP(F290,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F290" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>688</v>
+        <v>839</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="34">
       <c r="A291" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B291">
@@ -14328,23 +14338,23 @@
         <v>50</v>
       </c>
       <c r="C291" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_50</v>
       </c>
       <c r="E291" t="str">
         <f>VLOOKUP(F291,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F291" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="34">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B292">
@@ -14352,7 +14362,7 @@
         <v>51</v>
       </c>
       <c r="C292" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_51</v>
       </c>
       <c r="E292" t="str">
@@ -14363,12 +14373,12 @@
         <v>5</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>841</v>
+        <v>688</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="34">
       <c r="A293" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B293">
@@ -14376,7 +14386,7 @@
         <v>52</v>
       </c>
       <c r="C293" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_52</v>
       </c>
       <c r="E293" t="str">
@@ -14387,12 +14397,12 @@
         <v>5</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>842</v>
+        <v>808</v>
       </c>
     </row>
     <row r="294" spans="1:7" ht="34">
       <c r="A294" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B294">
@@ -14400,7 +14410,7 @@
         <v>53</v>
       </c>
       <c r="C294" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_53</v>
       </c>
       <c r="E294" t="str">
@@ -14411,12 +14421,12 @@
         <v>5</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>689</v>
+        <v>841</v>
       </c>
     </row>
     <row r="295" spans="1:7" ht="34">
       <c r="A295" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B295">
@@ -14424,7 +14434,7 @@
         <v>54</v>
       </c>
       <c r="C295" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_54</v>
       </c>
       <c r="E295" t="str">
@@ -14435,12 +14445,12 @@
         <v>5</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="34">
       <c r="A296" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>NODE_31</v>
       </c>
       <c r="B296">
@@ -14448,7 +14458,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>NODE_31_55</v>
       </c>
       <c r="E296" t="str">
@@ -14459,6 +14469,54 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="34">
+      <c r="A297" t="str">
+        <f t="shared" si="52"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B297">
+        <f t="shared" si="27"/>
+        <v>56</v>
+      </c>
+      <c r="C297" t="str">
+        <f t="shared" si="53"/>
+        <v>NODE_31_56</v>
+      </c>
+      <c r="E297" t="str">
+        <f>VLOOKUP(F297,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F297" t="s">
+        <v>5</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298" t="str">
+        <f t="shared" si="52"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B298">
+        <f t="shared" si="27"/>
+        <v>57</v>
+      </c>
+      <c r="C298" t="str">
+        <f t="shared" si="53"/>
+        <v>NODE_31_57</v>
+      </c>
+      <c r="E298" t="str">
+        <f>VLOOKUP(F298,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F298" t="s">
+        <v>5</v>
+      </c>
+      <c r="G298" s="3" t="s">
         <v>711</v>
       </c>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DBBFCA-0798-4C7A-BD0E-6DD971FB0A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1400" windowWidth="25820" windowHeight="16220" activeTab="5"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
   <externalReferences>
     <externalReference r:id="rId8"/>
   </externalReferences>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="846">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2627,10 +2628,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>흑흑.. 형님ㅜㅜ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이..이런!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2735,10 +2732,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자 그럼, 다음에 또 보자고~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>그대는 그대의 일을 하시오.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3122,10 +3115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이야앗!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>..? 관공?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3152,11 +3141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3년동안 제삿밥만 먹더니
-살이 좀 빠졌구나, 막내야.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>아깝군. 이대로만 갔어도 
 좋은 흐름이었는데..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3175,20 +3159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> '동소'라고 했던가? 네 놈을 위왕에
-봉하라는 상소를 올렸다지?ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>어리석은!! 난 한 나라의 신하일 뿐,
-천하를 편안하게 하는 것 외엔 관심없다!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅋㅋ 곧 죽을 놈이 말이 많구나!!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>..번개?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3324,14 +3294,51 @@
   </si>
   <si>
     <t>푸우욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혀..형님.. 그런..ㅜㅜ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 놈이!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅋㅋ 곧 죽을 놈이
+말이 많구나!!ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 놈 이름이..
+[동소]..라고 했던가??</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유비 형님 3년상 치르느라 고생했다.
+살이 좀 빠졌구나, 막내야..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어리석은!! 나는 한 나라의 신하일 뿐,
+천하를 편안하게 하는 것 외엔 관심없다!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 놈을 위왕으로 책봉하라고
+황제를 부추겼다지?ㅋ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자 그럼, 다음에 또 보자~</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3599,7 +3606,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Overview"/>
@@ -3893,7 +3900,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3925,9 +3932,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3959,6 +3984,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4134,9 +4177,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4145,15 +4188,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D68"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="38.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>384</v>
       </c>
@@ -4167,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4181,7 +4224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>83</v>
       </c>
@@ -4189,7 +4232,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>86</v>
       </c>
@@ -4197,7 +4240,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>93</v>
       </c>
@@ -4205,7 +4248,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>91</v>
       </c>
@@ -4213,7 +4256,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>92</v>
       </c>
@@ -4221,7 +4264,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>90</v>
       </c>
@@ -4229,7 +4272,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>85</v>
       </c>
@@ -4237,7 +4280,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>87</v>
       </c>
@@ -4245,7 +4288,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>89</v>
       </c>
@@ -4253,7 +4296,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>88</v>
       </c>
@@ -4261,7 +4304,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>114</v>
       </c>
@@ -4269,7 +4312,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>118</v>
       </c>
@@ -4277,7 +4320,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>115</v>
       </c>
@@ -4285,7 +4328,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>117</v>
       </c>
@@ -4293,7 +4336,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>116</v>
       </c>
@@ -4301,7 +4344,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>113</v>
       </c>
@@ -4309,7 +4352,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>106</v>
       </c>
@@ -4317,7 +4360,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>112</v>
       </c>
@@ -4325,7 +4368,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>103</v>
       </c>
@@ -4333,7 +4376,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>105</v>
       </c>
@@ -4341,7 +4384,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>104</v>
       </c>
@@ -4349,7 +4392,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" s="17" t="s">
         <v>154</v>
       </c>
@@ -4357,7 +4400,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" s="17" t="s">
         <v>155</v>
       </c>
@@ -4365,7 +4408,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" s="17" t="s">
         <v>156</v>
       </c>
@@ -4373,7 +4416,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" s="17" t="s">
         <v>157</v>
       </c>
@@ -4381,7 +4424,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" s="17" t="s">
         <v>153</v>
       </c>
@@ -4389,7 +4432,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>63</v>
       </c>
@@ -4397,7 +4440,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>65</v>
       </c>
@@ -4405,7 +4448,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="2:3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>66</v>
       </c>
@@ -4413,7 +4456,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="2:3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>69</v>
       </c>
@@ -4421,7 +4464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>61</v>
       </c>
@@ -4429,7 +4472,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>151</v>
       </c>
@@ -4437,7 +4480,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>74</v>
       </c>
@@ -4445,7 +4488,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>150</v>
       </c>
@@ -4453,7 +4496,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>80</v>
       </c>
@@ -4461,7 +4504,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>152</v>
       </c>
@@ -4469,7 +4512,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>53</v>
       </c>
@@ -4478,7 +4521,7 @@
       </c>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>164</v>
       </c>
@@ -4486,7 +4529,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>267</v>
       </c>
@@ -4494,7 +4537,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>265</v>
       </c>
@@ -4502,7 +4545,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>264</v>
       </c>
@@ -4510,7 +4553,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>266</v>
       </c>
@@ -4518,7 +4561,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>163</v>
       </c>
@@ -4526,7 +4569,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>161</v>
       </c>
@@ -4534,7 +4577,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>162</v>
       </c>
@@ -4542,7 +4585,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>543</v>
       </c>
@@ -4554,7 +4597,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>544</v>
       </c>
@@ -4566,7 +4609,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>545</v>
       </c>
@@ -4578,7 +4621,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>546</v>
       </c>
@@ -4590,7 +4633,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>542</v>
       </c>
@@ -4602,7 +4645,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>552</v>
       </c>
@@ -4610,7 +4653,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>520</v>
       </c>
@@ -4618,7 +4661,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>516</v>
       </c>
@@ -4626,7 +4669,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>521</v>
       </c>
@@ -4634,7 +4677,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>517</v>
       </c>
@@ -4642,7 +4685,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>519</v>
       </c>
@@ -4650,7 +4693,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>515</v>
       </c>
@@ -4658,7 +4701,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>522</v>
       </c>
@@ -4666,7 +4709,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>518</v>
       </c>
@@ -4674,7 +4717,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>286</v>
       </c>
@@ -4685,7 +4728,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>282</v>
       </c>
@@ -4696,7 +4739,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>287</v>
       </c>
@@ -4707,7 +4750,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="65" spans="2:4">
+    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>288</v>
       </c>
@@ -4718,7 +4761,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
+    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>285</v>
       </c>
@@ -4729,7 +4772,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="67" spans="2:4">
+    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>283</v>
       </c>
@@ -4740,7 +4783,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="68" spans="2:4">
+    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>284</v>
       </c>
@@ -4752,7 +4795,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A3:D68">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D68">
     <sortCondition ref="B3:B68"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4762,16 +4805,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.375" style="6" customWidth="1"/>
     <col min="2" max="2" width="28.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>125</v>
       </c>
@@ -4785,7 +4828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
@@ -4799,7 +4842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>126</v>
       </c>
@@ -4812,7 +4855,7 @@
       </c>
       <c r="D3" s="18"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>127</v>
       </c>
@@ -4825,7 +4868,7 @@
       </c>
       <c r="D4" s="18"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>128</v>
       </c>
@@ -4838,7 +4881,7 @@
       </c>
       <c r="D5" s="18"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>129</v>
       </c>
@@ -4851,7 +4894,7 @@
       </c>
       <c r="D6" s="18"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>130</v>
       </c>
@@ -4864,7 +4907,7 @@
       </c>
       <c r="D7" s="18"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>131</v>
       </c>
@@ -4877,7 +4920,7 @@
       </c>
       <c r="D8" s="18"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>132</v>
       </c>
@@ -4890,7 +4933,7 @@
       </c>
       <c r="D9" s="18"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>133</v>
       </c>
@@ -4903,7 +4946,7 @@
       </c>
       <c r="D10" s="18"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>134</v>
       </c>
@@ -4916,7 +4959,7 @@
       </c>
       <c r="D11" s="18"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>135</v>
       </c>
@@ -4929,23 +4972,23 @@
       </c>
       <c r="D12" s="18"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
       <c r="D13" s="18"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
       <c r="D14" s="18"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
       <c r="D15" s="18"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="D16" s="18"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="17"/>
       <c r="D17" s="18"/>
     </row>
@@ -4957,18 +5000,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G102"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="50.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="50.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>450</v>
       </c>
@@ -4991,7 +5034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -5012,7 +5055,7 @@
       </c>
       <c r="G2" s="37"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -5026,7 +5069,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="27"/>
       <c r="C4" s="27"/>
@@ -5040,7 +5083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
       <c r="C5" s="27"/>
@@ -5054,7 +5097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
       <c r="C6" s="27"/>
@@ -5068,7 +5111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
       <c r="C7" s="27"/>
@@ -5082,7 +5125,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -5096,7 +5139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>479</v>
       </c>
@@ -5117,7 +5160,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>479</v>
       </c>
@@ -5138,7 +5181,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>479</v>
       </c>
@@ -5159,7 +5202,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>479</v>
       </c>
@@ -5180,7 +5223,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>479</v>
       </c>
@@ -5201,7 +5244,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>479</v>
       </c>
@@ -5222,7 +5265,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>479</v>
       </c>
@@ -5243,7 +5286,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>479</v>
       </c>
@@ -5264,7 +5307,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>479</v>
       </c>
@@ -5285,7 +5328,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>479</v>
       </c>
@@ -5306,7 +5349,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>479</v>
       </c>
@@ -5327,7 +5370,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>479</v>
       </c>
@@ -5348,7 +5391,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>479</v>
       </c>
@@ -5369,7 +5412,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
         <v>479</v>
       </c>
@@ -5390,7 +5433,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
         <v>479</v>
       </c>
@@ -5411,7 +5454,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
         <v>479</v>
       </c>
@@ -5432,7 +5475,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
         <v>479</v>
       </c>
@@ -5453,7 +5496,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
         <v>479</v>
       </c>
@@ -5474,7 +5517,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="s">
         <v>479</v>
       </c>
@@ -5495,7 +5538,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="s">
         <v>479</v>
       </c>
@@ -5516,7 +5559,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="34">
+    <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
         <v>464</v>
       </c>
@@ -5535,7 +5578,7 @@
       </c>
       <c r="F29" s="38"/>
     </row>
-    <row r="30" spans="1:6" ht="34">
+    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
         <v>464</v>
       </c>
@@ -5554,7 +5597,7 @@
       </c>
       <c r="F30" s="38"/>
     </row>
-    <row r="31" spans="1:6" ht="34">
+    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
         <v>464</v>
       </c>
@@ -5573,7 +5616,7 @@
       </c>
       <c r="F31" s="38"/>
     </row>
-    <row r="32" spans="1:6" ht="34">
+    <row r="32" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
         <v>464</v>
       </c>
@@ -5592,7 +5635,7 @@
       </c>
       <c r="F32" s="38"/>
     </row>
-    <row r="33" spans="1:6" ht="34">
+    <row r="33" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
         <v>464</v>
       </c>
@@ -5611,7 +5654,7 @@
       </c>
       <c r="F33" s="38"/>
     </row>
-    <row r="34" spans="1:6" ht="34">
+    <row r="34" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
         <v>464</v>
       </c>
@@ -5630,7 +5673,7 @@
       </c>
       <c r="F34" s="38"/>
     </row>
-    <row r="35" spans="1:6" ht="34">
+    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
         <v>464</v>
       </c>
@@ -5649,7 +5692,7 @@
       </c>
       <c r="F35" s="38"/>
     </row>
-    <row r="36" spans="1:6" ht="34">
+    <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A36" s="27" t="s">
         <v>464</v>
       </c>
@@ -5668,7 +5711,7 @@
       </c>
       <c r="F36" s="38"/>
     </row>
-    <row r="37" spans="1:6" ht="34">
+    <row r="37" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="27" t="s">
         <v>464</v>
       </c>
@@ -5687,7 +5730,7 @@
       </c>
       <c r="F37" s="38"/>
     </row>
-    <row r="38" spans="1:6" ht="34">
+    <row r="38" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A38" s="27" t="s">
         <v>464</v>
       </c>
@@ -5706,7 +5749,7 @@
       </c>
       <c r="F38" s="38"/>
     </row>
-    <row r="39" spans="1:6" ht="34">
+    <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
         <v>464</v>
       </c>
@@ -5725,7 +5768,7 @@
       </c>
       <c r="F39" s="38"/>
     </row>
-    <row r="40" spans="1:6" ht="34">
+    <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="27" t="s">
         <v>464</v>
       </c>
@@ -5744,7 +5787,7 @@
       </c>
       <c r="F40" s="38"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="27" t="s">
         <v>464</v>
       </c>
@@ -5765,7 +5808,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="34">
+    <row r="42" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
         <v>464</v>
       </c>
@@ -5786,7 +5829,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="34">
+    <row r="43" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
         <v>464</v>
       </c>
@@ -5807,7 +5850,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="34">
+    <row r="44" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
         <v>464</v>
       </c>
@@ -5828,7 +5871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
         <v>464</v>
       </c>
@@ -5849,7 +5892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="34">
+    <row r="46" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" s="27" t="s">
         <v>464</v>
       </c>
@@ -5870,7 +5913,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="34">
+    <row r="47" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A47" s="27" t="s">
         <v>464</v>
       </c>
@@ -5891,7 +5934,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="34">
+    <row r="48" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
         <v>464</v>
       </c>
@@ -5912,7 +5955,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="27"/>
       <c r="B49" s="27"/>
       <c r="C49" s="27"/>
@@ -5926,7 +5969,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="27"/>
       <c r="B50" s="27"/>
       <c r="C50" s="27"/>
@@ -5940,7 +5983,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="27"/>
       <c r="B51" s="27"/>
       <c r="C51" s="27"/>
@@ -5954,7 +5997,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="27"/>
       <c r="B52" s="27"/>
       <c r="C52" s="27"/>
@@ -5968,7 +6011,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="27"/>
       <c r="B53" s="27"/>
       <c r="C53" s="27"/>
@@ -5982,7 +6025,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="27"/>
       <c r="B54" s="27"/>
       <c r="C54" s="27"/>
@@ -5996,7 +6039,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="27"/>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
@@ -6010,7 +6053,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="27"/>
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
@@ -6024,7 +6067,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="27"/>
       <c r="B57" s="27"/>
       <c r="C57" s="27"/>
@@ -6038,7 +6081,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="27"/>
       <c r="B58" s="27"/>
       <c r="C58" s="27"/>
@@ -6052,7 +6095,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="27"/>
       <c r="B59" s="27"/>
       <c r="C59" s="27"/>
@@ -6066,7 +6109,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="27"/>
       <c r="B60" s="27"/>
       <c r="C60" s="27"/>
@@ -6080,7 +6123,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="27" t="s">
         <v>451</v>
       </c>
@@ -6099,7 +6142,7 @@
       </c>
       <c r="F61" s="38"/>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="27" t="s">
         <v>451</v>
       </c>
@@ -6118,7 +6161,7 @@
       </c>
       <c r="F62" s="38"/>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="27" t="s">
         <v>451</v>
       </c>
@@ -6137,7 +6180,7 @@
       </c>
       <c r="F63" s="38"/>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="27" t="s">
         <v>451</v>
       </c>
@@ -6156,7 +6199,7 @@
       </c>
       <c r="F64" s="38"/>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="27" t="s">
         <v>451</v>
       </c>
@@ -6175,7 +6218,7 @@
       </c>
       <c r="F65" s="38"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="27" t="s">
         <v>451</v>
       </c>
@@ -6194,7 +6237,7 @@
       </c>
       <c r="F66" s="38"/>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="27" t="s">
         <v>451</v>
       </c>
@@ -6213,7 +6256,7 @@
       </c>
       <c r="F67" s="38"/>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="27" t="s">
         <v>451</v>
       </c>
@@ -6232,7 +6275,7 @@
       </c>
       <c r="F68" s="38"/>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="27" t="s">
         <v>451</v>
       </c>
@@ -6251,7 +6294,7 @@
       </c>
       <c r="F69" s="38"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="27" t="s">
         <v>451</v>
       </c>
@@ -6270,7 +6313,7 @@
       </c>
       <c r="F70" s="38"/>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="27" t="s">
         <v>451</v>
       </c>
@@ -6289,7 +6332,7 @@
       </c>
       <c r="F71" s="38"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="27" t="s">
         <v>451</v>
       </c>
@@ -6308,7 +6351,7 @@
       </c>
       <c r="F72" s="38"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="27" t="s">
         <v>451</v>
       </c>
@@ -6327,7 +6370,7 @@
       </c>
       <c r="F73" s="38"/>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="27" t="s">
         <v>451</v>
       </c>
@@ -6346,7 +6389,7 @@
       </c>
       <c r="F74" s="38"/>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="27" t="s">
         <v>451</v>
       </c>
@@ -6365,7 +6408,7 @@
       </c>
       <c r="F75" s="38"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="27" t="s">
         <v>451</v>
       </c>
@@ -6384,7 +6427,7 @@
       </c>
       <c r="F76" s="38"/>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="27" t="s">
         <v>451</v>
       </c>
@@ -6403,7 +6446,7 @@
       </c>
       <c r="F77" s="38"/>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="27" t="s">
         <v>451</v>
       </c>
@@ -6422,7 +6465,7 @@
       </c>
       <c r="F78" s="38"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="27" t="s">
         <v>451</v>
       </c>
@@ -6441,7 +6484,7 @@
       </c>
       <c r="F79" s="38"/>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="27" t="s">
         <v>451</v>
       </c>
@@ -6460,7 +6503,7 @@
       </c>
       <c r="F80" s="38"/>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="27"/>
       <c r="B81" s="27"/>
       <c r="C81" s="27"/>
@@ -6472,7 +6515,7 @@
       </c>
       <c r="F81" s="38"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="27"/>
       <c r="B82" s="27"/>
       <c r="C82" s="27"/>
@@ -6484,7 +6527,7 @@
       </c>
       <c r="F82" s="38"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="27"/>
       <c r="B83" s="27"/>
       <c r="C83" s="27"/>
@@ -6496,7 +6539,7 @@
       </c>
       <c r="F83" s="38"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="27"/>
       <c r="B84" s="27"/>
       <c r="C84" s="27"/>
@@ -6508,7 +6551,7 @@
       </c>
       <c r="F84" s="38"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="27"/>
       <c r="B85" s="27"/>
       <c r="C85" s="27"/>
@@ -6520,7 +6563,7 @@
       </c>
       <c r="F85" s="38"/>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="27"/>
       <c r="B86" s="27"/>
       <c r="C86" s="27"/>
@@ -6532,7 +6575,7 @@
       </c>
       <c r="F86" s="38"/>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="27" t="s">
         <v>451</v>
       </c>
@@ -6551,7 +6594,7 @@
       </c>
       <c r="F87" s="38"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="27" t="s">
         <v>451</v>
       </c>
@@ -6570,7 +6613,7 @@
       </c>
       <c r="F88" s="38"/>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="27" t="s">
         <v>451</v>
       </c>
@@ -6589,7 +6632,7 @@
       </c>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="27" t="s">
         <v>451</v>
       </c>
@@ -6608,7 +6651,7 @@
       </c>
       <c r="F90" s="38"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="27" t="s">
         <v>451</v>
       </c>
@@ -6627,7 +6670,7 @@
       </c>
       <c r="F91" s="38"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="27" t="s">
         <v>451</v>
       </c>
@@ -6646,12 +6689,12 @@
       </c>
       <c r="F92" s="38"/>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C93" s="27" t="s">
         <v>447</v>
@@ -6661,16 +6704,16 @@
         <v>NAME_WEI_FANJIANG</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F93" s="38"/>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="27" t="s">
         <v>451</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C94" s="27" t="s">
         <v>447</v>
@@ -6680,11 +6723,11 @@
         <v>NAME_WEI_ZHANGDA</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F94" s="38"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="27" t="s">
         <v>479</v>
       </c>
@@ -6703,7 +6746,7 @@
       </c>
       <c r="F95" s="38"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="27" t="s">
         <v>479</v>
       </c>
@@ -6722,7 +6765,7 @@
       </c>
       <c r="F96" s="38"/>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="27" t="s">
         <v>479</v>
       </c>
@@ -6741,7 +6784,7 @@
       </c>
       <c r="F97" s="38"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="27" t="s">
         <v>479</v>
       </c>
@@ -6760,7 +6803,7 @@
       </c>
       <c r="F98" s="38"/>
     </row>
-    <row r="99" spans="1:6" ht="34">
+    <row r="99" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A99" s="27" t="s">
         <v>464</v>
       </c>
@@ -6779,7 +6822,7 @@
       </c>
       <c r="F99" s="38"/>
     </row>
-    <row r="100" spans="1:6" ht="34">
+    <row r="100" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A100" s="27" t="s">
         <v>464</v>
       </c>
@@ -6798,7 +6841,7 @@
       </c>
       <c r="F100" s="38"/>
     </row>
-    <row r="101" spans="1:6" ht="34">
+    <row r="101" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A101" s="27" t="s">
         <v>464</v>
       </c>
@@ -6817,7 +6860,7 @@
       </c>
       <c r="F101" s="38"/>
     </row>
-    <row r="102" spans="1:6" ht="34">
+    <row r="102" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A102" s="27" t="s">
         <v>464</v>
       </c>
@@ -6837,7 +6880,7 @@
       <c r="F102" s="38"/>
     </row>
   </sheetData>
-  <sortState ref="A3:G66">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G66">
     <sortCondition ref="D3:D66"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6847,19 +6890,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.25" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.58203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.33203125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="6.08203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="6.125" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>166</v>
       </c>
@@ -6876,7 +6919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
@@ -6891,7 +6934,7 @@
       </c>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>168</v>
       </c>
@@ -6905,7 +6948,7 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>169</v>
       </c>
@@ -6919,7 +6962,7 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>170</v>
       </c>
@@ -6933,7 +6976,7 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>171</v>
       </c>
@@ -6947,7 +6990,7 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>172</v>
       </c>
@@ -6961,7 +7004,7 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>173</v>
       </c>
@@ -6975,7 +7018,7 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>174</v>
       </c>
@@ -6989,7 +7032,7 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>175</v>
       </c>
@@ -7003,7 +7046,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>176</v>
       </c>
@@ -7017,7 +7060,7 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>177</v>
       </c>
@@ -7031,7 +7074,7 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>167</v>
       </c>
@@ -7045,7 +7088,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>178</v>
       </c>
@@ -7059,7 +7102,7 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>179</v>
       </c>
@@ -7073,7 +7116,7 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>180</v>
       </c>
@@ -7087,7 +7130,7 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>181</v>
       </c>
@@ -7101,7 +7144,7 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>182</v>
       </c>
@@ -7115,7 +7158,7 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>183</v>
       </c>
@@ -7129,7 +7172,7 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>184</v>
       </c>
@@ -7143,7 +7186,7 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>185</v>
       </c>
@@ -7157,7 +7200,7 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>186</v>
       </c>
@@ -7171,7 +7214,7 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>187</v>
       </c>
@@ -7185,7 +7228,7 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>188</v>
       </c>
@@ -7199,7 +7242,7 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>189</v>
       </c>
@@ -7213,7 +7256,7 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>190</v>
       </c>
@@ -7227,7 +7270,7 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>191</v>
       </c>
@@ -7241,7 +7284,7 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>192</v>
       </c>
@@ -7255,7 +7298,7 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>193</v>
       </c>
@@ -7269,7 +7312,7 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>194</v>
       </c>
@@ -7283,7 +7326,7 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>195</v>
       </c>
@@ -7297,7 +7340,7 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>196</v>
       </c>
@@ -7311,7 +7354,7 @@
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>197</v>
       </c>
@@ -7325,7 +7368,7 @@
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>198</v>
       </c>
@@ -7339,7 +7382,7 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>199</v>
       </c>
@@ -7353,7 +7396,7 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>200</v>
       </c>
@@ -7367,7 +7410,7 @@
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>201</v>
       </c>
@@ -7381,7 +7424,7 @@
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>202</v>
       </c>
@@ -7395,7 +7438,7 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>203</v>
       </c>
@@ -7409,7 +7452,7 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>204</v>
       </c>
@@ -7423,7 +7466,7 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>205</v>
       </c>
@@ -7437,7 +7480,7 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>206</v>
       </c>
@@ -7451,7 +7494,7 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>207</v>
       </c>
@@ -7465,7 +7508,7 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>208</v>
       </c>
@@ -7479,7 +7522,7 @@
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>209</v>
       </c>
@@ -7493,7 +7536,7 @@
       <c r="D45" s="11"/>
       <c r="E45" s="11"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>210</v>
       </c>
@@ -7507,7 +7550,7 @@
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>211</v>
       </c>
@@ -7529,22 +7572,22 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J298"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J300"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.58203125" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
     <col min="6" max="6" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.83203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="50.33203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="6.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="50.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
@@ -7573,7 +7616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -7600,7 +7643,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>411</v>
       </c>
@@ -7622,7 +7665,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" ref="A4:A26" si="1">A3</f>
         <v>NODE_2</v>
@@ -7646,7 +7689,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7660,7 +7703,7 @@
         <v>NODE_2_2</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7684,7 +7727,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34">
+    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7704,7 +7747,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7728,7 +7771,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="34">
+    <row r="9" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7752,7 +7795,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7766,7 +7809,7 @@
         <v>NODE_2_7</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="34">
+    <row r="11" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7790,7 +7833,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="34">
+    <row r="12" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7814,7 +7857,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="34">
+    <row r="13" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7838,7 +7881,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="34">
+    <row r="14" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7862,7 +7905,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="34">
+    <row r="15" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7886,7 +7929,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="51">
+    <row r="16" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7906,7 +7949,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7930,7 +7973,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7954,7 +7997,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7968,7 +8011,7 @@
         <v>NODE_2_16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="34">
+    <row r="20" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -7992,7 +8035,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8016,7 +8059,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="34">
+    <row r="22" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8040,7 +8083,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8064,7 +8107,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="34">
+    <row r="24" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8088,7 +8131,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="51">
+    <row r="25" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8112,7 +8155,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" si="1"/>
         <v>NODE_2</v>
@@ -8136,7 +8179,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="34">
+    <row r="27" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>561</v>
       </c>
@@ -8158,7 +8201,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" ref="A28:A52" si="3">A27</f>
         <v>NODE_30B</v>
@@ -8182,7 +8225,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="34">
+    <row r="29" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8206,7 +8249,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="34">
+    <row r="30" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8230,7 +8273,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8254,7 +8297,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="34">
+    <row r="32" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8278,7 +8321,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="34">
+    <row r="33" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8302,7 +8345,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8326,7 +8369,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="34">
+    <row r="35" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8350,7 +8393,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="34">
+    <row r="36" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8374,7 +8417,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8398,7 +8441,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8412,7 +8455,7 @@
         <v>NODE_30B_11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="34">
+    <row r="39" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8436,7 +8479,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="34">
+    <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8460,7 +8503,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8484,7 +8527,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="34">
+    <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8505,10 +8548,10 @@
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="34">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8532,7 +8575,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8559,7 +8602,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="34">
+    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8586,7 +8629,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="34">
+    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8613,7 +8656,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8640,7 +8683,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="34">
+    <row r="48" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8667,7 +8710,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="34">
+    <row r="49" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8691,7 +8734,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8715,7 +8758,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="34">
+    <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8739,7 +8782,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" si="3"/>
         <v>NODE_30B</v>
@@ -8763,7 +8806,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>587</v>
       </c>
@@ -8785,7 +8828,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="34">
+    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f>A54</f>
         <v>NODE_16</v>
@@ -8809,7 +8852,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="34">
+    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f>A55</f>
         <v>NODE_16</v>
@@ -8833,7 +8876,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" ref="A57:A115" si="7">A56</f>
         <v>NODE_16</v>
@@ -8857,7 +8900,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="34">
+    <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8881,7 +8924,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="34">
+    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8905,7 +8948,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="34">
+    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8929,7 +8972,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8953,7 +8996,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8977,7 +9020,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -8998,10 +9041,10 @@
         <v>7</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9022,10 +9065,10 @@
         <v>591</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="34">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9046,10 +9089,10 @@
         <v>591</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9073,7 +9116,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="34">
+    <row r="67" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9097,7 +9140,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9121,7 +9164,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="34">
+    <row r="69" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9145,7 +9188,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="34">
+    <row r="70" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9169,7 +9212,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="34">
+    <row r="71" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9190,10 +9233,10 @@
         <v>589</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="34">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9214,12 +9257,12 @@
         <v>589</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="H72"/>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" ht="34">
+    <row r="73" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9243,7 +9286,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="34">
+    <row r="74" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9267,7 +9310,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9291,7 +9334,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9315,7 +9358,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="34">
+    <row r="77" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9339,7 +9382,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9363,7 +9406,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9387,7 +9430,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9411,7 +9454,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9435,7 +9478,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="34">
+    <row r="82" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9459,7 +9502,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9480,10 +9523,10 @@
         <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9507,7 +9550,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9531,7 +9574,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9555,7 +9598,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="34">
+    <row r="87" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9576,10 +9619,10 @@
         <v>599</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9603,7 +9646,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9627,7 +9670,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9651,7 +9694,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="34">
+    <row r="91" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9672,10 +9715,10 @@
         <v>599</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9699,7 +9742,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9723,7 +9766,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9747,7 +9790,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="34">
+    <row r="95" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9768,10 +9811,10 @@
         <v>600</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="34">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9792,10 +9835,10 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9819,7 +9862,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9843,7 +9886,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="34">
+    <row r="99" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9867,7 +9910,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="34">
+    <row r="100" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9891,7 +9934,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="34">
+    <row r="101" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9918,7 +9961,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="34">
+    <row r="102" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9945,7 +9988,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9972,7 +10015,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="34">
+    <row r="104" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -9999,7 +10042,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="34">
+    <row r="105" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10026,7 +10069,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="34">
+    <row r="106" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10053,7 +10096,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="34">
+    <row r="107" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10080,7 +10123,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10107,7 +10150,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10134,7 +10177,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10161,7 +10204,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="34">
+    <row r="111" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10185,10 +10228,10 @@
         <v>600</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="34">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10215,7 +10258,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10242,7 +10285,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="34">
+    <row r="114" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10266,10 +10309,10 @@
         <v>5</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="34">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f t="shared" si="7"/>
         <v>NODE_16</v>
@@ -10293,10 +10336,10 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="34">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f t="shared" ref="A116:A119" si="10">A115</f>
         <v>NODE_16</v>
@@ -10323,7 +10366,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="34">
+    <row r="117" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10347,10 +10390,10 @@
         <v>600</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10374,10 +10417,10 @@
         <v>5</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f t="shared" si="10"/>
         <v>NODE_16</v>
@@ -10404,7 +10447,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>666</v>
       </c>
@@ -10423,10 +10466,10 @@
         <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="34">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>666</v>
       </c>
@@ -10446,10 +10489,10 @@
         <v>591</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="34">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>666</v>
       </c>
@@ -10469,10 +10512,10 @@
         <v>7</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>666</v>
       </c>
@@ -10492,10 +10535,10 @@
         <v>7</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="34">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>666</v>
       </c>
@@ -10515,11 +10558,11 @@
         <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="J125" s="3"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>666</v>
       </c>
@@ -10539,10 +10582,10 @@
         <v>591</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>666</v>
       </c>
@@ -10565,7 +10608,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>666</v>
       </c>
@@ -10588,7 +10631,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="34">
+    <row r="129" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>666</v>
       </c>
@@ -10608,10 +10651,10 @@
         <v>7</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>666</v>
       </c>
@@ -10631,10 +10674,10 @@
         <v>7</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>666</v>
       </c>
@@ -10657,7 +10700,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="34">
+    <row r="132" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>666</v>
       </c>
@@ -10677,10 +10720,10 @@
         <v>7</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="34">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>666</v>
       </c>
@@ -10700,10 +10743,10 @@
         <v>51</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="34">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>666</v>
       </c>
@@ -10723,10 +10766,10 @@
         <v>7</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>666</v>
       </c>
@@ -10749,7 +10792,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>666</v>
       </c>
@@ -10769,10 +10812,10 @@
         <v>657</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="34">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>666</v>
       </c>
@@ -10792,10 +10835,10 @@
         <v>657</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>666</v>
       </c>
@@ -10815,10 +10858,10 @@
         <v>51</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="51">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>666</v>
       </c>
@@ -10838,10 +10881,10 @@
         <v>657</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>666</v>
       </c>
@@ -10864,7 +10907,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>666</v>
       </c>
@@ -10887,7 +10930,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>666</v>
       </c>
@@ -10907,10 +10950,10 @@
         <v>657</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="34">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>666</v>
       </c>
@@ -10933,7 +10976,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>666</v>
       </c>
@@ -10956,7 +10999,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="34">
+    <row r="145" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>666</v>
       </c>
@@ -10979,7 +11022,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="34">
+    <row r="146" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>666</v>
       </c>
@@ -10999,10 +11042,10 @@
         <v>7</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>666</v>
       </c>
@@ -11022,10 +11065,10 @@
         <v>51</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="34">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>666</v>
       </c>
@@ -11048,7 +11091,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="34">
+    <row r="149" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>666</v>
       </c>
@@ -11071,7 +11114,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="34">
+    <row r="150" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>666</v>
       </c>
@@ -11091,10 +11134,10 @@
         <v>51</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="34">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>666</v>
       </c>
@@ -11114,10 +11157,10 @@
         <v>51</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>666</v>
       </c>
@@ -11137,10 +11180,10 @@
         <v>657</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>666</v>
       </c>
@@ -11160,10 +11203,10 @@
         <v>591</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>666</v>
       </c>
@@ -11186,7 +11229,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="34">
+    <row r="155" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>666</v>
       </c>
@@ -11206,10 +11249,10 @@
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>666</v>
       </c>
@@ -11232,7 +11275,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="34">
+    <row r="157" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>666</v>
       </c>
@@ -11252,10 +11295,10 @@
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>666</v>
       </c>
@@ -11278,7 +11321,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>666</v>
       </c>
@@ -11301,7 +11344,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>676</v>
       </c>
@@ -11320,10 +11363,10 @@
         <v>591</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="34">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A162" t="str">
         <f>A161</f>
         <v>NODE_28</v>
@@ -11347,7 +11390,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="34">
+    <row r="163" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f t="shared" ref="A163:A199" si="17">A162</f>
         <v>NODE_28</v>
@@ -11371,7 +11414,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="34">
+    <row r="164" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A164" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11392,10 +11435,10 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11419,7 +11462,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11443,7 +11486,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11464,10 +11507,10 @@
         <v>406</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="34">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11488,10 +11531,10 @@
         <v>407</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="34">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11515,7 +11558,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11536,10 +11579,10 @@
         <v>591</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11563,7 +11606,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11577,7 +11620,7 @@
         <v>NODE_28_11</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11591,16 +11634,16 @@
         <v>NODE_28_12</v>
       </c>
       <c r="E173" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F173" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11614,16 +11657,16 @@
         <v>NODE_28_13</v>
       </c>
       <c r="E174" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F174" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11637,16 +11680,16 @@
         <v>NODE_28_14</v>
       </c>
       <c r="E175" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F175" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11667,10 +11710,10 @@
         <v>7</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="34">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11691,10 +11734,10 @@
         <v>591</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11718,7 +11761,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11739,10 +11782,10 @@
         <v>591</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11762,10 +11805,10 @@
         <v>415</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="34">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A181" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11786,10 +11829,10 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="34">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A182" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11810,10 +11853,10 @@
         <v>7</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11834,10 +11877,10 @@
         <v>406</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11858,10 +11901,10 @@
         <v>591</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11885,7 +11928,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11905,10 +11948,10 @@
         <v>674</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11928,10 +11971,10 @@
         <v>674</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11955,7 +11998,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -11979,7 +12022,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12003,7 +12046,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="34">
+    <row r="191" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A191" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12023,10 +12066,10 @@
         <v>674</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="34">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A192" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12047,10 +12090,10 @@
         <v>7</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" ht="34">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A193" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12071,10 +12114,10 @@
         <v>7</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12097,7 +12140,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="34">
+    <row r="195" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A195" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12117,10 +12160,10 @@
         <v>674</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="34">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A196" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12140,10 +12183,10 @@
         <v>674</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12163,10 +12206,10 @@
         <v>674</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12190,7 +12233,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="34">
+    <row r="199" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A199" t="str">
         <f t="shared" si="17"/>
         <v>NODE_28</v>
@@ -12211,10 +12254,10 @@
         <v>406</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="34">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>678</v>
       </c>
@@ -12233,10 +12276,10 @@
         <v>406</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="str">
         <f>A201</f>
         <v>NODE_29</v>
@@ -12257,10 +12300,10 @@
         <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="str">
         <f t="shared" ref="A203:A239" si="23">A202</f>
         <v>NODE_29</v>
@@ -12284,7 +12327,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12305,10 +12348,10 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="34">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A205" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12329,10 +12372,10 @@
         <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="34">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A206" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12353,10 +12396,10 @@
         <v>406</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12377,10 +12420,10 @@
         <v>407</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12404,7 +12447,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12425,10 +12468,10 @@
         <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12449,10 +12492,10 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="34">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A211" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12476,7 +12519,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12497,10 +12540,10 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="34">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A213" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12521,10 +12564,10 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="34">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A214" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12545,10 +12588,10 @@
         <v>7</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="34">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A215" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12569,10 +12612,10 @@
         <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12593,10 +12636,10 @@
         <v>11</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12617,10 +12660,10 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12641,10 +12684,10 @@
         <v>11</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12665,10 +12708,10 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12692,7 +12735,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="34">
+    <row r="221" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A221" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12713,10 +12756,10 @@
         <v>11</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" ht="34">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A222" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12737,10 +12780,10 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12764,7 +12807,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="34">
+    <row r="224" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A224" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12785,10 +12828,10 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12809,10 +12852,10 @@
         <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="34">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A226" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12833,10 +12876,10 @@
         <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12857,10 +12900,10 @@
         <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="34">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A228" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12881,10 +12924,10 @@
         <v>591</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12905,10 +12948,10 @@
         <v>7</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="34">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A230" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12929,10 +12972,10 @@
         <v>591</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="34">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A231" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12953,10 +12996,10 @@
         <v>591</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12977,10 +13020,10 @@
         <v>7</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -12994,7 +13037,7 @@
         <v>NODE_29_32</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13018,7 +13061,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="34">
+    <row r="235" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A235" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13039,10 +13082,10 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13063,10 +13106,10 @@
         <v>7</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13087,10 +13130,10 @@
         <v>406</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="34">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A238" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13111,10 +13154,10 @@
         <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="34">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A239" t="str">
         <f t="shared" si="23"/>
         <v>NODE_29</v>
@@ -13135,12 +13178,12 @@
         <v>406</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -13157,16 +13200,16 @@
         <v>403</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="str">
         <f>A241</f>
         <v>NODE_31</v>
       </c>
       <c r="B242">
-        <f t="shared" ref="B242:B298" si="27">B241+1</f>
+        <f t="shared" ref="B242:B300" si="27">B241+1</f>
         <v>1</v>
       </c>
       <c r="C242" t="str">
@@ -13181,12 +13224,12 @@
         <v>403</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" ht="34">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A243" t="str">
-        <f t="shared" ref="A243:A261" si="29">A242</f>
+        <f t="shared" ref="A243:A300" si="29">A242</f>
         <v>NODE_31</v>
       </c>
       <c r="B243">
@@ -13194,7 +13237,7 @@
         <v>2</v>
       </c>
       <c r="C243" t="str">
-        <f t="shared" ref="C243:C250" si="30">CONCATENATE(A243, "_", B243, IF(D243&lt;&gt;"", "_"&amp;D243, ""))</f>
+        <f t="shared" ref="C243:C246" si="30">CONCATENATE(A243, "_", B243, IF(D243&lt;&gt;"", "_"&amp;D243, ""))</f>
         <v>NODE_31_2</v>
       </c>
       <c r="E243" t="str">
@@ -13205,10 +13248,10 @@
         <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13229,10 +13272,10 @@
         <v>51</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" ht="34">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A245" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13253,10 +13296,10 @@
         <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13277,10 +13320,10 @@
         <v>51</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="34">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A247" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13290,7 +13333,7 @@
         <v>6</v>
       </c>
       <c r="C247" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="C247" si="31">CONCATENATE(A247, "_", B247, IF(D247&lt;&gt;"", "_"&amp;D247, ""))</f>
         <v>NODE_31_6</v>
       </c>
       <c r="E247" t="str">
@@ -13300,11 +13343,11 @@
       <c r="F247" t="s">
         <v>9</v>
       </c>
-      <c r="G247" s="39" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="34">
+      <c r="G247" s="3" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13314,7 +13357,7 @@
         <v>7</v>
       </c>
       <c r="C248" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="C248:C300" si="32">CONCATENATE(A248, "_", B248, IF(D248&lt;&gt;"", "_"&amp;D248, ""))</f>
         <v>NODE_31_7</v>
       </c>
       <c r="E248" t="str">
@@ -13325,10 +13368,10 @@
         <v>51</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A249" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13338,7 +13381,7 @@
         <v>8</v>
       </c>
       <c r="C249" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_8</v>
       </c>
       <c r="E249" t="str">
@@ -13348,11 +13391,11 @@
       <c r="F249" t="s">
         <v>9</v>
       </c>
-      <c r="G249" s="3" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7">
+      <c r="G249" s="39" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A250" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13362,7 +13405,7 @@
         <v>9</v>
       </c>
       <c r="C250" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_9</v>
       </c>
       <c r="E250" t="str">
@@ -13373,10 +13416,10 @@
         <v>51</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A251" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13386,7 +13429,7 @@
         <v>10</v>
       </c>
       <c r="C251" t="str">
-        <f t="shared" ref="C251:C254" si="31">CONCATENATE(A251, "_", B251, IF(D251&lt;&gt;"", "_"&amp;D251, ""))</f>
+        <f t="shared" si="32"/>
         <v>NODE_31_10</v>
       </c>
       <c r="E251" t="str">
@@ -13397,10 +13440,10 @@
         <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13410,7 +13453,7 @@
         <v>11</v>
       </c>
       <c r="C252" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_11</v>
       </c>
       <c r="E252" t="str">
@@ -13421,10 +13464,10 @@
         <v>51</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" ht="34">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13434,21 +13477,21 @@
         <v>12</v>
       </c>
       <c r="C253" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_12</v>
       </c>
       <c r="E253" t="str">
         <f>VLOOKUP(F253,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F253" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13458,7 +13501,7 @@
         <v>13</v>
       </c>
       <c r="C254" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_13</v>
       </c>
       <c r="E254" t="str">
@@ -13469,10 +13512,10 @@
         <v>51</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="34">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A255" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13482,21 +13525,21 @@
         <v>14</v>
       </c>
       <c r="C255" t="str">
-        <f t="shared" ref="C255:C261" si="32">CONCATENATE(A255, "_", B255, IF(D255&lt;&gt;"", "_"&amp;D255, ""))</f>
+        <f t="shared" si="32"/>
         <v>NODE_31_14</v>
       </c>
       <c r="E255" t="str">
         <f>VLOOKUP(F255,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangLiao</v>
+        <v>GuanYu</v>
       </c>
       <c r="F255" t="s">
-        <v>591</v>
+        <v>7</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13517,10 +13560,10 @@
         <v>51</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" ht="34">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A257" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13535,16 +13578,16 @@
       </c>
       <c r="E257" t="str">
         <f>VLOOKUP(F257,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>ZhangLiao</v>
       </c>
       <c r="F257" t="s">
-        <v>9</v>
+        <v>591</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="34">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13559,16 +13602,16 @@
       </c>
       <c r="E258" t="str">
         <f>VLOOKUP(F258,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>CaoCao</v>
       </c>
       <c r="F258" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A259" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13589,10 +13632,10 @@
         <v>9</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A260" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13607,16 +13650,16 @@
       </c>
       <c r="E260" t="str">
         <f>VLOOKUP(F260,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F260" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="34">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="str">
         <f t="shared" si="29"/>
         <v>NODE_31</v>
@@ -13631,18 +13674,18 @@
       </c>
       <c r="E261" t="str">
         <f>VLOOKUP(F261,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F261" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" ht="34">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="str">
-        <f t="shared" ref="A262" si="33">A261</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B262">
@@ -13650,7 +13693,7 @@
         <v>21</v>
       </c>
       <c r="C262" t="str">
-        <f t="shared" ref="C262:C280" si="34">CONCATENATE(A262, "_", B262, IF(D262&lt;&gt;"", "_"&amp;D262, ""))</f>
+        <f t="shared" si="32"/>
         <v>NODE_31_21</v>
       </c>
       <c r="E262" t="str">
@@ -13661,12 +13704,12 @@
         <v>9</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A263" t="str">
-        <f t="shared" ref="A263" si="35">A262</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B263">
@@ -13674,7 +13717,7 @@
         <v>22</v>
       </c>
       <c r="C263" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_22</v>
       </c>
       <c r="E263" t="str">
@@ -13685,12 +13728,12 @@
         <v>7</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A264" t="str">
-        <f t="shared" ref="A264" si="36">A263</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B264">
@@ -13698,13 +13741,23 @@
         <v>23</v>
       </c>
       <c r="C264" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_23</v>
       </c>
-    </row>
-    <row r="265" spans="1:7">
+      <c r="E264" t="str">
+        <f>VLOOKUP(F264,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>ZhangFei</v>
+      </c>
+      <c r="F264" t="s">
+        <v>9</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="str">
-        <f t="shared" ref="A265" si="37">A264</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B265">
@@ -13712,23 +13765,23 @@
         <v>24</v>
       </c>
       <c r="C265" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_24</v>
       </c>
       <c r="E265" t="str">
         <f>VLOOKUP(F265,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F265" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="34">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="str">
-        <f t="shared" ref="A266" si="38">A265</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B266">
@@ -13736,23 +13789,17 @@
         <v>25</v>
       </c>
       <c r="C266" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_25</v>
       </c>
-      <c r="E266" t="str">
+      <c r="E266" t="e">
         <f>VLOOKUP(F266,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
-      </c>
-      <c r="F266" t="s">
-        <v>9</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="34">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="str">
-        <f t="shared" ref="A267" si="39">A266</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B267">
@@ -13760,23 +13807,23 @@
         <v>26</v>
       </c>
       <c r="C267" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_26</v>
       </c>
       <c r="E267" t="str">
         <f>VLOOKUP(F267,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F267" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="34">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A268" t="str">
-        <f t="shared" ref="A268" si="40">A267</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B268">
@@ -13784,23 +13831,23 @@
         <v>27</v>
       </c>
       <c r="C268" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_27</v>
       </c>
       <c r="E268" t="str">
         <f>VLOOKUP(F268,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F268" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A269" t="str">
-        <f t="shared" ref="A269" si="41">A268</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B269">
@@ -13808,23 +13855,23 @@
         <v>28</v>
       </c>
       <c r="C269" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_28</v>
       </c>
       <c r="E269" t="str">
         <f>VLOOKUP(F269,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F269" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A270" t="str">
-        <f t="shared" ref="A270" si="42">A269</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B270">
@@ -13832,7 +13879,7 @@
         <v>29</v>
       </c>
       <c r="C270" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_29</v>
       </c>
       <c r="E270" t="str">
@@ -13843,12 +13890,12 @@
         <v>7</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="34">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="str">
-        <f t="shared" ref="A271" si="43">A270</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B271">
@@ -13856,7 +13903,7 @@
         <v>30</v>
       </c>
       <c r="C271" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_30</v>
       </c>
       <c r="E271" t="str">
@@ -13867,12 +13914,12 @@
         <v>9</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="str">
-        <f t="shared" ref="A272" si="44">A271</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B272">
@@ -13880,7 +13927,7 @@
         <v>31</v>
       </c>
       <c r="C272" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_31</v>
       </c>
       <c r="E272" t="str">
@@ -13891,12 +13938,12 @@
         <v>7</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A273" t="str">
-        <f t="shared" ref="A273" si="45">A272</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B273">
@@ -13904,7 +13951,7 @@
         <v>32</v>
       </c>
       <c r="C273" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_32</v>
       </c>
       <c r="E273" t="str">
@@ -13915,12 +13962,12 @@
         <v>9</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" ht="34">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="str">
-        <f t="shared" ref="A274" si="46">A273</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B274">
@@ -13928,7 +13975,7 @@
         <v>33</v>
       </c>
       <c r="C274" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_33</v>
       </c>
       <c r="E274" t="str">
@@ -13939,12 +13986,12 @@
         <v>7</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" ht="34">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="str">
-        <f t="shared" ref="A275" si="47">A274</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B275">
@@ -13952,23 +13999,23 @@
         <v>34</v>
       </c>
       <c r="C275" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_34</v>
       </c>
       <c r="E275" t="str">
         <f>VLOOKUP(F275,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F275" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" ht="34">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A276" t="str">
-        <f t="shared" ref="A276" si="48">A275</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B276">
@@ -13976,23 +14023,23 @@
         <v>35</v>
       </c>
       <c r="C276" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_35</v>
       </c>
       <c r="E276" t="str">
         <f>VLOOKUP(F276,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F276" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" ht="51">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A277" t="str">
-        <f t="shared" ref="A277" si="49">A276</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B277">
@@ -14000,7 +14047,7 @@
         <v>36</v>
       </c>
       <c r="C277" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_36</v>
       </c>
       <c r="E277" t="str">
@@ -14011,12 +14058,12 @@
         <v>7</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A278" t="str">
-        <f t="shared" ref="A278" si="50">A277</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B278">
@@ -14024,7 +14071,7 @@
         <v>37</v>
       </c>
       <c r="C278" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_37</v>
       </c>
       <c r="E278" t="str">
@@ -14035,12 +14082,12 @@
         <v>9</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" ht="34">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A279" t="str">
-        <f t="shared" ref="A279" si="51">A278</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B279">
@@ -14048,7 +14095,7 @@
         <v>38</v>
       </c>
       <c r="C279" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_38</v>
       </c>
       <c r="E279" t="str">
@@ -14059,12 +14106,12 @@
         <v>7</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="str">
-        <f t="shared" ref="A280:A298" si="52">A279</f>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B280">
@@ -14072,25 +14119,23 @@
         <v>39</v>
       </c>
       <c r="C280" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_39</v>
       </c>
       <c r="E280" t="str">
         <f>VLOOKUP(F280,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>FanJiang</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F280" t="s">
-        <v>691</v>
+        <v>9</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="H280"/>
-      <c r="I280" s="3"/>
-    </row>
-    <row r="281" spans="1:9">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A281" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B281">
@@ -14098,23 +14143,23 @@
         <v>40</v>
       </c>
       <c r="C281" t="str">
-        <f t="shared" ref="C281:C298" si="53">CONCATENATE(A281, "_", B281, IF(D281&lt;&gt;"", "_"&amp;D281, ""))</f>
+        <f t="shared" si="32"/>
         <v>NODE_31_40</v>
       </c>
       <c r="E281" t="str">
         <f>VLOOKUP(F281,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>GuanYu</v>
       </c>
       <c r="F281" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B282">
@@ -14122,7 +14167,7 @@
         <v>41</v>
       </c>
       <c r="C282" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_41</v>
       </c>
       <c r="E282" t="str">
@@ -14130,15 +14175,17 @@
         <v>FanJiang</v>
       </c>
       <c r="F282" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9">
+        <v>836</v>
+      </c>
+      <c r="H282"/>
+      <c r="I282" s="3"/>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B283">
@@ -14146,23 +14193,23 @@
         <v>42</v>
       </c>
       <c r="C283" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_42</v>
       </c>
       <c r="E283" t="str">
         <f>VLOOKUP(F283,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F283" t="s">
-        <v>692</v>
+        <v>9</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" ht="34">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B284">
@@ -14170,23 +14217,23 @@
         <v>43</v>
       </c>
       <c r="C284" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_43</v>
       </c>
       <c r="E284" t="str">
         <f>VLOOKUP(F284,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangDa</v>
+        <v>FanJiang</v>
       </c>
       <c r="F284" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B285">
@@ -14194,23 +14241,23 @@
         <v>44</v>
       </c>
       <c r="C285" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_44</v>
       </c>
       <c r="E285" t="str">
         <f>VLOOKUP(F285,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhangFei</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F285" t="s">
-        <v>9</v>
+        <v>691</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="A286" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B286">
@@ -14218,23 +14265,23 @@
         <v>45</v>
       </c>
       <c r="C286" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_45</v>
       </c>
       <c r="E286" t="str">
         <f>VLOOKUP(F286,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangDa</v>
       </c>
       <c r="F286" t="s">
-        <v>7</v>
+        <v>691</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B287">
@@ -14242,23 +14289,23 @@
         <v>46</v>
       </c>
       <c r="C287" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_46</v>
       </c>
       <c r="E287" t="str">
         <f>VLOOKUP(F287,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>GuanYu</v>
+        <v>ZhangFei</v>
       </c>
       <c r="F287" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B288">
@@ -14266,7 +14313,7 @@
         <v>47</v>
       </c>
       <c r="C288" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_47</v>
       </c>
       <c r="E288" t="str">
@@ -14277,12 +14324,12 @@
         <v>7</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B289">
@@ -14290,23 +14337,23 @@
         <v>48</v>
       </c>
       <c r="C289" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_48</v>
       </c>
       <c r="E289" t="str">
         <f>VLOOKUP(F289,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F289" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B290">
@@ -14314,23 +14361,23 @@
         <v>49</v>
       </c>
       <c r="C290" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_49</v>
       </c>
       <c r="E290" t="str">
         <f>VLOOKUP(F290,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>ZhaoYun</v>
+        <v>GuanYu</v>
       </c>
       <c r="F290" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="34">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B291">
@@ -14338,7 +14385,7 @@
         <v>50</v>
       </c>
       <c r="C291" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_50</v>
       </c>
       <c r="E291" t="str">
@@ -14349,12 +14396,12 @@
         <v>11</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B292">
@@ -14362,23 +14409,23 @@
         <v>51</v>
       </c>
       <c r="C292" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_51</v>
       </c>
       <c r="E292" t="str">
         <f>VLOOKUP(F292,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F292" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="34">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A293" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B293">
@@ -14386,31 +14433,31 @@
         <v>52</v>
       </c>
       <c r="C293" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_52</v>
       </c>
       <c r="E293" t="str">
         <f>VLOOKUP(F293,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
-        <v>LiuBei</v>
+        <v>ZhaoYun</v>
       </c>
       <c r="F293" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="34">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="str">
-        <f t="shared" si="52"/>
+        <f>A293</f>
         <v>NODE_31</v>
       </c>
       <c r="B294">
-        <f t="shared" si="27"/>
+        <f>B293+1</f>
         <v>53</v>
       </c>
       <c r="C294" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_53</v>
       </c>
       <c r="E294" t="str">
@@ -14421,12 +14468,12 @@
         <v>5</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="34">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A295" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B295">
@@ -14434,7 +14481,7 @@
         <v>54</v>
       </c>
       <c r="C295" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_54</v>
       </c>
       <c r="E295" t="str">
@@ -14445,12 +14492,12 @@
         <v>5</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" ht="34">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A296" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B296">
@@ -14458,7 +14505,7 @@
         <v>55</v>
       </c>
       <c r="C296" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_55</v>
       </c>
       <c r="E296" t="str">
@@ -14469,12 +14516,12 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" ht="34">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A297" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B297">
@@ -14482,7 +14529,7 @@
         <v>56</v>
       </c>
       <c r="C297" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_56</v>
       </c>
       <c r="E297" t="str">
@@ -14493,12 +14540,12 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A298" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="29"/>
         <v>NODE_31</v>
       </c>
       <c r="B298">
@@ -14506,7 +14553,7 @@
         <v>57</v>
       </c>
       <c r="C298" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="32"/>
         <v>NODE_31_57</v>
       </c>
       <c r="E298" t="str">
@@ -14517,7 +14564,55 @@
         <v>5</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>711</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A299" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B299">
+        <f t="shared" si="27"/>
+        <v>58</v>
+      </c>
+      <c r="C299" t="str">
+        <f t="shared" si="32"/>
+        <v>NODE_31_58</v>
+      </c>
+      <c r="E299" t="str">
+        <f>VLOOKUP(F299,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F299" t="s">
+        <v>5</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A300" t="str">
+        <f t="shared" si="29"/>
+        <v>NODE_31</v>
+      </c>
+      <c r="B300">
+        <f t="shared" si="27"/>
+        <v>59</v>
+      </c>
+      <c r="C300" t="str">
+        <f t="shared" si="32"/>
+        <v>NODE_31_59</v>
+      </c>
+      <c r="E300" t="str">
+        <f>VLOOKUP(F300,[1]HeroData!$A$3:$B$118,2, FALSE)</f>
+        <v>LiuBei</v>
+      </c>
+      <c r="F300" t="s">
+        <v>5</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>845</v>
       </c>
     </row>
   </sheetData>
@@ -14528,18 +14623,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G126"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="65.75" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>363</v>
       </c>
@@ -14562,7 +14657,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -14585,7 +14680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>364</v>
       </c>
@@ -14602,7 +14697,7 @@
       </c>
       <c r="F3" s="21"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>364</v>
       </c>
@@ -14619,7 +14714,7 @@
       </c>
       <c r="F4" s="21"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>364</v>
       </c>
@@ -14636,7 +14731,7 @@
       </c>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>364</v>
       </c>
@@ -14653,7 +14748,7 @@
       </c>
       <c r="F6" s="21"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>364</v>
       </c>
@@ -14670,7 +14765,7 @@
       </c>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>364</v>
       </c>
@@ -14687,7 +14782,7 @@
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>364</v>
       </c>
@@ -14704,7 +14799,7 @@
       </c>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>364</v>
       </c>
@@ -14721,7 +14816,7 @@
       </c>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>364</v>
       </c>
@@ -14738,7 +14833,7 @@
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>364</v>
       </c>
@@ -14755,7 +14850,7 @@
       </c>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>364</v>
       </c>
@@ -14772,7 +14867,7 @@
       </c>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>364</v>
       </c>
@@ -14789,7 +14884,7 @@
       </c>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>364</v>
       </c>
@@ -14806,7 +14901,7 @@
       </c>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>364</v>
       </c>
@@ -14823,7 +14918,7 @@
       </c>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>364</v>
       </c>
@@ -14840,7 +14935,7 @@
       </c>
       <c r="F17" s="21"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>364</v>
       </c>
@@ -14857,7 +14952,7 @@
       </c>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>364</v>
       </c>
@@ -14874,7 +14969,7 @@
       </c>
       <c r="F19" s="21"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>364</v>
       </c>
@@ -14891,7 +14986,7 @@
       </c>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>364</v>
       </c>
@@ -14908,7 +15003,7 @@
       </c>
       <c r="F21" s="21"/>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="27" t="s">
         <v>364</v>
       </c>
@@ -14925,7 +15020,7 @@
       </c>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="27" t="s">
         <v>364</v>
       </c>
@@ -14942,7 +15037,7 @@
       </c>
       <c r="F23" s="21"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
         <v>364</v>
       </c>
@@ -14959,7 +15054,7 @@
       </c>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="27" t="s">
         <v>364</v>
       </c>
@@ -14976,7 +15071,7 @@
       </c>
       <c r="F25" s="21"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
         <v>364</v>
       </c>
@@ -14993,7 +15088,7 @@
       </c>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="27" t="s">
         <v>364</v>
       </c>
@@ -15010,7 +15105,7 @@
       </c>
       <c r="F27" s="21"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="s">
         <v>364</v>
       </c>
@@ -15027,7 +15122,7 @@
       </c>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="27" t="s">
         <v>364</v>
       </c>
@@ -15044,7 +15139,7 @@
       </c>
       <c r="F29" s="21"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="27" t="s">
         <v>364</v>
       </c>
@@ -15061,7 +15156,7 @@
       </c>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="27" t="s">
         <v>364</v>
       </c>
@@ -15078,7 +15173,7 @@
       </c>
       <c r="F31" s="21"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
         <v>364</v>
       </c>
@@ -15095,7 +15190,7 @@
       </c>
       <c r="F32" s="21"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="27" t="s">
         <v>364</v>
       </c>
@@ -15112,7 +15207,7 @@
       </c>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="27" t="s">
         <v>364</v>
       </c>
@@ -15125,11 +15220,11 @@
         <v>NODE_27_TITLE</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F34" s="21"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="27" t="s">
         <v>364</v>
       </c>
@@ -15142,11 +15237,11 @@
         <v>NODE_28_TITLE</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F35" s="24"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>364</v>
       </c>
@@ -15159,11 +15254,11 @@
         <v>NODE_29_TITLE</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>364</v>
       </c>
@@ -15180,7 +15275,7 @@
       </c>
       <c r="F37" s="33"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>364</v>
       </c>
@@ -15197,7 +15292,7 @@
       </c>
       <c r="F38" s="21"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>364</v>
       </c>
@@ -15214,12 +15309,12 @@
       </c>
       <c r="F39" s="21"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
         <v>364</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="20" t="str">
@@ -15227,11 +15322,11 @@
         <v>NODE_31_TITLE</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F40" s="21"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="27" t="s">
         <v>369</v>
       </c>
@@ -15248,7 +15343,7 @@
       </c>
       <c r="F41" s="21"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="27" t="s">
         <v>369</v>
       </c>
@@ -15265,7 +15360,7 @@
       </c>
       <c r="F42" s="21"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="27" t="s">
         <v>369</v>
       </c>
@@ -15282,7 +15377,7 @@
       </c>
       <c r="F43" s="21"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="27" t="s">
         <v>369</v>
       </c>
@@ -15299,7 +15394,7 @@
       </c>
       <c r="F44" s="21"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
         <v>369</v>
       </c>
@@ -15316,7 +15411,7 @@
       </c>
       <c r="F45" s="21"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="27" t="s">
         <v>369</v>
       </c>
@@ -15333,7 +15428,7 @@
       </c>
       <c r="F46" s="21"/>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="27" t="s">
         <v>369</v>
       </c>
@@ -15350,7 +15445,7 @@
       </c>
       <c r="F47" s="21"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="27" t="s">
         <v>369</v>
       </c>
@@ -15367,7 +15462,7 @@
       </c>
       <c r="F48" s="21"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="27" t="s">
         <v>369</v>
       </c>
@@ -15384,7 +15479,7 @@
       </c>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="27" t="s">
         <v>369</v>
       </c>
@@ -15401,7 +15496,7 @@
       </c>
       <c r="F50" s="21"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="27" t="s">
         <v>369</v>
       </c>
@@ -15418,7 +15513,7 @@
       </c>
       <c r="F51" s="21"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="27" t="s">
         <v>369</v>
       </c>
@@ -15435,7 +15530,7 @@
       </c>
       <c r="F52" s="21"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="27" t="s">
         <v>369</v>
       </c>
@@ -15452,7 +15547,7 @@
       </c>
       <c r="F53" s="21"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="27" t="s">
         <v>369</v>
       </c>
@@ -15470,7 +15565,7 @@
       <c r="F54" s="21"/>
       <c r="G54" s="35"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="27" t="s">
         <v>369</v>
       </c>
@@ -15488,7 +15583,7 @@
       <c r="F55" s="21"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="27" t="s">
         <v>369</v>
       </c>
@@ -15506,7 +15601,7 @@
       <c r="F56" s="21"/>
       <c r="G56" s="35"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="27" t="s">
         <v>369</v>
       </c>
@@ -15524,7 +15619,7 @@
       <c r="F57" s="21"/>
       <c r="G57" s="35"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="27" t="s">
         <v>369</v>
       </c>
@@ -15542,7 +15637,7 @@
       <c r="F58" s="21"/>
       <c r="G58" s="35"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="27" t="s">
         <v>369</v>
       </c>
@@ -15560,7 +15655,7 @@
       <c r="F59" s="21"/>
       <c r="G59" s="35"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="27" t="s">
         <v>369</v>
       </c>
@@ -15578,7 +15673,7 @@
       <c r="F60" s="21"/>
       <c r="G60" s="35"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="27" t="s">
         <v>369</v>
       </c>
@@ -15596,7 +15691,7 @@
       <c r="F61" s="21"/>
       <c r="G61" s="35"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="27" t="s">
         <v>369</v>
       </c>
@@ -15614,7 +15709,7 @@
       <c r="F62" s="21"/>
       <c r="G62" s="35"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="27" t="s">
         <v>369</v>
       </c>
@@ -15632,7 +15727,7 @@
       <c r="F63" s="21"/>
       <c r="G63" s="35"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="27" t="s">
         <v>369</v>
       </c>
@@ -15650,7 +15745,7 @@
       <c r="F64" s="21"/>
       <c r="G64" s="35"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="27" t="s">
         <v>369</v>
       </c>
@@ -15668,7 +15763,7 @@
       <c r="F65" s="21"/>
       <c r="G65" s="35"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="27" t="s">
         <v>369</v>
       </c>
@@ -15686,7 +15781,7 @@
       <c r="F66" s="21"/>
       <c r="G66" s="35"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="27" t="s">
         <v>369</v>
       </c>
@@ -15704,7 +15799,7 @@
       <c r="F67" s="21"/>
       <c r="G67" s="35"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="27" t="s">
         <v>369</v>
       </c>
@@ -15722,7 +15817,7 @@
       <c r="F68" s="21"/>
       <c r="G68" s="35"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="27" t="s">
         <v>369</v>
       </c>
@@ -15740,7 +15835,7 @@
       <c r="F69" s="21"/>
       <c r="G69" s="35"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="27" t="s">
         <v>369</v>
       </c>
@@ -15758,7 +15853,7 @@
       <c r="F70" s="21"/>
       <c r="G70" s="35"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="27" t="s">
         <v>369</v>
       </c>
@@ -15775,7 +15870,7 @@
       </c>
       <c r="F71" s="21"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="27" t="s">
         <v>369</v>
       </c>
@@ -15788,11 +15883,11 @@
         <v>NODE_27_DESC</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F72" s="21"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="27" t="s">
         <v>369</v>
       </c>
@@ -15805,11 +15900,11 @@
         <v>NODE_28_DESC</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F73" s="24"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="27" t="s">
         <v>369</v>
       </c>
@@ -15822,11 +15917,11 @@
         <v>NODE_29_DESC</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="F74" s="21"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="27" t="s">
         <v>369</v>
       </c>
@@ -15843,7 +15938,7 @@
       </c>
       <c r="F75" s="33"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="27" t="s">
         <v>369</v>
       </c>
@@ -15860,7 +15955,7 @@
       </c>
       <c r="F76" s="24"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="27" t="s">
         <v>369</v>
       </c>
@@ -15877,12 +15972,12 @@
       </c>
       <c r="F77" s="21"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="27" t="s">
         <v>369</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="20" t="str">
@@ -15890,11 +15985,11 @@
         <v>NODE_31_DESC</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F78" s="21"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="21" t="s">
         <v>365</v>
       </c>
@@ -15911,7 +16006,7 @@
       <c r="E79" s="29"/>
       <c r="F79" s="21"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>365</v>
       </c>
@@ -15928,7 +16023,7 @@
       <c r="E80" s="29"/>
       <c r="F80" s="21"/>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>365</v>
       </c>
@@ -15945,7 +16040,7 @@
       <c r="E81" s="29"/>
       <c r="F81" s="21"/>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
         <v>365</v>
       </c>
@@ -15962,7 +16057,7 @@
       <c r="E82" s="29"/>
       <c r="F82" s="21"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>365</v>
       </c>
@@ -15979,7 +16074,7 @@
       <c r="E83" s="29"/>
       <c r="F83" s="21"/>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
         <v>365</v>
       </c>
@@ -15996,7 +16091,7 @@
       <c r="E84" s="29"/>
       <c r="F84" s="21"/>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="21" t="s">
         <v>365</v>
       </c>
@@ -16013,7 +16108,7 @@
       <c r="E85" s="29"/>
       <c r="F85" s="21"/>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="21" t="s">
         <v>365</v>
       </c>
@@ -16030,7 +16125,7 @@
       <c r="E86" s="29"/>
       <c r="F86" s="21"/>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>365</v>
       </c>
@@ -16047,7 +16142,7 @@
       <c r="E87" s="29"/>
       <c r="F87" s="21"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="21" t="s">
         <v>365</v>
       </c>
@@ -16064,7 +16159,7 @@
       <c r="E88" s="29"/>
       <c r="F88" s="21"/>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="21" t="s">
         <v>365</v>
       </c>
@@ -16081,7 +16176,7 @@
       <c r="E89" s="29"/>
       <c r="F89" s="21"/>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="21" t="s">
         <v>365</v>
       </c>
@@ -16098,7 +16193,7 @@
       <c r="E90" s="29"/>
       <c r="F90" s="21"/>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
         <v>365</v>
       </c>
@@ -16115,7 +16210,7 @@
       <c r="E91" s="29"/>
       <c r="F91" s="21"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="21" t="s">
         <v>365</v>
       </c>
@@ -16132,7 +16227,7 @@
       <c r="E92" s="29"/>
       <c r="F92" s="21"/>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="21" t="s">
         <v>365</v>
       </c>
@@ -16149,7 +16244,7 @@
       <c r="E93" s="29"/>
       <c r="F93" s="21"/>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="21" t="s">
         <v>365</v>
       </c>
@@ -16166,7 +16261,7 @@
       <c r="E94" s="29"/>
       <c r="F94" s="21"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
         <v>365</v>
       </c>
@@ -16183,7 +16278,7 @@
       <c r="E95" s="29"/>
       <c r="F95" s="21"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
         <v>365</v>
       </c>
@@ -16200,7 +16295,7 @@
       <c r="E96" s="29"/>
       <c r="F96" s="21"/>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="21" t="s">
         <v>365</v>
       </c>
@@ -16217,7 +16312,7 @@
       <c r="E97" s="29"/>
       <c r="F97" s="21"/>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="21" t="s">
         <v>365</v>
       </c>
@@ -16234,7 +16329,7 @@
       <c r="E98" s="29"/>
       <c r="F98" s="21"/>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>365</v>
       </c>
@@ -16251,7 +16346,7 @@
       <c r="E99" s="29"/>
       <c r="F99" s="21"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
         <v>365</v>
       </c>
@@ -16268,7 +16363,7 @@
       <c r="E100" s="29"/>
       <c r="F100" s="21"/>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="21" t="s">
         <v>365</v>
       </c>
@@ -16285,7 +16380,7 @@
       <c r="E101" s="29"/>
       <c r="F101" s="21"/>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
         <v>365</v>
       </c>
@@ -16302,7 +16397,7 @@
       <c r="E102" s="29"/>
       <c r="F102" s="21"/>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>367</v>
       </c>
@@ -16322,7 +16417,7 @@
       </c>
       <c r="F103" s="21"/>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="21" t="s">
         <v>367</v>
       </c>
@@ -16342,7 +16437,7 @@
       </c>
       <c r="F104" s="21"/>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="21" t="s">
         <v>367</v>
       </c>
@@ -16362,7 +16457,7 @@
       </c>
       <c r="F105" s="21"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="21" t="s">
         <v>367</v>
       </c>
@@ -16382,7 +16477,7 @@
       </c>
       <c r="F106" s="21"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="21" t="s">
         <v>367</v>
       </c>
@@ -16402,7 +16497,7 @@
       </c>
       <c r="F107" s="21"/>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="21" t="s">
         <v>367</v>
       </c>
@@ -16422,7 +16517,7 @@
       </c>
       <c r="F108" s="21"/>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="21" t="s">
         <v>367</v>
       </c>
@@ -16442,7 +16537,7 @@
       </c>
       <c r="F109" s="21"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="21" t="s">
         <v>367</v>
       </c>
@@ -16462,7 +16557,7 @@
       </c>
       <c r="F110" s="21"/>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="21" t="s">
         <v>367</v>
       </c>
@@ -16482,7 +16577,7 @@
       </c>
       <c r="F111" s="21"/>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="21" t="s">
         <v>367</v>
       </c>
@@ -16502,7 +16597,7 @@
       </c>
       <c r="F112" s="21"/>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="21" t="s">
         <v>367</v>
       </c>
@@ -16522,7 +16617,7 @@
       </c>
       <c r="F113" s="21"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="21" t="s">
         <v>367</v>
       </c>
@@ -16542,7 +16637,7 @@
       </c>
       <c r="F114" s="21"/>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="21" t="s">
         <v>367</v>
       </c>
@@ -16562,7 +16657,7 @@
       </c>
       <c r="F115" s="21"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="21" t="s">
         <v>367</v>
       </c>
@@ -16582,7 +16677,7 @@
       </c>
       <c r="F116" s="21"/>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="21" t="s">
         <v>367</v>
       </c>
@@ -16602,7 +16697,7 @@
       </c>
       <c r="F117" s="21"/>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="21" t="s">
         <v>367</v>
       </c>
@@ -16622,7 +16717,7 @@
       </c>
       <c r="F118" s="21"/>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="21" t="s">
         <v>367</v>
       </c>
@@ -16642,7 +16737,7 @@
       </c>
       <c r="F119" s="21"/>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="21" t="s">
         <v>367</v>
       </c>
@@ -16662,7 +16757,7 @@
       </c>
       <c r="F120" s="21"/>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="21" t="s">
         <v>367</v>
       </c>
@@ -16682,7 +16777,7 @@
       </c>
       <c r="F121" s="21"/>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="21" t="s">
         <v>367</v>
       </c>
@@ -16702,7 +16797,7 @@
       </c>
       <c r="F122" s="21"/>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>367</v>
       </c>
@@ -16722,7 +16817,7 @@
       </c>
       <c r="F123" s="21"/>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>367</v>
       </c>
@@ -16742,7 +16837,7 @@
       </c>
       <c r="F124" s="21"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="21" t="s">
         <v>367</v>
       </c>
@@ -16762,7 +16857,7 @@
       </c>
       <c r="F125" s="21"/>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
         <v>367</v>
       </c>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DBBFCA-0798-4C7A-BD0E-6DD971FB0A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2BB692-FF43-4D8D-BECC-4B318E541E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="848">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3044,10 +3044,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이제야 안심이구나ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>너는.. 그 악귀를 물리친
 영웅이 되는 것이다.. 크읔</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3163,10 +3159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㅋㅋㅋ 오거라ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>시끄럽다!! 큰 형님을 죽음으로 몰고,
 역적 조조에게 붙어버린 배신자놈!!</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3187,11 +3179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ㅋㅋㅋ 겨우 이정도가
-장익덕의 힘이더냐?ㅋ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>백성들에게는 그런 신의 존재가
 필요하다. 그러니 네가..</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3331,6 +3318,27 @@
   </si>
   <si>
     <t>자 그럼, 다음에 또 보자~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후훗. 이제야 안심이구나.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>훗, 겨우 이정도가
+장익덕의 힘이더냐?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오거라.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈에 띄는 건 싫군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문추의 목을 높이 들어라</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9523,7 +9531,7 @@
         <v>599</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -9619,7 +9627,7 @@
         <v>599</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -9835,7 +9843,7 @@
         <v>5</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -10228,7 +10236,7 @@
         <v>600</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -10309,7 +10317,7 @@
         <v>5</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -10336,7 +10344,7 @@
         <v>600</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="33" x14ac:dyDescent="0.3">
@@ -11435,7 +11443,7 @@
         <v>406</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -11829,7 +11837,7 @@
         <v>406</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12300,7 +12308,7 @@
         <v>406</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -12348,7 +12356,7 @@
         <v>406</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12372,7 +12380,7 @@
         <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12468,7 +12476,7 @@
         <v>11</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -12492,7 +12500,7 @@
         <v>7</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12540,7 +12548,7 @@
         <v>7</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12564,7 +12572,7 @@
         <v>11</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12660,7 +12668,7 @@
         <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -12708,7 +12716,7 @@
         <v>7</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -12780,7 +12788,7 @@
         <v>7</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -12828,7 +12836,7 @@
         <v>11</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -12852,7 +12860,7 @@
         <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="226" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -12876,7 +12884,7 @@
         <v>591</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -13082,7 +13090,7 @@
         <v>7</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -13130,7 +13138,7 @@
         <v>406</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13154,7 +13162,7 @@
         <v>7</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="239" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13178,7 +13186,7 @@
         <v>406</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -13200,7 +13208,7 @@
         <v>403</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -13224,7 +13232,7 @@
         <v>403</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13248,7 +13256,7 @@
         <v>9</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -13272,7 +13280,7 @@
         <v>51</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13296,7 +13304,7 @@
         <v>9</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -13344,7 +13352,7 @@
         <v>9</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -13392,7 +13400,7 @@
         <v>9</v>
       </c>
       <c r="G249" s="39" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="250" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13416,7 +13424,7 @@
         <v>51</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="251" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13440,7 +13448,7 @@
         <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -13464,7 +13472,7 @@
         <v>51</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -13488,7 +13496,7 @@
         <v>9</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -13512,7 +13520,7 @@
         <v>51</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="255" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13536,7 +13544,7 @@
         <v>7</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -13584,7 +13592,7 @@
         <v>591</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -13608,7 +13616,7 @@
         <v>51</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13632,7 +13640,7 @@
         <v>9</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="260" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13656,7 +13664,7 @@
         <v>7</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -13680,7 +13688,7 @@
         <v>9</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -13704,7 +13712,7 @@
         <v>9</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="263" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -13752,7 +13760,7 @@
         <v>9</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -13776,7 +13784,7 @@
         <v>7</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>809</v>
+        <v>845</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -13890,7 +13898,7 @@
         <v>7</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>814</v>
+        <v>844</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -13986,7 +13994,7 @@
         <v>7</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>782</v>
+        <v>843</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.3">
@@ -14058,7 +14066,7 @@
         <v>7</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -14130,7 +14138,7 @@
         <v>9</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -14154,7 +14162,7 @@
         <v>7</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
@@ -14178,7 +14186,7 @@
         <v>690</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="H282"/>
       <c r="I282" s="3"/>
@@ -14228,7 +14236,7 @@
         <v>690</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.3">
@@ -14252,7 +14260,7 @@
         <v>691</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="33" x14ac:dyDescent="0.3">
@@ -14276,7 +14284,7 @@
         <v>691</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.3">
@@ -14300,7 +14308,7 @@
         <v>9</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
@@ -14324,7 +14332,7 @@
         <v>7</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -14348,7 +14356,7 @@
         <v>7</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -14372,7 +14380,7 @@
         <v>7</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -14420,7 +14428,7 @@
         <v>11</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="293" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -14444,7 +14452,7 @@
         <v>11</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -14492,7 +14500,7 @@
         <v>5</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="296" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -14516,7 +14524,7 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="297" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -14540,7 +14548,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="298" spans="1:7" ht="33" x14ac:dyDescent="0.3">
@@ -14612,7 +14620,7 @@
         <v>5</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -16261,7 +16269,7 @@
       <c r="E94" s="29"/>
       <c r="F94" s="21"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="33" x14ac:dyDescent="0.2">
       <c r="A95" s="21" t="s">
         <v>365</v>
       </c>
@@ -16275,10 +16283,12 @@
         <f t="shared" si="6"/>
         <v>NODE_16_CHOICE_1</v>
       </c>
-      <c r="E95" s="29"/>
+      <c r="E95" s="38" t="s">
+        <v>609</v>
+      </c>
       <c r="F95" s="21"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="33" x14ac:dyDescent="0.2">
       <c r="A96" s="21" t="s">
         <v>365</v>
       </c>
@@ -16292,7 +16302,9 @@
         <f t="shared" si="6"/>
         <v>NODE_16_CHOICE_2</v>
       </c>
-      <c r="E96" s="29"/>
+      <c r="E96" s="38" t="s">
+        <v>610</v>
+      </c>
       <c r="F96" s="21"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
@@ -16731,9 +16743,8 @@
         <f t="shared" si="8"/>
         <v>NODE_16_CHOICE_1_DESC</v>
       </c>
-      <c r="E119" s="29" t="str">
-        <f t="shared" si="7"/>
-        <v>선택1</v>
+      <c r="E119" s="29" t="s">
+        <v>846</v>
       </c>
       <c r="F119" s="21"/>
     </row>
@@ -16751,9 +16762,8 @@
         <f t="shared" si="8"/>
         <v>NODE_16_CHOICE_2_DESC</v>
       </c>
-      <c r="E120" s="29" t="str">
-        <f t="shared" si="7"/>
-        <v>선택2</v>
+      <c r="E120" s="29" t="s">
+        <v>847</v>
       </c>
       <c r="F120" s="21"/>
     </row>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2BB692-FF43-4D8D-BECC-4B318E541E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E56788-0657-402E-9D45-6D2AA2640696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="3015" windowWidth="16200" windowHeight="11295" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -15,9 +15,10 @@
     <sheet name="String_Treasure" sheetId="7" r:id="rId5"/>
     <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId6"/>
     <sheet name="String_Story" sheetId="8" r:id="rId7"/>
+    <sheet name="String_Guide" sheetId="9" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="853">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3339,6 +3340,50 @@
   </si>
   <si>
     <t>문추의 목을 높이 들어라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동하기</t>
+  </si>
+  <si>
+    <t>기본공격 하기</t>
+  </si>
+  <si>
+    <t>스킬 사용하기</t>
+  </si>
+  <si>
+    <t>대쉬 사용하기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스토리모드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클리어하기</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3346,7 +3391,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3394,6 +3439,26 @@
       <charset val="129"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3409,7 +3474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -3469,13 +3534,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3594,6 +3694,39 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16892,4 +17025,1017 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C9C28B-7BC2-4F36-AD7E-E1E794C14C4A}">
+  <dimension ref="A1:G126"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.75" style="49" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19">
+        <v>1</v>
+      </c>
+      <c r="D3" s="41" t="str">
+        <f>TEXT(C3,"0000")&amp;"_"&amp;A3</f>
+        <v>0001_TITLE</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>848</v>
+      </c>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="str">
+        <f>A3</f>
+        <v>TITLE</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19">
+        <f>C3+1</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="41" t="str">
+        <f>TEXT(C4,"0000")&amp;"_"&amp;A4</f>
+        <v>0002_TITLE</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>849</v>
+      </c>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="str">
+        <f t="shared" ref="A5:A7" si="0">A4</f>
+        <v>TITLE</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19">
+        <f t="shared" ref="C5:C7" si="1">C4+1</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="41" t="str">
+        <f t="shared" ref="D5:D7" si="2">TEXT(C5,"0000")&amp;"_"&amp;A5</f>
+        <v>0003_TITLE</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>850</v>
+      </c>
+      <c r="F5" s="43"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>TITLE</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="41" t="str">
+        <f t="shared" si="2"/>
+        <v>0004_TITLE</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>851</v>
+      </c>
+      <c r="F6" s="43"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>TITLE</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="41" t="str">
+        <f t="shared" si="2"/>
+        <v>0005_TITLE</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>852</v>
+      </c>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="41"/>
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="41"/>
+      <c r="F9" s="43"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="27"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="41"/>
+      <c r="F10" s="43"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="41"/>
+      <c r="F11" s="43"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="41"/>
+      <c r="F12" s="43"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="41"/>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="41"/>
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="41"/>
+      <c r="F15" s="43"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="41"/>
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="41"/>
+      <c r="F17" s="43"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="27"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="41"/>
+      <c r="F18" s="43"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="41"/>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="27"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="41"/>
+      <c r="F20" s="43"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="41"/>
+      <c r="F21" s="43"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="27"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="41"/>
+      <c r="F22" s="43"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="27"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="41"/>
+      <c r="F23" s="43"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="27"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="41"/>
+      <c r="F24" s="43"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="41"/>
+      <c r="F25" s="43"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="41"/>
+      <c r="F26" s="43"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="41"/>
+      <c r="F27" s="43"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="27"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="41"/>
+      <c r="F28" s="43"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="27"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="41"/>
+      <c r="F29" s="43"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="27"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="41"/>
+      <c r="F30" s="43"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="41"/>
+      <c r="F31" s="43"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="41"/>
+      <c r="F32" s="43"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="41"/>
+      <c r="F33" s="43"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="27"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="41"/>
+      <c r="F34" s="43"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="42"/>
+      <c r="F35" s="44"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="21"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="41"/>
+      <c r="F36" s="43"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="21"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="41"/>
+      <c r="F37" s="45"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="21"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="41"/>
+      <c r="F38" s="43"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="21"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="41"/>
+      <c r="F39" s="43"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="21"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="43"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="43"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="41"/>
+      <c r="F42" s="43"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="27"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="41"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="27"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="41"/>
+      <c r="F45" s="43"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="27"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="41"/>
+      <c r="F46" s="43"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="27"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="41"/>
+      <c r="F47" s="43"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="27"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="41"/>
+      <c r="F48" s="43"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="27"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="41"/>
+      <c r="F49" s="43"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="27"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="41"/>
+      <c r="F50" s="43"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="27"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="41"/>
+      <c r="F51" s="43"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="27"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="41"/>
+      <c r="F52" s="43"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="27"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="41"/>
+      <c r="F53" s="43"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="27"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="41"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="35"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="27"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="41"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="35"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="27"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="41"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="35"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="27"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="41"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="35"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="27"/>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="41"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="35"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="27"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="41"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="35"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="27"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="41"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="35"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="27"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="41"/>
+      <c r="F61" s="43"/>
+      <c r="G61" s="35"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="27"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="41"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="35"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="27"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="41"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="35"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="27"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="41"/>
+      <c r="F64" s="43"/>
+      <c r="G64" s="35"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="27"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="41"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="35"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="27"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="41"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="35"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="27"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="41"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="35"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="27"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="41"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="35"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="27"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="41"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="35"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="27"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="41"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="35"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="27"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="41"/>
+      <c r="F71" s="43"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="27"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="41"/>
+      <c r="F72" s="43"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="27"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="41"/>
+      <c r="F73" s="44"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="27"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="41"/>
+      <c r="F74" s="43"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="27"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="41"/>
+      <c r="F75" s="45"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="27"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="41"/>
+      <c r="F76" s="44"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="27"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="41"/>
+      <c r="F77" s="43"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="27"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="41"/>
+      <c r="F78" s="43"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="21"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="41"/>
+      <c r="F79" s="43"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="21"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="41"/>
+      <c r="F80" s="43"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="21"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="41"/>
+      <c r="F81" s="43"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="21"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="41"/>
+      <c r="F82" s="43"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="21"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="41"/>
+      <c r="F83" s="43"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="21"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="41"/>
+      <c r="F84" s="43"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="21"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="41"/>
+      <c r="F85" s="43"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="21"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="41"/>
+      <c r="F86" s="43"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="21"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="41"/>
+      <c r="F87" s="43"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="21"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="41"/>
+      <c r="F88" s="43"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="21"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="41"/>
+      <c r="F89" s="43"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="21"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="41"/>
+      <c r="F90" s="43"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="21"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="41"/>
+      <c r="F91" s="43"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="21"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="41"/>
+      <c r="F92" s="43"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="21"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="41"/>
+      <c r="F93" s="43"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="21"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="41"/>
+      <c r="F94" s="43"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="21"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="43"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="21"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="43"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="21"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="41"/>
+      <c r="F97" s="43"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="21"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="41"/>
+      <c r="F98" s="43"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="21"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="41"/>
+      <c r="F99" s="43"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="21"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="41"/>
+      <c r="F100" s="43"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="21"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="41"/>
+      <c r="F101" s="43"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="21"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="41"/>
+      <c r="F102" s="43"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="21"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="41"/>
+      <c r="F103" s="43"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="21"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="41"/>
+      <c r="F104" s="43"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c